--- a/data/rendimenti_etf.xlsx
+++ b/data/rendimenti_etf.xlsx
@@ -533,7 +533,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Aggiornato il 06/10/2026 09:16 da yield_etf.xlsx</t>
+          <t>Aggiornato il 07/10/2026 10:56 da yield_etf.csv</t>
         </is>
       </c>
     </row>
@@ -658,13 +658,13 @@
         <v/>
       </c>
       <c r="H5" s="8" t="n">
-        <v>0.0389</v>
+        <v>0.039</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>0.05019999999999999</v>
+        <v>0.0506</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="K5" s="9" t="n"/>
       <c r="L5" s="9" t="n"/>
@@ -724,10 +724,10 @@
         <v>0.03759999999999999</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0.04650000000000001</v>
+        <v>0.0469</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0004</v>
       </c>
       <c r="K6" s="9" t="n"/>
       <c r="L6" s="9" t="n"/>
@@ -747,7 +747,7 @@
         <v/>
       </c>
       <c r="Q6" s="12" t="n">
-        <v>28.21</v>
+        <v>28.34</v>
       </c>
     </row>
     <row r="7">
@@ -784,13 +784,13 @@
         <v/>
       </c>
       <c r="H7" s="8" t="n">
-        <v>0.0354</v>
+        <v>0.0355</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0.0462</v>
+        <v>0.0466</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="K7" s="9" t="n"/>
       <c r="L7" s="9" t="n"/>
@@ -810,7 +810,7 @@
         <v/>
       </c>
       <c r="Q7" s="12" t="n">
-        <v>4.79</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="8">
@@ -850,10 +850,10 @@
         <v>0.0365</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>0.0461</v>
+        <v>0.04650000000000001</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.0206</v>
+        <v>0.0004</v>
       </c>
       <c r="K8" s="9" t="n"/>
       <c r="L8" s="9" t="n"/>
@@ -873,7 +873,7 @@
         <v/>
       </c>
       <c r="Q8" s="12" t="n">
-        <v>29.04</v>
+        <v>29.15</v>
       </c>
     </row>
     <row r="9">
@@ -913,10 +913,10 @@
         <v>0.0349</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>0.0459</v>
+        <v>0.0464</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="K9" s="9" t="n"/>
       <c r="L9" s="9" t="n"/>
@@ -936,7 +936,7 @@
         <v/>
       </c>
       <c r="Q9" s="12" t="n">
-        <v>4.79</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="10">
@@ -976,10 +976,10 @@
         <v>0.0363</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>0.0458</v>
+        <v>0.0463</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="K10" s="9" t="n"/>
       <c r="L10" s="9" t="n"/>
@@ -999,7 +999,7 @@
         <v/>
       </c>
       <c r="Q10" s="12" t="n">
-        <v>4.71</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="11">
@@ -1039,10 +1039,10 @@
         <v>0.0347</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>0.0455</v>
+        <v>0.0459</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="K11" s="9" t="n"/>
       <c r="L11" s="9" t="n"/>
@@ -1062,7 +1062,7 @@
         <v/>
       </c>
       <c r="Q11" s="12" t="n">
-        <v>33.42</v>
+        <v>33.53</v>
       </c>
     </row>
     <row r="12">
@@ -1099,13 +1099,13 @@
         <v/>
       </c>
       <c r="H12" s="8" t="n">
-        <v>0.0347</v>
+        <v>0.0346</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>0.045</v>
+        <v>0.0454</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="K12" s="9" t="n"/>
       <c r="L12" s="9" t="n"/>
@@ -1125,7 +1125,7 @@
         <v/>
       </c>
       <c r="Q12" s="12" t="n">
-        <v>4.72</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="13">
@@ -1165,10 +1165,10 @@
         <v>0.034</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0.0447</v>
+        <v>0.0451</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.0196</v>
+        <v>0.0004</v>
       </c>
       <c r="K13" s="9" t="n"/>
       <c r="L13" s="9" t="n"/>
@@ -1188,7 +1188,7 @@
         <v/>
       </c>
       <c r="Q13" s="12" t="n">
-        <v>9.279999999999999</v>
+        <v>9.31</v>
       </c>
     </row>
     <row r="14">
@@ -1228,10 +1228,10 @@
         <v>0.034</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>0.0447</v>
+        <v>0.0451</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.0196</v>
+        <v>0.0004</v>
       </c>
       <c r="K14" s="9" t="n"/>
       <c r="L14" s="9" t="n"/>
@@ -1251,7 +1251,7 @@
         <v/>
       </c>
       <c r="Q14" s="12" t="n">
-        <v>27.81</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="15">
@@ -1288,13 +1288,13 @@
         <v/>
       </c>
       <c r="H15" s="8" t="n">
-        <v>0.0332</v>
+        <v>0.0331</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>0.0443</v>
+        <v>0.0447</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="K15" s="9" t="n"/>
       <c r="L15" s="9" t="n"/>
@@ -1314,7 +1314,7 @@
         <v/>
       </c>
       <c r="Q15" s="12" t="n">
-        <v>4.76</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="16">
@@ -1354,10 +1354,10 @@
         <v>0.0282</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>0.0438</v>
+        <v>0.0441</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.0001</v>
+        <v>0.0003</v>
       </c>
       <c r="K16" s="9" t="n"/>
       <c r="L16" s="9" t="n"/>
@@ -1377,7 +1377,7 @@
         <v/>
       </c>
       <c r="Q16" s="12" t="n">
-        <v>34.2</v>
+        <v>34.29</v>
       </c>
     </row>
     <row r="17">
@@ -1414,13 +1414,13 @@
         <v/>
       </c>
       <c r="H17" s="8" t="n">
-        <v>0.0336</v>
+        <v>0.0335</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>0.0445</v>
+        <v>0.04480000000000001</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0</v>
+        <v>0.0003</v>
       </c>
       <c r="K17" s="9" t="n"/>
       <c r="L17" s="9" t="n"/>
@@ -1440,7 +1440,7 @@
         <v/>
       </c>
       <c r="Q17" s="12" t="n">
-        <v>5.09</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="18">
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="H18" s="8" t="n">
-        <v>0.0299</v>
+        <v>0.03</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>0.043</v>
+        <v>0.0435</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="K18" s="9" t="n"/>
       <c r="L18" s="9" t="n"/>
@@ -1503,7 +1503,7 @@
         <v/>
       </c>
       <c r="Q18" s="12" t="n">
-        <v>4.81</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="19">
@@ -1543,10 +1543,10 @@
         <v>0.0169</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>0.0362</v>
+        <v>0.0365</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>-0.0004</v>
+        <v>0.0003</v>
       </c>
       <c r="K19" s="9" t="n"/>
       <c r="L19" s="9" t="n"/>
@@ -1566,7 +1566,7 @@
         <v/>
       </c>
       <c r="Q19" s="12" t="n">
-        <v>9.8202</v>
+        <v>9.844900000000001</v>
       </c>
     </row>
     <row r="20">
@@ -1603,13 +1603,13 @@
         <v/>
       </c>
       <c r="H20" s="8" t="n">
-        <v>0.0284</v>
+        <v>0.0285</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>0.0424</v>
+        <v>0.0428</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="K20" s="9" t="n"/>
       <c r="L20" s="9" t="n"/>
@@ -1669,10 +1669,10 @@
         <v>0.0269</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>0.0424</v>
+        <v>0.04269999999999999</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0</v>
+        <v>0.0003</v>
       </c>
       <c r="K21" s="9" t="n"/>
       <c r="L21" s="9" t="n"/>
@@ -1692,7 +1692,7 @@
         <v/>
       </c>
       <c r="Q21" s="12" t="n">
-        <v>10.4073</v>
+        <v>10.3893</v>
       </c>
     </row>
     <row r="22">
@@ -1732,10 +1732,10 @@
         <v>0.0269</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>0.0424</v>
+        <v>0.04269999999999999</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0</v>
+        <v>0.0003</v>
       </c>
       <c r="K22" s="9" t="n"/>
       <c r="L22" s="9" t="n"/>
@@ -1755,23 +1755,23 @@
         <v/>
       </c>
       <c r="Q22" s="12" t="n">
-        <v>10.0222</v>
+        <v>10.0049</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>IE000I25S1V5</t>
+          <t>LU2673523135</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>47848</v>
+        <v>48121</v>
       </c>
       <c r="G23" s="7">
         <f>IF(F23="","",MAX(0,YEARFRAC(TODAY(),F23)))</f>
@@ -1795,15 +1795,15 @@
         <v>0.0287</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>0.0421</v>
+        <v>0.0424</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="K23" s="9" t="n"/>
       <c r="L23" s="9" t="n"/>
       <c r="M23" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N23" s="10">
         <f>IF(D23="Govt",$B$1,$B$2)</f>
@@ -1818,23 +1818,23 @@
         <v/>
       </c>
       <c r="Q23" s="12" t="n">
-        <v>5.34</v>
+        <v>9.789999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>IE000W6YTDH7</t>
+          <t>LU2673523481</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>47848</v>
+        <v>48121</v>
       </c>
       <c r="G24" s="7">
         <f>IF(F24="","",MAX(0,YEARFRAC(TODAY(),F24)))</f>
@@ -1858,15 +1858,15 @@
         <v>0.0287</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>0.0421</v>
+        <v>0.0424</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="K24" s="9" t="n"/>
       <c r="L24" s="9" t="n"/>
       <c r="M24" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N24" s="10">
         <f>IF(D24="Govt",$B$1,$B$2)</f>
@@ -1881,23 +1881,23 @@
         <v/>
       </c>
       <c r="Q24" s="12" t="n">
-        <v>4.9741</v>
+        <v>29.28</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1C</t>
+          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>LU2673523135</t>
+          <t>IE000I25S1V5</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="F25" s="6" t="n">
-        <v>48121</v>
+        <v>47848</v>
       </c>
       <c r="G25" s="7">
         <f>IF(F25="","",MAX(0,YEARFRAC(TODAY(),F25)))</f>
@@ -1921,15 +1921,15 @@
         <v>0.0287</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>0.042</v>
+        <v>0.0421</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="K25" s="9" t="n"/>
       <c r="L25" s="9" t="n"/>
       <c r="M25" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="N25" s="10">
         <f>IF(D25="Govt",$B$1,$B$2)</f>
@@ -1944,23 +1944,23 @@
         <v/>
       </c>
       <c r="Q25" s="12" t="n">
-        <v>9.77</v>
+        <v>5.3502</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>LU2673523481</t>
+          <t>IE000W6YTDH7</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -1974,7 +1974,7 @@
         </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>48121</v>
+        <v>47848</v>
       </c>
       <c r="G26" s="7">
         <f>IF(F26="","",MAX(0,YEARFRAC(TODAY(),F26)))</f>
@@ -1984,15 +1984,15 @@
         <v>0.0287</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>0.042</v>
+        <v>0.0421</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="K26" s="9" t="n"/>
       <c r="L26" s="9" t="n"/>
       <c r="M26" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="N26" s="10">
         <f>IF(D26="Govt",$B$1,$B$2)</f>
@@ -2007,7 +2007,7 @@
         <v/>
       </c>
       <c r="Q26" s="12" t="n">
-        <v>29.25</v>
+        <v>4.9836</v>
       </c>
     </row>
     <row r="27">
@@ -2044,13 +2044,13 @@
         <v/>
       </c>
       <c r="H27" s="8" t="n">
-        <v>0.0208</v>
+        <v>0.0207</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>0.0353</v>
+        <v>0.0356</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>-0.0004</v>
+        <v>0.0003</v>
       </c>
       <c r="K27" s="9" t="n"/>
       <c r="L27" s="9" t="n"/>
@@ -2070,23 +2070,23 @@
         <v/>
       </c>
       <c r="Q27" s="12" t="n">
-        <v>9.976800000000001</v>
+        <v>9.9948</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2028 Term € Italy Govt Bond UCITS ETF</t>
+          <t>Xtrackers II Target Maturity Sept 2029 Italy and Spain Government Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>IE000Q2EQ5K8</t>
+          <t>LU0484969463</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -2096,24 +2096,24 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F28" s="6" t="n">
-        <v>47118</v>
+        <v>47391</v>
       </c>
       <c r="G28" s="7">
         <f>IF(F28="","",MAX(0,YEARFRAC(TODAY(),F28)))</f>
         <v/>
       </c>
       <c r="H28" s="8" t="n">
-        <v>0.026</v>
+        <v>0.0297</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>0.0347</v>
+        <v>0.0351</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="K28" s="9" t="n"/>
       <c r="L28" s="9" t="n"/>
@@ -2133,50 +2133,50 @@
         <v/>
       </c>
       <c r="Q28" s="12" t="n">
-        <v>5.05</v>
+        <v>204.61</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2029 Italy and Spain Government Bond UCITS ETF 1C</t>
+          <t>iShares iBonds Dec 2030 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>LU0484969463</t>
+          <t>IE000LX17BP9</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F29" s="6" t="n">
-        <v>47391</v>
+        <v>47848</v>
       </c>
       <c r="G29" s="7">
         <f>IF(F29="","",MAX(0,YEARFRAC(TODAY(),F29)))</f>
         <v/>
       </c>
       <c r="H29" s="8" t="n">
-        <v>0.0297</v>
+        <v>0.0279</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>0.0347</v>
+        <v>0.04099999999999999</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.0089</v>
+        <v>0.0003</v>
       </c>
       <c r="K29" s="9" t="n"/>
       <c r="L29" s="9" t="n"/>
@@ -2196,23 +2196,23 @@
         <v/>
       </c>
       <c r="Q29" s="12" t="n">
-        <v>204.21</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2030 Term € Corp UCITS ETF</t>
+          <t>Xtrackers II Target Maturity Sept 2030 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>IE000LX17BP9</t>
+          <t>LU2809864296</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -2226,20 +2226,20 @@
         </is>
       </c>
       <c r="F30" s="6" t="n">
-        <v>47848</v>
+        <v>47756</v>
       </c>
       <c r="G30" s="7">
         <f>IF(F30="","",MAX(0,YEARFRAC(TODAY(),F30)))</f>
         <v/>
       </c>
       <c r="H30" s="8" t="n">
-        <v>0.0279</v>
+        <v>0.0271</v>
       </c>
       <c r="I30" s="8" t="n">
-        <v>0.0407</v>
+        <v>0.0409</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0</v>
+        <v>0.0003</v>
       </c>
       <c r="K30" s="9" t="n"/>
       <c r="L30" s="9" t="n"/>
@@ -2259,28 +2259,28 @@
         <v/>
       </c>
       <c r="Q30" s="12" t="n">
-        <v>4.98</v>
+        <v>35.23</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2030 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>Amundi Fixed Maturity 2028 Euro Government Bond Yield + UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>LU2809864296</t>
+          <t>LU2780871666</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -2289,25 +2289,25 @@
         </is>
       </c>
       <c r="F31" s="6" t="n">
-        <v>47756</v>
+        <v>47118</v>
       </c>
       <c r="G31" s="7">
         <f>IF(F31="","",MAX(0,YEARFRAC(TODAY(),F31)))</f>
         <v/>
       </c>
       <c r="H31" s="8" t="n">
-        <v>0.0271</v>
+        <v>0.0229</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>0.0406</v>
+        <v>0.0341</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.0002</v>
+        <v>0.0004</v>
       </c>
       <c r="K31" s="9" t="n"/>
       <c r="L31" s="9" t="n"/>
       <c r="M31" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N31" s="10">
         <f>IF(D31="Govt",$B$1,$B$2)</f>
@@ -2322,55 +2322,55 @@
         <v/>
       </c>
       <c r="Q31" s="12" t="n">
-        <v>35.2</v>
+        <v>10.2881</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>iShares iBonds Dec 2028 Term € Italy Govt Bond UCITS ETF</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>IE000P5IB8I8</t>
+          <t>IE000Q2EQ5K8</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F32" s="6" t="n">
-        <v>47483</v>
+        <v>47118</v>
       </c>
       <c r="G32" s="7">
         <f>IF(F32="","",MAX(0,YEARFRAC(TODAY(),F32)))</f>
         <v/>
       </c>
       <c r="H32" s="8" t="n">
-        <v>0.0242</v>
+        <v>0.026</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>0.0398</v>
+        <v>0.0342</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0</v>
+        <v>-0.0005</v>
       </c>
       <c r="K32" s="9" t="n"/>
       <c r="L32" s="9" t="n"/>
       <c r="M32" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N32" s="10">
         <f>IF(D32="Govt",$B$1,$B$2)</f>
@@ -2385,7 +2385,7 @@
         <v/>
       </c>
       <c r="Q32" s="12" t="n">
-        <v>5.4204</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="33">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>IE000ZC4C5Q1</t>
+          <t>IE000P5IB8I8</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F33" s="6" t="n">
@@ -2448,28 +2448,28 @@
         <v/>
       </c>
       <c r="Q33" s="12" t="n">
-        <v>5.0508</v>
+        <v>5.4257</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2028 Euro Government Bond Yield + UCITS ETF Dist</t>
+          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>LU2780871666</t>
+          <t>IE000ZC4C5Q1</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -2478,25 +2478,25 @@
         </is>
       </c>
       <c r="F34" s="6" t="n">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="G34" s="7">
         <f>IF(F34="","",MAX(0,YEARFRAC(TODAY(),F34)))</f>
         <v/>
       </c>
       <c r="H34" s="8" t="n">
-        <v>0.023</v>
+        <v>0.0242</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>0.0337</v>
+        <v>0.0398</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>-0.0004</v>
+        <v>0</v>
       </c>
       <c r="K34" s="9" t="n"/>
       <c r="L34" s="9" t="n"/>
       <c r="M34" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="N34" s="10">
         <f>IF(D34="Govt",$B$1,$B$2)</f>
@@ -2511,7 +2511,7 @@
         <v/>
       </c>
       <c r="Q34" s="12" t="n">
-        <v>10.2802</v>
+        <v>5.0558</v>
       </c>
     </row>
     <row r="35">
@@ -2554,7 +2554,7 @@
         <v>0.0334</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>-0.0004</v>
+        <v>0</v>
       </c>
       <c r="K35" s="9" t="n"/>
       <c r="L35" s="9" t="n"/>
@@ -2574,7 +2574,7 @@
         <v/>
       </c>
       <c r="Q35" s="12" t="n">
-        <v>10.2711</v>
+        <v>10.2777</v>
       </c>
     </row>
     <row r="36">
@@ -2617,7 +2617,7 @@
         <v>0.0334</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>-0.0004</v>
+        <v>0</v>
       </c>
       <c r="K36" s="9" t="n"/>
       <c r="L36" s="9" t="n"/>
@@ -2637,7 +2637,7 @@
         <v/>
       </c>
       <c r="Q36" s="12" t="n">
-        <v>10.0706</v>
+        <v>10.0771</v>
       </c>
     </row>
     <row r="37">
@@ -2677,10 +2677,10 @@
         <v>0.0251</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>0.0388</v>
+        <v>0.039</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="K37" s="9" t="n"/>
       <c r="L37" s="9" t="n"/>
@@ -2700,7 +2700,7 @@
         <v/>
       </c>
       <c r="Q37" s="12" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="38">
@@ -2740,10 +2740,10 @@
         <v>0.0245</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>0.0385</v>
+        <v>0.0387</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.0132</v>
+        <v>0.0002</v>
       </c>
       <c r="K38" s="9" t="n"/>
       <c r="L38" s="9" t="n"/>
@@ -2763,7 +2763,7 @@
         <v/>
       </c>
       <c r="Q38" s="12" t="n">
-        <v>25.77</v>
+        <v>25.78</v>
       </c>
     </row>
     <row r="39">
@@ -2803,10 +2803,10 @@
         <v>0.0245</v>
       </c>
       <c r="I39" s="8" t="n">
-        <v>0.0385</v>
+        <v>0.0387</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.0132</v>
+        <v>0.0002</v>
       </c>
       <c r="K39" s="9" t="n"/>
       <c r="L39" s="9" t="n"/>
@@ -2826,23 +2826,23 @@
         <v/>
       </c>
       <c r="Q39" s="12" t="n">
-        <v>9.16</v>
+        <v>9.17</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>BNP Paribas</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2028 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2029 UCITS ETF C</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>IE00079EUF59</t>
+          <t>LU2823896811</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -2856,25 +2856,25 @@
         </is>
       </c>
       <c r="F40" s="6" t="n">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="G40" s="7">
         <f>IF(F40="","",MAX(0,YEARFRAC(TODAY(),F40)))</f>
         <v/>
       </c>
       <c r="H40" s="8" t="n">
-        <v>0.0242</v>
+        <v>0.0235</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>0.0383</v>
+        <v>0.0385</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="K40" s="9" t="n"/>
       <c r="L40" s="9" t="n"/>
       <c r="M40" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N40" s="10">
         <f>IF(D40="Govt",$B$1,$B$2)</f>
@@ -2889,23 +2889,23 @@
         <v/>
       </c>
       <c r="Q40" s="12" t="n">
-        <v>5.5679</v>
+        <v>10.6511</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>BNP Paribas</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2028 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2029 UCITS ETF D</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>IE000LKGEZQ6</t>
+          <t>LU2823896738</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -2919,25 +2919,25 @@
         </is>
       </c>
       <c r="F41" s="6" t="n">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="G41" s="7">
         <f>IF(F41="","",MAX(0,YEARFRAC(TODAY(),F41)))</f>
         <v/>
       </c>
       <c r="H41" s="8" t="n">
-        <v>0.0242</v>
+        <v>0.0235</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>0.0383</v>
+        <v>0.0385</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="K41" s="9" t="n"/>
       <c r="L41" s="9" t="n"/>
       <c r="M41" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N41" s="10">
         <f>IF(D41="Govt",$B$1,$B$2)</f>
@@ -2952,23 +2952,23 @@
         <v/>
       </c>
       <c r="Q41" s="12" t="n">
-        <v>5.2074</v>
+        <v>10.2901</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BNP Paribas</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2029 UCITS ETF C</t>
+          <t>Invesco BulletShares 2028 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>LU2823896811</t>
+          <t>IE00079EUF59</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -2982,14 +2982,14 @@
         </is>
       </c>
       <c r="F42" s="6" t="n">
-        <v>47483</v>
+        <v>47118</v>
       </c>
       <c r="G42" s="7">
         <f>IF(F42="","",MAX(0,YEARFRAC(TODAY(),F42)))</f>
         <v/>
       </c>
       <c r="H42" s="8" t="n">
-        <v>0.0235</v>
+        <v>0.0242</v>
       </c>
       <c r="I42" s="8" t="n">
         <v>0.0383</v>
@@ -3000,7 +3000,7 @@
       <c r="K42" s="9" t="n"/>
       <c r="L42" s="9" t="n"/>
       <c r="M42" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="N42" s="10">
         <f>IF(D42="Govt",$B$1,$B$2)</f>
@@ -3015,23 +3015,23 @@
         <v/>
       </c>
       <c r="Q42" s="12" t="n">
-        <v>10.655</v>
+        <v>5.5692</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BNP Paribas</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2029 UCITS ETF D</t>
+          <t>Invesco BulletShares 2028 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>LU2823896738</t>
+          <t>IE000LKGEZQ6</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -3045,14 +3045,14 @@
         </is>
       </c>
       <c r="F43" s="6" t="n">
-        <v>47483</v>
+        <v>47118</v>
       </c>
       <c r="G43" s="7">
         <f>IF(F43="","",MAX(0,YEARFRAC(TODAY(),F43)))</f>
         <v/>
       </c>
       <c r="H43" s="8" t="n">
-        <v>0.0235</v>
+        <v>0.0242</v>
       </c>
       <c r="I43" s="8" t="n">
         <v>0.0383</v>
@@ -3063,7 +3063,7 @@
       <c r="K43" s="9" t="n"/>
       <c r="L43" s="9" t="n"/>
       <c r="M43" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="N43" s="10">
         <f>IF(D43="Govt",$B$1,$B$2)</f>
@@ -3078,7 +3078,7 @@
         <v/>
       </c>
       <c r="Q43" s="12" t="n">
-        <v>10.2938</v>
+        <v>5.2086</v>
       </c>
     </row>
     <row r="44">
@@ -3118,10 +3118,10 @@
         <v>0.0214</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>0.0371</v>
+        <v>0.0373</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="K44" s="9" t="n"/>
       <c r="L44" s="9" t="n"/>
@@ -3147,22 +3147,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2028 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>Amundi Fixed Maturity 2027 Italy BTP Government Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>LU2810185665</t>
+          <t>LU2780872128</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -3171,25 +3171,25 @@
         </is>
       </c>
       <c r="F45" s="6" t="n">
-        <v>47026</v>
+        <v>46752</v>
       </c>
       <c r="G45" s="7">
         <f>IF(F45="","",MAX(0,YEARFRAC(TODAY(),F45)))</f>
         <v/>
       </c>
       <c r="H45" s="8" t="n">
-        <v>0.0207</v>
+        <v>0.0265</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>0.0366</v>
+        <v>0.0313</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.0004</v>
+        <v>0.0008</v>
       </c>
       <c r="K45" s="9" t="n"/>
       <c r="L45" s="9" t="n"/>
       <c r="M45" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N45" s="10">
         <f>IF(D45="Govt",$B$1,$B$2)</f>
@@ -3204,28 +3204,28 @@
         <v/>
       </c>
       <c r="Q45" s="12" t="n">
-        <v>35.75</v>
+        <v>10.3323</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2027 Italy BTP Government Bond UCITS ETF Dist</t>
+          <t>Xtrackers II Target Maturity Sept 2028 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>LU2780872128</t>
+          <t>LU2810185665</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -3234,25 +3234,25 @@
         </is>
       </c>
       <c r="F46" s="6" t="n">
-        <v>46752</v>
+        <v>47026</v>
       </c>
       <c r="G46" s="7">
         <f>IF(F46="","",MAX(0,YEARFRAC(TODAY(),F46)))</f>
         <v/>
       </c>
       <c r="H46" s="8" t="n">
-        <v>0.0265</v>
+        <v>0.0207</v>
       </c>
       <c r="I46" s="8" t="n">
-        <v>0.0305</v>
+        <v>0.0368</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0002</v>
       </c>
       <c r="K46" s="9" t="n"/>
       <c r="L46" s="9" t="n"/>
       <c r="M46" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N46" s="10">
         <f>IF(D46="Govt",$B$1,$B$2)</f>
@@ -3267,7 +3267,7 @@
         <v/>
       </c>
       <c r="Q46" s="12" t="n">
-        <v>10.3289</v>
+        <v>35.75</v>
       </c>
     </row>
     <row r="47">
@@ -3307,10 +3307,10 @@
         <v>0.015</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>0.0299</v>
+        <v>0.0296</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>-0.0001</v>
+        <v>-0.0003</v>
       </c>
       <c r="K47" s="9" t="n"/>
       <c r="L47" s="9" t="n"/>
@@ -3330,7 +3330,7 @@
         <v/>
       </c>
       <c r="Q47" s="12" t="n">
-        <v>10.1703</v>
+        <v>10.1716</v>
       </c>
     </row>
     <row r="48">
@@ -3341,12 +3341,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2026 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>Amundi Fixed Maturity 2027 German Bund Government Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>LU2872291278</t>
+          <t>LU2780871823</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -3356,24 +3356,24 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
-        <v>46387</v>
+        <v>46752</v>
       </c>
       <c r="G48" s="7">
         <f>IF(F48="","",MAX(0,YEARFRAC(TODAY(),F48)))</f>
         <v/>
       </c>
       <c r="H48" s="8" t="n">
-        <v>0.0023</v>
+        <v>0.0105</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>0.0293</v>
+        <v>0.0284</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.003</v>
+        <v>-0.0008</v>
       </c>
       <c r="K48" s="9" t="n"/>
       <c r="L48" s="9" t="n"/>
@@ -3393,33 +3393,33 @@
         <v/>
       </c>
       <c r="Q48" s="12" t="n">
-        <v>10.2535</v>
+        <v>10.3434</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2027 German Bund Government Bond UCITS ETF Dist</t>
+          <t>iShares iBonds Dec 2027 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>LU2780871823</t>
+          <t>IE000ZOI8OK5</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F49" s="6" t="n">
@@ -3430,18 +3430,18 @@
         <v/>
       </c>
       <c r="H49" s="8" t="n">
-        <v>0.0105</v>
+        <v>0.0195</v>
       </c>
       <c r="I49" s="8" t="n">
-        <v>0.0292</v>
+        <v>0.0333</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0.0001</v>
       </c>
       <c r="K49" s="9" t="n"/>
       <c r="L49" s="9" t="n"/>
       <c r="M49" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N49" s="10">
         <f>IF(D49="Govt",$B$1,$B$2)</f>
@@ -3456,7 +3456,7 @@
         <v/>
       </c>
       <c r="Q49" s="12" t="n">
-        <v>10.3443</v>
+        <v>5.65</v>
       </c>
     </row>
     <row r="50">
@@ -3519,7 +3519,7 @@
         <v/>
       </c>
       <c r="Q50" s="12" t="n">
-        <v>5.7041</v>
+        <v>5.7046</v>
       </c>
     </row>
     <row r="51">
@@ -3582,23 +3582,23 @@
         <v/>
       </c>
       <c r="Q51" s="12" t="n">
-        <v>5.332</v>
+        <v>5.3325</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2027 Term € Corp UCITS ETF</t>
+          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>IE000ZOI8OK5</t>
+          <t>LU2673523218</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -3608,24 +3608,24 @@
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F52" s="6" t="n">
-        <v>46752</v>
+        <v>46660</v>
       </c>
       <c r="G52" s="7">
         <f>IF(F52="","",MAX(0,YEARFRAC(TODAY(),F52)))</f>
         <v/>
       </c>
       <c r="H52" s="8" t="n">
-        <v>0.0195</v>
+        <v>0.0187</v>
       </c>
       <c r="I52" s="8" t="n">
-        <v>0.0332</v>
+        <v>0.0325</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="K52" s="9" t="n"/>
       <c r="L52" s="9" t="n"/>
@@ -3645,7 +3645,7 @@
         <v/>
       </c>
       <c r="Q52" s="12" t="n">
-        <v>5.65</v>
+        <v>25.95</v>
       </c>
     </row>
     <row r="53">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LU2673523218</t>
+          <t>LU2673522830</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F53" s="6" t="n">
@@ -3682,13 +3682,13 @@
         <v/>
       </c>
       <c r="H53" s="8" t="n">
-        <v>0.0186</v>
+        <v>0.0187</v>
       </c>
       <c r="I53" s="8" t="n">
-        <v>0.032</v>
+        <v>0.0325</v>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.0063</v>
+        <v>0.0005</v>
       </c>
       <c r="K53" s="9" t="n"/>
       <c r="L53" s="9" t="n"/>
@@ -3708,50 +3708,50 @@
         <v/>
       </c>
       <c r="Q53" s="12" t="n">
-        <v>25.94</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1C</t>
+          <t>iShares iBonds Dec 2026 Term € Italy Govt Bond UCITS ETF</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>LU2673522830</t>
+          <t>IE000LZ7BZW8</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F54" s="6" t="n">
-        <v>46660</v>
+        <v>46387</v>
       </c>
       <c r="G54" s="7">
         <f>IF(F54="","",MAX(0,YEARFRAC(TODAY(),F54)))</f>
         <v/>
       </c>
       <c r="H54" s="8" t="n">
-        <v>0.0186</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="I54" s="8" t="n">
-        <v>0.032</v>
+        <v>0.0272</v>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.0063</v>
+        <v>0.0002</v>
       </c>
       <c r="K54" s="9" t="n"/>
       <c r="L54" s="9" t="n"/>
@@ -3771,23 +3771,23 @@
         <v/>
       </c>
       <c r="Q54" s="12" t="n">
-        <v>9.300000000000001</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2026 Term € Italy Govt Bond UCITS ETF</t>
+          <t>Amundi Fixed Maturity 2026 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>IE000LZ7BZW8</t>
+          <t>LU2872291278</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F55" s="6" t="n">
@@ -3808,18 +3808,18 @@
         <v/>
       </c>
       <c r="H55" s="8" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0023</v>
       </c>
       <c r="I55" s="8" t="n">
-        <v>0.027</v>
+        <v>0.0261</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0</v>
+        <v>-0.0032</v>
       </c>
       <c r="K55" s="9" t="n"/>
       <c r="L55" s="9" t="n"/>
       <c r="M55" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N55" s="10">
         <f>IF(D55="Govt",$B$1,$B$2)</f>
@@ -3834,7 +3834,7 @@
         <v/>
       </c>
       <c r="Q55" s="12" t="n">
-        <v>5.06</v>
+        <v>10.2545</v>
       </c>
     </row>
     <row r="56">
@@ -3897,7 +3897,7 @@
         <v/>
       </c>
       <c r="Q56" s="12" t="n">
-        <v>5.7887</v>
+        <v>5.7896</v>
       </c>
     </row>
     <row r="57">
@@ -3960,7 +3960,7 @@
         <v/>
       </c>
       <c r="Q57" s="12" t="n">
-        <v>5.4127</v>
+        <v>5.4135</v>
       </c>
     </row>
     <row r="58">
@@ -3997,13 +3997,13 @@
         <v/>
       </c>
       <c r="H58" s="8" t="n">
-        <v>0.0061</v>
+        <v>0.0063</v>
       </c>
       <c r="I58" s="8" t="n">
-        <v>0.0278</v>
+        <v>0.0283</v>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="K58" s="9" t="n"/>
       <c r="L58" s="9" t="n"/>

--- a/data/rendimenti_etf.xlsx
+++ b/data/rendimenti_etf.xlsx
@@ -533,7 +533,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Aggiornato il 07/10/2026 10:56 da yield_etf.csv</t>
+          <t>Aggiornato il 08/10/2026 09:03 da yield_etf.csv</t>
         </is>
       </c>
     </row>
@@ -661,10 +661,10 @@
         <v>0.039</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>0.0506</v>
+        <v>0.0495</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.0004</v>
+        <v>-0.0011</v>
       </c>
       <c r="K5" s="9" t="n"/>
       <c r="L5" s="9" t="n"/>
@@ -684,7 +684,7 @@
         <v/>
       </c>
       <c r="Q5" s="12" t="n">
-        <v>4.88</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="6">
@@ -724,10 +724,10 @@
         <v>0.03759999999999999</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0.0469</v>
+        <v>0.046</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.0004</v>
+        <v>-0.0009</v>
       </c>
       <c r="K6" s="9" t="n"/>
       <c r="L6" s="9" t="n"/>
@@ -784,13 +784,13 @@
         <v/>
       </c>
       <c r="H7" s="8" t="n">
-        <v>0.0355</v>
+        <v>0.0356</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0.0466</v>
+        <v>0.0458</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.0004</v>
+        <v>-0.0008</v>
       </c>
       <c r="K7" s="9" t="n"/>
       <c r="L7" s="9" t="n"/>
@@ -810,7 +810,7 @@
         <v/>
       </c>
       <c r="Q7" s="12" t="n">
-        <v>4.81</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="8">
@@ -850,10 +850,10 @@
         <v>0.0365</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>0.04650000000000001</v>
+        <v>0.0457</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.0004</v>
+        <v>-0.0008</v>
       </c>
       <c r="K8" s="9" t="n"/>
       <c r="L8" s="9" t="n"/>
@@ -913,10 +913,10 @@
         <v>0.0349</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>0.0464</v>
+        <v>0.04559999999999999</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.0005</v>
+        <v>-0.0008</v>
       </c>
       <c r="K9" s="9" t="n"/>
       <c r="L9" s="9" t="n"/>
@@ -976,10 +976,10 @@
         <v>0.0363</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>0.0463</v>
+        <v>0.0454</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.0005</v>
+        <v>-0.0009</v>
       </c>
       <c r="K10" s="9" t="n"/>
       <c r="L10" s="9" t="n"/>
@@ -1039,10 +1039,10 @@
         <v>0.0347</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>0.0459</v>
+        <v>0.045</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.0004</v>
+        <v>-0.0009</v>
       </c>
       <c r="K11" s="9" t="n"/>
       <c r="L11" s="9" t="n"/>
@@ -1102,10 +1102,10 @@
         <v>0.0346</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>0.0454</v>
+        <v>0.0446</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.0004</v>
+        <v>-0.0008</v>
       </c>
       <c r="K12" s="9" t="n"/>
       <c r="L12" s="9" t="n"/>
@@ -1125,7 +1125,7 @@
         <v/>
       </c>
       <c r="Q12" s="12" t="n">
-        <v>4.75</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="13">
@@ -1162,13 +1162,13 @@
         <v/>
       </c>
       <c r="H13" s="8" t="n">
-        <v>0.034</v>
+        <v>0.0339</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0.0451</v>
+        <v>0.0443</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.0004</v>
+        <v>-0.0008</v>
       </c>
       <c r="K13" s="9" t="n"/>
       <c r="L13" s="9" t="n"/>
@@ -1225,13 +1225,13 @@
         <v/>
       </c>
       <c r="H14" s="8" t="n">
-        <v>0.034</v>
+        <v>0.0339</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>0.0451</v>
+        <v>0.0443</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.0004</v>
+        <v>-0.0008</v>
       </c>
       <c r="K14" s="9" t="n"/>
       <c r="L14" s="9" t="n"/>
@@ -1291,10 +1291,10 @@
         <v>0.0331</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>0.0447</v>
+        <v>0.04389999999999999</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.0004</v>
+        <v>-0.0008</v>
       </c>
       <c r="K15" s="9" t="n"/>
       <c r="L15" s="9" t="n"/>
@@ -1354,10 +1354,10 @@
         <v>0.0282</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>0.0441</v>
+        <v>0.0433</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.0003</v>
+        <v>-0.0008</v>
       </c>
       <c r="K16" s="9" t="n"/>
       <c r="L16" s="9" t="n"/>
@@ -1414,13 +1414,13 @@
         <v/>
       </c>
       <c r="H17" s="8" t="n">
-        <v>0.0335</v>
+        <v>0.0334</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>0.04480000000000001</v>
+        <v>0.0438</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.0003</v>
+        <v>-0.001</v>
       </c>
       <c r="K17" s="9" t="n"/>
       <c r="L17" s="9" t="n"/>
@@ -1446,49 +1446,49 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2032 Term € Corp UCITS ETF</t>
+          <t>Amundi Fixed Maturity 2030 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>IE0000MR4GH9</t>
+          <t>LU3120976132</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>48579</v>
+        <v>47848</v>
       </c>
       <c r="G18" s="7">
         <f>IF(F18="","",MAX(0,YEARFRAC(TODAY(),F18)))</f>
         <v/>
       </c>
       <c r="H18" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0169</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>0.0435</v>
+        <v>0.0361</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.0005</v>
+        <v>-0.0004</v>
       </c>
       <c r="K18" s="9" t="n"/>
       <c r="L18" s="9" t="n"/>
       <c r="M18" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N18" s="10">
         <f>IF(D18="Govt",$B$1,$B$2)</f>
@@ -1503,55 +1503,55 @@
         <v/>
       </c>
       <c r="Q18" s="12" t="n">
-        <v>4.82</v>
+        <v>9.832800000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2030 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>iShares iBonds Dec 2032 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LU3120976132</t>
+          <t>IE0000MR4GH9</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>47848</v>
+        <v>48579</v>
       </c>
       <c r="G19" s="7">
         <f>IF(F19="","",MAX(0,YEARFRAC(TODAY(),F19)))</f>
         <v/>
       </c>
       <c r="H19" s="8" t="n">
-        <v>0.0169</v>
+        <v>0.03</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>0.0365</v>
+        <v>0.0428</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.0003</v>
+        <v>-0.0007</v>
       </c>
       <c r="K19" s="9" t="n"/>
       <c r="L19" s="9" t="n"/>
       <c r="M19" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N19" s="10">
         <f>IF(D19="Govt",$B$1,$B$2)</f>
@@ -1566,23 +1566,23 @@
         <v/>
       </c>
       <c r="Q19" s="12" t="n">
-        <v>9.844900000000001</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>BNP Paribas</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2031 Term € Corp UCITS ETF</t>
+          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2032 UCITS ETF C</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>IE000I2WYEU9</t>
+          <t>LU2823895847</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -1592,24 +1592,24 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>48213</v>
+        <v>48579</v>
       </c>
       <c r="G20" s="7">
         <f>IF(F20="","",MAX(0,YEARFRAC(TODAY(),F20)))</f>
         <v/>
       </c>
       <c r="H20" s="8" t="n">
-        <v>0.0285</v>
+        <v>0.0269</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>0.0428</v>
+        <v>0.04269999999999999</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.0004</v>
+        <v>0</v>
       </c>
       <c r="K20" s="9" t="n"/>
       <c r="L20" s="9" t="n"/>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="Q20" s="12" t="n">
-        <v>4.87</v>
+        <v>10.4273</v>
       </c>
     </row>
     <row r="21">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2032 UCITS ETF C</t>
+          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2032 UCITS ETF D</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>LU2823895847</t>
+          <t>LU2823895763</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F21" s="6" t="n">
@@ -1672,7 +1672,7 @@
         <v>0.04269999999999999</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.0003</v>
+        <v>0</v>
       </c>
       <c r="K21" s="9" t="n"/>
       <c r="L21" s="9" t="n"/>
@@ -1692,23 +1692,23 @@
         <v/>
       </c>
       <c r="Q21" s="12" t="n">
-        <v>10.3893</v>
+        <v>10.0415</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BNP Paribas</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2032 UCITS ETF D</t>
+          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>LU2823895763</t>
+          <t>IE000I25S1V5</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1718,29 +1718,29 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>48579</v>
+        <v>47848</v>
       </c>
       <c r="G22" s="7">
         <f>IF(F22="","",MAX(0,YEARFRAC(TODAY(),F22)))</f>
         <v/>
       </c>
       <c r="H22" s="8" t="n">
-        <v>0.0269</v>
+        <v>0.0287</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>0.04269999999999999</v>
+        <v>0.0421</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.0003</v>
+        <v>0</v>
       </c>
       <c r="K22" s="9" t="n"/>
       <c r="L22" s="9" t="n"/>
       <c r="M22" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="N22" s="10">
         <f>IF(D22="Govt",$B$1,$B$2)</f>
@@ -1755,23 +1755,23 @@
         <v/>
       </c>
       <c r="Q22" s="12" t="n">
-        <v>10.0049</v>
+        <v>5.354</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1C</t>
+          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>LU2673523135</t>
+          <t>IE000W6YTDH7</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -1781,11 +1781,11 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>48121</v>
+        <v>47848</v>
       </c>
       <c r="G23" s="7">
         <f>IF(F23="","",MAX(0,YEARFRAC(TODAY(),F23)))</f>
@@ -1795,15 +1795,15 @@
         <v>0.0287</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>0.0424</v>
+        <v>0.0421</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.0004</v>
+        <v>0</v>
       </c>
       <c r="K23" s="9" t="n"/>
       <c r="L23" s="9" t="n"/>
       <c r="M23" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="N23" s="10">
         <f>IF(D23="Govt",$B$1,$B$2)</f>
@@ -1818,23 +1818,23 @@
         <v/>
       </c>
       <c r="Q23" s="12" t="n">
-        <v>9.789999999999999</v>
+        <v>4.9871</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>iShares iBonds Dec 2031 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>LU2673523481</t>
+          <t>IE000I2WYEU9</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -1848,20 +1848,20 @@
         </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>48121</v>
+        <v>48213</v>
       </c>
       <c r="G24" s="7">
         <f>IF(F24="","",MAX(0,YEARFRAC(TODAY(),F24)))</f>
         <v/>
       </c>
       <c r="H24" s="8" t="n">
-        <v>0.0287</v>
+        <v>0.0284</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>0.0424</v>
+        <v>0.0421</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.0004</v>
+        <v>-0.0007</v>
       </c>
       <c r="K24" s="9" t="n"/>
       <c r="L24" s="9" t="n"/>
@@ -1881,28 +1881,28 @@
         <v/>
       </c>
       <c r="Q24" s="12" t="n">
-        <v>29.28</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>Amundi Fixed Maturity 2029 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>IE000I25S1V5</t>
+          <t>LU2872291781</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -1911,25 +1911,25 @@
         </is>
       </c>
       <c r="F25" s="6" t="n">
-        <v>47848</v>
+        <v>47483</v>
       </c>
       <c r="G25" s="7">
         <f>IF(F25="","",MAX(0,YEARFRAC(TODAY(),F25)))</f>
         <v/>
       </c>
       <c r="H25" s="8" t="n">
-        <v>0.0287</v>
+        <v>0.0207</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>0.0421</v>
+        <v>0.0354</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0</v>
+        <v>-0.0002</v>
       </c>
       <c r="K25" s="9" t="n"/>
       <c r="L25" s="9" t="n"/>
       <c r="M25" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0009</v>
       </c>
       <c r="N25" s="10">
         <f>IF(D25="Govt",$B$1,$B$2)</f>
@@ -1944,23 +1944,23 @@
         <v/>
       </c>
       <c r="Q25" s="12" t="n">
-        <v>5.3502</v>
+        <v>9.9861</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>IE000W6YTDH7</t>
+          <t>LU2673523135</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -1970,11 +1970,11 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>47848</v>
+        <v>48121</v>
       </c>
       <c r="G26" s="7">
         <f>IF(F26="","",MAX(0,YEARFRAC(TODAY(),F26)))</f>
@@ -1984,15 +1984,15 @@
         <v>0.0287</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>0.0421</v>
+        <v>0.0418</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="K26" s="9" t="n"/>
       <c r="L26" s="9" t="n"/>
       <c r="M26" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N26" s="10">
         <f>IF(D26="Govt",$B$1,$B$2)</f>
@@ -2007,55 +2007,55 @@
         <v/>
       </c>
       <c r="Q26" s="12" t="n">
-        <v>4.9836</v>
+        <v>9.789999999999999</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2029 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>LU2872291781</t>
+          <t>LU2673523481</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F27" s="6" t="n">
-        <v>47483</v>
+        <v>48121</v>
       </c>
       <c r="G27" s="7">
         <f>IF(F27="","",MAX(0,YEARFRAC(TODAY(),F27)))</f>
         <v/>
       </c>
       <c r="H27" s="8" t="n">
-        <v>0.0207</v>
+        <v>0.0287</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>0.0356</v>
+        <v>0.0418</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.0003</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="K27" s="9" t="n"/>
       <c r="L27" s="9" t="n"/>
       <c r="M27" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N27" s="10">
         <f>IF(D27="Govt",$B$1,$B$2)</f>
@@ -2070,7 +2070,7 @@
         <v/>
       </c>
       <c r="Q27" s="12" t="n">
-        <v>9.9948</v>
+        <v>29.28</v>
       </c>
     </row>
     <row r="28">
@@ -2110,10 +2110,10 @@
         <v>0.0297</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>0.0351</v>
+        <v>0.0345</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.0004</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="K28" s="9" t="n"/>
       <c r="L28" s="9" t="n"/>
@@ -2173,10 +2173,10 @@
         <v>0.0279</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>0.04099999999999999</v>
+        <v>0.0404</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.0003</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="K29" s="9" t="n"/>
       <c r="L29" s="9" t="n"/>
@@ -2236,10 +2236,10 @@
         <v>0.0271</v>
       </c>
       <c r="I30" s="8" t="n">
-        <v>0.0409</v>
+        <v>0.0404</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.0003</v>
+        <v>-0.0005</v>
       </c>
       <c r="K30" s="9" t="n"/>
       <c r="L30" s="9" t="n"/>
@@ -2265,49 +2265,49 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2028 Euro Government Bond Yield + UCITS ETF Dist</t>
+          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>LU2780871666</t>
+          <t>IE000P5IB8I8</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F31" s="6" t="n">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="G31" s="7">
         <f>IF(F31="","",MAX(0,YEARFRAC(TODAY(),F31)))</f>
         <v/>
       </c>
       <c r="H31" s="8" t="n">
-        <v>0.0229</v>
+        <v>0.0242</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>0.0341</v>
+        <v>0.0398</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.0004</v>
+        <v>0</v>
       </c>
       <c r="K31" s="9" t="n"/>
       <c r="L31" s="9" t="n"/>
       <c r="M31" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="N31" s="10">
         <f>IF(D31="Govt",$B$1,$B$2)</f>
@@ -2322,28 +2322,28 @@
         <v/>
       </c>
       <c r="Q31" s="12" t="n">
-        <v>10.2881</v>
+        <v>5.4292</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2028 Term € Italy Govt Bond UCITS ETF</t>
+          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>IE000Q2EQ5K8</t>
+          <t>IE000ZC4C5Q1</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -2352,25 +2352,25 @@
         </is>
       </c>
       <c r="F32" s="6" t="n">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="G32" s="7">
         <f>IF(F32="","",MAX(0,YEARFRAC(TODAY(),F32)))</f>
         <v/>
       </c>
       <c r="H32" s="8" t="n">
-        <v>0.026</v>
+        <v>0.0242</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>0.0342</v>
+        <v>0.0398</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>-0.0005</v>
+        <v>0</v>
       </c>
       <c r="K32" s="9" t="n"/>
       <c r="L32" s="9" t="n"/>
       <c r="M32" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="N32" s="10">
         <f>IF(D32="Govt",$B$1,$B$2)</f>
@@ -2385,55 +2385,55 @@
         <v/>
       </c>
       <c r="Q32" s="12" t="n">
-        <v>5.06</v>
+        <v>5.059</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>Amundi Fixed Maturity 2028 Euro Government Bond Yield + UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>IE000P5IB8I8</t>
+          <t>LU2780871666</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F33" s="6" t="n">
-        <v>47483</v>
+        <v>47118</v>
       </c>
       <c r="G33" s="7">
         <f>IF(F33="","",MAX(0,YEARFRAC(TODAY(),F33)))</f>
         <v/>
       </c>
       <c r="H33" s="8" t="n">
-        <v>0.0242</v>
+        <v>0.0229</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>0.0398</v>
+        <v>0.0335</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="K33" s="9" t="n"/>
       <c r="L33" s="9" t="n"/>
       <c r="M33" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0009</v>
       </c>
       <c r="N33" s="10">
         <f>IF(D33="Govt",$B$1,$B$2)</f>
@@ -2448,28 +2448,28 @@
         <v/>
       </c>
       <c r="Q33" s="12" t="n">
-        <v>5.4257</v>
+        <v>10.2855</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>iShares iBonds Dec 2028 Term € Italy Govt Bond UCITS ETF</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>IE000ZC4C5Q1</t>
+          <t>IE000Q2EQ5K8</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -2478,25 +2478,25 @@
         </is>
       </c>
       <c r="F34" s="6" t="n">
-        <v>47483</v>
+        <v>47118</v>
       </c>
       <c r="G34" s="7">
         <f>IF(F34="","",MAX(0,YEARFRAC(TODAY(),F34)))</f>
         <v/>
       </c>
       <c r="H34" s="8" t="n">
-        <v>0.0242</v>
+        <v>0.026</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>0.0398</v>
+        <v>0.0336</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="K34" s="9" t="n"/>
       <c r="L34" s="9" t="n"/>
       <c r="M34" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N34" s="10">
         <f>IF(D34="Govt",$B$1,$B$2)</f>
@@ -2511,7 +2511,7 @@
         <v/>
       </c>
       <c r="Q34" s="12" t="n">
-        <v>5.0558</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="35">
@@ -2551,10 +2551,10 @@
         <v>0.0184</v>
       </c>
       <c r="I35" s="8" t="n">
-        <v>0.0334</v>
+        <v>0.0331</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0</v>
+        <v>-0.0003</v>
       </c>
       <c r="K35" s="9" t="n"/>
       <c r="L35" s="9" t="n"/>
@@ -2574,7 +2574,7 @@
         <v/>
       </c>
       <c r="Q35" s="12" t="n">
-        <v>10.2777</v>
+        <v>10.277</v>
       </c>
     </row>
     <row r="36">
@@ -2614,10 +2614,10 @@
         <v>0.0184</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>0.0334</v>
+        <v>0.0331</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0</v>
+        <v>-0.0003</v>
       </c>
       <c r="K36" s="9" t="n"/>
       <c r="L36" s="9" t="n"/>
@@ -2637,7 +2637,7 @@
         <v/>
       </c>
       <c r="Q36" s="12" t="n">
-        <v>10.0771</v>
+        <v>10.0764</v>
       </c>
     </row>
     <row r="37">
@@ -2674,13 +2674,13 @@
         <v/>
       </c>
       <c r="H37" s="8" t="n">
-        <v>0.0251</v>
+        <v>0.0252</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>0.039</v>
+        <v>0.0387</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.0002</v>
+        <v>-0.0003</v>
       </c>
       <c r="K37" s="9" t="n"/>
       <c r="L37" s="9" t="n"/>
@@ -2706,17 +2706,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>BNP Paribas</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2029 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2029 UCITS ETF C</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LU2673523309</t>
+          <t>LU2823896811</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -2726,24 +2726,24 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F38" s="6" t="n">
-        <v>47391</v>
+        <v>47483</v>
       </c>
       <c r="G38" s="7">
         <f>IF(F38="","",MAX(0,YEARFRAC(TODAY(),F38)))</f>
         <v/>
       </c>
       <c r="H38" s="8" t="n">
-        <v>0.0245</v>
+        <v>0.0235</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>0.0387</v>
+        <v>0.0385</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="K38" s="9" t="n"/>
       <c r="L38" s="9" t="n"/>
@@ -2763,23 +2763,23 @@
         <v/>
       </c>
       <c r="Q38" s="12" t="n">
-        <v>25.78</v>
+        <v>10.6619</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>BNP Paribas</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2029 EUR Corporate Bond UCITS ETF 1C</t>
+          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2029 UCITS ETF D</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>LU2673522913</t>
+          <t>LU2823896738</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -2789,24 +2789,24 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F39" s="6" t="n">
-        <v>47391</v>
+        <v>47483</v>
       </c>
       <c r="G39" s="7">
         <f>IF(F39="","",MAX(0,YEARFRAC(TODAY(),F39)))</f>
         <v/>
       </c>
       <c r="H39" s="8" t="n">
-        <v>0.0245</v>
+        <v>0.0235</v>
       </c>
       <c r="I39" s="8" t="n">
-        <v>0.0387</v>
+        <v>0.0385</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="K39" s="9" t="n"/>
       <c r="L39" s="9" t="n"/>
@@ -2826,23 +2826,23 @@
         <v/>
       </c>
       <c r="Q39" s="12" t="n">
-        <v>9.17</v>
+        <v>10.3006</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BNP Paribas</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2029 UCITS ETF C</t>
+          <t>Invesco BulletShares 2028 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>LU2823896811</t>
+          <t>IE00079EUF59</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -2856,25 +2856,25 @@
         </is>
       </c>
       <c r="F40" s="6" t="n">
-        <v>47483</v>
+        <v>47118</v>
       </c>
       <c r="G40" s="7">
         <f>IF(F40="","",MAX(0,YEARFRAC(TODAY(),F40)))</f>
         <v/>
       </c>
       <c r="H40" s="8" t="n">
-        <v>0.0235</v>
+        <v>0.0242</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>0.0385</v>
+        <v>0.0383</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="K40" s="9" t="n"/>
       <c r="L40" s="9" t="n"/>
       <c r="M40" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="N40" s="10">
         <f>IF(D40="Govt",$B$1,$B$2)</f>
@@ -2889,23 +2889,23 @@
         <v/>
       </c>
       <c r="Q40" s="12" t="n">
-        <v>10.6511</v>
+        <v>5.5713</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BNP Paribas</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2029 UCITS ETF D</t>
+          <t>Invesco BulletShares 2028 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>LU2823896738</t>
+          <t>IE000LKGEZQ6</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -2919,25 +2919,25 @@
         </is>
       </c>
       <c r="F41" s="6" t="n">
-        <v>47483</v>
+        <v>47118</v>
       </c>
       <c r="G41" s="7">
         <f>IF(F41="","",MAX(0,YEARFRAC(TODAY(),F41)))</f>
         <v/>
       </c>
       <c r="H41" s="8" t="n">
-        <v>0.0235</v>
+        <v>0.0242</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>0.0385</v>
+        <v>0.0383</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="K41" s="9" t="n"/>
       <c r="L41" s="9" t="n"/>
       <c r="M41" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="N41" s="10">
         <f>IF(D41="Govt",$B$1,$B$2)</f>
@@ -2952,23 +2952,23 @@
         <v/>
       </c>
       <c r="Q41" s="12" t="n">
-        <v>10.2901</v>
+        <v>5.2105</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2028 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>Xtrackers II Target Maturity Sept 2029 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>IE00079EUF59</t>
+          <t>LU2673523309</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -2978,29 +2978,29 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
-        <v>47118</v>
+        <v>47391</v>
       </c>
       <c r="G42" s="7">
         <f>IF(F42="","",MAX(0,YEARFRAC(TODAY(),F42)))</f>
         <v/>
       </c>
       <c r="H42" s="8" t="n">
-        <v>0.0242</v>
+        <v>0.0245</v>
       </c>
       <c r="I42" s="8" t="n">
-        <v>0.0383</v>
+        <v>0.0384</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0</v>
+        <v>-0.0003</v>
       </c>
       <c r="K42" s="9" t="n"/>
       <c r="L42" s="9" t="n"/>
       <c r="M42" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N42" s="10">
         <f>IF(D42="Govt",$B$1,$B$2)</f>
@@ -3015,23 +3015,23 @@
         <v/>
       </c>
       <c r="Q42" s="12" t="n">
-        <v>5.5692</v>
+        <v>25.78</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2028 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>Xtrackers II Target Maturity Sept 2029 EUR Corporate Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>IE000LKGEZQ6</t>
+          <t>LU2673522913</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -3041,29 +3041,29 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
-        <v>47118</v>
+        <v>47391</v>
       </c>
       <c r="G43" s="7">
         <f>IF(F43="","",MAX(0,YEARFRAC(TODAY(),F43)))</f>
         <v/>
       </c>
       <c r="H43" s="8" t="n">
-        <v>0.0242</v>
+        <v>0.0245</v>
       </c>
       <c r="I43" s="8" t="n">
-        <v>0.0383</v>
+        <v>0.0384</v>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0</v>
+        <v>-0.0003</v>
       </c>
       <c r="K43" s="9" t="n"/>
       <c r="L43" s="9" t="n"/>
       <c r="M43" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N43" s="10">
         <f>IF(D43="Govt",$B$1,$B$2)</f>
@@ -3078,7 +3078,7 @@
         <v/>
       </c>
       <c r="Q43" s="12" t="n">
-        <v>5.2086</v>
+        <v>9.17</v>
       </c>
     </row>
     <row r="44">
@@ -3115,13 +3115,13 @@
         <v/>
       </c>
       <c r="H44" s="8" t="n">
-        <v>0.0214</v>
+        <v>0.0213</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>0.0373</v>
+        <v>0.0371</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.0002</v>
+        <v>-0.0002</v>
       </c>
       <c r="K44" s="9" t="n"/>
       <c r="L44" s="9" t="n"/>
@@ -3181,10 +3181,10 @@
         <v>0.0265</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>0.0313</v>
+        <v>0.0311</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.0008</v>
+        <v>-0.0002</v>
       </c>
       <c r="K45" s="9" t="n"/>
       <c r="L45" s="9" t="n"/>
@@ -3204,7 +3204,7 @@
         <v/>
       </c>
       <c r="Q45" s="12" t="n">
-        <v>10.3323</v>
+        <v>10.3322</v>
       </c>
     </row>
     <row r="46">
@@ -3247,7 +3247,7 @@
         <v>0.0368</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="K46" s="9" t="n"/>
       <c r="L46" s="9" t="n"/>
@@ -3307,10 +3307,10 @@
         <v>0.015</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>0.0296</v>
+        <v>0.0297</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0.0001</v>
       </c>
       <c r="K47" s="9" t="n"/>
       <c r="L47" s="9" t="n"/>
@@ -3330,7 +3330,7 @@
         <v/>
       </c>
       <c r="Q47" s="12" t="n">
-        <v>10.1716</v>
+        <v>10.1722</v>
       </c>
     </row>
     <row r="48">
@@ -3370,10 +3370,10 @@
         <v>0.0105</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>0.0284</v>
+        <v>0.0283</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>-0.0008</v>
+        <v>-0.0001</v>
       </c>
       <c r="K48" s="9" t="n"/>
       <c r="L48" s="9" t="n"/>
@@ -3393,7 +3393,7 @@
         <v/>
       </c>
       <c r="Q48" s="12" t="n">
-        <v>10.3434</v>
+        <v>10.3457</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         <v>0.0333</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="K49" s="9" t="n"/>
       <c r="L49" s="9" t="n"/>
@@ -3519,7 +3519,7 @@
         <v/>
       </c>
       <c r="Q50" s="12" t="n">
-        <v>5.7046</v>
+        <v>5.7051</v>
       </c>
     </row>
     <row r="51">
@@ -3582,7 +3582,7 @@
         <v/>
       </c>
       <c r="Q51" s="12" t="n">
-        <v>5.3325</v>
+        <v>5.333</v>
       </c>
     </row>
     <row r="52">
@@ -3622,10 +3622,10 @@
         <v>0.0187</v>
       </c>
       <c r="I52" s="8" t="n">
-        <v>0.0325</v>
+        <v>0.03240000000000001</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.0005</v>
+        <v>-0.0001</v>
       </c>
       <c r="K52" s="9" t="n"/>
       <c r="L52" s="9" t="n"/>
@@ -3685,10 +3685,10 @@
         <v>0.0187</v>
       </c>
       <c r="I53" s="8" t="n">
-        <v>0.0325</v>
+        <v>0.03240000000000001</v>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.0005</v>
+        <v>-0.0001</v>
       </c>
       <c r="K53" s="9" t="n"/>
       <c r="L53" s="9" t="n"/>
@@ -3748,10 +3748,10 @@
         <v>0.008800000000000001</v>
       </c>
       <c r="I54" s="8" t="n">
-        <v>0.0272</v>
+        <v>0.0271</v>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.0002</v>
+        <v>-0.0001</v>
       </c>
       <c r="K54" s="9" t="n"/>
       <c r="L54" s="9" t="n"/>
@@ -3811,10 +3811,10 @@
         <v>0.0023</v>
       </c>
       <c r="I55" s="8" t="n">
-        <v>0.0261</v>
+        <v>0.0265</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>-0.0032</v>
+        <v>0.0004</v>
       </c>
       <c r="K55" s="9" t="n"/>
       <c r="L55" s="9" t="n"/>
@@ -3834,7 +3834,7 @@
         <v/>
       </c>
       <c r="Q55" s="12" t="n">
-        <v>10.2545</v>
+        <v>10.2553</v>
       </c>
     </row>
     <row r="56">
@@ -3897,7 +3897,7 @@
         <v/>
       </c>
       <c r="Q56" s="12" t="n">
-        <v>5.7896</v>
+        <v>5.79</v>
       </c>
     </row>
     <row r="57">
@@ -3960,7 +3960,7 @@
         <v/>
       </c>
       <c r="Q57" s="12" t="n">
-        <v>5.4135</v>
+        <v>5.4139</v>
       </c>
     </row>
     <row r="58">
@@ -3997,13 +3997,13 @@
         <v/>
       </c>
       <c r="H58" s="8" t="n">
-        <v>0.0063</v>
+        <v>0.0061</v>
       </c>
       <c r="I58" s="8" t="n">
-        <v>0.0283</v>
+        <v>0.0282</v>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.0005</v>
+        <v>-0.0001</v>
       </c>
       <c r="K58" s="9" t="n"/>
       <c r="L58" s="9" t="n"/>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="Q58" s="12" t="n">
-        <v>5.05</v>
+        <v>5.06</v>
       </c>
     </row>
   </sheetData>

--- a/data/rendimenti_etf.xlsx
+++ b/data/rendimenti_etf.xlsx
@@ -533,7 +533,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Aggiornato il 08/10/2026 09:03 da yield_etf.csv</t>
+          <t>Aggiornato il 09/10/2026 09:03 da yield_etf.csv</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
         <v>0.0495</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>-0.0011</v>
+        <v>0</v>
       </c>
       <c r="K5" s="9" t="n"/>
       <c r="L5" s="9" t="n"/>
@@ -684,7 +684,7 @@
         <v/>
       </c>
       <c r="Q5" s="12" t="n">
-        <v>4.89</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="6">
@@ -724,10 +724,10 @@
         <v>0.03759999999999999</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0.046</v>
+        <v>0.0463</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>-0.0009</v>
+        <v>0.0003</v>
       </c>
       <c r="K6" s="9" t="n"/>
       <c r="L6" s="9" t="n"/>
@@ -747,7 +747,7 @@
         <v/>
       </c>
       <c r="Q6" s="12" t="n">
-        <v>28.34</v>
+        <v>28.28</v>
       </c>
     </row>
     <row r="7">
@@ -787,10 +787,10 @@
         <v>0.0356</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0.0458</v>
+        <v>0.046</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>-0.0008</v>
+        <v>0.0002</v>
       </c>
       <c r="K7" s="9" t="n"/>
       <c r="L7" s="9" t="n"/>
@@ -850,10 +850,10 @@
         <v>0.0365</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>0.0457</v>
+        <v>0.0459</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>-0.0008</v>
+        <v>0.0002</v>
       </c>
       <c r="K8" s="9" t="n"/>
       <c r="L8" s="9" t="n"/>
@@ -873,7 +873,7 @@
         <v/>
       </c>
       <c r="Q8" s="12" t="n">
-        <v>29.15</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="9">
@@ -913,10 +913,10 @@
         <v>0.0349</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>0.04559999999999999</v>
+        <v>0.0458</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>-0.0008</v>
+        <v>0.0002</v>
       </c>
       <c r="K9" s="9" t="n"/>
       <c r="L9" s="9" t="n"/>
@@ -936,7 +936,7 @@
         <v/>
       </c>
       <c r="Q9" s="12" t="n">
-        <v>4.8</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="10">
@@ -976,10 +976,10 @@
         <v>0.0363</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>0.0454</v>
+        <v>0.04559999999999999</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>-0.0009</v>
+        <v>0.0002</v>
       </c>
       <c r="K10" s="9" t="n"/>
       <c r="L10" s="9" t="n"/>
@@ -999,7 +999,7 @@
         <v/>
       </c>
       <c r="Q10" s="12" t="n">
-        <v>4.72</v>
+        <v>4.71</v>
       </c>
     </row>
     <row r="11">
@@ -1039,10 +1039,10 @@
         <v>0.0347</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>0.045</v>
+        <v>0.0452</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>-0.0009</v>
+        <v>0.0002</v>
       </c>
       <c r="K11" s="9" t="n"/>
       <c r="L11" s="9" t="n"/>
@@ -1062,7 +1062,7 @@
         <v/>
       </c>
       <c r="Q11" s="12" t="n">
-        <v>33.53</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="12">
@@ -1102,10 +1102,10 @@
         <v>0.0346</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>0.0446</v>
+        <v>0.0447</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>-0.0008</v>
+        <v>0.0001</v>
       </c>
       <c r="K12" s="9" t="n"/>
       <c r="L12" s="9" t="n"/>
@@ -1131,17 +1131,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2033 EUR Corporate Bond UCITS ETF 1C</t>
+          <t>iShares iBonds Dec 2033 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LU2673523051</t>
+          <t>IE000E0NL9T3</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -1151,24 +1151,24 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>48852</v>
+        <v>48944</v>
       </c>
       <c r="G13" s="7">
         <f>IF(F13="","",MAX(0,YEARFRAC(TODAY(),F13)))</f>
         <v/>
       </c>
       <c r="H13" s="8" t="n">
-        <v>0.0339</v>
+        <v>0.0331</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0.0443</v>
+        <v>0.044</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>-0.0008</v>
+        <v>0.0001</v>
       </c>
       <c r="K13" s="9" t="n"/>
       <c r="L13" s="9" t="n"/>
@@ -1188,7 +1188,7 @@
         <v/>
       </c>
       <c r="Q13" s="12" t="n">
-        <v>9.31</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="14">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2033 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>Xtrackers II Target Maturity Sept 2033 EUR Corporate Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LU2673523564</t>
+          <t>LU2673523051</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F14" s="6" t="n">
@@ -1225,10 +1225,10 @@
         <v/>
       </c>
       <c r="H14" s="8" t="n">
-        <v>0.0339</v>
+        <v>0.0338</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>0.0443</v>
+        <v>0.0435</v>
       </c>
       <c r="J14" s="9" t="n">
         <v>-0.0008</v>
@@ -1251,23 +1251,23 @@
         <v/>
       </c>
       <c r="Q14" s="12" t="n">
-        <v>27.9</v>
+        <v>9.31</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2033 Term € Corp UCITS ETF</t>
+          <t>Xtrackers II Target Maturity Sept 2033 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>IE000E0NL9T3</t>
+          <t>LU2673523564</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -1281,17 +1281,17 @@
         </is>
       </c>
       <c r="F15" s="6" t="n">
-        <v>48944</v>
+        <v>48852</v>
       </c>
       <c r="G15" s="7">
         <f>IF(F15="","",MAX(0,YEARFRAC(TODAY(),F15)))</f>
         <v/>
       </c>
       <c r="H15" s="8" t="n">
-        <v>0.0331</v>
+        <v>0.0338</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>0.04389999999999999</v>
+        <v>0.0435</v>
       </c>
       <c r="J15" s="9" t="n">
         <v>-0.0008</v>
@@ -1314,7 +1314,7 @@
         <v/>
       </c>
       <c r="Q15" s="12" t="n">
-        <v>4.77</v>
+        <v>27.89</v>
       </c>
     </row>
     <row r="16">
@@ -1354,10 +1354,10 @@
         <v>0.0282</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>0.0433</v>
+        <v>0.0434</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>-0.0008</v>
+        <v>0.0001</v>
       </c>
       <c r="K16" s="9" t="n"/>
       <c r="L16" s="9" t="n"/>
@@ -1414,13 +1414,13 @@
         <v/>
       </c>
       <c r="H17" s="8" t="n">
-        <v>0.0334</v>
+        <v>0.034</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>0.0438</v>
+        <v>0.04389999999999999</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>-0.001</v>
+        <v>0.0001</v>
       </c>
       <c r="K17" s="9" t="n"/>
       <c r="L17" s="9" t="n"/>
@@ -1440,7 +1440,7 @@
         <v/>
       </c>
       <c r="Q17" s="12" t="n">
-        <v>5.1</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="18">
@@ -1480,10 +1480,10 @@
         <v>0.0169</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>0.0361</v>
+        <v>0.0362</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>-0.0004</v>
+        <v>0.0001</v>
       </c>
       <c r="K18" s="9" t="n"/>
       <c r="L18" s="9" t="n"/>
@@ -1503,7 +1503,7 @@
         <v/>
       </c>
       <c r="Q18" s="12" t="n">
-        <v>9.832800000000001</v>
+        <v>9.8261</v>
       </c>
     </row>
     <row r="19">
@@ -1543,10 +1543,10 @@
         <v>0.03</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>0.0428</v>
+        <v>0.04269999999999999</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>-0.0007</v>
+        <v>-0.0001</v>
       </c>
       <c r="K19" s="9" t="n"/>
       <c r="L19" s="9" t="n"/>
@@ -1572,17 +1572,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BNP Paribas</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2032 UCITS ETF C</t>
+          <t>iShares iBonds Dec 2031 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LU2823895847</t>
+          <t>IE000I2WYEU9</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -1592,24 +1592,24 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>48579</v>
+        <v>48213</v>
       </c>
       <c r="G20" s="7">
         <f>IF(F20="","",MAX(0,YEARFRAC(TODAY(),F20)))</f>
         <v/>
       </c>
       <c r="H20" s="8" t="n">
-        <v>0.0269</v>
+        <v>0.0285</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>0.04269999999999999</v>
+        <v>0.042</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0</v>
+        <v>-0.0001</v>
       </c>
       <c r="K20" s="9" t="n"/>
       <c r="L20" s="9" t="n"/>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="Q20" s="12" t="n">
-        <v>10.4273</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="21">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2032 UCITS ETF D</t>
+          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2032 UCITS ETF C</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>LU2823895763</t>
+          <t>LU2823895847</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F21" s="6" t="n">
@@ -1669,10 +1669,10 @@
         <v>0.0269</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>0.04269999999999999</v>
+        <v>0.04190000000000001</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0</v>
+        <v>-0.0008</v>
       </c>
       <c r="K21" s="9" t="n"/>
       <c r="L21" s="9" t="n"/>
@@ -1692,23 +1692,23 @@
         <v/>
       </c>
       <c r="Q21" s="12" t="n">
-        <v>10.0415</v>
+        <v>10.4295</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>BNP Paribas</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2032 UCITS ETF D</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>IE000I25S1V5</t>
+          <t>LU2823895763</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1718,29 +1718,29 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>47848</v>
+        <v>48579</v>
       </c>
       <c r="G22" s="7">
         <f>IF(F22="","",MAX(0,YEARFRAC(TODAY(),F22)))</f>
         <v/>
       </c>
       <c r="H22" s="8" t="n">
-        <v>0.0287</v>
+        <v>0.0269</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>0.0421</v>
+        <v>0.04190000000000001</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0</v>
+        <v>-0.0008</v>
       </c>
       <c r="K22" s="9" t="n"/>
       <c r="L22" s="9" t="n"/>
       <c r="M22" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N22" s="10">
         <f>IF(D22="Govt",$B$1,$B$2)</f>
@@ -1755,55 +1755,55 @@
         <v/>
       </c>
       <c r="Q22" s="12" t="n">
-        <v>5.354</v>
+        <v>10.0436</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>Amundi Fixed Maturity 2029 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>IE000W6YTDH7</t>
+          <t>LU2872291781</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>47848</v>
+        <v>47483</v>
       </c>
       <c r="G23" s="7">
         <f>IF(F23="","",MAX(0,YEARFRAC(TODAY(),F23)))</f>
         <v/>
       </c>
       <c r="H23" s="8" t="n">
-        <v>0.0287</v>
+        <v>0.0208</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>0.0421</v>
+        <v>0.0353</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0</v>
+        <v>-0.0001</v>
       </c>
       <c r="K23" s="9" t="n"/>
       <c r="L23" s="9" t="n"/>
       <c r="M23" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0009</v>
       </c>
       <c r="N23" s="10">
         <f>IF(D23="Govt",$B$1,$B$2)</f>
@@ -1818,23 +1818,23 @@
         <v/>
       </c>
       <c r="Q23" s="12" t="n">
-        <v>4.9871</v>
+        <v>9.982200000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2031 Term € Corp UCITS ETF</t>
+          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>IE000I2WYEU9</t>
+          <t>LU2673523135</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -1844,24 +1844,24 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>48213</v>
+        <v>48121</v>
       </c>
       <c r="G24" s="7">
         <f>IF(F24="","",MAX(0,YEARFRAC(TODAY(),F24)))</f>
         <v/>
       </c>
       <c r="H24" s="8" t="n">
-        <v>0.0284</v>
+        <v>0.0287</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>0.0421</v>
+        <v>0.0417</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>-0.0007</v>
+        <v>-0.0001</v>
       </c>
       <c r="K24" s="9" t="n"/>
       <c r="L24" s="9" t="n"/>
@@ -1881,55 +1881,55 @@
         <v/>
       </c>
       <c r="Q24" s="12" t="n">
-        <v>4.87</v>
+        <v>9.789999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2029 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>LU2872291781</t>
+          <t>LU2673523481</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F25" s="6" t="n">
-        <v>47483</v>
+        <v>48121</v>
       </c>
       <c r="G25" s="7">
         <f>IF(F25="","",MAX(0,YEARFRAC(TODAY(),F25)))</f>
         <v/>
       </c>
       <c r="H25" s="8" t="n">
-        <v>0.0207</v>
+        <v>0.0287</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>0.0354</v>
+        <v>0.0417</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>-0.0002</v>
+        <v>-0.0001</v>
       </c>
       <c r="K25" s="9" t="n"/>
       <c r="L25" s="9" t="n"/>
       <c r="M25" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N25" s="10">
         <f>IF(D25="Govt",$B$1,$B$2)</f>
@@ -1944,7 +1944,7 @@
         <v/>
       </c>
       <c r="Q25" s="12" t="n">
-        <v>9.9861</v>
+        <v>29.3</v>
       </c>
     </row>
     <row r="26">
@@ -1955,17 +1955,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1C</t>
+          <t>Xtrackers II Target Maturity Sept 2029 Italy and Spain Government Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>LU2673523135</t>
+          <t>LU0484969463</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -1974,20 +1974,20 @@
         </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>48121</v>
+        <v>47391</v>
       </c>
       <c r="G26" s="7">
         <f>IF(F26="","",MAX(0,YEARFRAC(TODAY(),F26)))</f>
         <v/>
       </c>
       <c r="H26" s="8" t="n">
-        <v>0.0287</v>
+        <v>0.0297</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>0.0418</v>
+        <v>0.0347</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0002</v>
       </c>
       <c r="K26" s="9" t="n"/>
       <c r="L26" s="9" t="n"/>
@@ -2007,23 +2007,23 @@
         <v/>
       </c>
       <c r="Q26" s="12" t="n">
-        <v>9.789999999999999</v>
+        <v>204.58</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>LU2673523481</t>
+          <t>IE000I25S1V5</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -2033,11 +2033,11 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F27" s="6" t="n">
-        <v>48121</v>
+        <v>47848</v>
       </c>
       <c r="G27" s="7">
         <f>IF(F27="","",MAX(0,YEARFRAC(TODAY(),F27)))</f>
@@ -2047,15 +2047,15 @@
         <v>0.0287</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>0.0418</v>
+        <v>0.0406</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0015</v>
       </c>
       <c r="K27" s="9" t="n"/>
       <c r="L27" s="9" t="n"/>
       <c r="M27" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="N27" s="10">
         <f>IF(D27="Govt",$B$1,$B$2)</f>
@@ -2070,55 +2070,55 @@
         <v/>
       </c>
       <c r="Q27" s="12" t="n">
-        <v>29.28</v>
+        <v>5.3469</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2029 Italy and Spain Government Bond UCITS ETF 1C</t>
+          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>LU0484969463</t>
+          <t>IE000W6YTDH7</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F28" s="6" t="n">
-        <v>47391</v>
+        <v>47848</v>
       </c>
       <c r="G28" s="7">
         <f>IF(F28="","",MAX(0,YEARFRAC(TODAY(),F28)))</f>
         <v/>
       </c>
       <c r="H28" s="8" t="n">
-        <v>0.0297</v>
+        <v>0.0286</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>0.0345</v>
+        <v>0.0406</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0015</v>
       </c>
       <c r="K28" s="9" t="n"/>
       <c r="L28" s="9" t="n"/>
       <c r="M28" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="N28" s="10">
         <f>IF(D28="Govt",$B$1,$B$2)</f>
@@ -2133,7 +2133,7 @@
         <v/>
       </c>
       <c r="Q28" s="12" t="n">
-        <v>204.61</v>
+        <v>4.9806</v>
       </c>
     </row>
     <row r="29">
@@ -2173,10 +2173,10 @@
         <v>0.0279</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>0.0404</v>
+        <v>0.0403</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0001</v>
       </c>
       <c r="K29" s="9" t="n"/>
       <c r="L29" s="9" t="n"/>
@@ -2236,10 +2236,10 @@
         <v>0.0271</v>
       </c>
       <c r="I30" s="8" t="n">
-        <v>0.0404</v>
+        <v>0.04019999999999999</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>-0.0005</v>
+        <v>-0.0002</v>
       </c>
       <c r="K30" s="9" t="n"/>
       <c r="L30" s="9" t="n"/>
@@ -2259,55 +2259,55 @@
         <v/>
       </c>
       <c r="Q30" s="12" t="n">
-        <v>35.23</v>
+        <v>35.26</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>iShares iBonds Dec 2028 Term € Italy Govt Bond UCITS ETF</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>IE000P5IB8I8</t>
+          <t>IE000Q2EQ5K8</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F31" s="6" t="n">
-        <v>47483</v>
+        <v>47118</v>
       </c>
       <c r="G31" s="7">
         <f>IF(F31="","",MAX(0,YEARFRAC(TODAY(),F31)))</f>
         <v/>
       </c>
       <c r="H31" s="8" t="n">
-        <v>0.0242</v>
+        <v>0.026</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>0.0398</v>
+        <v>0.0337</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="K31" s="9" t="n"/>
       <c r="L31" s="9" t="n"/>
       <c r="M31" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N31" s="10">
         <f>IF(D31="Govt",$B$1,$B$2)</f>
@@ -2322,28 +2322,28 @@
         <v/>
       </c>
       <c r="Q31" s="12" t="n">
-        <v>5.4292</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>Amundi Fixed Maturity 2028 Euro Government Bond Yield + UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>IE000ZC4C5Q1</t>
+          <t>LU2780871666</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -2352,25 +2352,25 @@
         </is>
       </c>
       <c r="F32" s="6" t="n">
-        <v>47483</v>
+        <v>47118</v>
       </c>
       <c r="G32" s="7">
         <f>IF(F32="","",MAX(0,YEARFRAC(TODAY(),F32)))</f>
         <v/>
       </c>
       <c r="H32" s="8" t="n">
-        <v>0.0242</v>
+        <v>0.0229</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>0.0398</v>
+        <v>0.0332</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0</v>
+        <v>-0.0003</v>
       </c>
       <c r="K32" s="9" t="n"/>
       <c r="L32" s="9" t="n"/>
       <c r="M32" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0009</v>
       </c>
       <c r="N32" s="10">
         <f>IF(D32="Govt",$B$1,$B$2)</f>
@@ -2385,7 +2385,7 @@
         <v/>
       </c>
       <c r="Q32" s="12" t="n">
-        <v>5.059</v>
+        <v>10.2843</v>
       </c>
     </row>
     <row r="33">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2028 Euro Government Bond Yield + UCITS ETF Dist</t>
+          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>LU2780871666</t>
+          <t>LU2780871401</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -2422,13 +2422,13 @@
         <v/>
       </c>
       <c r="H33" s="8" t="n">
-        <v>0.0229</v>
+        <v>0.0184</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>0.0335</v>
+        <v>0.0328</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0003</v>
       </c>
       <c r="K33" s="9" t="n"/>
       <c r="L33" s="9" t="n"/>
@@ -2448,23 +2448,23 @@
         <v/>
       </c>
       <c r="Q33" s="12" t="n">
-        <v>10.2855</v>
+        <v>10.2744</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2028 Term € Italy Govt Bond UCITS ETF</t>
+          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>IE000Q2EQ5K8</t>
+          <t>LU2780871310</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F34" s="6" t="n">
@@ -2485,18 +2485,18 @@
         <v/>
       </c>
       <c r="H34" s="8" t="n">
-        <v>0.026</v>
+        <v>0.0184</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>0.0336</v>
+        <v>0.0328</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0003</v>
       </c>
       <c r="K34" s="9" t="n"/>
       <c r="L34" s="9" t="n"/>
       <c r="M34" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N34" s="10">
         <f>IF(D34="Govt",$B$1,$B$2)</f>
@@ -2511,55 +2511,55 @@
         <v/>
       </c>
       <c r="Q34" s="12" t="n">
-        <v>5.06</v>
+        <v>10.0739</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Dist</t>
+          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>LU2780871401</t>
+          <t>IE000P5IB8I8</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F35" s="6" t="n">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="G35" s="7">
         <f>IF(F35="","",MAX(0,YEARFRAC(TODAY(),F35)))</f>
         <v/>
       </c>
       <c r="H35" s="8" t="n">
-        <v>0.0184</v>
+        <v>0.0242</v>
       </c>
       <c r="I35" s="8" t="n">
-        <v>0.0331</v>
+        <v>0.0386</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>-0.0003</v>
+        <v>-0.0012</v>
       </c>
       <c r="K35" s="9" t="n"/>
       <c r="L35" s="9" t="n"/>
       <c r="M35" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="N35" s="10">
         <f>IF(D35="Govt",$B$1,$B$2)</f>
@@ -2574,55 +2574,55 @@
         <v/>
       </c>
       <c r="Q35" s="12" t="n">
-        <v>10.277</v>
+        <v>5.4242</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>LU2780871310</t>
+          <t>IE000ZC4C5Q1</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F36" s="6" t="n">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="G36" s="7">
         <f>IF(F36="","",MAX(0,YEARFRAC(TODAY(),F36)))</f>
         <v/>
       </c>
       <c r="H36" s="8" t="n">
-        <v>0.0184</v>
+        <v>0.0242</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>0.0331</v>
+        <v>0.0386</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>-0.0003</v>
+        <v>-0.0012</v>
       </c>
       <c r="K36" s="9" t="n"/>
       <c r="L36" s="9" t="n"/>
       <c r="M36" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="N36" s="10">
         <f>IF(D36="Govt",$B$1,$B$2)</f>
@@ -2637,7 +2637,7 @@
         <v/>
       </c>
       <c r="Q36" s="12" t="n">
-        <v>10.0764</v>
+        <v>5.0543</v>
       </c>
     </row>
     <row r="37">
@@ -2677,10 +2677,10 @@
         <v>0.0252</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>0.0387</v>
+        <v>0.0385</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>-0.0003</v>
+        <v>-0.0002</v>
       </c>
       <c r="K37" s="9" t="n"/>
       <c r="L37" s="9" t="n"/>
@@ -2700,23 +2700,23 @@
         <v/>
       </c>
       <c r="Q37" s="12" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BNP Paribas</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2029 UCITS ETF C</t>
+          <t>Xtrackers II Target Maturity Sept 2029 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LU2823896811</t>
+          <t>LU2673523309</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -2726,24 +2726,24 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F38" s="6" t="n">
-        <v>47483</v>
+        <v>47391</v>
       </c>
       <c r="G38" s="7">
         <f>IF(F38="","",MAX(0,YEARFRAC(TODAY(),F38)))</f>
         <v/>
       </c>
       <c r="H38" s="8" t="n">
-        <v>0.0235</v>
+        <v>0.0245</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>0.0385</v>
+        <v>0.0382</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0</v>
+        <v>-0.0002</v>
       </c>
       <c r="K38" s="9" t="n"/>
       <c r="L38" s="9" t="n"/>
@@ -2763,23 +2763,23 @@
         <v/>
       </c>
       <c r="Q38" s="12" t="n">
-        <v>10.6619</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BNP Paribas</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2029 UCITS ETF D</t>
+          <t>Xtrackers II Target Maturity Sept 2029 EUR Corporate Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>LU2823896738</t>
+          <t>LU2673522913</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -2789,24 +2789,24 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F39" s="6" t="n">
-        <v>47483</v>
+        <v>47391</v>
       </c>
       <c r="G39" s="7">
         <f>IF(F39="","",MAX(0,YEARFRAC(TODAY(),F39)))</f>
         <v/>
       </c>
       <c r="H39" s="8" t="n">
-        <v>0.0235</v>
+        <v>0.0245</v>
       </c>
       <c r="I39" s="8" t="n">
-        <v>0.0385</v>
+        <v>0.0382</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0</v>
+        <v>-0.0002</v>
       </c>
       <c r="K39" s="9" t="n"/>
       <c r="L39" s="9" t="n"/>
@@ -2826,23 +2826,23 @@
         <v/>
       </c>
       <c r="Q39" s="12" t="n">
-        <v>10.3006</v>
+        <v>9.17</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>BNP Paribas</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2028 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2029 UCITS ETF C</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>IE00079EUF59</t>
+          <t>LU2823896811</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -2856,25 +2856,25 @@
         </is>
       </c>
       <c r="F40" s="6" t="n">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="G40" s="7">
         <f>IF(F40="","",MAX(0,YEARFRAC(TODAY(),F40)))</f>
         <v/>
       </c>
       <c r="H40" s="8" t="n">
-        <v>0.0242</v>
+        <v>0.0235</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>0.0383</v>
+        <v>0.0379</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="K40" s="9" t="n"/>
       <c r="L40" s="9" t="n"/>
       <c r="M40" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N40" s="10">
         <f>IF(D40="Govt",$B$1,$B$2)</f>
@@ -2889,23 +2889,23 @@
         <v/>
       </c>
       <c r="Q40" s="12" t="n">
-        <v>5.5713</v>
+        <v>10.6685</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>BNP Paribas</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2028 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2029 UCITS ETF D</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>IE000LKGEZQ6</t>
+          <t>LU2823896738</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -2919,25 +2919,25 @@
         </is>
       </c>
       <c r="F41" s="6" t="n">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="G41" s="7">
         <f>IF(F41="","",MAX(0,YEARFRAC(TODAY(),F41)))</f>
         <v/>
       </c>
       <c r="H41" s="8" t="n">
-        <v>0.0242</v>
+        <v>0.0235</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>0.0383</v>
+        <v>0.0379</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="K41" s="9" t="n"/>
       <c r="L41" s="9" t="n"/>
       <c r="M41" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N41" s="10">
         <f>IF(D41="Govt",$B$1,$B$2)</f>
@@ -2952,23 +2952,23 @@
         <v/>
       </c>
       <c r="Q41" s="12" t="n">
-        <v>5.2105</v>
+        <v>10.3069</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2029 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>Invesco BulletShares 2028 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>LU2673523309</t>
+          <t>IE00079EUF59</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -2978,29 +2978,29 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
-        <v>47391</v>
+        <v>47118</v>
       </c>
       <c r="G42" s="7">
         <f>IF(F42="","",MAX(0,YEARFRAC(TODAY(),F42)))</f>
         <v/>
       </c>
       <c r="H42" s="8" t="n">
-        <v>0.0245</v>
+        <v>0.0242</v>
       </c>
       <c r="I42" s="8" t="n">
-        <v>0.0384</v>
+        <v>0.0375</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>-0.0003</v>
+        <v>-0.0008</v>
       </c>
       <c r="K42" s="9" t="n"/>
       <c r="L42" s="9" t="n"/>
       <c r="M42" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="N42" s="10">
         <f>IF(D42="Govt",$B$1,$B$2)</f>
@@ -3015,23 +3015,23 @@
         <v/>
       </c>
       <c r="Q42" s="12" t="n">
-        <v>25.78</v>
+        <v>5.5687</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2029 EUR Corporate Bond UCITS ETF 1C</t>
+          <t>Invesco BulletShares 2028 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>LU2673522913</t>
+          <t>IE000LKGEZQ6</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -3041,29 +3041,29 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
-        <v>47391</v>
+        <v>47118</v>
       </c>
       <c r="G43" s="7">
         <f>IF(F43="","",MAX(0,YEARFRAC(TODAY(),F43)))</f>
         <v/>
       </c>
       <c r="H43" s="8" t="n">
-        <v>0.0245</v>
+        <v>0.0242</v>
       </c>
       <c r="I43" s="8" t="n">
-        <v>0.0384</v>
+        <v>0.0375</v>
       </c>
       <c r="J43" s="9" t="n">
-        <v>-0.0003</v>
+        <v>-0.0008</v>
       </c>
       <c r="K43" s="9" t="n"/>
       <c r="L43" s="9" t="n"/>
       <c r="M43" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="N43" s="10">
         <f>IF(D43="Govt",$B$1,$B$2)</f>
@@ -3078,7 +3078,7 @@
         <v/>
       </c>
       <c r="Q43" s="12" t="n">
-        <v>9.17</v>
+        <v>5.2081</v>
       </c>
     </row>
     <row r="44">
@@ -3115,13 +3115,13 @@
         <v/>
       </c>
       <c r="H44" s="8" t="n">
-        <v>0.0213</v>
+        <v>0.0214</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>0.0371</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>-0.0002</v>
+        <v>-0.0001</v>
       </c>
       <c r="K44" s="9" t="n"/>
       <c r="L44" s="9" t="n"/>
@@ -3147,22 +3147,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2027 Italy BTP Government Bond UCITS ETF Dist</t>
+          <t>Xtrackers II Target Maturity Sept 2028 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>LU2780872128</t>
+          <t>LU2810185665</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -3171,25 +3171,25 @@
         </is>
       </c>
       <c r="F45" s="6" t="n">
-        <v>46752</v>
+        <v>47026</v>
       </c>
       <c r="G45" s="7">
         <f>IF(F45="","",MAX(0,YEARFRAC(TODAY(),F45)))</f>
         <v/>
       </c>
       <c r="H45" s="8" t="n">
-        <v>0.0265</v>
+        <v>0.0207</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>0.0311</v>
+        <v>0.0367</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>-0.0002</v>
+        <v>-0.0001</v>
       </c>
       <c r="K45" s="9" t="n"/>
       <c r="L45" s="9" t="n"/>
       <c r="M45" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N45" s="10">
         <f>IF(D45="Govt",$B$1,$B$2)</f>
@@ -3204,28 +3204,28 @@
         <v/>
       </c>
       <c r="Q45" s="12" t="n">
-        <v>10.3322</v>
+        <v>35.76</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2028 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>Amundi Fixed Maturity 2027 Italy BTP Government Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>LU2810185665</t>
+          <t>LU2780872128</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -3234,25 +3234,25 @@
         </is>
       </c>
       <c r="F46" s="6" t="n">
-        <v>47026</v>
+        <v>46752</v>
       </c>
       <c r="G46" s="7">
         <f>IF(F46="","",MAX(0,YEARFRAC(TODAY(),F46)))</f>
         <v/>
       </c>
       <c r="H46" s="8" t="n">
-        <v>0.0207</v>
+        <v>0.0265</v>
       </c>
       <c r="I46" s="8" t="n">
-        <v>0.0368</v>
+        <v>0.0307</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0</v>
+        <v>-0.0004</v>
       </c>
       <c r="K46" s="9" t="n"/>
       <c r="L46" s="9" t="n"/>
       <c r="M46" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N46" s="10">
         <f>IF(D46="Govt",$B$1,$B$2)</f>
@@ -3267,7 +3267,7 @@
         <v/>
       </c>
       <c r="Q46" s="12" t="n">
-        <v>35.75</v>
+        <v>10.3334</v>
       </c>
     </row>
     <row r="47">
@@ -3307,10 +3307,10 @@
         <v>0.015</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>0.0297</v>
+        <v>0.0295</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.0001</v>
+        <v>-0.0002</v>
       </c>
       <c r="K47" s="9" t="n"/>
       <c r="L47" s="9" t="n"/>
@@ -3330,33 +3330,33 @@
         <v/>
       </c>
       <c r="Q47" s="12" t="n">
-        <v>10.1722</v>
+        <v>10.1734</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2027 German Bund Government Bond UCITS ETF Dist</t>
+          <t>Invesco BulletShares 2027 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>LU2780871823</t>
+          <t>IE000LGHLQ71</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
@@ -3367,18 +3367,18 @@
         <v/>
       </c>
       <c r="H48" s="8" t="n">
-        <v>0.0105</v>
+        <v>0.0197</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>0.0283</v>
+        <v>0.0335</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0.0004</v>
       </c>
       <c r="K48" s="9" t="n"/>
       <c r="L48" s="9" t="n"/>
       <c r="M48" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="N48" s="10">
         <f>IF(D48="Govt",$B$1,$B$2)</f>
@@ -3393,23 +3393,23 @@
         <v/>
       </c>
       <c r="Q48" s="12" t="n">
-        <v>10.3457</v>
+        <v>5.7054</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2027 Term € Corp UCITS ETF</t>
+          <t>Invesco BulletShares 2027 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>IE000ZOI8OK5</t>
+          <t>IE000XOS4OJ6</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F49" s="6" t="n">
@@ -3430,18 +3430,18 @@
         <v/>
       </c>
       <c r="H49" s="8" t="n">
-        <v>0.0195</v>
+        <v>0.0197</v>
       </c>
       <c r="I49" s="8" t="n">
-        <v>0.0333</v>
+        <v>0.0335</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="K49" s="9" t="n"/>
       <c r="L49" s="9" t="n"/>
       <c r="M49" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="N49" s="10">
         <f>IF(D49="Govt",$B$1,$B$2)</f>
@@ -3456,33 +3456,33 @@
         <v/>
       </c>
       <c r="Q49" s="12" t="n">
-        <v>5.65</v>
+        <v>5.3332</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2027 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>Amundi Fixed Maturity 2027 German Bund Government Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>IE000LGHLQ71</t>
+          <t>LU2780871823</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
@@ -3493,10 +3493,10 @@
         <v/>
       </c>
       <c r="H50" s="8" t="n">
-        <v>0.0193</v>
+        <v>0.0105</v>
       </c>
       <c r="I50" s="8" t="n">
-        <v>0.0331</v>
+        <v>0.0283</v>
       </c>
       <c r="J50" s="9" t="n">
         <v>0</v>
@@ -3504,7 +3504,7 @@
       <c r="K50" s="9" t="n"/>
       <c r="L50" s="9" t="n"/>
       <c r="M50" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0009</v>
       </c>
       <c r="N50" s="10">
         <f>IF(D50="Govt",$B$1,$B$2)</f>
@@ -3519,23 +3519,23 @@
         <v/>
       </c>
       <c r="Q50" s="12" t="n">
-        <v>5.7051</v>
+        <v>10.3457</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2027 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>iShares iBonds Dec 2027 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>IE000XOS4OJ6</t>
+          <t>IE000ZOI8OK5</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F51" s="6" t="n">
@@ -3556,10 +3556,10 @@
         <v/>
       </c>
       <c r="H51" s="8" t="n">
-        <v>0.0193</v>
+        <v>0.0195</v>
       </c>
       <c r="I51" s="8" t="n">
-        <v>0.0331</v>
+        <v>0.0333</v>
       </c>
       <c r="J51" s="9" t="n">
         <v>0</v>
@@ -3567,7 +3567,7 @@
       <c r="K51" s="9" t="n"/>
       <c r="L51" s="9" t="n"/>
       <c r="M51" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N51" s="10">
         <f>IF(D51="Govt",$B$1,$B$2)</f>
@@ -3582,7 +3582,7 @@
         <v/>
       </c>
       <c r="Q51" s="12" t="n">
-        <v>5.333</v>
+        <v>5.65</v>
       </c>
     </row>
     <row r="52">
@@ -3619,13 +3619,13 @@
         <v/>
       </c>
       <c r="H52" s="8" t="n">
-        <v>0.0187</v>
+        <v>0.0186</v>
       </c>
       <c r="I52" s="8" t="n">
-        <v>0.03240000000000001</v>
+        <v>0.0325</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0.0001</v>
       </c>
       <c r="K52" s="9" t="n"/>
       <c r="L52" s="9" t="n"/>
@@ -3682,13 +3682,13 @@
         <v/>
       </c>
       <c r="H53" s="8" t="n">
-        <v>0.0187</v>
+        <v>0.0186</v>
       </c>
       <c r="I53" s="8" t="n">
-        <v>0.03240000000000001</v>
+        <v>0.0325</v>
       </c>
       <c r="J53" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0.0001</v>
       </c>
       <c r="K53" s="9" t="n"/>
       <c r="L53" s="9" t="n"/>
@@ -3714,17 +3714,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2026 Term € Italy Govt Bond UCITS ETF</t>
+          <t>Amundi Fixed Maturity 2026 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>IE000LZ7BZW8</t>
+          <t>LU2872291278</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F54" s="6" t="n">
@@ -3745,18 +3745,18 @@
         <v/>
       </c>
       <c r="H54" s="8" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0023</v>
       </c>
       <c r="I54" s="8" t="n">
-        <v>0.0271</v>
+        <v>0.0269</v>
       </c>
       <c r="J54" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0.0004</v>
       </c>
       <c r="K54" s="9" t="n"/>
       <c r="L54" s="9" t="n"/>
       <c r="M54" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N54" s="10">
         <f>IF(D54="Govt",$B$1,$B$2)</f>
@@ -3771,23 +3771,23 @@
         <v/>
       </c>
       <c r="Q54" s="12" t="n">
-        <v>5.06</v>
+        <v>10.2574</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2026 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>iShares iBonds Dec 2026 Term € Italy Govt Bond UCITS ETF</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>LU2872291278</t>
+          <t>IE000LZ7BZW8</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F55" s="6" t="n">
@@ -3808,18 +3808,18 @@
         <v/>
       </c>
       <c r="H55" s="8" t="n">
-        <v>0.0023</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="I55" s="8" t="n">
-        <v>0.0265</v>
+        <v>0.027</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.0004</v>
+        <v>-0.0001</v>
       </c>
       <c r="K55" s="9" t="n"/>
       <c r="L55" s="9" t="n"/>
       <c r="M55" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N55" s="10">
         <f>IF(D55="Govt",$B$1,$B$2)</f>
@@ -3834,7 +3834,7 @@
         <v/>
       </c>
       <c r="Q55" s="12" t="n">
-        <v>10.2553</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="56">
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="H56" s="8" t="n">
-        <v>0.0131</v>
+        <v>0.0119</v>
       </c>
       <c r="I56" s="8" t="n">
-        <v>0.0294</v>
+        <v>0.0298</v>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="K56" s="9" t="n"/>
       <c r="L56" s="9" t="n"/>
@@ -3897,7 +3897,7 @@
         <v/>
       </c>
       <c r="Q56" s="12" t="n">
-        <v>5.79</v>
+        <v>5.7911</v>
       </c>
     </row>
     <row r="57">
@@ -3934,13 +3934,13 @@
         <v/>
       </c>
       <c r="H57" s="8" t="n">
-        <v>0.0131</v>
+        <v>0.0119</v>
       </c>
       <c r="I57" s="8" t="n">
-        <v>0.0294</v>
+        <v>0.0298</v>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="K57" s="9" t="n"/>
       <c r="L57" s="9" t="n"/>
@@ -3960,7 +3960,7 @@
         <v/>
       </c>
       <c r="Q57" s="12" t="n">
-        <v>5.4139</v>
+        <v>5.4149</v>
       </c>
     </row>
     <row r="58">
@@ -3997,10 +3997,10 @@
         <v/>
       </c>
       <c r="H58" s="8" t="n">
-        <v>0.0061</v>
+        <v>0.0059</v>
       </c>
       <c r="I58" s="8" t="n">
-        <v>0.0282</v>
+        <v>0.0281</v>
       </c>
       <c r="J58" s="9" t="n">
         <v>-0.0001</v>

--- a/data/rendimenti_etf.xlsx
+++ b/data/rendimenti_etf.xlsx
@@ -533,7 +533,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Aggiornato il 09/10/2026 09:03 da yield_etf.csv</t>
+          <t>Aggiornato il 12/10/2026 14:41 da yield_etf.csv</t>
         </is>
       </c>
     </row>
@@ -661,10 +661,10 @@
         <v>0.039</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>0.0495</v>
+        <v>0.0501</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="K5" s="9" t="n"/>
       <c r="L5" s="9" t="n"/>
@@ -690,17 +690,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2036 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>iShares iBonds Dec 2036 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LU3152892629</t>
+          <t>IE000RQJBQI6</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -714,20 +714,20 @@
         </is>
       </c>
       <c r="F6" s="6" t="n">
-        <v>49948</v>
+        <v>50040</v>
       </c>
       <c r="G6" s="7">
         <f>IF(F6="","",MAX(0,YEARFRAC(TODAY(),F6)))</f>
         <v/>
       </c>
       <c r="H6" s="8" t="n">
-        <v>0.03759999999999999</v>
+        <v>0.0355</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0.0463</v>
+        <v>0.0459</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.0003</v>
+        <v>-0.0001</v>
       </c>
       <c r="K6" s="9" t="n"/>
       <c r="L6" s="9" t="n"/>
@@ -747,7 +747,7 @@
         <v/>
       </c>
       <c r="Q6" s="12" t="n">
-        <v>28.28</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="7">
@@ -758,12 +758,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2036 Term € Corp UCITS ETF</t>
+          <t>iShares iBonds Dec 2037 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>IE000RQJBQI6</t>
+          <t>IE000PWSK6H1</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -777,20 +777,20 @@
         </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>50040</v>
+        <v>50405</v>
       </c>
       <c r="G7" s="7">
         <f>IF(F7="","",MAX(0,YEARFRAC(TODAY(),F7)))</f>
         <v/>
       </c>
       <c r="H7" s="8" t="n">
-        <v>0.0356</v>
+        <v>0.0349</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0.046</v>
+        <v>0.0457</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.0002</v>
+        <v>-0.0001</v>
       </c>
       <c r="K7" s="9" t="n"/>
       <c r="L7" s="9" t="n"/>
@@ -816,17 +816,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2035 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>iShares iBonds Dec 2035 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LU3152892546</t>
+          <t>IE000WLR06P0</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -840,20 +840,20 @@
         </is>
       </c>
       <c r="F8" s="6" t="n">
-        <v>49582</v>
+        <v>49674</v>
       </c>
       <c r="G8" s="7">
         <f>IF(F8="","",MAX(0,YEARFRAC(TODAY(),F8)))</f>
         <v/>
       </c>
       <c r="H8" s="8" t="n">
-        <v>0.0365</v>
+        <v>0.0367</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>0.0459</v>
+        <v>0.0455</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.0002</v>
+        <v>-0.0001</v>
       </c>
       <c r="K8" s="9" t="n"/>
       <c r="L8" s="9" t="n"/>
@@ -873,7 +873,7 @@
         <v/>
       </c>
       <c r="Q8" s="12" t="n">
-        <v>29.1</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="9">
@@ -884,12 +884,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2037 Term € Corp UCITS ETF</t>
+          <t>iShares iBonds Dec 2034 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>IE000PWSK6H1</t>
+          <t>IE000SBJO6L2</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -903,20 +903,20 @@
         </is>
       </c>
       <c r="F9" s="6" t="n">
-        <v>50405</v>
+        <v>49309</v>
       </c>
       <c r="G9" s="7">
         <f>IF(F9="","",MAX(0,YEARFRAC(TODAY(),F9)))</f>
         <v/>
       </c>
       <c r="H9" s="8" t="n">
-        <v>0.0349</v>
+        <v>0.0346</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>0.0458</v>
+        <v>0.0447</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="K9" s="9" t="n"/>
       <c r="L9" s="9" t="n"/>
@@ -936,7 +936,7 @@
         <v/>
       </c>
       <c r="Q9" s="12" t="n">
-        <v>4.79</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="10">
@@ -947,12 +947,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2035 Term € Corp UCITS ETF</t>
+          <t>iShares iBonds Dec 2033 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IE000WLR06P0</t>
+          <t>IE000E0NL9T3</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -966,20 +966,20 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>49674</v>
+        <v>48944</v>
       </c>
       <c r="G10" s="7">
         <f>IF(F10="","",MAX(0,YEARFRAC(TODAY(),F10)))</f>
         <v/>
       </c>
       <c r="H10" s="8" t="n">
-        <v>0.0363</v>
+        <v>0.0331</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>0.04559999999999999</v>
+        <v>0.044</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="K10" s="9" t="n"/>
       <c r="L10" s="9" t="n"/>
@@ -999,7 +999,7 @@
         <v/>
       </c>
       <c r="Q10" s="12" t="n">
-        <v>4.71</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="11">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2034 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>Xtrackers II Target Maturity Sept 2033 EUR Corporate Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LU2809864619</t>
+          <t>LU2673523051</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -1025,24 +1025,24 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F11" s="6" t="n">
-        <v>49217</v>
+        <v>48852</v>
       </c>
       <c r="G11" s="7">
         <f>IF(F11="","",MAX(0,YEARFRAC(TODAY(),F11)))</f>
         <v/>
       </c>
       <c r="H11" s="8" t="n">
-        <v>0.0347</v>
+        <v>0.0338</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>0.0452</v>
+        <v>0.044</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.0002</v>
+        <v>0.0005</v>
       </c>
       <c r="K11" s="9" t="n"/>
       <c r="L11" s="9" t="n"/>
@@ -1062,23 +1062,23 @@
         <v/>
       </c>
       <c r="Q11" s="12" t="n">
-        <v>33.5</v>
+        <v>9.31</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2034 Term € Corp UCITS ETF</t>
+          <t>Xtrackers II Target Maturity Sept 2033 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>IE000SBJO6L2</t>
+          <t>LU2673523564</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -1092,20 +1092,20 @@
         </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>49309</v>
+        <v>48852</v>
       </c>
       <c r="G12" s="7">
         <f>IF(F12="","",MAX(0,YEARFRAC(TODAY(),F12)))</f>
         <v/>
       </c>
       <c r="H12" s="8" t="n">
-        <v>0.0346</v>
+        <v>0.0338</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>0.0447</v>
+        <v>0.044</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.0001</v>
+        <v>0.0005</v>
       </c>
       <c r="K12" s="9" t="n"/>
       <c r="L12" s="9" t="n"/>
@@ -1125,7 +1125,7 @@
         <v/>
       </c>
       <c r="Q12" s="12" t="n">
-        <v>4.74</v>
+        <v>27.88</v>
       </c>
     </row>
     <row r="13">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2033 Term € Corp UCITS ETF</t>
+          <t>iShares iBonds Dec 2028 Term € Corp Crossover UCITS ETF</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>IE000E0NL9T3</t>
+          <t>IE0003HV7CS6</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -1151,29 +1151,29 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>48944</v>
+        <v>47118</v>
       </c>
       <c r="G13" s="7">
         <f>IF(F13="","",MAX(0,YEARFRAC(TODAY(),F13)))</f>
         <v/>
       </c>
       <c r="H13" s="8" t="n">
-        <v>0.0331</v>
+        <v>0.0334</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0.044</v>
+        <v>0.0444</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.0001</v>
+        <v>0.0005</v>
       </c>
       <c r="K13" s="9" t="n"/>
       <c r="L13" s="9" t="n"/>
       <c r="M13" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.002</v>
       </c>
       <c r="N13" s="10">
         <f>IF(D13="Govt",$B$1,$B$2)</f>
@@ -1188,23 +1188,23 @@
         <v/>
       </c>
       <c r="Q13" s="12" t="n">
-        <v>4.76</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2033 EUR Corporate Bond UCITS ETF 1C</t>
+          <t>iShares iBonds Dec 2032 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LU2673523051</t>
+          <t>IE0000MR4GH9</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -1214,24 +1214,24 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F14" s="6" t="n">
-        <v>48852</v>
+        <v>48579</v>
       </c>
       <c r="G14" s="7">
         <f>IF(F14="","",MAX(0,YEARFRAC(TODAY(),F14)))</f>
         <v/>
       </c>
       <c r="H14" s="8" t="n">
-        <v>0.0338</v>
+        <v>0.0301</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>0.0435</v>
+        <v>0.0429</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>-0.0008</v>
+        <v>0.0002</v>
       </c>
       <c r="K14" s="9" t="n"/>
       <c r="L14" s="9" t="n"/>
@@ -1251,23 +1251,23 @@
         <v/>
       </c>
       <c r="Q14" s="12" t="n">
-        <v>9.31</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2033 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>iShares iBonds Dec 2031 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>LU2673523564</t>
+          <t>IE000I2WYEU9</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -1281,20 +1281,20 @@
         </is>
       </c>
       <c r="F15" s="6" t="n">
-        <v>48852</v>
+        <v>48213</v>
       </c>
       <c r="G15" s="7">
         <f>IF(F15="","",MAX(0,YEARFRAC(TODAY(),F15)))</f>
         <v/>
       </c>
       <c r="H15" s="8" t="n">
-        <v>0.0338</v>
+        <v>0.0285</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>0.0435</v>
+        <v>0.04219999999999999</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>-0.0008</v>
+        <v>0.0002</v>
       </c>
       <c r="K15" s="9" t="n"/>
       <c r="L15" s="9" t="n"/>
@@ -1314,55 +1314,55 @@
         <v/>
       </c>
       <c r="Q15" s="12" t="n">
-        <v>27.89</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2032 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>Amundi Fixed Maturity 2030 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LU2809864452</t>
+          <t>LU3120976132</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>48487</v>
+        <v>47848</v>
       </c>
       <c r="G16" s="7">
         <f>IF(F16="","",MAX(0,YEARFRAC(TODAY(),F16)))</f>
         <v/>
       </c>
       <c r="H16" s="8" t="n">
-        <v>0.0282</v>
+        <v>0.0169</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>0.0434</v>
+        <v>0.0355</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.0001</v>
+        <v>-0.0007</v>
       </c>
       <c r="K16" s="9" t="n"/>
       <c r="L16" s="9" t="n"/>
       <c r="M16" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N16" s="10">
         <f>IF(D16="Govt",$B$1,$B$2)</f>
@@ -1377,23 +1377,23 @@
         <v/>
       </c>
       <c r="Q16" s="12" t="n">
-        <v>34.29</v>
+        <v>9.830500000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>BNP Paribas</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2028 Term € Corp Crossover UCITS ETF</t>
+          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2032 UCITS ETF C</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>IE0003HV7CS6</t>
+          <t>LU2823895847</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -1407,25 +1407,25 @@
         </is>
       </c>
       <c r="F17" s="6" t="n">
-        <v>47118</v>
+        <v>48579</v>
       </c>
       <c r="G17" s="7">
         <f>IF(F17="","",MAX(0,YEARFRAC(TODAY(),F17)))</f>
         <v/>
       </c>
       <c r="H17" s="8" t="n">
-        <v>0.034</v>
+        <v>0.0269</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>0.04389999999999999</v>
+        <v>0.0421</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="K17" s="9" t="n"/>
       <c r="L17" s="9" t="n"/>
       <c r="M17" s="8" t="n">
-        <v>0.002</v>
+        <v>0.0012</v>
       </c>
       <c r="N17" s="10">
         <f>IF(D17="Govt",$B$1,$B$2)</f>
@@ -1440,55 +1440,55 @@
         <v/>
       </c>
       <c r="Q17" s="12" t="n">
-        <v>5.09</v>
+        <v>10.4237</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>BNP Paribas</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2030 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2032 UCITS ETF D</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LU3120976132</t>
+          <t>LU2823895763</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>47848</v>
+        <v>48579</v>
       </c>
       <c r="G18" s="7">
         <f>IF(F18="","",MAX(0,YEARFRAC(TODAY(),F18)))</f>
         <v/>
       </c>
       <c r="H18" s="8" t="n">
-        <v>0.0169</v>
+        <v>0.0269</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>0.0362</v>
+        <v>0.0421</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="K18" s="9" t="n"/>
       <c r="L18" s="9" t="n"/>
       <c r="M18" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N18" s="10">
         <f>IF(D18="Govt",$B$1,$B$2)</f>
@@ -1503,23 +1503,23 @@
         <v/>
       </c>
       <c r="Q18" s="12" t="n">
-        <v>9.8261</v>
+        <v>10.0381</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2032 Term € Corp UCITS ETF</t>
+          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>IE0000MR4GH9</t>
+          <t>LU2673523135</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -1529,24 +1529,24 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>48579</v>
+        <v>48121</v>
       </c>
       <c r="G19" s="7">
         <f>IF(F19="","",MAX(0,YEARFRAC(TODAY(),F19)))</f>
         <v/>
       </c>
       <c r="H19" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0287</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>0.04269999999999999</v>
+        <v>0.04190000000000001</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="K19" s="9" t="n"/>
       <c r="L19" s="9" t="n"/>
@@ -1566,23 +1566,23 @@
         <v/>
       </c>
       <c r="Q19" s="12" t="n">
-        <v>4.82</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2031 Term € Corp UCITS ETF</t>
+          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>IE000I2WYEU9</t>
+          <t>LU2673523481</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -1596,20 +1596,20 @@
         </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>48213</v>
+        <v>48121</v>
       </c>
       <c r="G20" s="7">
         <f>IF(F20="","",MAX(0,YEARFRAC(TODAY(),F20)))</f>
         <v/>
       </c>
       <c r="H20" s="8" t="n">
-        <v>0.0285</v>
+        <v>0.0287</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>0.042</v>
+        <v>0.04190000000000001</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="K20" s="9" t="n"/>
       <c r="L20" s="9" t="n"/>
@@ -1629,28 +1629,28 @@
         <v/>
       </c>
       <c r="Q20" s="12" t="n">
-        <v>4.87</v>
+        <v>29.28</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BNP Paribas</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2032 UCITS ETF C</t>
+          <t>Amundi Fixed Maturity 2029 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>LU2823895847</t>
+          <t>LU2872291781</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -1659,25 +1659,25 @@
         </is>
       </c>
       <c r="F21" s="6" t="n">
-        <v>48579</v>
+        <v>47483</v>
       </c>
       <c r="G21" s="7">
         <f>IF(F21="","",MAX(0,YEARFRAC(TODAY(),F21)))</f>
         <v/>
       </c>
       <c r="H21" s="8" t="n">
-        <v>0.0269</v>
+        <v>0.0208</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>0.04190000000000001</v>
+        <v>0.0346</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>-0.0008</v>
+        <v>-0.0007</v>
       </c>
       <c r="K21" s="9" t="n"/>
       <c r="L21" s="9" t="n"/>
       <c r="M21" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N21" s="10">
         <f>IF(D21="Govt",$B$1,$B$2)</f>
@@ -1692,23 +1692,23 @@
         <v/>
       </c>
       <c r="Q21" s="12" t="n">
-        <v>10.4295</v>
+        <v>9.985900000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BNP Paribas</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2032 UCITS ETF D</t>
+          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>LU2823895763</t>
+          <t>IE000I25S1V5</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1718,29 +1718,29 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>48579</v>
+        <v>47848</v>
       </c>
       <c r="G22" s="7">
         <f>IF(F22="","",MAX(0,YEARFRAC(TODAY(),F22)))</f>
         <v/>
       </c>
       <c r="H22" s="8" t="n">
-        <v>0.0269</v>
+        <v>0.0286</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>0.04190000000000001</v>
+        <v>0.0406</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>-0.0008</v>
+        <v>0</v>
       </c>
       <c r="K22" s="9" t="n"/>
       <c r="L22" s="9" t="n"/>
       <c r="M22" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="N22" s="10">
         <f>IF(D22="Govt",$B$1,$B$2)</f>
@@ -1755,55 +1755,55 @@
         <v/>
       </c>
       <c r="Q22" s="12" t="n">
-        <v>10.0436</v>
+        <v>5.3493</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2029 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>LU2872291781</t>
+          <t>IE000W6YTDH7</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>47483</v>
+        <v>47848</v>
       </c>
       <c r="G23" s="7">
         <f>IF(F23="","",MAX(0,YEARFRAC(TODAY(),F23)))</f>
         <v/>
       </c>
       <c r="H23" s="8" t="n">
-        <v>0.0208</v>
+        <v>0.0286</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>0.0353</v>
+        <v>0.0406</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0</v>
       </c>
       <c r="K23" s="9" t="n"/>
       <c r="L23" s="9" t="n"/>
       <c r="M23" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="N23" s="10">
         <f>IF(D23="Govt",$B$1,$B$2)</f>
@@ -1818,23 +1818,23 @@
         <v/>
       </c>
       <c r="Q23" s="12" t="n">
-        <v>9.982200000000001</v>
+        <v>4.9828</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1C</t>
+          <t>iShares iBonds Dec 2030 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>LU2673523135</t>
+          <t>IE000LX17BP9</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -1844,24 +1844,24 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>48121</v>
+        <v>47848</v>
       </c>
       <c r="G24" s="7">
         <f>IF(F24="","",MAX(0,YEARFRAC(TODAY(),F24)))</f>
         <v/>
       </c>
       <c r="H24" s="8" t="n">
-        <v>0.0287</v>
+        <v>0.028</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>0.0417</v>
+        <v>0.0406</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0.0003</v>
       </c>
       <c r="K24" s="9" t="n"/>
       <c r="L24" s="9" t="n"/>
@@ -1881,28 +1881,28 @@
         <v/>
       </c>
       <c r="Q24" s="12" t="n">
-        <v>9.789999999999999</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>iShares iBonds Dec 2028 Term € Italy Govt Bond UCITS ETF</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>LU2673523481</t>
+          <t>IE000Q2EQ5K8</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -1911,20 +1911,20 @@
         </is>
       </c>
       <c r="F25" s="6" t="n">
-        <v>48121</v>
+        <v>47118</v>
       </c>
       <c r="G25" s="7">
         <f>IF(F25="","",MAX(0,YEARFRAC(TODAY(),F25)))</f>
         <v/>
       </c>
       <c r="H25" s="8" t="n">
-        <v>0.0287</v>
+        <v>0.026</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>0.0417</v>
+        <v>0.034</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0.0003</v>
       </c>
       <c r="K25" s="9" t="n"/>
       <c r="L25" s="9" t="n"/>
@@ -1944,23 +1944,23 @@
         <v/>
       </c>
       <c r="Q25" s="12" t="n">
-        <v>29.3</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2029 Italy and Spain Government Bond UCITS ETF 1C</t>
+          <t>Amundi Fixed Maturity 2028 Euro Government Bond Yield + UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>LU0484969463</t>
+          <t>LU2780871666</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -1970,29 +1970,29 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>47391</v>
+        <v>47118</v>
       </c>
       <c r="G26" s="7">
         <f>IF(F26="","",MAX(0,YEARFRAC(TODAY(),F26)))</f>
         <v/>
       </c>
       <c r="H26" s="8" t="n">
-        <v>0.0297</v>
+        <v>0.023</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>0.0347</v>
+        <v>0.0328</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.0002</v>
+        <v>-0.0004</v>
       </c>
       <c r="K26" s="9" t="n"/>
       <c r="L26" s="9" t="n"/>
       <c r="M26" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N26" s="10">
         <f>IF(D26="Govt",$B$1,$B$2)</f>
@@ -2007,23 +2007,23 @@
         <v/>
       </c>
       <c r="Q26" s="12" t="n">
-        <v>204.58</v>
+        <v>10.285</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>iShares iBonds Dec 2029 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>IE000I25S1V5</t>
+          <t>IE000IHURBR0</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -2033,29 +2033,29 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F27" s="6" t="n">
-        <v>47848</v>
+        <v>47483</v>
       </c>
       <c r="G27" s="7">
         <f>IF(F27="","",MAX(0,YEARFRAC(TODAY(),F27)))</f>
         <v/>
       </c>
       <c r="H27" s="8" t="n">
-        <v>0.0287</v>
+        <v>0.0252</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>0.0406</v>
+        <v>0.0389</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>-0.0015</v>
+        <v>0.0004</v>
       </c>
       <c r="K27" s="9" t="n"/>
       <c r="L27" s="9" t="n"/>
       <c r="M27" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N27" s="10">
         <f>IF(D27="Govt",$B$1,$B$2)</f>
@@ -2070,7 +2070,7 @@
         <v/>
       </c>
       <c r="Q27" s="12" t="n">
-        <v>5.3469</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="28">
@@ -2081,12 +2081,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>IE000W6YTDH7</t>
+          <t>IE000P5IB8I8</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -2096,24 +2096,24 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F28" s="6" t="n">
-        <v>47848</v>
+        <v>47483</v>
       </c>
       <c r="G28" s="7">
         <f>IF(F28="","",MAX(0,YEARFRAC(TODAY(),F28)))</f>
         <v/>
       </c>
       <c r="H28" s="8" t="n">
-        <v>0.0286</v>
+        <v>0.0242</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>0.0406</v>
+        <v>0.0386</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>-0.0015</v>
+        <v>0</v>
       </c>
       <c r="K28" s="9" t="n"/>
       <c r="L28" s="9" t="n"/>
@@ -2133,23 +2133,23 @@
         <v/>
       </c>
       <c r="Q28" s="12" t="n">
-        <v>4.9806</v>
+        <v>5.4253</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2030 Term € Corp UCITS ETF</t>
+          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>IE000LX17BP9</t>
+          <t>IE000ZC4C5Q1</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -2163,25 +2163,25 @@
         </is>
       </c>
       <c r="F29" s="6" t="n">
-        <v>47848</v>
+        <v>47483</v>
       </c>
       <c r="G29" s="7">
         <f>IF(F29="","",MAX(0,YEARFRAC(TODAY(),F29)))</f>
         <v/>
       </c>
       <c r="H29" s="8" t="n">
-        <v>0.0279</v>
+        <v>0.0242</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>0.0403</v>
+        <v>0.0386</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0</v>
       </c>
       <c r="K29" s="9" t="n"/>
       <c r="L29" s="9" t="n"/>
       <c r="M29" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="N29" s="10">
         <f>IF(D29="Govt",$B$1,$B$2)</f>
@@ -2196,7 +2196,7 @@
         <v/>
       </c>
       <c r="Q29" s="12" t="n">
-        <v>4.99</v>
+        <v>5.0554</v>
       </c>
     </row>
     <row r="30">
@@ -2207,12 +2207,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2030 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>Xtrackers II Target Maturity Sept 2029 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>LU2809864296</t>
+          <t>LU2673523309</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -2226,20 +2226,20 @@
         </is>
       </c>
       <c r="F30" s="6" t="n">
-        <v>47756</v>
+        <v>47391</v>
       </c>
       <c r="G30" s="7">
         <f>IF(F30="","",MAX(0,YEARFRAC(TODAY(),F30)))</f>
         <v/>
       </c>
       <c r="H30" s="8" t="n">
-        <v>0.0271</v>
+        <v>0.0245</v>
       </c>
       <c r="I30" s="8" t="n">
-        <v>0.04019999999999999</v>
+        <v>0.0386</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0004</v>
       </c>
       <c r="K30" s="9" t="n"/>
       <c r="L30" s="9" t="n"/>
@@ -2259,50 +2259,50 @@
         <v/>
       </c>
       <c r="Q30" s="12" t="n">
-        <v>35.26</v>
+        <v>25.78</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2028 Term € Italy Govt Bond UCITS ETF</t>
+          <t>Xtrackers II Target Maturity Sept 2029 EUR Corporate Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>IE000Q2EQ5K8</t>
+          <t>LU2673522913</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F31" s="6" t="n">
-        <v>47118</v>
+        <v>47391</v>
       </c>
       <c r="G31" s="7">
         <f>IF(F31="","",MAX(0,YEARFRAC(TODAY(),F31)))</f>
         <v/>
       </c>
       <c r="H31" s="8" t="n">
-        <v>0.026</v>
+        <v>0.0245</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>0.0337</v>
+        <v>0.0386</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.0001</v>
+        <v>0.0004</v>
       </c>
       <c r="K31" s="9" t="n"/>
       <c r="L31" s="9" t="n"/>
@@ -2322,7 +2322,7 @@
         <v/>
       </c>
       <c r="Q31" s="12" t="n">
-        <v>5.06</v>
+        <v>9.17</v>
       </c>
     </row>
     <row r="32">
@@ -2333,12 +2333,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2028 Euro Government Bond Yield + UCITS ETF Dist</t>
+          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>LU2780871666</t>
+          <t>LU2780871401</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -2359,10 +2359,10 @@
         <v/>
       </c>
       <c r="H32" s="8" t="n">
-        <v>0.0229</v>
+        <v>0.0184</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>0.0332</v>
+        <v>0.0325</v>
       </c>
       <c r="J32" s="9" t="n">
         <v>-0.0003</v>
@@ -2385,7 +2385,7 @@
         <v/>
       </c>
       <c r="Q32" s="12" t="n">
-        <v>10.2843</v>
+        <v>10.2754</v>
       </c>
     </row>
     <row r="33">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Dist</t>
+          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>LU2780871401</t>
+          <t>LU2780871310</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F33" s="6" t="n">
@@ -2425,7 +2425,7 @@
         <v>0.0184</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>0.0328</v>
+        <v>0.0325</v>
       </c>
       <c r="J33" s="9" t="n">
         <v>-0.0003</v>
@@ -2448,28 +2448,28 @@
         <v/>
       </c>
       <c r="Q33" s="12" t="n">
-        <v>10.2744</v>
+        <v>10.0748</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>BNP Paribas</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2029 UCITS ETF C</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>LU2780871310</t>
+          <t>LU2823896811</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -2478,25 +2478,25 @@
         </is>
       </c>
       <c r="F34" s="6" t="n">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="G34" s="7">
         <f>IF(F34="","",MAX(0,YEARFRAC(TODAY(),F34)))</f>
         <v/>
       </c>
       <c r="H34" s="8" t="n">
-        <v>0.0184</v>
+        <v>0.0235</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>0.0328</v>
+        <v>0.0382</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0.0003</v>
       </c>
       <c r="K34" s="9" t="n"/>
       <c r="L34" s="9" t="n"/>
       <c r="M34" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N34" s="10">
         <f>IF(D34="Govt",$B$1,$B$2)</f>
@@ -2511,23 +2511,23 @@
         <v/>
       </c>
       <c r="Q34" s="12" t="n">
-        <v>10.0739</v>
+        <v>10.6604</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>BNP Paribas</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2029 UCITS ETF D</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>IE000P5IB8I8</t>
+          <t>LU2823896738</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F35" s="6" t="n">
@@ -2548,18 +2548,18 @@
         <v/>
       </c>
       <c r="H35" s="8" t="n">
-        <v>0.0242</v>
+        <v>0.0235</v>
       </c>
       <c r="I35" s="8" t="n">
-        <v>0.0386</v>
+        <v>0.0382</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>-0.0012</v>
+        <v>0.0003</v>
       </c>
       <c r="K35" s="9" t="n"/>
       <c r="L35" s="9" t="n"/>
       <c r="M35" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N35" s="10">
         <f>IF(D35="Govt",$B$1,$B$2)</f>
@@ -2574,7 +2574,7 @@
         <v/>
       </c>
       <c r="Q35" s="12" t="n">
-        <v>5.4242</v>
+        <v>10.2991</v>
       </c>
     </row>
     <row r="36">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>Invesco BulletShares 2028 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>IE000ZC4C5Q1</t>
+          <t>IE00079EUF59</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -2600,11 +2600,11 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F36" s="6" t="n">
-        <v>47483</v>
+        <v>47118</v>
       </c>
       <c r="G36" s="7">
         <f>IF(F36="","",MAX(0,YEARFRAC(TODAY(),F36)))</f>
@@ -2614,10 +2614,10 @@
         <v>0.0242</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>0.0386</v>
+        <v>0.0375</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>-0.0012</v>
+        <v>0</v>
       </c>
       <c r="K36" s="9" t="n"/>
       <c r="L36" s="9" t="n"/>
@@ -2637,23 +2637,23 @@
         <v/>
       </c>
       <c r="Q36" s="12" t="n">
-        <v>5.0543</v>
+        <v>5.5695</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2029 Term € Corp UCITS ETF</t>
+          <t>Invesco BulletShares 2028 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>IE000IHURBR0</t>
+          <t>IE000LKGEZQ6</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -2667,25 +2667,25 @@
         </is>
       </c>
       <c r="F37" s="6" t="n">
-        <v>47483</v>
+        <v>47118</v>
       </c>
       <c r="G37" s="7">
         <f>IF(F37="","",MAX(0,YEARFRAC(TODAY(),F37)))</f>
         <v/>
       </c>
       <c r="H37" s="8" t="n">
-        <v>0.0252</v>
+        <v>0.0242</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>0.0385</v>
+        <v>0.0375</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0</v>
       </c>
       <c r="K37" s="9" t="n"/>
       <c r="L37" s="9" t="n"/>
       <c r="M37" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="N37" s="10">
         <f>IF(D37="Govt",$B$1,$B$2)</f>
@@ -2700,23 +2700,23 @@
         <v/>
       </c>
       <c r="Q37" s="12" t="n">
-        <v>5.03</v>
+        <v>5.2089</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2029 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>iShares iBonds Dec 2028 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LU2673523309</t>
+          <t>IE000264WWY0</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -2730,20 +2730,20 @@
         </is>
       </c>
       <c r="F38" s="6" t="n">
-        <v>47391</v>
+        <v>47118</v>
       </c>
       <c r="G38" s="7">
         <f>IF(F38="","",MAX(0,YEARFRAC(TODAY(),F38)))</f>
         <v/>
       </c>
       <c r="H38" s="8" t="n">
-        <v>0.0245</v>
+        <v>0.0213</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>0.0382</v>
+        <v>0.0373</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0003</v>
       </c>
       <c r="K38" s="9" t="n"/>
       <c r="L38" s="9" t="n"/>
@@ -2763,7 +2763,7 @@
         <v/>
       </c>
       <c r="Q38" s="12" t="n">
-        <v>25.8</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="39">
@@ -2774,12 +2774,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2029 EUR Corporate Bond UCITS ETF 1C</t>
+          <t>Xtrackers II Target Maturity Sept 2028 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>LU2673522913</t>
+          <t>LU2810185665</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -2789,24 +2789,24 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F39" s="6" t="n">
-        <v>47391</v>
+        <v>47026</v>
       </c>
       <c r="G39" s="7">
         <f>IF(F39="","",MAX(0,YEARFRAC(TODAY(),F39)))</f>
         <v/>
       </c>
       <c r="H39" s="8" t="n">
-        <v>0.0245</v>
+        <v>0.0207</v>
       </c>
       <c r="I39" s="8" t="n">
-        <v>0.0382</v>
+        <v>0.0369</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0002</v>
       </c>
       <c r="K39" s="9" t="n"/>
       <c r="L39" s="9" t="n"/>
@@ -2826,55 +2826,55 @@
         <v/>
       </c>
       <c r="Q39" s="12" t="n">
-        <v>9.17</v>
+        <v>35.76</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BNP Paribas</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2029 UCITS ETF C</t>
+          <t>Amundi Fixed Maturity 2027 Italy BTP Government Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>LU2823896811</t>
+          <t>LU2780872128</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F40" s="6" t="n">
-        <v>47483</v>
+        <v>46752</v>
       </c>
       <c r="G40" s="7">
         <f>IF(F40="","",MAX(0,YEARFRAC(TODAY(),F40)))</f>
         <v/>
       </c>
       <c r="H40" s="8" t="n">
-        <v>0.0235</v>
+        <v>0.0265</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>0.0379</v>
+        <v>0.0305</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0002</v>
       </c>
       <c r="K40" s="9" t="n"/>
       <c r="L40" s="9" t="n"/>
       <c r="M40" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N40" s="10">
         <f>IF(D40="Govt",$B$1,$B$2)</f>
@@ -2889,55 +2889,55 @@
         <v/>
       </c>
       <c r="Q40" s="12" t="n">
-        <v>10.6685</v>
+        <v>10.3332</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BNP Paribas</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2029 UCITS ETF D</t>
+          <t>Amundi Fixed Maturity 2027 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>LU2823896738</t>
+          <t>LU2872291435</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F41" s="6" t="n">
-        <v>47483</v>
+        <v>46752</v>
       </c>
       <c r="G41" s="7">
         <f>IF(F41="","",MAX(0,YEARFRAC(TODAY(),F41)))</f>
         <v/>
       </c>
       <c r="H41" s="8" t="n">
-        <v>0.0235</v>
+        <v>0.015</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>0.0379</v>
+        <v>0.0294</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0001</v>
       </c>
       <c r="K41" s="9" t="n"/>
       <c r="L41" s="9" t="n"/>
       <c r="M41" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N41" s="10">
         <f>IF(D41="Govt",$B$1,$B$2)</f>
@@ -2952,55 +2952,55 @@
         <v/>
       </c>
       <c r="Q41" s="12" t="n">
-        <v>10.3069</v>
+        <v>10.1744</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2028 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>Amundi Fixed Maturity 2027 German Bund Government Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>IE00079EUF59</t>
+          <t>LU2780871823</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
-        <v>47118</v>
+        <v>46752</v>
       </c>
       <c r="G42" s="7">
         <f>IF(F42="","",MAX(0,YEARFRAC(TODAY(),F42)))</f>
         <v/>
       </c>
       <c r="H42" s="8" t="n">
-        <v>0.0242</v>
+        <v>0.0105</v>
       </c>
       <c r="I42" s="8" t="n">
-        <v>0.0375</v>
+        <v>0.0284</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>-0.0008</v>
+        <v>0.0001</v>
       </c>
       <c r="K42" s="9" t="n"/>
       <c r="L42" s="9" t="n"/>
       <c r="M42" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0009</v>
       </c>
       <c r="N42" s="10">
         <f>IF(D42="Govt",$B$1,$B$2)</f>
@@ -3015,7 +3015,7 @@
         <v/>
       </c>
       <c r="Q42" s="12" t="n">
-        <v>5.5687</v>
+        <v>10.3477</v>
       </c>
     </row>
     <row r="43">
@@ -3026,12 +3026,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2028 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>Invesco BulletShares 2027 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>IE000LKGEZQ6</t>
+          <t>IE000LGHLQ71</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -3041,24 +3041,24 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
-        <v>47118</v>
+        <v>46752</v>
       </c>
       <c r="G43" s="7">
         <f>IF(F43="","",MAX(0,YEARFRAC(TODAY(),F43)))</f>
         <v/>
       </c>
       <c r="H43" s="8" t="n">
-        <v>0.0242</v>
+        <v>0.0197</v>
       </c>
       <c r="I43" s="8" t="n">
-        <v>0.0375</v>
+        <v>0.0335</v>
       </c>
       <c r="J43" s="9" t="n">
-        <v>-0.0008</v>
+        <v>0</v>
       </c>
       <c r="K43" s="9" t="n"/>
       <c r="L43" s="9" t="n"/>
@@ -3078,23 +3078,23 @@
         <v/>
       </c>
       <c r="Q43" s="12" t="n">
-        <v>5.2081</v>
+        <v>5.7061</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2028 Term € Corp UCITS ETF</t>
+          <t>Invesco BulletShares 2027 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>IE000264WWY0</t>
+          <t>IE000XOS4OJ6</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -3108,25 +3108,25 @@
         </is>
       </c>
       <c r="F44" s="6" t="n">
-        <v>47118</v>
+        <v>46752</v>
       </c>
       <c r="G44" s="7">
         <f>IF(F44="","",MAX(0,YEARFRAC(TODAY(),F44)))</f>
         <v/>
       </c>
       <c r="H44" s="8" t="n">
-        <v>0.0214</v>
+        <v>0.0197</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.0335</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0</v>
       </c>
       <c r="K44" s="9" t="n"/>
       <c r="L44" s="9" t="n"/>
       <c r="M44" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="N44" s="10">
         <f>IF(D44="Govt",$B$1,$B$2)</f>
@@ -3141,23 +3141,23 @@
         <v/>
       </c>
       <c r="Q44" s="12" t="n">
-        <v>5.1</v>
+        <v>5.3339</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2028 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>iShares iBonds Dec 2027 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>LU2810185665</t>
+          <t>IE000ZOI8OK5</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -3167,24 +3167,24 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F45" s="6" t="n">
-        <v>47026</v>
+        <v>46752</v>
       </c>
       <c r="G45" s="7">
         <f>IF(F45="","",MAX(0,YEARFRAC(TODAY(),F45)))</f>
         <v/>
       </c>
       <c r="H45" s="8" t="n">
-        <v>0.0207</v>
+        <v>0.0195</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>0.0367</v>
+        <v>0.0333</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0</v>
       </c>
       <c r="K45" s="9" t="n"/>
       <c r="L45" s="9" t="n"/>
@@ -3204,28 +3204,28 @@
         <v/>
       </c>
       <c r="Q45" s="12" t="n">
-        <v>35.76</v>
+        <v>5.65</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2027 Italy BTP Government Bond UCITS ETF Dist</t>
+          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>LU2780872128</t>
+          <t>LU2673523218</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -3234,25 +3234,25 @@
         </is>
       </c>
       <c r="F46" s="6" t="n">
-        <v>46752</v>
+        <v>46660</v>
       </c>
       <c r="G46" s="7">
         <f>IF(F46="","",MAX(0,YEARFRAC(TODAY(),F46)))</f>
         <v/>
       </c>
       <c r="H46" s="8" t="n">
-        <v>0.0265</v>
+        <v>0.0186</v>
       </c>
       <c r="I46" s="8" t="n">
-        <v>0.0307</v>
+        <v>0.032</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>-0.0004</v>
+        <v>-0.0005</v>
       </c>
       <c r="K46" s="9" t="n"/>
       <c r="L46" s="9" t="n"/>
       <c r="M46" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N46" s="10">
         <f>IF(D46="Govt",$B$1,$B$2)</f>
@@ -3267,28 +3267,28 @@
         <v/>
       </c>
       <c r="Q46" s="12" t="n">
-        <v>10.3334</v>
+        <v>25.96</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2027 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>LU2872291435</t>
+          <t>LU2673522830</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -3297,25 +3297,25 @@
         </is>
       </c>
       <c r="F47" s="6" t="n">
-        <v>46752</v>
+        <v>46660</v>
       </c>
       <c r="G47" s="7">
         <f>IF(F47="","",MAX(0,YEARFRAC(TODAY(),F47)))</f>
         <v/>
       </c>
       <c r="H47" s="8" t="n">
-        <v>0.015</v>
+        <v>0.0186</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>0.0295</v>
+        <v>0.032</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>-0.0002</v>
+        <v>-0.0005</v>
       </c>
       <c r="K47" s="9" t="n"/>
       <c r="L47" s="9" t="n"/>
       <c r="M47" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N47" s="10">
         <f>IF(D47="Govt",$B$1,$B$2)</f>
@@ -3330,55 +3330,55 @@
         <v/>
       </c>
       <c r="Q47" s="12" t="n">
-        <v>10.1734</v>
+        <v>9.31</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2027 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>iShares iBonds Dec 2026 Term € Italy Govt Bond UCITS ETF</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>IE000LGHLQ71</t>
+          <t>IE000LZ7BZW8</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
-        <v>46752</v>
+        <v>46387</v>
       </c>
       <c r="G48" s="7">
         <f>IF(F48="","",MAX(0,YEARFRAC(TODAY(),F48)))</f>
         <v/>
       </c>
       <c r="H48" s="8" t="n">
-        <v>0.0197</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>0.0335</v>
+        <v>0.0269</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.0004</v>
+        <v>-0.0001</v>
       </c>
       <c r="K48" s="9" t="n"/>
       <c r="L48" s="9" t="n"/>
       <c r="M48" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N48" s="10">
         <f>IF(D48="Govt",$B$1,$B$2)</f>
@@ -3393,55 +3393,55 @@
         <v/>
       </c>
       <c r="Q48" s="12" t="n">
-        <v>5.7054</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2027 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>Amundi Fixed Maturity 2026 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>IE000XOS4OJ6</t>
+          <t>LU2872291278</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F49" s="6" t="n">
-        <v>46752</v>
+        <v>46387</v>
       </c>
       <c r="G49" s="7">
         <f>IF(F49="","",MAX(0,YEARFRAC(TODAY(),F49)))</f>
         <v/>
       </c>
       <c r="H49" s="8" t="n">
-        <v>0.0197</v>
+        <v>0.0023</v>
       </c>
       <c r="I49" s="8" t="n">
-        <v>0.0335</v>
+        <v>0.0264</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.0004</v>
+        <v>-0.0005</v>
       </c>
       <c r="K49" s="9" t="n"/>
       <c r="L49" s="9" t="n"/>
       <c r="M49" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0009</v>
       </c>
       <c r="N49" s="10">
         <f>IF(D49="Govt",$B$1,$B$2)</f>
@@ -3456,47 +3456,47 @@
         <v/>
       </c>
       <c r="Q49" s="12" t="n">
-        <v>5.3332</v>
+        <v>10.258</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2027 German Bund Government Bond UCITS ETF Dist</t>
+          <t>Invesco BulletShares 2026 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>LU2780871823</t>
+          <t>IE0004QWOTD5</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
-        <v>46752</v>
+        <v>46387</v>
       </c>
       <c r="G50" s="7">
         <f>IF(F50="","",MAX(0,YEARFRAC(TODAY(),F50)))</f>
         <v/>
       </c>
       <c r="H50" s="8" t="n">
-        <v>0.0105</v>
+        <v>0.0119</v>
       </c>
       <c r="I50" s="8" t="n">
-        <v>0.0283</v>
+        <v>0.0298</v>
       </c>
       <c r="J50" s="9" t="n">
         <v>0</v>
@@ -3504,7 +3504,7 @@
       <c r="K50" s="9" t="n"/>
       <c r="L50" s="9" t="n"/>
       <c r="M50" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="N50" s="10">
         <f>IF(D50="Govt",$B$1,$B$2)</f>
@@ -3519,23 +3519,23 @@
         <v/>
       </c>
       <c r="Q50" s="12" t="n">
-        <v>10.3457</v>
+        <v>5.7916</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2027 Term € Corp UCITS ETF</t>
+          <t>Invesco BulletShares 2026 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>IE000ZOI8OK5</t>
+          <t>IE000AYJ75E5</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
@@ -3545,21 +3545,21 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F51" s="6" t="n">
-        <v>46752</v>
+        <v>46387</v>
       </c>
       <c r="G51" s="7">
         <f>IF(F51="","",MAX(0,YEARFRAC(TODAY(),F51)))</f>
         <v/>
       </c>
       <c r="H51" s="8" t="n">
-        <v>0.0195</v>
+        <v>0.0119</v>
       </c>
       <c r="I51" s="8" t="n">
-        <v>0.0333</v>
+        <v>0.0298</v>
       </c>
       <c r="J51" s="9" t="n">
         <v>0</v>
@@ -3567,7 +3567,7 @@
       <c r="K51" s="9" t="n"/>
       <c r="L51" s="9" t="n"/>
       <c r="M51" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="N51" s="10">
         <f>IF(D51="Govt",$B$1,$B$2)</f>
@@ -3582,23 +3582,23 @@
         <v/>
       </c>
       <c r="Q51" s="12" t="n">
-        <v>5.65</v>
+        <v>5.4154</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>iShares iBonds Dec 2026 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>LU2673523218</t>
+          <t>IE000SIZJ2B2</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -3612,20 +3612,20 @@
         </is>
       </c>
       <c r="F52" s="6" t="n">
-        <v>46660</v>
+        <v>46387</v>
       </c>
       <c r="G52" s="7">
         <f>IF(F52="","",MAX(0,YEARFRAC(TODAY(),F52)))</f>
         <v/>
       </c>
       <c r="H52" s="8" t="n">
-        <v>0.0186</v>
+        <v>0.0059</v>
       </c>
       <c r="I52" s="8" t="n">
-        <v>0.0325</v>
+        <v>0.0273</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.0001</v>
+        <v>-0.0008</v>
       </c>
       <c r="K52" s="9" t="n"/>
       <c r="L52" s="9" t="n"/>
@@ -3645,7 +3645,7 @@
         <v/>
       </c>
       <c r="Q52" s="12" t="n">
-        <v>25.95</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="53">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1C</t>
+          <t>Xtrackers II Target Maturity Sept 2030 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LU2673522830</t>
+          <t>LU2809864296</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -3671,25 +3671,19 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F53" s="6" t="n">
-        <v>46660</v>
+        <v>47756</v>
       </c>
       <c r="G53" s="7">
         <f>IF(F53="","",MAX(0,YEARFRAC(TODAY(),F53)))</f>
         <v/>
       </c>
-      <c r="H53" s="8" t="n">
-        <v>0.0186</v>
-      </c>
-      <c r="I53" s="8" t="n">
-        <v>0.0325</v>
-      </c>
-      <c r="J53" s="9" t="n">
-        <v>0.0001</v>
-      </c>
+      <c r="H53" s="8" t="n"/>
+      <c r="I53" s="8" t="n"/>
+      <c r="J53" s="9" t="n"/>
       <c r="K53" s="9" t="n"/>
       <c r="L53" s="9" t="n"/>
       <c r="M53" s="8" t="n">
@@ -3707,56 +3701,48 @@
         <f>IF(I53="","",(I53-M53)*(1-N53))</f>
         <v/>
       </c>
-      <c r="Q53" s="12" t="n">
-        <v>9.300000000000001</v>
-      </c>
+      <c r="Q53" s="12" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2026 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>Xtrackers II Target Maturity Sept 2032 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>LU2872291278</t>
+          <t>LU2809864452</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F54" s="6" t="n">
-        <v>46387</v>
+        <v>48487</v>
       </c>
       <c r="G54" s="7">
         <f>IF(F54="","",MAX(0,YEARFRAC(TODAY(),F54)))</f>
         <v/>
       </c>
-      <c r="H54" s="8" t="n">
-        <v>0.0023</v>
-      </c>
-      <c r="I54" s="8" t="n">
-        <v>0.0269</v>
-      </c>
-      <c r="J54" s="9" t="n">
-        <v>0.0004</v>
-      </c>
+      <c r="H54" s="8" t="n"/>
+      <c r="I54" s="8" t="n"/>
+      <c r="J54" s="9" t="n"/>
       <c r="K54" s="9" t="n"/>
       <c r="L54" s="9" t="n"/>
       <c r="M54" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N54" s="10">
         <f>IF(D54="Govt",$B$1,$B$2)</f>
@@ -3770,29 +3756,27 @@
         <f>IF(I54="","",(I54-M54)*(1-N54))</f>
         <v/>
       </c>
-      <c r="Q54" s="12" t="n">
-        <v>10.2574</v>
-      </c>
+      <c r="Q54" s="12" t="n"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2026 Term € Italy Govt Bond UCITS ETF</t>
+          <t>Xtrackers II Target Maturity Sept 2035 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>IE000LZ7BZW8</t>
+          <t>LU3152892546</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -3801,21 +3785,15 @@
         </is>
       </c>
       <c r="F55" s="6" t="n">
-        <v>46387</v>
+        <v>49582</v>
       </c>
       <c r="G55" s="7">
         <f>IF(F55="","",MAX(0,YEARFRAC(TODAY(),F55)))</f>
         <v/>
       </c>
-      <c r="H55" s="8" t="n">
-        <v>0.008800000000000001</v>
-      </c>
-      <c r="I55" s="8" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="J55" s="9" t="n">
-        <v>-0.0001</v>
-      </c>
+      <c r="H55" s="8" t="n"/>
+      <c r="I55" s="8" t="n"/>
+      <c r="J55" s="9" t="n"/>
       <c r="K55" s="9" t="n"/>
       <c r="L55" s="9" t="n"/>
       <c r="M55" s="8" t="n">
@@ -3833,24 +3811,22 @@
         <f>IF(I55="","",(I55-M55)*(1-N55))</f>
         <v/>
       </c>
-      <c r="Q55" s="12" t="n">
-        <v>5.06</v>
-      </c>
+      <c r="Q55" s="12" t="n"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2026 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>Xtrackers II Target Maturity Sept 2034 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>IE0004QWOTD5</t>
+          <t>LU2809864619</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -3860,29 +3836,23 @@
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F56" s="6" t="n">
-        <v>46387</v>
+        <v>49217</v>
       </c>
       <c r="G56" s="7">
         <f>IF(F56="","",MAX(0,YEARFRAC(TODAY(),F56)))</f>
         <v/>
       </c>
-      <c r="H56" s="8" t="n">
-        <v>0.0119</v>
-      </c>
-      <c r="I56" s="8" t="n">
-        <v>0.0298</v>
-      </c>
-      <c r="J56" s="9" t="n">
-        <v>0.0004</v>
-      </c>
+      <c r="H56" s="8" t="n"/>
+      <c r="I56" s="8" t="n"/>
+      <c r="J56" s="9" t="n"/>
       <c r="K56" s="9" t="n"/>
       <c r="L56" s="9" t="n"/>
       <c r="M56" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N56" s="10">
         <f>IF(D56="Govt",$B$1,$B$2)</f>
@@ -3896,24 +3866,22 @@
         <f>IF(I56="","",(I56-M56)*(1-N56))</f>
         <v/>
       </c>
-      <c r="Q56" s="12" t="n">
-        <v>5.7911</v>
-      </c>
+      <c r="Q56" s="12" t="n"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2026 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>Xtrackers II Target Maturity Sept 2036 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>IE000AYJ75E5</t>
+          <t>LU3152892629</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
@@ -3927,25 +3895,19 @@
         </is>
       </c>
       <c r="F57" s="6" t="n">
-        <v>46387</v>
+        <v>49948</v>
       </c>
       <c r="G57" s="7">
         <f>IF(F57="","",MAX(0,YEARFRAC(TODAY(),F57)))</f>
         <v/>
       </c>
-      <c r="H57" s="8" t="n">
-        <v>0.0119</v>
-      </c>
-      <c r="I57" s="8" t="n">
-        <v>0.0298</v>
-      </c>
-      <c r="J57" s="9" t="n">
-        <v>0.0004</v>
-      </c>
+      <c r="H57" s="8" t="n"/>
+      <c r="I57" s="8" t="n"/>
+      <c r="J57" s="9" t="n"/>
       <c r="K57" s="9" t="n"/>
       <c r="L57" s="9" t="n"/>
       <c r="M57" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N57" s="10">
         <f>IF(D57="Govt",$B$1,$B$2)</f>
@@ -3959,52 +3921,44 @@
         <f>IF(I57="","",(I57-M57)*(1-N57))</f>
         <v/>
       </c>
-      <c r="Q57" s="12" t="n">
-        <v>5.4149</v>
-      </c>
+      <c r="Q57" s="12" t="n"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2026 Term € Corp UCITS ETF</t>
+          <t>Xtrackers II Target Maturity Sept 2029 Italy and Spain Government Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>IE000SIZJ2B2</t>
+          <t>LU0484969463</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F58" s="6" t="n">
-        <v>46387</v>
+        <v>47391</v>
       </c>
       <c r="G58" s="7">
         <f>IF(F58="","",MAX(0,YEARFRAC(TODAY(),F58)))</f>
         <v/>
       </c>
-      <c r="H58" s="8" t="n">
-        <v>0.0059</v>
-      </c>
-      <c r="I58" s="8" t="n">
-        <v>0.0281</v>
-      </c>
-      <c r="J58" s="9" t="n">
-        <v>-0.0001</v>
-      </c>
+      <c r="H58" s="8" t="n"/>
+      <c r="I58" s="8" t="n"/>
+      <c r="J58" s="9" t="n"/>
       <c r="K58" s="9" t="n"/>
       <c r="L58" s="9" t="n"/>
       <c r="M58" s="8" t="n">
@@ -4022,9 +3976,7 @@
         <f>IF(I58="","",(I58-M58)*(1-N58))</f>
         <v/>
       </c>
-      <c r="Q58" s="12" t="n">
-        <v>5.06</v>
-      </c>
+      <c r="Q58" s="12" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="J5:J58">

--- a/data/rendimenti_etf.xlsx
+++ b/data/rendimenti_etf.xlsx
@@ -533,7 +533,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Aggiornato il 12/10/2026 14:41 da yield_etf.csv</t>
+          <t>Aggiornato il 12/10/2026 14:48 da yield_etf.csv</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2036 Term € Corp UCITS ETF</t>
+          <t>Xtrackers II Target Maturity Sept 2036 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>IE000RQJBQI6</t>
+          <t>LU3152892629</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -714,17 +714,17 @@
         </is>
       </c>
       <c r="F6" s="6" t="n">
-        <v>50040</v>
+        <v>49948</v>
       </c>
       <c r="G6" s="7">
         <f>IF(F6="","",MAX(0,YEARFRAC(TODAY(),F6)))</f>
         <v/>
       </c>
       <c r="H6" s="8" t="n">
-        <v>0.0355</v>
+        <v>0.03759999999999999</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0.0459</v>
+        <v>0.0462</v>
       </c>
       <c r="J6" s="9" t="n">
         <v>-0.0001</v>
@@ -747,7 +747,7 @@
         <v/>
       </c>
       <c r="Q6" s="12" t="n">
-        <v>4.81</v>
+        <v>28.31</v>
       </c>
     </row>
     <row r="7">
@@ -758,12 +758,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2037 Term € Corp UCITS ETF</t>
+          <t>iShares iBonds Dec 2036 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>IE000PWSK6H1</t>
+          <t>IE000RQJBQI6</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -777,17 +777,17 @@
         </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>50405</v>
+        <v>50040</v>
       </c>
       <c r="G7" s="7">
         <f>IF(F7="","",MAX(0,YEARFRAC(TODAY(),F7)))</f>
         <v/>
       </c>
       <c r="H7" s="8" t="n">
-        <v>0.0349</v>
+        <v>0.0355</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0.0457</v>
+        <v>0.0459</v>
       </c>
       <c r="J7" s="9" t="n">
         <v>-0.0001</v>
@@ -810,23 +810,23 @@
         <v/>
       </c>
       <c r="Q7" s="12" t="n">
-        <v>4.8</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2035 Term € Corp UCITS ETF</t>
+          <t>Xtrackers II Target Maturity Sept 2035 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>IE000WLR06P0</t>
+          <t>LU3152892546</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -840,17 +840,17 @@
         </is>
       </c>
       <c r="F8" s="6" t="n">
-        <v>49674</v>
+        <v>49582</v>
       </c>
       <c r="G8" s="7">
         <f>IF(F8="","",MAX(0,YEARFRAC(TODAY(),F8)))</f>
         <v/>
       </c>
       <c r="H8" s="8" t="n">
-        <v>0.0367</v>
+        <v>0.0365</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>0.0455</v>
+        <v>0.0458</v>
       </c>
       <c r="J8" s="9" t="n">
         <v>-0.0001</v>
@@ -873,7 +873,7 @@
         <v/>
       </c>
       <c r="Q8" s="12" t="n">
-        <v>4.72</v>
+        <v>29.13</v>
       </c>
     </row>
     <row r="9">
@@ -884,12 +884,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2034 Term € Corp UCITS ETF</t>
+          <t>iShares iBonds Dec 2037 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>IE000SBJO6L2</t>
+          <t>IE000PWSK6H1</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -903,20 +903,20 @@
         </is>
       </c>
       <c r="F9" s="6" t="n">
-        <v>49309</v>
+        <v>50405</v>
       </c>
       <c r="G9" s="7">
         <f>IF(F9="","",MAX(0,YEARFRAC(TODAY(),F9)))</f>
         <v/>
       </c>
       <c r="H9" s="8" t="n">
-        <v>0.0346</v>
+        <v>0.0349</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>0.0447</v>
+        <v>0.0457</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0</v>
+        <v>-0.0001</v>
       </c>
       <c r="K9" s="9" t="n"/>
       <c r="L9" s="9" t="n"/>
@@ -936,7 +936,7 @@
         <v/>
       </c>
       <c r="Q9" s="12" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="10">
@@ -947,12 +947,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2033 Term € Corp UCITS ETF</t>
+          <t>iShares iBonds Dec 2035 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IE000E0NL9T3</t>
+          <t>IE000WLR06P0</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -966,20 +966,20 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>48944</v>
+        <v>49674</v>
       </c>
       <c r="G10" s="7">
         <f>IF(F10="","",MAX(0,YEARFRAC(TODAY(),F10)))</f>
         <v/>
       </c>
       <c r="H10" s="8" t="n">
-        <v>0.0331</v>
+        <v>0.0367</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>0.044</v>
+        <v>0.0455</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0</v>
+        <v>-0.0001</v>
       </c>
       <c r="K10" s="9" t="n"/>
       <c r="L10" s="9" t="n"/>
@@ -999,7 +999,7 @@
         <v/>
       </c>
       <c r="Q10" s="12" t="n">
-        <v>4.77</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="11">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2033 EUR Corporate Bond UCITS ETF 1C</t>
+          <t>Xtrackers II Target Maturity Sept 2034 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LU2673523051</t>
+          <t>LU2809864619</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -1025,24 +1025,24 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F11" s="6" t="n">
-        <v>48852</v>
+        <v>49217</v>
       </c>
       <c r="G11" s="7">
         <f>IF(F11="","",MAX(0,YEARFRAC(TODAY(),F11)))</f>
         <v/>
       </c>
       <c r="H11" s="8" t="n">
-        <v>0.0338</v>
+        <v>0.0347</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>0.044</v>
+        <v>0.0452</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.0005</v>
+        <v>0</v>
       </c>
       <c r="K11" s="9" t="n"/>
       <c r="L11" s="9" t="n"/>
@@ -1062,23 +1062,23 @@
         <v/>
       </c>
       <c r="Q11" s="12" t="n">
-        <v>9.31</v>
+        <v>33.51</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2033 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>iShares iBonds Dec 2034 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LU2673523564</t>
+          <t>IE000SBJO6L2</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -1092,20 +1092,20 @@
         </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>48852</v>
+        <v>49309</v>
       </c>
       <c r="G12" s="7">
         <f>IF(F12="","",MAX(0,YEARFRAC(TODAY(),F12)))</f>
         <v/>
       </c>
       <c r="H12" s="8" t="n">
-        <v>0.0338</v>
+        <v>0.0346</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>0.044</v>
+        <v>0.0447</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.0005</v>
+        <v>0</v>
       </c>
       <c r="K12" s="9" t="n"/>
       <c r="L12" s="9" t="n"/>
@@ -1125,7 +1125,7 @@
         <v/>
       </c>
       <c r="Q12" s="12" t="n">
-        <v>27.88</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="13">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2028 Term € Corp Crossover UCITS ETF</t>
+          <t>iShares iBonds Dec 2033 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>IE0003HV7CS6</t>
+          <t>IE000E0NL9T3</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -1151,29 +1151,29 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>47118</v>
+        <v>48944</v>
       </c>
       <c r="G13" s="7">
         <f>IF(F13="","",MAX(0,YEARFRAC(TODAY(),F13)))</f>
         <v/>
       </c>
       <c r="H13" s="8" t="n">
-        <v>0.0334</v>
+        <v>0.0331</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0.0444</v>
+        <v>0.044</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.0005</v>
+        <v>0</v>
       </c>
       <c r="K13" s="9" t="n"/>
       <c r="L13" s="9" t="n"/>
       <c r="M13" s="8" t="n">
-        <v>0.002</v>
+        <v>0.0012</v>
       </c>
       <c r="N13" s="10">
         <f>IF(D13="Govt",$B$1,$B$2)</f>
@@ -1188,23 +1188,23 @@
         <v/>
       </c>
       <c r="Q13" s="12" t="n">
-        <v>5.1</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2032 Term € Corp UCITS ETF</t>
+          <t>Xtrackers II Target Maturity Sept 2033 EUR Corporate Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>IE0000MR4GH9</t>
+          <t>LU2673523051</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -1214,24 +1214,24 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F14" s="6" t="n">
-        <v>48579</v>
+        <v>48852</v>
       </c>
       <c r="G14" s="7">
         <f>IF(F14="","",MAX(0,YEARFRAC(TODAY(),F14)))</f>
         <v/>
       </c>
       <c r="H14" s="8" t="n">
-        <v>0.0301</v>
+        <v>0.0338</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>0.0429</v>
+        <v>0.044</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.0002</v>
+        <v>0.0005</v>
       </c>
       <c r="K14" s="9" t="n"/>
       <c r="L14" s="9" t="n"/>
@@ -1251,23 +1251,23 @@
         <v/>
       </c>
       <c r="Q14" s="12" t="n">
-        <v>4.82</v>
+        <v>9.31</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2031 Term € Corp UCITS ETF</t>
+          <t>Xtrackers II Target Maturity Sept 2033 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>IE000I2WYEU9</t>
+          <t>LU2673523564</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -1281,20 +1281,20 @@
         </is>
       </c>
       <c r="F15" s="6" t="n">
-        <v>48213</v>
+        <v>48852</v>
       </c>
       <c r="G15" s="7">
         <f>IF(F15="","",MAX(0,YEARFRAC(TODAY(),F15)))</f>
         <v/>
       </c>
       <c r="H15" s="8" t="n">
-        <v>0.0285</v>
+        <v>0.0338</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>0.04219999999999999</v>
+        <v>0.044</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.0002</v>
+        <v>0.0005</v>
       </c>
       <c r="K15" s="9" t="n"/>
       <c r="L15" s="9" t="n"/>
@@ -1314,28 +1314,28 @@
         <v/>
       </c>
       <c r="Q15" s="12" t="n">
-        <v>4.87</v>
+        <v>27.88</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2030 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>iShares iBonds Dec 2028 Term € Corp Crossover UCITS ETF</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LU3120976132</t>
+          <t>IE0003HV7CS6</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -1344,25 +1344,25 @@
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>47848</v>
+        <v>47118</v>
       </c>
       <c r="G16" s="7">
         <f>IF(F16="","",MAX(0,YEARFRAC(TODAY(),F16)))</f>
         <v/>
       </c>
       <c r="H16" s="8" t="n">
-        <v>0.0169</v>
+        <v>0.0334</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>0.0355</v>
+        <v>0.0444</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>-0.0007</v>
+        <v>0.0005</v>
       </c>
       <c r="K16" s="9" t="n"/>
       <c r="L16" s="9" t="n"/>
       <c r="M16" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.002</v>
       </c>
       <c r="N16" s="10">
         <f>IF(D16="Govt",$B$1,$B$2)</f>
@@ -1377,23 +1377,23 @@
         <v/>
       </c>
       <c r="Q16" s="12" t="n">
-        <v>9.830500000000001</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BNP Paribas</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2032 UCITS ETF C</t>
+          <t>Xtrackers II Target Maturity Sept 2032 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LU2823895847</t>
+          <t>LU2809864452</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -1403,24 +1403,24 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
-        <v>48579</v>
+        <v>48487</v>
       </c>
       <c r="G17" s="7">
         <f>IF(F17="","",MAX(0,YEARFRAC(TODAY(),F17)))</f>
         <v/>
       </c>
       <c r="H17" s="8" t="n">
-        <v>0.0269</v>
+        <v>0.0282</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>0.0421</v>
+        <v>0.0435</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="K17" s="9" t="n"/>
       <c r="L17" s="9" t="n"/>
@@ -1440,23 +1440,23 @@
         <v/>
       </c>
       <c r="Q17" s="12" t="n">
-        <v>10.4237</v>
+        <v>34.27</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BNP Paribas</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2032 UCITS ETF D</t>
+          <t>iShares iBonds Dec 2032 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LU2823895763</t>
+          <t>IE0000MR4GH9</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -1477,10 +1477,10 @@
         <v/>
       </c>
       <c r="H18" s="8" t="n">
-        <v>0.0269</v>
+        <v>0.0301</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>0.0421</v>
+        <v>0.0429</v>
       </c>
       <c r="J18" s="9" t="n">
         <v>0.0002</v>
@@ -1503,23 +1503,23 @@
         <v/>
       </c>
       <c r="Q18" s="12" t="n">
-        <v>10.0381</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1C</t>
+          <t>iShares iBonds Dec 2031 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LU2673523135</t>
+          <t>IE000I2WYEU9</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -1529,21 +1529,21 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>48121</v>
+        <v>48213</v>
       </c>
       <c r="G19" s="7">
         <f>IF(F19="","",MAX(0,YEARFRAC(TODAY(),F19)))</f>
         <v/>
       </c>
       <c r="H19" s="8" t="n">
-        <v>0.0287</v>
+        <v>0.0285</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>0.04190000000000001</v>
+        <v>0.04219999999999999</v>
       </c>
       <c r="J19" s="9" t="n">
         <v>0.0002</v>
@@ -1566,55 +1566,55 @@
         <v/>
       </c>
       <c r="Q19" s="12" t="n">
-        <v>9.779999999999999</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>Amundi Fixed Maturity 2030 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LU2673523481</t>
+          <t>LU3120976132</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>48121</v>
+        <v>47848</v>
       </c>
       <c r="G20" s="7">
         <f>IF(F20="","",MAX(0,YEARFRAC(TODAY(),F20)))</f>
         <v/>
       </c>
       <c r="H20" s="8" t="n">
-        <v>0.0287</v>
+        <v>0.0169</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>0.04190000000000001</v>
+        <v>0.0355</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.0002</v>
+        <v>-0.0007</v>
       </c>
       <c r="K20" s="9" t="n"/>
       <c r="L20" s="9" t="n"/>
       <c r="M20" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N20" s="10">
         <f>IF(D20="Govt",$B$1,$B$2)</f>
@@ -1629,28 +1629,28 @@
         <v/>
       </c>
       <c r="Q20" s="12" t="n">
-        <v>29.28</v>
+        <v>9.830500000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>BNP Paribas</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2029 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2032 UCITS ETF C</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>LU2872291781</t>
+          <t>LU2823895847</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -1659,25 +1659,25 @@
         </is>
       </c>
       <c r="F21" s="6" t="n">
-        <v>47483</v>
+        <v>48579</v>
       </c>
       <c r="G21" s="7">
         <f>IF(F21="","",MAX(0,YEARFRAC(TODAY(),F21)))</f>
         <v/>
       </c>
       <c r="H21" s="8" t="n">
-        <v>0.0208</v>
+        <v>0.0269</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>0.0346</v>
+        <v>0.0421</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>-0.0007</v>
+        <v>0.0002</v>
       </c>
       <c r="K21" s="9" t="n"/>
       <c r="L21" s="9" t="n"/>
       <c r="M21" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N21" s="10">
         <f>IF(D21="Govt",$B$1,$B$2)</f>
@@ -1692,23 +1692,23 @@
         <v/>
       </c>
       <c r="Q21" s="12" t="n">
-        <v>9.985900000000001</v>
+        <v>10.4237</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>BNP Paribas</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2032 UCITS ETF D</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>IE000I25S1V5</t>
+          <t>LU2823895763</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1718,29 +1718,29 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>47848</v>
+        <v>48579</v>
       </c>
       <c r="G22" s="7">
         <f>IF(F22="","",MAX(0,YEARFRAC(TODAY(),F22)))</f>
         <v/>
       </c>
       <c r="H22" s="8" t="n">
-        <v>0.0286</v>
+        <v>0.0269</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>0.0406</v>
+        <v>0.0421</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="K22" s="9" t="n"/>
       <c r="L22" s="9" t="n"/>
       <c r="M22" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N22" s="10">
         <f>IF(D22="Govt",$B$1,$B$2)</f>
@@ -1755,23 +1755,23 @@
         <v/>
       </c>
       <c r="Q22" s="12" t="n">
-        <v>5.3493</v>
+        <v>10.0381</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>IE000W6YTDH7</t>
+          <t>LU2673523135</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -1781,29 +1781,29 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>47848</v>
+        <v>48121</v>
       </c>
       <c r="G23" s="7">
         <f>IF(F23="","",MAX(0,YEARFRAC(TODAY(),F23)))</f>
         <v/>
       </c>
       <c r="H23" s="8" t="n">
-        <v>0.0286</v>
+        <v>0.0287</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>0.0406</v>
+        <v>0.04190000000000001</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="K23" s="9" t="n"/>
       <c r="L23" s="9" t="n"/>
       <c r="M23" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N23" s="10">
         <f>IF(D23="Govt",$B$1,$B$2)</f>
@@ -1818,23 +1818,23 @@
         <v/>
       </c>
       <c r="Q23" s="12" t="n">
-        <v>4.9828</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2030 Term € Corp UCITS ETF</t>
+          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>IE000LX17BP9</t>
+          <t>LU2673523481</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -1848,20 +1848,20 @@
         </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>47848</v>
+        <v>48121</v>
       </c>
       <c r="G24" s="7">
         <f>IF(F24="","",MAX(0,YEARFRAC(TODAY(),F24)))</f>
         <v/>
       </c>
       <c r="H24" s="8" t="n">
-        <v>0.028</v>
+        <v>0.0287</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>0.0406</v>
+        <v>0.04190000000000001</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.0003</v>
+        <v>0.0002</v>
       </c>
       <c r="K24" s="9" t="n"/>
       <c r="L24" s="9" t="n"/>
@@ -1881,23 +1881,23 @@
         <v/>
       </c>
       <c r="Q24" s="12" t="n">
-        <v>4.99</v>
+        <v>29.28</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2028 Term € Italy Govt Bond UCITS ETF</t>
+          <t>Amundi Fixed Maturity 2029 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>IE000Q2EQ5K8</t>
+          <t>LU2872291781</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -1907,29 +1907,29 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F25" s="6" t="n">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="G25" s="7">
         <f>IF(F25="","",MAX(0,YEARFRAC(TODAY(),F25)))</f>
         <v/>
       </c>
       <c r="H25" s="8" t="n">
-        <v>0.026</v>
+        <v>0.0208</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>0.034</v>
+        <v>0.0346</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.0003</v>
+        <v>-0.0007</v>
       </c>
       <c r="K25" s="9" t="n"/>
       <c r="L25" s="9" t="n"/>
       <c r="M25" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N25" s="10">
         <f>IF(D25="Govt",$B$1,$B$2)</f>
@@ -1944,23 +1944,23 @@
         <v/>
       </c>
       <c r="Q25" s="12" t="n">
-        <v>5.06</v>
+        <v>9.985900000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2028 Euro Government Bond Yield + UCITS ETF Dist</t>
+          <t>Xtrackers II Target Maturity Sept 2029 Italy and Spain Government Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>LU2780871666</t>
+          <t>LU0484969463</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -1970,29 +1970,29 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>47118</v>
+        <v>47391</v>
       </c>
       <c r="G26" s="7">
         <f>IF(F26="","",MAX(0,YEARFRAC(TODAY(),F26)))</f>
         <v/>
       </c>
       <c r="H26" s="8" t="n">
-        <v>0.023</v>
+        <v>0.0297</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>0.0328</v>
+        <v>0.0349</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>-0.0004</v>
+        <v>0.0002</v>
       </c>
       <c r="K26" s="9" t="n"/>
       <c r="L26" s="9" t="n"/>
       <c r="M26" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N26" s="10">
         <f>IF(D26="Govt",$B$1,$B$2)</f>
@@ -2007,23 +2007,23 @@
         <v/>
       </c>
       <c r="Q26" s="12" t="n">
-        <v>10.285</v>
+        <v>204.53</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2029 Term € Corp UCITS ETF</t>
+          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>IE000IHURBR0</t>
+          <t>IE000I25S1V5</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -2033,29 +2033,29 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F27" s="6" t="n">
-        <v>47483</v>
+        <v>47848</v>
       </c>
       <c r="G27" s="7">
         <f>IF(F27="","",MAX(0,YEARFRAC(TODAY(),F27)))</f>
         <v/>
       </c>
       <c r="H27" s="8" t="n">
-        <v>0.0252</v>
+        <v>0.0286</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>0.0389</v>
+        <v>0.0406</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.0004</v>
+        <v>0</v>
       </c>
       <c r="K27" s="9" t="n"/>
       <c r="L27" s="9" t="n"/>
       <c r="M27" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="N27" s="10">
         <f>IF(D27="Govt",$B$1,$B$2)</f>
@@ -2070,7 +2070,7 @@
         <v/>
       </c>
       <c r="Q27" s="12" t="n">
-        <v>5.04</v>
+        <v>5.3493</v>
       </c>
     </row>
     <row r="28">
@@ -2081,12 +2081,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>IE000P5IB8I8</t>
+          <t>IE000W6YTDH7</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -2096,21 +2096,21 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F28" s="6" t="n">
-        <v>47483</v>
+        <v>47848</v>
       </c>
       <c r="G28" s="7">
         <f>IF(F28="","",MAX(0,YEARFRAC(TODAY(),F28)))</f>
         <v/>
       </c>
       <c r="H28" s="8" t="n">
-        <v>0.0242</v>
+        <v>0.0286</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>0.0386</v>
+        <v>0.0406</v>
       </c>
       <c r="J28" s="9" t="n">
         <v>0</v>
@@ -2133,23 +2133,23 @@
         <v/>
       </c>
       <c r="Q28" s="12" t="n">
-        <v>5.4253</v>
+        <v>4.9828</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>iShares iBonds Dec 2030 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>IE000ZC4C5Q1</t>
+          <t>IE000LX17BP9</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -2163,25 +2163,25 @@
         </is>
       </c>
       <c r="F29" s="6" t="n">
-        <v>47483</v>
+        <v>47848</v>
       </c>
       <c r="G29" s="7">
         <f>IF(F29="","",MAX(0,YEARFRAC(TODAY(),F29)))</f>
         <v/>
       </c>
       <c r="H29" s="8" t="n">
-        <v>0.0242</v>
+        <v>0.028</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>0.0386</v>
+        <v>0.0406</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0</v>
+        <v>0.0003</v>
       </c>
       <c r="K29" s="9" t="n"/>
       <c r="L29" s="9" t="n"/>
       <c r="M29" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N29" s="10">
         <f>IF(D29="Govt",$B$1,$B$2)</f>
@@ -2196,7 +2196,7 @@
         <v/>
       </c>
       <c r="Q29" s="12" t="n">
-        <v>5.0554</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="30">
@@ -2207,12 +2207,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2029 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>Xtrackers II Target Maturity Sept 2030 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>LU2673523309</t>
+          <t>LU2809864296</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -2226,20 +2226,20 @@
         </is>
       </c>
       <c r="F30" s="6" t="n">
-        <v>47391</v>
+        <v>47756</v>
       </c>
       <c r="G30" s="7">
         <f>IF(F30="","",MAX(0,YEARFRAC(TODAY(),F30)))</f>
         <v/>
       </c>
       <c r="H30" s="8" t="n">
-        <v>0.0245</v>
+        <v>0.0271</v>
       </c>
       <c r="I30" s="8" t="n">
-        <v>0.0386</v>
+        <v>0.0405</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.0004</v>
+        <v>0.0003</v>
       </c>
       <c r="K30" s="9" t="n"/>
       <c r="L30" s="9" t="n"/>
@@ -2259,50 +2259,50 @@
         <v/>
       </c>
       <c r="Q30" s="12" t="n">
-        <v>25.78</v>
+        <v>35.23</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2029 EUR Corporate Bond UCITS ETF 1C</t>
+          <t>iShares iBonds Dec 2028 Term € Italy Govt Bond UCITS ETF</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>LU2673522913</t>
+          <t>IE000Q2EQ5K8</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F31" s="6" t="n">
-        <v>47391</v>
+        <v>47118</v>
       </c>
       <c r="G31" s="7">
         <f>IF(F31="","",MAX(0,YEARFRAC(TODAY(),F31)))</f>
         <v/>
       </c>
       <c r="H31" s="8" t="n">
-        <v>0.0245</v>
+        <v>0.026</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>0.0386</v>
+        <v>0.034</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.0004</v>
+        <v>0.0003</v>
       </c>
       <c r="K31" s="9" t="n"/>
       <c r="L31" s="9" t="n"/>
@@ -2322,7 +2322,7 @@
         <v/>
       </c>
       <c r="Q31" s="12" t="n">
-        <v>9.17</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="32">
@@ -2333,12 +2333,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Dist</t>
+          <t>Amundi Fixed Maturity 2028 Euro Government Bond Yield + UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>LU2780871401</t>
+          <t>LU2780871666</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -2359,13 +2359,13 @@
         <v/>
       </c>
       <c r="H32" s="8" t="n">
-        <v>0.0184</v>
+        <v>0.023</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>0.0325</v>
+        <v>0.0328</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>-0.0003</v>
+        <v>-0.0004</v>
       </c>
       <c r="K32" s="9" t="n"/>
       <c r="L32" s="9" t="n"/>
@@ -2385,55 +2385,55 @@
         <v/>
       </c>
       <c r="Q32" s="12" t="n">
-        <v>10.2754</v>
+        <v>10.285</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>iShares iBonds Dec 2029 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>LU2780871310</t>
+          <t>IE000IHURBR0</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F33" s="6" t="n">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="G33" s="7">
         <f>IF(F33="","",MAX(0,YEARFRAC(TODAY(),F33)))</f>
         <v/>
       </c>
       <c r="H33" s="8" t="n">
-        <v>0.0184</v>
+        <v>0.0252</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>0.0325</v>
+        <v>0.0389</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0.0004</v>
       </c>
       <c r="K33" s="9" t="n"/>
       <c r="L33" s="9" t="n"/>
       <c r="M33" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N33" s="10">
         <f>IF(D33="Govt",$B$1,$B$2)</f>
@@ -2448,23 +2448,23 @@
         <v/>
       </c>
       <c r="Q33" s="12" t="n">
-        <v>10.0748</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BNP Paribas</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2029 UCITS ETF C</t>
+          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>LU2823896811</t>
+          <t>IE000P5IB8I8</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -2485,18 +2485,18 @@
         <v/>
       </c>
       <c r="H34" s="8" t="n">
-        <v>0.0235</v>
+        <v>0.0242</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>0.0382</v>
+        <v>0.0386</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.0003</v>
+        <v>0</v>
       </c>
       <c r="K34" s="9" t="n"/>
       <c r="L34" s="9" t="n"/>
       <c r="M34" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="N34" s="10">
         <f>IF(D34="Govt",$B$1,$B$2)</f>
@@ -2511,23 +2511,23 @@
         <v/>
       </c>
       <c r="Q34" s="12" t="n">
-        <v>10.6604</v>
+        <v>5.4253</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BNP Paribas</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2029 UCITS ETF D</t>
+          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>LU2823896738</t>
+          <t>IE000ZC4C5Q1</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -2548,18 +2548,18 @@
         <v/>
       </c>
       <c r="H35" s="8" t="n">
-        <v>0.0235</v>
+        <v>0.0242</v>
       </c>
       <c r="I35" s="8" t="n">
-        <v>0.0382</v>
+        <v>0.0386</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.0003</v>
+        <v>0</v>
       </c>
       <c r="K35" s="9" t="n"/>
       <c r="L35" s="9" t="n"/>
       <c r="M35" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="N35" s="10">
         <f>IF(D35="Govt",$B$1,$B$2)</f>
@@ -2574,23 +2574,23 @@
         <v/>
       </c>
       <c r="Q35" s="12" t="n">
-        <v>10.2991</v>
+        <v>5.0554</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2028 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>Xtrackers II Target Maturity Sept 2029 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>IE00079EUF59</t>
+          <t>LU2673523309</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -2600,29 +2600,29 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F36" s="6" t="n">
-        <v>47118</v>
+        <v>47391</v>
       </c>
       <c r="G36" s="7">
         <f>IF(F36="","",MAX(0,YEARFRAC(TODAY(),F36)))</f>
         <v/>
       </c>
       <c r="H36" s="8" t="n">
-        <v>0.0242</v>
+        <v>0.0245</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>0.0375</v>
+        <v>0.0386</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="K36" s="9" t="n"/>
       <c r="L36" s="9" t="n"/>
       <c r="M36" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N36" s="10">
         <f>IF(D36="Govt",$B$1,$B$2)</f>
@@ -2637,23 +2637,23 @@
         <v/>
       </c>
       <c r="Q36" s="12" t="n">
-        <v>5.5695</v>
+        <v>25.78</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2028 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>Xtrackers II Target Maturity Sept 2029 EUR Corporate Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>IE000LKGEZQ6</t>
+          <t>LU2673522913</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -2663,29 +2663,29 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F37" s="6" t="n">
-        <v>47118</v>
+        <v>47391</v>
       </c>
       <c r="G37" s="7">
         <f>IF(F37="","",MAX(0,YEARFRAC(TODAY(),F37)))</f>
         <v/>
       </c>
       <c r="H37" s="8" t="n">
-        <v>0.0242</v>
+        <v>0.0245</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>0.0375</v>
+        <v>0.0386</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="K37" s="9" t="n"/>
       <c r="L37" s="9" t="n"/>
       <c r="M37" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N37" s="10">
         <f>IF(D37="Govt",$B$1,$B$2)</f>
@@ -2700,28 +2700,28 @@
         <v/>
       </c>
       <c r="Q37" s="12" t="n">
-        <v>5.2089</v>
+        <v>9.17</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2028 Term € Corp UCITS ETF</t>
+          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>IE000264WWY0</t>
+          <t>LU2780871401</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -2737,18 +2737,18 @@
         <v/>
       </c>
       <c r="H38" s="8" t="n">
-        <v>0.0213</v>
+        <v>0.0184</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>0.0373</v>
+        <v>0.0325</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.0003</v>
+        <v>-0.0003</v>
       </c>
       <c r="K38" s="9" t="n"/>
       <c r="L38" s="9" t="n"/>
       <c r="M38" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N38" s="10">
         <f>IF(D38="Govt",$B$1,$B$2)</f>
@@ -2763,55 +2763,55 @@
         <v/>
       </c>
       <c r="Q38" s="12" t="n">
-        <v>5.1</v>
+        <v>10.2754</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2028 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>LU2810185665</t>
+          <t>LU2780871310</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F39" s="6" t="n">
-        <v>47026</v>
+        <v>47118</v>
       </c>
       <c r="G39" s="7">
         <f>IF(F39="","",MAX(0,YEARFRAC(TODAY(),F39)))</f>
         <v/>
       </c>
       <c r="H39" s="8" t="n">
-        <v>0.0207</v>
+        <v>0.0184</v>
       </c>
       <c r="I39" s="8" t="n">
-        <v>0.0369</v>
+        <v>0.0325</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.0002</v>
+        <v>-0.0003</v>
       </c>
       <c r="K39" s="9" t="n"/>
       <c r="L39" s="9" t="n"/>
       <c r="M39" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N39" s="10">
         <f>IF(D39="Govt",$B$1,$B$2)</f>
@@ -2826,55 +2826,55 @@
         <v/>
       </c>
       <c r="Q39" s="12" t="n">
-        <v>35.76</v>
+        <v>10.0748</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>BNP Paribas</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2027 Italy BTP Government Bond UCITS ETF Dist</t>
+          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2029 UCITS ETF C</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>LU2780872128</t>
+          <t>LU2823896811</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F40" s="6" t="n">
-        <v>46752</v>
+        <v>47483</v>
       </c>
       <c r="G40" s="7">
         <f>IF(F40="","",MAX(0,YEARFRAC(TODAY(),F40)))</f>
         <v/>
       </c>
       <c r="H40" s="8" t="n">
-        <v>0.0265</v>
+        <v>0.0235</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>0.0305</v>
+        <v>0.0382</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0003</v>
       </c>
       <c r="K40" s="9" t="n"/>
       <c r="L40" s="9" t="n"/>
       <c r="M40" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N40" s="10">
         <f>IF(D40="Govt",$B$1,$B$2)</f>
@@ -2889,55 +2889,55 @@
         <v/>
       </c>
       <c r="Q40" s="12" t="n">
-        <v>10.3332</v>
+        <v>10.6604</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>BNP Paribas</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2027 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2029 UCITS ETF D</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>LU2872291435</t>
+          <t>LU2823896738</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F41" s="6" t="n">
-        <v>46752</v>
+        <v>47483</v>
       </c>
       <c r="G41" s="7">
         <f>IF(F41="","",MAX(0,YEARFRAC(TODAY(),F41)))</f>
         <v/>
       </c>
       <c r="H41" s="8" t="n">
-        <v>0.015</v>
+        <v>0.0235</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>0.0294</v>
+        <v>0.0382</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0.0003</v>
       </c>
       <c r="K41" s="9" t="n"/>
       <c r="L41" s="9" t="n"/>
       <c r="M41" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N41" s="10">
         <f>IF(D41="Govt",$B$1,$B$2)</f>
@@ -2952,55 +2952,55 @@
         <v/>
       </c>
       <c r="Q41" s="12" t="n">
-        <v>10.1744</v>
+        <v>10.2991</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2027 German Bund Government Bond UCITS ETF Dist</t>
+          <t>Invesco BulletShares 2028 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>LU2780871823</t>
+          <t>IE00079EUF59</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
-        <v>46752</v>
+        <v>47118</v>
       </c>
       <c r="G42" s="7">
         <f>IF(F42="","",MAX(0,YEARFRAC(TODAY(),F42)))</f>
         <v/>
       </c>
       <c r="H42" s="8" t="n">
-        <v>0.0105</v>
+        <v>0.0242</v>
       </c>
       <c r="I42" s="8" t="n">
-        <v>0.0284</v>
+        <v>0.0375</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="K42" s="9" t="n"/>
       <c r="L42" s="9" t="n"/>
       <c r="M42" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="N42" s="10">
         <f>IF(D42="Govt",$B$1,$B$2)</f>
@@ -3015,7 +3015,7 @@
         <v/>
       </c>
       <c r="Q42" s="12" t="n">
-        <v>10.3477</v>
+        <v>5.5695</v>
       </c>
     </row>
     <row r="43">
@@ -3026,12 +3026,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2027 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>Invesco BulletShares 2028 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>IE000LGHLQ71</t>
+          <t>IE000LKGEZQ6</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -3041,21 +3041,21 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
-        <v>46752</v>
+        <v>47118</v>
       </c>
       <c r="G43" s="7">
         <f>IF(F43="","",MAX(0,YEARFRAC(TODAY(),F43)))</f>
         <v/>
       </c>
       <c r="H43" s="8" t="n">
-        <v>0.0197</v>
+        <v>0.0242</v>
       </c>
       <c r="I43" s="8" t="n">
-        <v>0.0335</v>
+        <v>0.0375</v>
       </c>
       <c r="J43" s="9" t="n">
         <v>0</v>
@@ -3078,23 +3078,23 @@
         <v/>
       </c>
       <c r="Q43" s="12" t="n">
-        <v>5.7061</v>
+        <v>5.2089</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2027 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>iShares iBonds Dec 2028 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>IE000XOS4OJ6</t>
+          <t>IE000264WWY0</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -3108,25 +3108,25 @@
         </is>
       </c>
       <c r="F44" s="6" t="n">
-        <v>46752</v>
+        <v>47118</v>
       </c>
       <c r="G44" s="7">
         <f>IF(F44="","",MAX(0,YEARFRAC(TODAY(),F44)))</f>
         <v/>
       </c>
       <c r="H44" s="8" t="n">
-        <v>0.0197</v>
+        <v>0.0213</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>0.0335</v>
+        <v>0.0373</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0</v>
+        <v>0.0003</v>
       </c>
       <c r="K44" s="9" t="n"/>
       <c r="L44" s="9" t="n"/>
       <c r="M44" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N44" s="10">
         <f>IF(D44="Govt",$B$1,$B$2)</f>
@@ -3141,23 +3141,23 @@
         <v/>
       </c>
       <c r="Q44" s="12" t="n">
-        <v>5.3339</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2027 Term € Corp UCITS ETF</t>
+          <t>Xtrackers II Target Maturity Sept 2028 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>IE000ZOI8OK5</t>
+          <t>LU2810185665</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -3167,24 +3167,24 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F45" s="6" t="n">
-        <v>46752</v>
+        <v>47026</v>
       </c>
       <c r="G45" s="7">
         <f>IF(F45="","",MAX(0,YEARFRAC(TODAY(),F45)))</f>
         <v/>
       </c>
       <c r="H45" s="8" t="n">
-        <v>0.0195</v>
+        <v>0.0207</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>0.0333</v>
+        <v>0.0369</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="K45" s="9" t="n"/>
       <c r="L45" s="9" t="n"/>
@@ -3204,28 +3204,28 @@
         <v/>
       </c>
       <c r="Q45" s="12" t="n">
-        <v>5.65</v>
+        <v>35.76</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>Amundi Fixed Maturity 2027 Italy BTP Government Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>LU2673523218</t>
+          <t>LU2780872128</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -3234,25 +3234,25 @@
         </is>
       </c>
       <c r="F46" s="6" t="n">
-        <v>46660</v>
+        <v>46752</v>
       </c>
       <c r="G46" s="7">
         <f>IF(F46="","",MAX(0,YEARFRAC(TODAY(),F46)))</f>
         <v/>
       </c>
       <c r="H46" s="8" t="n">
-        <v>0.0186</v>
+        <v>0.0265</v>
       </c>
       <c r="I46" s="8" t="n">
-        <v>0.032</v>
+        <v>0.0305</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>-0.0005</v>
+        <v>-0.0002</v>
       </c>
       <c r="K46" s="9" t="n"/>
       <c r="L46" s="9" t="n"/>
       <c r="M46" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N46" s="10">
         <f>IF(D46="Govt",$B$1,$B$2)</f>
@@ -3267,28 +3267,28 @@
         <v/>
       </c>
       <c r="Q46" s="12" t="n">
-        <v>25.96</v>
+        <v>10.3332</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1C</t>
+          <t>Amundi Fixed Maturity 2027 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>LU2673522830</t>
+          <t>LU2872291435</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -3297,25 +3297,25 @@
         </is>
       </c>
       <c r="F47" s="6" t="n">
-        <v>46660</v>
+        <v>46752</v>
       </c>
       <c r="G47" s="7">
         <f>IF(F47="","",MAX(0,YEARFRAC(TODAY(),F47)))</f>
         <v/>
       </c>
       <c r="H47" s="8" t="n">
-        <v>0.0186</v>
+        <v>0.015</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>0.032</v>
+        <v>0.0294</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>-0.0005</v>
+        <v>-0.0001</v>
       </c>
       <c r="K47" s="9" t="n"/>
       <c r="L47" s="9" t="n"/>
       <c r="M47" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N47" s="10">
         <f>IF(D47="Govt",$B$1,$B$2)</f>
@@ -3330,23 +3330,23 @@
         <v/>
       </c>
       <c r="Q47" s="12" t="n">
-        <v>9.31</v>
+        <v>10.1744</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2026 Term € Italy Govt Bond UCITS ETF</t>
+          <t>Amundi Fixed Maturity 2027 German Bund Government Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>IE000LZ7BZW8</t>
+          <t>LU2780871823</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -3360,25 +3360,25 @@
         </is>
       </c>
       <c r="F48" s="6" t="n">
-        <v>46387</v>
+        <v>46752</v>
       </c>
       <c r="G48" s="7">
         <f>IF(F48="","",MAX(0,YEARFRAC(TODAY(),F48)))</f>
         <v/>
       </c>
       <c r="H48" s="8" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0105</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>0.0269</v>
+        <v>0.0284</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0.0001</v>
       </c>
       <c r="K48" s="9" t="n"/>
       <c r="L48" s="9" t="n"/>
       <c r="M48" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N48" s="10">
         <f>IF(D48="Govt",$B$1,$B$2)</f>
@@ -3393,28 +3393,28 @@
         <v/>
       </c>
       <c r="Q48" s="12" t="n">
-        <v>5.06</v>
+        <v>10.3477</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2026 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>Invesco BulletShares 2027 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>LU2872291278</t>
+          <t>IE000LGHLQ71</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -3423,25 +3423,25 @@
         </is>
       </c>
       <c r="F49" s="6" t="n">
-        <v>46387</v>
+        <v>46752</v>
       </c>
       <c r="G49" s="7">
         <f>IF(F49="","",MAX(0,YEARFRAC(TODAY(),F49)))</f>
         <v/>
       </c>
       <c r="H49" s="8" t="n">
-        <v>0.0023</v>
+        <v>0.0197</v>
       </c>
       <c r="I49" s="8" t="n">
-        <v>0.0264</v>
+        <v>0.0335</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>-0.0005</v>
+        <v>0</v>
       </c>
       <c r="K49" s="9" t="n"/>
       <c r="L49" s="9" t="n"/>
       <c r="M49" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="N49" s="10">
         <f>IF(D49="Govt",$B$1,$B$2)</f>
@@ -3456,7 +3456,7 @@
         <v/>
       </c>
       <c r="Q49" s="12" t="n">
-        <v>10.258</v>
+        <v>5.7061</v>
       </c>
     </row>
     <row r="50">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2026 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>Invesco BulletShares 2027 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>IE0004QWOTD5</t>
+          <t>IE000XOS4OJ6</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -3482,21 +3482,21 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
-        <v>46387</v>
+        <v>46752</v>
       </c>
       <c r="G50" s="7">
         <f>IF(F50="","",MAX(0,YEARFRAC(TODAY(),F50)))</f>
         <v/>
       </c>
       <c r="H50" s="8" t="n">
-        <v>0.0119</v>
+        <v>0.0197</v>
       </c>
       <c r="I50" s="8" t="n">
-        <v>0.0298</v>
+        <v>0.0335</v>
       </c>
       <c r="J50" s="9" t="n">
         <v>0</v>
@@ -3519,23 +3519,23 @@
         <v/>
       </c>
       <c r="Q50" s="12" t="n">
-        <v>5.7916</v>
+        <v>5.3339</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2026 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>iShares iBonds Dec 2027 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>IE000AYJ75E5</t>
+          <t>IE000ZOI8OK5</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
@@ -3545,21 +3545,21 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F51" s="6" t="n">
-        <v>46387</v>
+        <v>46752</v>
       </c>
       <c r="G51" s="7">
         <f>IF(F51="","",MAX(0,YEARFRAC(TODAY(),F51)))</f>
         <v/>
       </c>
       <c r="H51" s="8" t="n">
-        <v>0.0119</v>
+        <v>0.0195</v>
       </c>
       <c r="I51" s="8" t="n">
-        <v>0.0298</v>
+        <v>0.0333</v>
       </c>
       <c r="J51" s="9" t="n">
         <v>0</v>
@@ -3567,7 +3567,7 @@
       <c r="K51" s="9" t="n"/>
       <c r="L51" s="9" t="n"/>
       <c r="M51" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N51" s="10">
         <f>IF(D51="Govt",$B$1,$B$2)</f>
@@ -3582,23 +3582,23 @@
         <v/>
       </c>
       <c r="Q51" s="12" t="n">
-        <v>5.4154</v>
+        <v>5.65</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2026 Term € Corp UCITS ETF</t>
+          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>IE000SIZJ2B2</t>
+          <t>LU2673523218</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -3612,20 +3612,20 @@
         </is>
       </c>
       <c r="F52" s="6" t="n">
-        <v>46387</v>
+        <v>46660</v>
       </c>
       <c r="G52" s="7">
         <f>IF(F52="","",MAX(0,YEARFRAC(TODAY(),F52)))</f>
         <v/>
       </c>
       <c r="H52" s="8" t="n">
-        <v>0.0059</v>
+        <v>0.0186</v>
       </c>
       <c r="I52" s="8" t="n">
-        <v>0.0273</v>
+        <v>0.032</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>-0.0008</v>
+        <v>-0.0005</v>
       </c>
       <c r="K52" s="9" t="n"/>
       <c r="L52" s="9" t="n"/>
@@ -3645,7 +3645,7 @@
         <v/>
       </c>
       <c r="Q52" s="12" t="n">
-        <v>5.06</v>
+        <v>25.96</v>
       </c>
     </row>
     <row r="53">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2030 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LU2809864296</t>
+          <t>LU2673522830</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -3671,19 +3671,25 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F53" s="6" t="n">
-        <v>47756</v>
+        <v>46660</v>
       </c>
       <c r="G53" s="7">
         <f>IF(F53="","",MAX(0,YEARFRAC(TODAY(),F53)))</f>
         <v/>
       </c>
-      <c r="H53" s="8" t="n"/>
-      <c r="I53" s="8" t="n"/>
-      <c r="J53" s="9" t="n"/>
+      <c r="H53" s="8" t="n">
+        <v>0.0186</v>
+      </c>
+      <c r="I53" s="8" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="J53" s="9" t="n">
+        <v>-0.0005</v>
+      </c>
       <c r="K53" s="9" t="n"/>
       <c r="L53" s="9" t="n"/>
       <c r="M53" s="8" t="n">
@@ -3701,27 +3707,29 @@
         <f>IF(I53="","",(I53-M53)*(1-N53))</f>
         <v/>
       </c>
-      <c r="Q53" s="12" t="n"/>
+      <c r="Q53" s="12" t="n">
+        <v>9.31</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2032 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>iShares iBonds Dec 2026 Term € Italy Govt Bond UCITS ETF</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>LU2809864452</t>
+          <t>IE000LZ7BZW8</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -3730,15 +3738,21 @@
         </is>
       </c>
       <c r="F54" s="6" t="n">
-        <v>48487</v>
+        <v>46387</v>
       </c>
       <c r="G54" s="7">
         <f>IF(F54="","",MAX(0,YEARFRAC(TODAY(),F54)))</f>
         <v/>
       </c>
-      <c r="H54" s="8" t="n"/>
-      <c r="I54" s="8" t="n"/>
-      <c r="J54" s="9" t="n"/>
+      <c r="H54" s="8" t="n">
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="I54" s="8" t="n">
+        <v>0.0269</v>
+      </c>
+      <c r="J54" s="9" t="n">
+        <v>-0.0001</v>
+      </c>
       <c r="K54" s="9" t="n"/>
       <c r="L54" s="9" t="n"/>
       <c r="M54" s="8" t="n">
@@ -3756,48 +3770,56 @@
         <f>IF(I54="","",(I54-M54)*(1-N54))</f>
         <v/>
       </c>
-      <c r="Q54" s="12" t="n"/>
+      <c r="Q54" s="12" t="n">
+        <v>5.06</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2035 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>Amundi Fixed Maturity 2026 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>LU3152892546</t>
+          <t>LU2872291278</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F55" s="6" t="n">
-        <v>49582</v>
+        <v>46387</v>
       </c>
       <c r="G55" s="7">
         <f>IF(F55="","",MAX(0,YEARFRAC(TODAY(),F55)))</f>
         <v/>
       </c>
-      <c r="H55" s="8" t="n"/>
-      <c r="I55" s="8" t="n"/>
-      <c r="J55" s="9" t="n"/>
+      <c r="H55" s="8" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="I55" s="8" t="n">
+        <v>0.0264</v>
+      </c>
+      <c r="J55" s="9" t="n">
+        <v>-0.0005</v>
+      </c>
       <c r="K55" s="9" t="n"/>
       <c r="L55" s="9" t="n"/>
       <c r="M55" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N55" s="10">
         <f>IF(D55="Govt",$B$1,$B$2)</f>
@@ -3811,22 +3833,24 @@
         <f>IF(I55="","",(I55-M55)*(1-N55))</f>
         <v/>
       </c>
-      <c r="Q55" s="12" t="n"/>
+      <c r="Q55" s="12" t="n">
+        <v>10.258</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2034 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>Invesco BulletShares 2026 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>LU2809864619</t>
+          <t>IE0004QWOTD5</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -3836,23 +3860,29 @@
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F56" s="6" t="n">
-        <v>49217</v>
+        <v>46387</v>
       </c>
       <c r="G56" s="7">
         <f>IF(F56="","",MAX(0,YEARFRAC(TODAY(),F56)))</f>
         <v/>
       </c>
-      <c r="H56" s="8" t="n"/>
-      <c r="I56" s="8" t="n"/>
-      <c r="J56" s="9" t="n"/>
+      <c r="H56" s="8" t="n">
+        <v>0.0119</v>
+      </c>
+      <c r="I56" s="8" t="n">
+        <v>0.0298</v>
+      </c>
+      <c r="J56" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="K56" s="9" t="n"/>
       <c r="L56" s="9" t="n"/>
       <c r="M56" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="N56" s="10">
         <f>IF(D56="Govt",$B$1,$B$2)</f>
@@ -3866,22 +3896,24 @@
         <f>IF(I56="","",(I56-M56)*(1-N56))</f>
         <v/>
       </c>
-      <c r="Q56" s="12" t="n"/>
+      <c r="Q56" s="12" t="n">
+        <v>5.7916</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2036 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>Invesco BulletShares 2026 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>LU3152892629</t>
+          <t>IE000AYJ75E5</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
@@ -3895,19 +3927,25 @@
         </is>
       </c>
       <c r="F57" s="6" t="n">
-        <v>49948</v>
+        <v>46387</v>
       </c>
       <c r="G57" s="7">
         <f>IF(F57="","",MAX(0,YEARFRAC(TODAY(),F57)))</f>
         <v/>
       </c>
-      <c r="H57" s="8" t="n"/>
-      <c r="I57" s="8" t="n"/>
-      <c r="J57" s="9" t="n"/>
+      <c r="H57" s="8" t="n">
+        <v>0.0119</v>
+      </c>
+      <c r="I57" s="8" t="n">
+        <v>0.0298</v>
+      </c>
+      <c r="J57" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="K57" s="9" t="n"/>
       <c r="L57" s="9" t="n"/>
       <c r="M57" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="N57" s="10">
         <f>IF(D57="Govt",$B$1,$B$2)</f>
@@ -3921,44 +3959,52 @@
         <f>IF(I57="","",(I57-M57)*(1-N57))</f>
         <v/>
       </c>
-      <c r="Q57" s="12" t="n"/>
+      <c r="Q57" s="12" t="n">
+        <v>5.4154</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2029 Italy and Spain Government Bond UCITS ETF 1C</t>
+          <t>iShares iBonds Dec 2026 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>LU0484969463</t>
+          <t>IE000SIZJ2B2</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F58" s="6" t="n">
-        <v>47391</v>
+        <v>46387</v>
       </c>
       <c r="G58" s="7">
         <f>IF(F58="","",MAX(0,YEARFRAC(TODAY(),F58)))</f>
         <v/>
       </c>
-      <c r="H58" s="8" t="n"/>
-      <c r="I58" s="8" t="n"/>
-      <c r="J58" s="9" t="n"/>
+      <c r="H58" s="8" t="n">
+        <v>0.0059</v>
+      </c>
+      <c r="I58" s="8" t="n">
+        <v>0.0273</v>
+      </c>
+      <c r="J58" s="9" t="n">
+        <v>-0.0008</v>
+      </c>
       <c r="K58" s="9" t="n"/>
       <c r="L58" s="9" t="n"/>
       <c r="M58" s="8" t="n">
@@ -3976,7 +4022,9 @@
         <f>IF(I58="","",(I58-M58)*(1-N58))</f>
         <v/>
       </c>
-      <c r="Q58" s="12" t="n"/>
+      <c r="Q58" s="12" t="n">
+        <v>5.06</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="J5:J58">

--- a/data/rendimenti_etf.xlsx
+++ b/data/rendimenti_etf.xlsx
@@ -533,7 +533,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Aggiornato il 12/10/2026 14:48 da yield_etf.csv</t>
+          <t>Aggiornato il 13/10/2026 09:32 da yield_etf.csv</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
         <v>0.0501</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0</v>
       </c>
       <c r="K5" s="9" t="n"/>
       <c r="L5" s="9" t="n"/>
@@ -727,7 +727,7 @@
         <v>0.0462</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0</v>
       </c>
       <c r="K6" s="9" t="n"/>
       <c r="L6" s="9" t="n"/>
@@ -790,7 +790,7 @@
         <v>0.0459</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0</v>
       </c>
       <c r="K7" s="9" t="n"/>
       <c r="L7" s="9" t="n"/>
@@ -810,7 +810,7 @@
         <v/>
       </c>
       <c r="Q7" s="12" t="n">
-        <v>4.81</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="8">
@@ -853,7 +853,7 @@
         <v>0.0458</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0</v>
       </c>
       <c r="K8" s="9" t="n"/>
       <c r="L8" s="9" t="n"/>
@@ -916,7 +916,7 @@
         <v>0.0457</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0</v>
       </c>
       <c r="K9" s="9" t="n"/>
       <c r="L9" s="9" t="n"/>
@@ -936,7 +936,7 @@
         <v/>
       </c>
       <c r="Q9" s="12" t="n">
-        <v>4.8</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="10">
@@ -979,7 +979,7 @@
         <v>0.0455</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0</v>
       </c>
       <c r="K10" s="9" t="n"/>
       <c r="L10" s="9" t="n"/>
@@ -999,7 +999,7 @@
         <v/>
       </c>
       <c r="Q10" s="12" t="n">
-        <v>4.72</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="11">
@@ -1231,7 +1231,7 @@
         <v>0.044</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.0005</v>
+        <v>0</v>
       </c>
       <c r="K14" s="9" t="n"/>
       <c r="L14" s="9" t="n"/>
@@ -1294,7 +1294,7 @@
         <v>0.044</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.0005</v>
+        <v>0</v>
       </c>
       <c r="K15" s="9" t="n"/>
       <c r="L15" s="9" t="n"/>
@@ -1357,7 +1357,7 @@
         <v>0.0444</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.0005</v>
+        <v>0</v>
       </c>
       <c r="K16" s="9" t="n"/>
       <c r="L16" s="9" t="n"/>
@@ -1420,7 +1420,7 @@
         <v>0.0435</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="K17" s="9" t="n"/>
       <c r="L17" s="9" t="n"/>
@@ -1483,7 +1483,7 @@
         <v>0.0429</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="K18" s="9" t="n"/>
       <c r="L18" s="9" t="n"/>
@@ -1509,41 +1509,41 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2031 Term € Corp UCITS ETF</t>
+          <t>Amundi Fixed Maturity 2030 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>IE000I2WYEU9</t>
+          <t>LU3120976132</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>48213</v>
+        <v>47848</v>
       </c>
       <c r="G19" s="7">
         <f>IF(F19="","",MAX(0,YEARFRAC(TODAY(),F19)))</f>
         <v/>
       </c>
       <c r="H19" s="8" t="n">
-        <v>0.0285</v>
+        <v>0.0169</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>0.04219999999999999</v>
+        <v>0.0357</v>
       </c>
       <c r="J19" s="9" t="n">
         <v>0.0002</v>
@@ -1551,7 +1551,7 @@
       <c r="K19" s="9" t="n"/>
       <c r="L19" s="9" t="n"/>
       <c r="M19" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N19" s="10">
         <f>IF(D19="Govt",$B$1,$B$2)</f>
@@ -1566,55 +1566,55 @@
         <v/>
       </c>
       <c r="Q19" s="12" t="n">
-        <v>4.87</v>
+        <v>9.8248</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2030 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>iShares iBonds Dec 2031 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LU3120976132</t>
+          <t>IE000I2WYEU9</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>47848</v>
+        <v>48213</v>
       </c>
       <c r="G20" s="7">
         <f>IF(F20="","",MAX(0,YEARFRAC(TODAY(),F20)))</f>
         <v/>
       </c>
       <c r="H20" s="8" t="n">
-        <v>0.0169</v>
+        <v>0.0285</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>0.0355</v>
+        <v>0.04219999999999999</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>-0.0007</v>
+        <v>0</v>
       </c>
       <c r="K20" s="9" t="n"/>
       <c r="L20" s="9" t="n"/>
       <c r="M20" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N20" s="10">
         <f>IF(D20="Govt",$B$1,$B$2)</f>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="Q20" s="12" t="n">
-        <v>9.830500000000001</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="21">
@@ -1672,7 +1672,7 @@
         <v>0.0421</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="K21" s="9" t="n"/>
       <c r="L21" s="9" t="n"/>
@@ -1735,7 +1735,7 @@
         <v>0.0421</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="K22" s="9" t="n"/>
       <c r="L22" s="9" t="n"/>
@@ -1798,7 +1798,7 @@
         <v>0.04190000000000001</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="K23" s="9" t="n"/>
       <c r="L23" s="9" t="n"/>
@@ -1861,7 +1861,7 @@
         <v>0.04190000000000001</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="K24" s="9" t="n"/>
       <c r="L24" s="9" t="n"/>
@@ -1921,10 +1921,10 @@
         <v>0.0208</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>0.0346</v>
+        <v>0.0348</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>-0.0007</v>
+        <v>0.0002</v>
       </c>
       <c r="K25" s="9" t="n"/>
       <c r="L25" s="9" t="n"/>
@@ -1944,7 +1944,7 @@
         <v/>
       </c>
       <c r="Q25" s="12" t="n">
-        <v>9.985900000000001</v>
+        <v>9.9818</v>
       </c>
     </row>
     <row r="26">
@@ -1987,7 +1987,7 @@
         <v>0.0349</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="K26" s="9" t="n"/>
       <c r="L26" s="9" t="n"/>
@@ -2070,7 +2070,7 @@
         <v/>
       </c>
       <c r="Q27" s="12" t="n">
-        <v>5.3493</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="28">
@@ -2133,7 +2133,7 @@
         <v/>
       </c>
       <c r="Q28" s="12" t="n">
-        <v>4.9828</v>
+        <v>4.9834</v>
       </c>
     </row>
     <row r="29">
@@ -2176,7 +2176,7 @@
         <v>0.0406</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.0003</v>
+        <v>0</v>
       </c>
       <c r="K29" s="9" t="n"/>
       <c r="L29" s="9" t="n"/>
@@ -2239,7 +2239,7 @@
         <v>0.0405</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.0003</v>
+        <v>0</v>
       </c>
       <c r="K30" s="9" t="n"/>
       <c r="L30" s="9" t="n"/>
@@ -2302,7 +2302,7 @@
         <v>0.034</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.0003</v>
+        <v>0</v>
       </c>
       <c r="K31" s="9" t="n"/>
       <c r="L31" s="9" t="n"/>
@@ -2359,13 +2359,13 @@
         <v/>
       </c>
       <c r="H32" s="8" t="n">
-        <v>0.023</v>
+        <v>0.0229</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>0.0328</v>
+        <v>0.0329</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>-0.0004</v>
+        <v>0.0001</v>
       </c>
       <c r="K32" s="9" t="n"/>
       <c r="L32" s="9" t="n"/>
@@ -2385,7 +2385,7 @@
         <v/>
       </c>
       <c r="Q32" s="12" t="n">
-        <v>10.285</v>
+        <v>10.2821</v>
       </c>
     </row>
     <row r="33">
@@ -2428,7 +2428,7 @@
         <v>0.0389</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.0004</v>
+        <v>0</v>
       </c>
       <c r="K33" s="9" t="n"/>
       <c r="L33" s="9" t="n"/>
@@ -2448,7 +2448,7 @@
         <v/>
       </c>
       <c r="Q33" s="12" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="34">
@@ -2511,7 +2511,7 @@
         <v/>
       </c>
       <c r="Q34" s="12" t="n">
-        <v>5.4253</v>
+        <v>5.4251</v>
       </c>
     </row>
     <row r="35">
@@ -2574,28 +2574,28 @@
         <v/>
       </c>
       <c r="Q35" s="12" t="n">
-        <v>5.0554</v>
+        <v>5.0552</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2029 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>LU2673523309</t>
+          <t>LU2780871401</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -2604,25 +2604,25 @@
         </is>
       </c>
       <c r="F36" s="6" t="n">
-        <v>47391</v>
+        <v>47118</v>
       </c>
       <c r="G36" s="7">
         <f>IF(F36="","",MAX(0,YEARFRAC(TODAY(),F36)))</f>
         <v/>
       </c>
       <c r="H36" s="8" t="n">
-        <v>0.0245</v>
+        <v>0.0184</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>0.0386</v>
+        <v>0.0326</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.0004</v>
+        <v>0.0001</v>
       </c>
       <c r="K36" s="9" t="n"/>
       <c r="L36" s="9" t="n"/>
       <c r="M36" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N36" s="10">
         <f>IF(D36="Govt",$B$1,$B$2)</f>
@@ -2637,28 +2637,28 @@
         <v/>
       </c>
       <c r="Q36" s="12" t="n">
-        <v>25.78</v>
+        <v>10.2724</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2029 EUR Corporate Bond UCITS ETF 1C</t>
+          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>LU2673522913</t>
+          <t>LU2780871310</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -2667,25 +2667,25 @@
         </is>
       </c>
       <c r="F37" s="6" t="n">
-        <v>47391</v>
+        <v>47118</v>
       </c>
       <c r="G37" s="7">
         <f>IF(F37="","",MAX(0,YEARFRAC(TODAY(),F37)))</f>
         <v/>
       </c>
       <c r="H37" s="8" t="n">
-        <v>0.0245</v>
+        <v>0.0184</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>0.0386</v>
+        <v>0.0326</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.0004</v>
+        <v>0.0001</v>
       </c>
       <c r="K37" s="9" t="n"/>
       <c r="L37" s="9" t="n"/>
       <c r="M37" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N37" s="10">
         <f>IF(D37="Govt",$B$1,$B$2)</f>
@@ -2700,28 +2700,28 @@
         <v/>
       </c>
       <c r="Q37" s="12" t="n">
-        <v>9.17</v>
+        <v>10.0719</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Dist</t>
+          <t>Xtrackers II Target Maturity Sept 2029 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LU2780871401</t>
+          <t>LU2673523309</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -2730,25 +2730,25 @@
         </is>
       </c>
       <c r="F38" s="6" t="n">
-        <v>47118</v>
+        <v>47391</v>
       </c>
       <c r="G38" s="7">
         <f>IF(F38="","",MAX(0,YEARFRAC(TODAY(),F38)))</f>
         <v/>
       </c>
       <c r="H38" s="8" t="n">
-        <v>0.0184</v>
+        <v>0.0245</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>0.0325</v>
+        <v>0.0386</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0</v>
       </c>
       <c r="K38" s="9" t="n"/>
       <c r="L38" s="9" t="n"/>
       <c r="M38" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N38" s="10">
         <f>IF(D38="Govt",$B$1,$B$2)</f>
@@ -2763,28 +2763,28 @@
         <v/>
       </c>
       <c r="Q38" s="12" t="n">
-        <v>10.2754</v>
+        <v>25.78</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>Xtrackers II Target Maturity Sept 2029 EUR Corporate Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>LU2780871310</t>
+          <t>LU2673522913</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -2793,25 +2793,25 @@
         </is>
       </c>
       <c r="F39" s="6" t="n">
-        <v>47118</v>
+        <v>47391</v>
       </c>
       <c r="G39" s="7">
         <f>IF(F39="","",MAX(0,YEARFRAC(TODAY(),F39)))</f>
         <v/>
       </c>
       <c r="H39" s="8" t="n">
-        <v>0.0184</v>
+        <v>0.0245</v>
       </c>
       <c r="I39" s="8" t="n">
-        <v>0.0325</v>
+        <v>0.0386</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0</v>
       </c>
       <c r="K39" s="9" t="n"/>
       <c r="L39" s="9" t="n"/>
       <c r="M39" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N39" s="10">
         <f>IF(D39="Govt",$B$1,$B$2)</f>
@@ -2826,7 +2826,7 @@
         <v/>
       </c>
       <c r="Q39" s="12" t="n">
-        <v>10.0748</v>
+        <v>9.17</v>
       </c>
     </row>
     <row r="40">
@@ -2869,7 +2869,7 @@
         <v>0.0382</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.0003</v>
+        <v>0</v>
       </c>
       <c r="K40" s="9" t="n"/>
       <c r="L40" s="9" t="n"/>
@@ -2932,7 +2932,7 @@
         <v>0.0382</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.0003</v>
+        <v>0</v>
       </c>
       <c r="K41" s="9" t="n"/>
       <c r="L41" s="9" t="n"/>
@@ -3015,7 +3015,7 @@
         <v/>
       </c>
       <c r="Q42" s="12" t="n">
-        <v>5.5695</v>
+        <v>5.5691</v>
       </c>
     </row>
     <row r="43">
@@ -3078,7 +3078,7 @@
         <v/>
       </c>
       <c r="Q43" s="12" t="n">
-        <v>5.2089</v>
+        <v>5.2084</v>
       </c>
     </row>
     <row r="44">
@@ -3121,7 +3121,7 @@
         <v>0.0373</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.0003</v>
+        <v>0</v>
       </c>
       <c r="K44" s="9" t="n"/>
       <c r="L44" s="9" t="n"/>
@@ -3184,7 +3184,7 @@
         <v>0.0369</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="K45" s="9" t="n"/>
       <c r="L45" s="9" t="n"/>
@@ -3244,10 +3244,10 @@
         <v>0.0265</v>
       </c>
       <c r="I46" s="8" t="n">
-        <v>0.0305</v>
+        <v>0.0306</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="K46" s="9" t="n"/>
       <c r="L46" s="9" t="n"/>
@@ -3267,7 +3267,7 @@
         <v/>
       </c>
       <c r="Q46" s="12" t="n">
-        <v>10.3332</v>
+        <v>10.3321</v>
       </c>
     </row>
     <row r="47">
@@ -3307,10 +3307,10 @@
         <v>0.015</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>0.0294</v>
+        <v>0.0295</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0.0001</v>
       </c>
       <c r="K47" s="9" t="n"/>
       <c r="L47" s="9" t="n"/>
@@ -3330,7 +3330,7 @@
         <v/>
       </c>
       <c r="Q47" s="12" t="n">
-        <v>10.1744</v>
+        <v>10.1732</v>
       </c>
     </row>
     <row r="48">
@@ -3370,7 +3370,7 @@
         <v>0.0105</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>0.0284</v>
+        <v>0.0285</v>
       </c>
       <c r="J48" s="9" t="n">
         <v>0.0001</v>
@@ -3393,7 +3393,7 @@
         <v/>
       </c>
       <c r="Q48" s="12" t="n">
-        <v>10.3477</v>
+        <v>10.3462</v>
       </c>
     </row>
     <row r="49">
@@ -3456,7 +3456,7 @@
         <v/>
       </c>
       <c r="Q49" s="12" t="n">
-        <v>5.7061</v>
+        <v>5.7067</v>
       </c>
     </row>
     <row r="50">
@@ -3519,7 +3519,7 @@
         <v/>
       </c>
       <c r="Q50" s="12" t="n">
-        <v>5.3339</v>
+        <v>5.3344</v>
       </c>
     </row>
     <row r="51">
@@ -3588,49 +3588,49 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>Amundi Fixed Maturity 2026 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>LU2673523218</t>
+          <t>LU2872291278</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F52" s="6" t="n">
-        <v>46660</v>
+        <v>46387</v>
       </c>
       <c r="G52" s="7">
         <f>IF(F52="","",MAX(0,YEARFRAC(TODAY(),F52)))</f>
         <v/>
       </c>
       <c r="H52" s="8" t="n">
-        <v>0.0186</v>
+        <v>0.0023</v>
       </c>
       <c r="I52" s="8" t="n">
-        <v>0.032</v>
+        <v>0.0272</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>-0.0005</v>
+        <v>0.0008</v>
       </c>
       <c r="K52" s="9" t="n"/>
       <c r="L52" s="9" t="n"/>
       <c r="M52" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N52" s="10">
         <f>IF(D52="Govt",$B$1,$B$2)</f>
@@ -3645,7 +3645,7 @@
         <v/>
       </c>
       <c r="Q52" s="12" t="n">
-        <v>25.96</v>
+        <v>10.2587</v>
       </c>
     </row>
     <row r="53">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1C</t>
+          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LU2673522830</t>
+          <t>LU2673523218</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F53" s="6" t="n">
@@ -3688,7 +3688,7 @@
         <v>0.032</v>
       </c>
       <c r="J53" s="9" t="n">
-        <v>-0.0005</v>
+        <v>0</v>
       </c>
       <c r="K53" s="9" t="n"/>
       <c r="L53" s="9" t="n"/>
@@ -3708,50 +3708,50 @@
         <v/>
       </c>
       <c r="Q53" s="12" t="n">
-        <v>9.31</v>
+        <v>25.96</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2026 Term € Italy Govt Bond UCITS ETF</t>
+          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>IE000LZ7BZW8</t>
+          <t>LU2673522830</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F54" s="6" t="n">
-        <v>46387</v>
+        <v>46660</v>
       </c>
       <c r="G54" s="7">
         <f>IF(F54="","",MAX(0,YEARFRAC(TODAY(),F54)))</f>
         <v/>
       </c>
       <c r="H54" s="8" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0186</v>
       </c>
       <c r="I54" s="8" t="n">
-        <v>0.0269</v>
+        <v>0.032</v>
       </c>
       <c r="J54" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0</v>
       </c>
       <c r="K54" s="9" t="n"/>
       <c r="L54" s="9" t="n"/>
@@ -3771,23 +3771,23 @@
         <v/>
       </c>
       <c r="Q54" s="12" t="n">
-        <v>5.06</v>
+        <v>9.31</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2026 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>iShares iBonds Dec 2026 Term € Italy Govt Bond UCITS ETF</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>LU2872291278</t>
+          <t>IE000LZ7BZW8</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F55" s="6" t="n">
@@ -3808,18 +3808,18 @@
         <v/>
       </c>
       <c r="H55" s="8" t="n">
-        <v>0.0023</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="I55" s="8" t="n">
-        <v>0.0264</v>
+        <v>0.0269</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>-0.0005</v>
+        <v>0</v>
       </c>
       <c r="K55" s="9" t="n"/>
       <c r="L55" s="9" t="n"/>
       <c r="M55" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N55" s="10">
         <f>IF(D55="Govt",$B$1,$B$2)</f>
@@ -3834,7 +3834,7 @@
         <v/>
       </c>
       <c r="Q55" s="12" t="n">
-        <v>10.258</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="56">
@@ -3897,7 +3897,7 @@
         <v/>
       </c>
       <c r="Q56" s="12" t="n">
-        <v>5.7916</v>
+        <v>5.7924</v>
       </c>
     </row>
     <row r="57">
@@ -3960,7 +3960,7 @@
         <v/>
       </c>
       <c r="Q57" s="12" t="n">
-        <v>5.4154</v>
+        <v>5.4161</v>
       </c>
     </row>
     <row r="58">
@@ -4003,7 +4003,7 @@
         <v>0.0273</v>
       </c>
       <c r="J58" s="9" t="n">
-        <v>-0.0008</v>
+        <v>0</v>
       </c>
       <c r="K58" s="9" t="n"/>
       <c r="L58" s="9" t="n"/>

--- a/data/rendimenti_etf.xlsx
+++ b/data/rendimenti_etf.xlsx
@@ -533,7 +533,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Aggiornato il 13/10/2026 09:32 da yield_etf.csv</t>
+          <t>Aggiornato il 14/10/2026 09:06 da yield_etf.csv</t>
         </is>
       </c>
     </row>
@@ -724,10 +724,10 @@
         <v>0.03759999999999999</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0.0462</v>
+        <v>0.0461</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0</v>
+        <v>-0.0001</v>
       </c>
       <c r="K6" s="9" t="n"/>
       <c r="L6" s="9" t="n"/>
@@ -747,7 +747,7 @@
         <v/>
       </c>
       <c r="Q6" s="12" t="n">
-        <v>28.31</v>
+        <v>28.35</v>
       </c>
     </row>
     <row r="7">
@@ -816,17 +816,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2035 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>iShares iBonds Dec 2037 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LU3152892546</t>
+          <t>IE000PWSK6H1</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -840,17 +840,17 @@
         </is>
       </c>
       <c r="F8" s="6" t="n">
-        <v>49582</v>
+        <v>50405</v>
       </c>
       <c r="G8" s="7">
         <f>IF(F8="","",MAX(0,YEARFRAC(TODAY(),F8)))</f>
         <v/>
       </c>
       <c r="H8" s="8" t="n">
-        <v>0.0365</v>
+        <v>0.0349</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>0.0458</v>
+        <v>0.0457</v>
       </c>
       <c r="J8" s="9" t="n">
         <v>0</v>
@@ -873,23 +873,23 @@
         <v/>
       </c>
       <c r="Q8" s="12" t="n">
-        <v>29.13</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2037 Term € Corp UCITS ETF</t>
+          <t>Xtrackers II Target Maturity Sept 2035 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>IE000PWSK6H1</t>
+          <t>LU3152892546</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -903,20 +903,20 @@
         </is>
       </c>
       <c r="F9" s="6" t="n">
-        <v>50405</v>
+        <v>49582</v>
       </c>
       <c r="G9" s="7">
         <f>IF(F9="","",MAX(0,YEARFRAC(TODAY(),F9)))</f>
         <v/>
       </c>
       <c r="H9" s="8" t="n">
-        <v>0.0349</v>
+        <v>0.0365</v>
       </c>
       <c r="I9" s="8" t="n">
         <v>0.0457</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0</v>
+        <v>-0.0001</v>
       </c>
       <c r="K9" s="9" t="n"/>
       <c r="L9" s="9" t="n"/>
@@ -936,7 +936,7 @@
         <v/>
       </c>
       <c r="Q9" s="12" t="n">
-        <v>4.81</v>
+        <v>29.16</v>
       </c>
     </row>
     <row r="10">
@@ -1039,10 +1039,10 @@
         <v>0.0347</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>0.0452</v>
+        <v>0.0451</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0</v>
+        <v>-0.0001</v>
       </c>
       <c r="K11" s="9" t="n"/>
       <c r="L11" s="9" t="n"/>
@@ -1062,7 +1062,7 @@
         <v/>
       </c>
       <c r="Q11" s="12" t="n">
-        <v>33.51</v>
+        <v>33.54</v>
       </c>
     </row>
     <row r="12">
@@ -1125,23 +1125,23 @@
         <v/>
       </c>
       <c r="Q12" s="12" t="n">
-        <v>4.75</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2033 Term € Corp UCITS ETF</t>
+          <t>Xtrackers II Target Maturity Sept 2033 EUR Corporate Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>IE000E0NL9T3</t>
+          <t>LU2673523051</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -1151,24 +1151,24 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>48944</v>
+        <v>48852</v>
       </c>
       <c r="G13" s="7">
         <f>IF(F13="","",MAX(0,YEARFRAC(TODAY(),F13)))</f>
         <v/>
       </c>
       <c r="H13" s="8" t="n">
-        <v>0.0331</v>
+        <v>0.0338</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0.044</v>
+        <v>0.0444</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="K13" s="9" t="n"/>
       <c r="L13" s="9" t="n"/>
@@ -1188,7 +1188,7 @@
         <v/>
       </c>
       <c r="Q13" s="12" t="n">
-        <v>4.77</v>
+        <v>9.31</v>
       </c>
     </row>
     <row r="14">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2033 EUR Corporate Bond UCITS ETF 1C</t>
+          <t>Xtrackers II Target Maturity Sept 2033 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LU2673523051</t>
+          <t>LU2673523564</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F14" s="6" t="n">
@@ -1228,10 +1228,10 @@
         <v>0.0338</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>0.044</v>
+        <v>0.0444</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="K14" s="9" t="n"/>
       <c r="L14" s="9" t="n"/>
@@ -1251,23 +1251,23 @@
         <v/>
       </c>
       <c r="Q14" s="12" t="n">
-        <v>9.31</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2033 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>iShares iBonds Dec 2033 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>LU2673523564</t>
+          <t>IE000E0NL9T3</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -1281,14 +1281,14 @@
         </is>
       </c>
       <c r="F15" s="6" t="n">
-        <v>48852</v>
+        <v>48944</v>
       </c>
       <c r="G15" s="7">
         <f>IF(F15="","",MAX(0,YEARFRAC(TODAY(),F15)))</f>
         <v/>
       </c>
       <c r="H15" s="8" t="n">
-        <v>0.0338</v>
+        <v>0.0331</v>
       </c>
       <c r="I15" s="8" t="n">
         <v>0.044</v>
@@ -1314,7 +1314,7 @@
         <v/>
       </c>
       <c r="Q15" s="12" t="n">
-        <v>27.88</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="16">
@@ -1440,7 +1440,7 @@
         <v/>
       </c>
       <c r="Q17" s="12" t="n">
-        <v>34.27</v>
+        <v>34.28</v>
       </c>
     </row>
     <row r="18">
@@ -1543,10 +1543,10 @@
         <v>0.0169</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>0.0357</v>
+        <v>0.0361</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.0002</v>
+        <v>0.0004</v>
       </c>
       <c r="K19" s="9" t="n"/>
       <c r="L19" s="9" t="n"/>
@@ -1566,7 +1566,7 @@
         <v/>
       </c>
       <c r="Q19" s="12" t="n">
-        <v>9.8248</v>
+        <v>9.834199999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1692,7 +1692,7 @@
         <v/>
       </c>
       <c r="Q21" s="12" t="n">
-        <v>10.4237</v>
+        <v>10.4282</v>
       </c>
     </row>
     <row r="22">
@@ -1755,7 +1755,7 @@
         <v/>
       </c>
       <c r="Q22" s="12" t="n">
-        <v>10.0381</v>
+        <v>10.0424</v>
       </c>
     </row>
     <row r="23">
@@ -1795,10 +1795,10 @@
         <v>0.0287</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>0.04190000000000001</v>
+        <v>0.042</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="K23" s="9" t="n"/>
       <c r="L23" s="9" t="n"/>
@@ -1818,7 +1818,7 @@
         <v/>
       </c>
       <c r="Q23" s="12" t="n">
-        <v>9.779999999999999</v>
+        <v>9.789999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -1858,10 +1858,10 @@
         <v>0.0287</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>0.04190000000000001</v>
+        <v>0.042</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="K24" s="9" t="n"/>
       <c r="L24" s="9" t="n"/>
@@ -1921,10 +1921,10 @@
         <v>0.0208</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>0.0348</v>
+        <v>0.0352</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.0002</v>
+        <v>0.0004</v>
       </c>
       <c r="K25" s="9" t="n"/>
       <c r="L25" s="9" t="n"/>
@@ -1944,7 +1944,7 @@
         <v/>
       </c>
       <c r="Q25" s="12" t="n">
-        <v>9.9818</v>
+        <v>9.9879</v>
       </c>
     </row>
     <row r="26">
@@ -1984,10 +1984,10 @@
         <v>0.0297</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>0.0349</v>
+        <v>0.0351</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="K26" s="9" t="n"/>
       <c r="L26" s="9" t="n"/>
@@ -2007,7 +2007,7 @@
         <v/>
       </c>
       <c r="Q26" s="12" t="n">
-        <v>204.53</v>
+        <v>204.52</v>
       </c>
     </row>
     <row r="27">
@@ -2070,7 +2070,7 @@
         <v/>
       </c>
       <c r="Q27" s="12" t="n">
-        <v>5.35</v>
+        <v>5.3519</v>
       </c>
     </row>
     <row r="28">
@@ -2133,7 +2133,7 @@
         <v/>
       </c>
       <c r="Q28" s="12" t="n">
-        <v>4.9834</v>
+        <v>4.9852</v>
       </c>
     </row>
     <row r="29">
@@ -2236,10 +2236,10 @@
         <v>0.0271</v>
       </c>
       <c r="I30" s="8" t="n">
-        <v>0.0405</v>
+        <v>0.0406</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="K30" s="9" t="n"/>
       <c r="L30" s="9" t="n"/>
@@ -2362,10 +2362,10 @@
         <v>0.0229</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>0.0329</v>
+        <v>0.0332</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.0001</v>
+        <v>0.0003</v>
       </c>
       <c r="K32" s="9" t="n"/>
       <c r="L32" s="9" t="n"/>
@@ -2385,28 +2385,28 @@
         <v/>
       </c>
       <c r="Q32" s="12" t="n">
-        <v>10.2821</v>
+        <v>10.2859</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2029 Term € Corp UCITS ETF</t>
+          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>IE000IHURBR0</t>
+          <t>LU2780871401</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -2415,25 +2415,25 @@
         </is>
       </c>
       <c r="F33" s="6" t="n">
-        <v>47483</v>
+        <v>47118</v>
       </c>
       <c r="G33" s="7">
         <f>IF(F33="","",MAX(0,YEARFRAC(TODAY(),F33)))</f>
         <v/>
       </c>
       <c r="H33" s="8" t="n">
-        <v>0.0252</v>
+        <v>0.0184</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>0.0389</v>
+        <v>0.0329</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0</v>
+        <v>0.0003</v>
       </c>
       <c r="K33" s="9" t="n"/>
       <c r="L33" s="9" t="n"/>
       <c r="M33" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N33" s="10">
         <f>IF(D33="Govt",$B$1,$B$2)</f>
@@ -2448,28 +2448,28 @@
         <v/>
       </c>
       <c r="Q33" s="12" t="n">
-        <v>5.03</v>
+        <v>10.2751</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>IE000P5IB8I8</t>
+          <t>LU2780871310</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -2478,25 +2478,25 @@
         </is>
       </c>
       <c r="F34" s="6" t="n">
-        <v>47483</v>
+        <v>47118</v>
       </c>
       <c r="G34" s="7">
         <f>IF(F34="","",MAX(0,YEARFRAC(TODAY(),F34)))</f>
         <v/>
       </c>
       <c r="H34" s="8" t="n">
-        <v>0.0242</v>
+        <v>0.0184</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>0.0386</v>
+        <v>0.0329</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0</v>
+        <v>0.0003</v>
       </c>
       <c r="K34" s="9" t="n"/>
       <c r="L34" s="9" t="n"/>
       <c r="M34" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0009</v>
       </c>
       <c r="N34" s="10">
         <f>IF(D34="Govt",$B$1,$B$2)</f>
@@ -2511,23 +2511,23 @@
         <v/>
       </c>
       <c r="Q34" s="12" t="n">
-        <v>5.4251</v>
+        <v>10.0745</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>iShares iBonds Dec 2029 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>IE000ZC4C5Q1</t>
+          <t>IE000IHURBR0</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -2548,10 +2548,10 @@
         <v/>
       </c>
       <c r="H35" s="8" t="n">
-        <v>0.0242</v>
+        <v>0.0252</v>
       </c>
       <c r="I35" s="8" t="n">
-        <v>0.0386</v>
+        <v>0.0389</v>
       </c>
       <c r="J35" s="9" t="n">
         <v>0</v>
@@ -2559,7 +2559,7 @@
       <c r="K35" s="9" t="n"/>
       <c r="L35" s="9" t="n"/>
       <c r="M35" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N35" s="10">
         <f>IF(D35="Govt",$B$1,$B$2)</f>
@@ -2574,55 +2574,55 @@
         <v/>
       </c>
       <c r="Q35" s="12" t="n">
-        <v>5.0552</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Dist</t>
+          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>LU2780871401</t>
+          <t>IE000P5IB8I8</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F36" s="6" t="n">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="G36" s="7">
         <f>IF(F36="","",MAX(0,YEARFRAC(TODAY(),F36)))</f>
         <v/>
       </c>
       <c r="H36" s="8" t="n">
-        <v>0.0184</v>
+        <v>0.0242</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>0.0326</v>
+        <v>0.0386</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="K36" s="9" t="n"/>
       <c r="L36" s="9" t="n"/>
       <c r="M36" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="N36" s="10">
         <f>IF(D36="Govt",$B$1,$B$2)</f>
@@ -2637,55 +2637,55 @@
         <v/>
       </c>
       <c r="Q36" s="12" t="n">
-        <v>10.2724</v>
+        <v>5.4261</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>LU2780871310</t>
+          <t>IE000ZC4C5Q1</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F37" s="6" t="n">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="G37" s="7">
         <f>IF(F37="","",MAX(0,YEARFRAC(TODAY(),F37)))</f>
         <v/>
       </c>
       <c r="H37" s="8" t="n">
-        <v>0.0184</v>
+        <v>0.0242</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>0.0326</v>
+        <v>0.0386</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="K37" s="9" t="n"/>
       <c r="L37" s="9" t="n"/>
       <c r="M37" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="N37" s="10">
         <f>IF(D37="Govt",$B$1,$B$2)</f>
@@ -2700,7 +2700,7 @@
         <v/>
       </c>
       <c r="Q37" s="12" t="n">
-        <v>10.0719</v>
+        <v>5.0561</v>
       </c>
     </row>
     <row r="38">
@@ -2740,10 +2740,10 @@
         <v>0.0245</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>0.0386</v>
+        <v>0.0387</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="K38" s="9" t="n"/>
       <c r="L38" s="9" t="n"/>
@@ -2803,10 +2803,10 @@
         <v>0.0245</v>
       </c>
       <c r="I39" s="8" t="n">
-        <v>0.0386</v>
+        <v>0.0387</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="K39" s="9" t="n"/>
       <c r="L39" s="9" t="n"/>
@@ -2866,10 +2866,10 @@
         <v>0.0235</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>0.0382</v>
+        <v>0.0383</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="K40" s="9" t="n"/>
       <c r="L40" s="9" t="n"/>
@@ -2889,7 +2889,7 @@
         <v/>
       </c>
       <c r="Q40" s="12" t="n">
-        <v>10.6604</v>
+        <v>10.6599</v>
       </c>
     </row>
     <row r="41">
@@ -2929,10 +2929,10 @@
         <v>0.0235</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>0.0382</v>
+        <v>0.0383</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="K41" s="9" t="n"/>
       <c r="L41" s="9" t="n"/>
@@ -2952,7 +2952,7 @@
         <v/>
       </c>
       <c r="Q41" s="12" t="n">
-        <v>10.2991</v>
+        <v>10.2986</v>
       </c>
     </row>
     <row r="42">
@@ -3015,7 +3015,7 @@
         <v/>
       </c>
       <c r="Q42" s="12" t="n">
-        <v>5.5691</v>
+        <v>5.5695</v>
       </c>
     </row>
     <row r="43">
@@ -3078,7 +3078,7 @@
         <v/>
       </c>
       <c r="Q43" s="12" t="n">
-        <v>5.2084</v>
+        <v>5.2089</v>
       </c>
     </row>
     <row r="44">
@@ -3181,10 +3181,10 @@
         <v>0.0207</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>0.0369</v>
+        <v>0.0372</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0</v>
+        <v>0.0003</v>
       </c>
       <c r="K45" s="9" t="n"/>
       <c r="L45" s="9" t="n"/>
@@ -3204,7 +3204,7 @@
         <v/>
       </c>
       <c r="Q45" s="12" t="n">
-        <v>35.76</v>
+        <v>35.75</v>
       </c>
     </row>
     <row r="46">
@@ -3247,7 +3247,7 @@
         <v>0.0306</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="K46" s="9" t="n"/>
       <c r="L46" s="9" t="n"/>
@@ -3267,7 +3267,7 @@
         <v/>
       </c>
       <c r="Q46" s="12" t="n">
-        <v>10.3321</v>
+        <v>10.3338</v>
       </c>
     </row>
     <row r="47">
@@ -3310,7 +3310,7 @@
         <v>0.0295</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="K47" s="9" t="n"/>
       <c r="L47" s="9" t="n"/>
@@ -3330,7 +3330,7 @@
         <v/>
       </c>
       <c r="Q47" s="12" t="n">
-        <v>10.1732</v>
+        <v>10.1739</v>
       </c>
     </row>
     <row r="48">
@@ -3373,7 +3373,7 @@
         <v>0.0285</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="K48" s="9" t="n"/>
       <c r="L48" s="9" t="n"/>
@@ -3393,7 +3393,7 @@
         <v/>
       </c>
       <c r="Q48" s="12" t="n">
-        <v>10.3462</v>
+        <v>10.346</v>
       </c>
     </row>
     <row r="49">
@@ -3456,7 +3456,7 @@
         <v/>
       </c>
       <c r="Q49" s="12" t="n">
-        <v>5.7067</v>
+        <v>5.7072</v>
       </c>
     </row>
     <row r="50">
@@ -3519,7 +3519,7 @@
         <v/>
       </c>
       <c r="Q50" s="12" t="n">
-        <v>5.3344</v>
+        <v>5.3349</v>
       </c>
     </row>
     <row r="51">
@@ -3588,49 +3588,49 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2026 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>LU2872291278</t>
+          <t>LU2673523218</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F52" s="6" t="n">
-        <v>46387</v>
+        <v>46660</v>
       </c>
       <c r="G52" s="7">
         <f>IF(F52="","",MAX(0,YEARFRAC(TODAY(),F52)))</f>
         <v/>
       </c>
       <c r="H52" s="8" t="n">
-        <v>0.0023</v>
+        <v>0.0186</v>
       </c>
       <c r="I52" s="8" t="n">
-        <v>0.0272</v>
+        <v>0.0321</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.0008</v>
+        <v>0.0001</v>
       </c>
       <c r="K52" s="9" t="n"/>
       <c r="L52" s="9" t="n"/>
       <c r="M52" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N52" s="10">
         <f>IF(D52="Govt",$B$1,$B$2)</f>
@@ -3645,7 +3645,7 @@
         <v/>
       </c>
       <c r="Q52" s="12" t="n">
-        <v>10.2587</v>
+        <v>25.96</v>
       </c>
     </row>
     <row r="53">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LU2673523218</t>
+          <t>LU2673522830</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F53" s="6" t="n">
@@ -3685,10 +3685,10 @@
         <v>0.0186</v>
       </c>
       <c r="I53" s="8" t="n">
-        <v>0.032</v>
+        <v>0.0321</v>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="K53" s="9" t="n"/>
       <c r="L53" s="9" t="n"/>
@@ -3708,47 +3708,47 @@
         <v/>
       </c>
       <c r="Q53" s="12" t="n">
-        <v>25.96</v>
+        <v>9.31</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1C</t>
+          <t>iShares iBonds Dec 2026 Term € Italy Govt Bond UCITS ETF</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>LU2673522830</t>
+          <t>IE000LZ7BZW8</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F54" s="6" t="n">
-        <v>46660</v>
+        <v>46387</v>
       </c>
       <c r="G54" s="7">
         <f>IF(F54="","",MAX(0,YEARFRAC(TODAY(),F54)))</f>
         <v/>
       </c>
       <c r="H54" s="8" t="n">
-        <v>0.0186</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="I54" s="8" t="n">
-        <v>0.032</v>
+        <v>0.0269</v>
       </c>
       <c r="J54" s="9" t="n">
         <v>0</v>
@@ -3771,23 +3771,23 @@
         <v/>
       </c>
       <c r="Q54" s="12" t="n">
-        <v>9.31</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2026 Term € Italy Govt Bond UCITS ETF</t>
+          <t>Amundi Fixed Maturity 2026 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>IE000LZ7BZW8</t>
+          <t>LU2872291278</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F55" s="6" t="n">
@@ -3808,18 +3808,18 @@
         <v/>
       </c>
       <c r="H55" s="8" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0023</v>
       </c>
       <c r="I55" s="8" t="n">
-        <v>0.0269</v>
+        <v>0.0257</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0</v>
+        <v>-0.0015</v>
       </c>
       <c r="K55" s="9" t="n"/>
       <c r="L55" s="9" t="n"/>
       <c r="M55" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N55" s="10">
         <f>IF(D55="Govt",$B$1,$B$2)</f>
@@ -3834,7 +3834,7 @@
         <v/>
       </c>
       <c r="Q55" s="12" t="n">
-        <v>5.06</v>
+        <v>10.2594</v>
       </c>
     </row>
     <row r="56">
@@ -3897,7 +3897,7 @@
         <v/>
       </c>
       <c r="Q56" s="12" t="n">
-        <v>5.7924</v>
+        <v>5.7929</v>
       </c>
     </row>
     <row r="57">
@@ -3960,7 +3960,7 @@
         <v/>
       </c>
       <c r="Q57" s="12" t="n">
-        <v>5.4161</v>
+        <v>5.4166</v>
       </c>
     </row>
     <row r="58">

--- a/data/rendimenti_etf.xlsx
+++ b/data/rendimenti_etf.xlsx
@@ -533,7 +533,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Aggiornato il 14/10/2026 09:06 da yield_etf.csv</t>
+          <t>Aggiornato il 15/10/2026 09:03 da yield_etf.csv</t>
         </is>
       </c>
     </row>
@@ -661,10 +661,10 @@
         <v>0.039</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>0.0501</v>
+        <v>0.0505</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="K5" s="9" t="n"/>
       <c r="L5" s="9" t="n"/>
@@ -724,10 +724,10 @@
         <v>0.03759999999999999</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0.0461</v>
+        <v>0.0459</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>-0.0001</v>
+        <v>-0.0002</v>
       </c>
       <c r="K6" s="9" t="n"/>
       <c r="L6" s="9" t="n"/>
@@ -747,23 +747,23 @@
         <v/>
       </c>
       <c r="Q6" s="12" t="n">
-        <v>28.35</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2036 Term € Corp UCITS ETF</t>
+          <t>Xtrackers II Target Maturity Sept 2035 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>IE000RQJBQI6</t>
+          <t>LU3152892546</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -777,20 +777,20 @@
         </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>50040</v>
+        <v>49582</v>
       </c>
       <c r="G7" s="7">
         <f>IF(F7="","",MAX(0,YEARFRAC(TODAY(),F7)))</f>
         <v/>
       </c>
       <c r="H7" s="8" t="n">
-        <v>0.0355</v>
+        <v>0.0365</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0.0459</v>
+        <v>0.04559999999999999</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0</v>
+        <v>-0.0001</v>
       </c>
       <c r="K7" s="9" t="n"/>
       <c r="L7" s="9" t="n"/>
@@ -810,7 +810,7 @@
         <v/>
       </c>
       <c r="Q7" s="12" t="n">
-        <v>4.82</v>
+        <v>29.19</v>
       </c>
     </row>
     <row r="8">
@@ -821,12 +821,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2037 Term € Corp UCITS ETF</t>
+          <t>iShares iBonds Dec 2036 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>IE000PWSK6H1</t>
+          <t>IE000RQJBQI6</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -840,20 +840,20 @@
         </is>
       </c>
       <c r="F8" s="6" t="n">
-        <v>50405</v>
+        <v>50040</v>
       </c>
       <c r="G8" s="7">
         <f>IF(F8="","",MAX(0,YEARFRAC(TODAY(),F8)))</f>
         <v/>
       </c>
       <c r="H8" s="8" t="n">
-        <v>0.0349</v>
+        <v>0.0355</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>0.0457</v>
+        <v>0.0455</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0</v>
+        <v>-0.0004</v>
       </c>
       <c r="K8" s="9" t="n"/>
       <c r="L8" s="9" t="n"/>
@@ -879,17 +879,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2035 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>iShares iBonds Dec 2037 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LU3152892546</t>
+          <t>IE000PWSK6H1</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -903,20 +903,20 @@
         </is>
       </c>
       <c r="F9" s="6" t="n">
-        <v>49582</v>
+        <v>50405</v>
       </c>
       <c r="G9" s="7">
         <f>IF(F9="","",MAX(0,YEARFRAC(TODAY(),F9)))</f>
         <v/>
       </c>
       <c r="H9" s="8" t="n">
-        <v>0.0365</v>
+        <v>0.0349</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>0.0457</v>
+        <v>0.0454</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>-0.0001</v>
+        <v>-0.0003</v>
       </c>
       <c r="K9" s="9" t="n"/>
       <c r="L9" s="9" t="n"/>
@@ -936,7 +936,7 @@
         <v/>
       </c>
       <c r="Q9" s="12" t="n">
-        <v>29.16</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="10">
@@ -973,13 +973,13 @@
         <v/>
       </c>
       <c r="H10" s="8" t="n">
-        <v>0.0367</v>
+        <v>0.0363</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>0.0455</v>
+        <v>0.0452</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0</v>
+        <v>-0.0003</v>
       </c>
       <c r="K10" s="9" t="n"/>
       <c r="L10" s="9" t="n"/>
@@ -1039,10 +1039,10 @@
         <v>0.0347</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>0.0451</v>
+        <v>0.0449</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>-0.0001</v>
+        <v>-0.0002</v>
       </c>
       <c r="K11" s="9" t="n"/>
       <c r="L11" s="9" t="n"/>
@@ -1062,7 +1062,7 @@
         <v/>
       </c>
       <c r="Q11" s="12" t="n">
-        <v>33.54</v>
+        <v>33.58</v>
       </c>
     </row>
     <row r="12">
@@ -1102,10 +1102,10 @@
         <v>0.0346</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>0.0447</v>
+        <v>0.0445</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0</v>
+        <v>-0.0002</v>
       </c>
       <c r="K12" s="9" t="n"/>
       <c r="L12" s="9" t="n"/>
@@ -1165,10 +1165,10 @@
         <v>0.0338</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0.0444</v>
+        <v>0.0443</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.0004</v>
+        <v>-0.0001</v>
       </c>
       <c r="K13" s="9" t="n"/>
       <c r="L13" s="9" t="n"/>
@@ -1188,7 +1188,7 @@
         <v/>
       </c>
       <c r="Q13" s="12" t="n">
-        <v>9.31</v>
+        <v>9.32</v>
       </c>
     </row>
     <row r="14">
@@ -1228,10 +1228,10 @@
         <v>0.0338</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>0.0444</v>
+        <v>0.0443</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.0004</v>
+        <v>-0.0001</v>
       </c>
       <c r="K14" s="9" t="n"/>
       <c r="L14" s="9" t="n"/>
@@ -1251,7 +1251,7 @@
         <v/>
       </c>
       <c r="Q14" s="12" t="n">
-        <v>27.9</v>
+        <v>27.92</v>
       </c>
     </row>
     <row r="15">
@@ -1291,10 +1291,10 @@
         <v>0.0331</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>0.044</v>
+        <v>0.0438</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0</v>
+        <v>-0.0002</v>
       </c>
       <c r="K15" s="9" t="n"/>
       <c r="L15" s="9" t="n"/>
@@ -1320,17 +1320,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2028 Term € Corp Crossover UCITS ETF</t>
+          <t>Xtrackers II Target Maturity Sept 2032 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>IE0003HV7CS6</t>
+          <t>LU2809864452</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -1340,29 +1340,29 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>47118</v>
+        <v>48487</v>
       </c>
       <c r="G16" s="7">
         <f>IF(F16="","",MAX(0,YEARFRAC(TODAY(),F16)))</f>
         <v/>
       </c>
       <c r="H16" s="8" t="n">
-        <v>0.0334</v>
+        <v>0.0282</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>0.0444</v>
+        <v>0.0434</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0</v>
+        <v>-0.0001</v>
       </c>
       <c r="K16" s="9" t="n"/>
       <c r="L16" s="9" t="n"/>
       <c r="M16" s="8" t="n">
-        <v>0.002</v>
+        <v>0.0012</v>
       </c>
       <c r="N16" s="10">
         <f>IF(D16="Govt",$B$1,$B$2)</f>
@@ -1377,23 +1377,23 @@
         <v/>
       </c>
       <c r="Q16" s="12" t="n">
-        <v>5.1</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2032 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>iShares iBonds Dec 2028 Term € Corp Crossover UCITS ETF</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LU2809864452</t>
+          <t>IE0003HV7CS6</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -1403,29 +1403,29 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
-        <v>48487</v>
+        <v>47118</v>
       </c>
       <c r="G17" s="7">
         <f>IF(F17="","",MAX(0,YEARFRAC(TODAY(),F17)))</f>
         <v/>
       </c>
       <c r="H17" s="8" t="n">
-        <v>0.0282</v>
+        <v>0.033</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>0.0435</v>
+        <v>0.0441</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0</v>
+        <v>-0.0003</v>
       </c>
       <c r="K17" s="9" t="n"/>
       <c r="L17" s="9" t="n"/>
       <c r="M17" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.002</v>
       </c>
       <c r="N17" s="10">
         <f>IF(D17="Govt",$B$1,$B$2)</f>
@@ -1440,7 +1440,7 @@
         <v/>
       </c>
       <c r="Q17" s="12" t="n">
-        <v>34.28</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="18">
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="H18" s="8" t="n">
-        <v>0.0301</v>
+        <v>0.03</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>0.0429</v>
+        <v>0.0428</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0</v>
+        <v>-0.0001</v>
       </c>
       <c r="K18" s="9" t="n"/>
       <c r="L18" s="9" t="n"/>
@@ -1503,7 +1503,7 @@
         <v/>
       </c>
       <c r="Q18" s="12" t="n">
-        <v>4.82</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="19">
@@ -1543,10 +1543,10 @@
         <v>0.0169</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>0.0361</v>
+        <v>0.036</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.0004</v>
+        <v>-0.0001</v>
       </c>
       <c r="K19" s="9" t="n"/>
       <c r="L19" s="9" t="n"/>
@@ -1566,7 +1566,7 @@
         <v/>
       </c>
       <c r="Q19" s="12" t="n">
-        <v>9.834199999999999</v>
+        <v>9.8316</v>
       </c>
     </row>
     <row r="20">
@@ -1606,10 +1606,10 @@
         <v>0.0285</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>0.04219999999999999</v>
+        <v>0.0421</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0</v>
+        <v>-0.0001</v>
       </c>
       <c r="K20" s="9" t="n"/>
       <c r="L20" s="9" t="n"/>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="Q20" s="12" t="n">
-        <v>4.87</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="21">
@@ -1692,7 +1692,7 @@
         <v/>
       </c>
       <c r="Q21" s="12" t="n">
-        <v>10.4282</v>
+        <v>10.4344</v>
       </c>
     </row>
     <row r="22">
@@ -1755,7 +1755,7 @@
         <v/>
       </c>
       <c r="Q22" s="12" t="n">
-        <v>10.0424</v>
+        <v>10.0484</v>
       </c>
     </row>
     <row r="23">
@@ -1795,10 +1795,10 @@
         <v>0.0287</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>0.042</v>
+        <v>0.04190000000000001</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.0001</v>
+        <v>-0.0001</v>
       </c>
       <c r="K23" s="9" t="n"/>
       <c r="L23" s="9" t="n"/>
@@ -1858,10 +1858,10 @@
         <v>0.0287</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>0.042</v>
+        <v>0.04190000000000001</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.0001</v>
+        <v>-0.0001</v>
       </c>
       <c r="K24" s="9" t="n"/>
       <c r="L24" s="9" t="n"/>
@@ -1881,7 +1881,7 @@
         <v/>
       </c>
       <c r="Q24" s="12" t="n">
-        <v>29.28</v>
+        <v>29.3</v>
       </c>
     </row>
     <row r="25">
@@ -1921,10 +1921,10 @@
         <v>0.0208</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>0.0352</v>
+        <v>0.0351</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.0004</v>
+        <v>-0.0001</v>
       </c>
       <c r="K25" s="9" t="n"/>
       <c r="L25" s="9" t="n"/>
@@ -1944,7 +1944,7 @@
         <v/>
       </c>
       <c r="Q25" s="12" t="n">
-        <v>9.9879</v>
+        <v>9.9885</v>
       </c>
     </row>
     <row r="26">
@@ -1984,10 +1984,10 @@
         <v>0.0297</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>0.0351</v>
+        <v>0.0349</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.0002</v>
+        <v>-0.0002</v>
       </c>
       <c r="K26" s="9" t="n"/>
       <c r="L26" s="9" t="n"/>
@@ -2007,7 +2007,7 @@
         <v/>
       </c>
       <c r="Q26" s="12" t="n">
-        <v>204.52</v>
+        <v>204.56</v>
       </c>
     </row>
     <row r="27">
@@ -2070,7 +2070,7 @@
         <v/>
       </c>
       <c r="Q27" s="12" t="n">
-        <v>5.3519</v>
+        <v>5.3558</v>
       </c>
     </row>
     <row r="28">
@@ -2133,7 +2133,7 @@
         <v/>
       </c>
       <c r="Q28" s="12" t="n">
-        <v>4.9852</v>
+        <v>4.9888</v>
       </c>
     </row>
     <row r="29">
@@ -2170,7 +2170,7 @@
         <v/>
       </c>
       <c r="H29" s="8" t="n">
-        <v>0.028</v>
+        <v>0.0282</v>
       </c>
       <c r="I29" s="8" t="n">
         <v>0.0406</v>
@@ -2233,13 +2233,13 @@
         <v/>
       </c>
       <c r="H30" s="8" t="n">
-        <v>0.0271</v>
+        <v>0.027</v>
       </c>
       <c r="I30" s="8" t="n">
-        <v>0.0406</v>
+        <v>0.0405</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.0001</v>
+        <v>-0.0001</v>
       </c>
       <c r="K30" s="9" t="n"/>
       <c r="L30" s="9" t="n"/>
@@ -2259,7 +2259,7 @@
         <v/>
       </c>
       <c r="Q30" s="12" t="n">
-        <v>35.23</v>
+        <v>35.25</v>
       </c>
     </row>
     <row r="31">
@@ -2299,10 +2299,10 @@
         <v>0.026</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>0.034</v>
+        <v>0.0341</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="K31" s="9" t="n"/>
       <c r="L31" s="9" t="n"/>
@@ -2365,7 +2365,7 @@
         <v>0.0332</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.0003</v>
+        <v>0</v>
       </c>
       <c r="K32" s="9" t="n"/>
       <c r="L32" s="9" t="n"/>
@@ -2385,7 +2385,7 @@
         <v/>
       </c>
       <c r="Q32" s="12" t="n">
-        <v>10.2859</v>
+        <v>10.2862</v>
       </c>
     </row>
     <row r="33">
@@ -2428,7 +2428,7 @@
         <v>0.0329</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.0003</v>
+        <v>0</v>
       </c>
       <c r="K33" s="9" t="n"/>
       <c r="L33" s="9" t="n"/>
@@ -2448,7 +2448,7 @@
         <v/>
       </c>
       <c r="Q33" s="12" t="n">
-        <v>10.2751</v>
+        <v>10.2781</v>
       </c>
     </row>
     <row r="34">
@@ -2491,7 +2491,7 @@
         <v>0.0329</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.0003</v>
+        <v>0</v>
       </c>
       <c r="K34" s="9" t="n"/>
       <c r="L34" s="9" t="n"/>
@@ -2511,7 +2511,7 @@
         <v/>
       </c>
       <c r="Q34" s="12" t="n">
-        <v>10.0745</v>
+        <v>10.0774</v>
       </c>
     </row>
     <row r="35">
@@ -2551,10 +2551,10 @@
         <v>0.0252</v>
       </c>
       <c r="I35" s="8" t="n">
-        <v>0.0389</v>
+        <v>0.039</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="K35" s="9" t="n"/>
       <c r="L35" s="9" t="n"/>
@@ -2637,7 +2637,7 @@
         <v/>
       </c>
       <c r="Q36" s="12" t="n">
-        <v>5.4261</v>
+        <v>5.4295</v>
       </c>
     </row>
     <row r="37">
@@ -2700,7 +2700,7 @@
         <v/>
       </c>
       <c r="Q37" s="12" t="n">
-        <v>5.0561</v>
+        <v>5.0593</v>
       </c>
     </row>
     <row r="38">
@@ -2743,7 +2743,7 @@
         <v>0.0387</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="K38" s="9" t="n"/>
       <c r="L38" s="9" t="n"/>
@@ -2806,7 +2806,7 @@
         <v>0.0387</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="K39" s="9" t="n"/>
       <c r="L39" s="9" t="n"/>
@@ -2866,7 +2866,7 @@
         <v>0.0235</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>0.0383</v>
+        <v>0.0384</v>
       </c>
       <c r="J40" s="9" t="n">
         <v>0.0001</v>
@@ -2889,7 +2889,7 @@
         <v/>
       </c>
       <c r="Q40" s="12" t="n">
-        <v>10.6599</v>
+        <v>10.6623</v>
       </c>
     </row>
     <row r="41">
@@ -2929,7 +2929,7 @@
         <v>0.0235</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>0.0383</v>
+        <v>0.0384</v>
       </c>
       <c r="J41" s="9" t="n">
         <v>0.0001</v>
@@ -2952,7 +2952,7 @@
         <v/>
       </c>
       <c r="Q41" s="12" t="n">
-        <v>10.2986</v>
+        <v>10.3009</v>
       </c>
     </row>
     <row r="42">
@@ -3015,7 +3015,7 @@
         <v/>
       </c>
       <c r="Q42" s="12" t="n">
-        <v>5.5695</v>
+        <v>5.5712</v>
       </c>
     </row>
     <row r="43">
@@ -3078,7 +3078,7 @@
         <v/>
       </c>
       <c r="Q43" s="12" t="n">
-        <v>5.2089</v>
+        <v>5.2104</v>
       </c>
     </row>
     <row r="44">
@@ -3118,10 +3118,10 @@
         <v>0.0213</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>0.0373</v>
+        <v>0.0375</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="K44" s="9" t="n"/>
       <c r="L44" s="9" t="n"/>
@@ -3184,7 +3184,7 @@
         <v>0.0372</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.0003</v>
+        <v>0</v>
       </c>
       <c r="K45" s="9" t="n"/>
       <c r="L45" s="9" t="n"/>
@@ -3204,7 +3204,7 @@
         <v/>
       </c>
       <c r="Q45" s="12" t="n">
-        <v>35.75</v>
+        <v>35.76</v>
       </c>
     </row>
     <row r="46">
@@ -3244,10 +3244,10 @@
         <v>0.0265</v>
       </c>
       <c r="I46" s="8" t="n">
-        <v>0.0306</v>
+        <v>0.0308</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="K46" s="9" t="n"/>
       <c r="L46" s="9" t="n"/>
@@ -3267,7 +3267,7 @@
         <v/>
       </c>
       <c r="Q46" s="12" t="n">
-        <v>10.3338</v>
+        <v>10.3351</v>
       </c>
     </row>
     <row r="47">
@@ -3307,10 +3307,10 @@
         <v>0.015</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>0.0295</v>
+        <v>0.0296</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="K47" s="9" t="n"/>
       <c r="L47" s="9" t="n"/>
@@ -3330,7 +3330,7 @@
         <v/>
       </c>
       <c r="Q47" s="12" t="n">
-        <v>10.1739</v>
+        <v>10.1754</v>
       </c>
     </row>
     <row r="48">
@@ -3370,10 +3370,10 @@
         <v>0.0105</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>0.0285</v>
+        <v>0.0284</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0</v>
+        <v>-0.0001</v>
       </c>
       <c r="K48" s="9" t="n"/>
       <c r="L48" s="9" t="n"/>
@@ -3393,7 +3393,7 @@
         <v/>
       </c>
       <c r="Q48" s="12" t="n">
-        <v>10.346</v>
+        <v>10.3481</v>
       </c>
     </row>
     <row r="49">
@@ -3456,7 +3456,7 @@
         <v/>
       </c>
       <c r="Q49" s="12" t="n">
-        <v>5.7072</v>
+        <v>5.7079</v>
       </c>
     </row>
     <row r="50">
@@ -3519,7 +3519,7 @@
         <v/>
       </c>
       <c r="Q50" s="12" t="n">
-        <v>5.3349</v>
+        <v>5.3356</v>
       </c>
     </row>
     <row r="51">
@@ -3559,10 +3559,10 @@
         <v>0.0195</v>
       </c>
       <c r="I51" s="8" t="n">
-        <v>0.0333</v>
+        <v>0.0335</v>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="K51" s="9" t="n"/>
       <c r="L51" s="9" t="n"/>
@@ -3622,10 +3622,10 @@
         <v>0.0186</v>
       </c>
       <c r="I52" s="8" t="n">
-        <v>0.0321</v>
+        <v>0.032</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.0001</v>
+        <v>-0.0001</v>
       </c>
       <c r="K52" s="9" t="n"/>
       <c r="L52" s="9" t="n"/>
@@ -3685,10 +3685,10 @@
         <v>0.0186</v>
       </c>
       <c r="I53" s="8" t="n">
-        <v>0.0321</v>
+        <v>0.032</v>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.0001</v>
+        <v>-0.0001</v>
       </c>
       <c r="K53" s="9" t="n"/>
       <c r="L53" s="9" t="n"/>
@@ -3814,7 +3814,7 @@
         <v>0.0257</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>-0.0015</v>
+        <v>0</v>
       </c>
       <c r="K55" s="9" t="n"/>
       <c r="L55" s="9" t="n"/>
@@ -3834,7 +3834,7 @@
         <v/>
       </c>
       <c r="Q55" s="12" t="n">
-        <v>10.2594</v>
+        <v>10.2601</v>
       </c>
     </row>
     <row r="56">
@@ -3897,7 +3897,7 @@
         <v/>
       </c>
       <c r="Q56" s="12" t="n">
-        <v>5.7929</v>
+        <v>5.7933</v>
       </c>
     </row>
     <row r="57">
@@ -3960,7 +3960,7 @@
         <v/>
       </c>
       <c r="Q57" s="12" t="n">
-        <v>5.4166</v>
+        <v>5.4169</v>
       </c>
     </row>
     <row r="58">
@@ -4000,10 +4000,10 @@
         <v>0.0059</v>
       </c>
       <c r="I58" s="8" t="n">
-        <v>0.0273</v>
+        <v>0.0276</v>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0</v>
+        <v>0.0003</v>
       </c>
       <c r="K58" s="9" t="n"/>
       <c r="L58" s="9" t="n"/>

--- a/data/rendimenti_etf.xlsx
+++ b/data/rendimenti_etf.xlsx
@@ -533,7 +533,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Aggiornato il 15/10/2026 09:03 da yield_etf.csv</t>
+          <t>Aggiornato il 16/10/2026 09:02 da yield_etf.csv</t>
         </is>
       </c>
     </row>
@@ -658,13 +658,13 @@
         <v/>
       </c>
       <c r="H5" s="8" t="n">
-        <v>0.039</v>
+        <v>0.0389</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>0.0505</v>
+        <v>0.05019999999999999</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.0004</v>
+        <v>-0.0003</v>
       </c>
       <c r="K5" s="9" t="n"/>
       <c r="L5" s="9" t="n"/>
@@ -727,7 +727,7 @@
         <v>0.0459</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0</v>
       </c>
       <c r="K6" s="9" t="n"/>
       <c r="L6" s="9" t="n"/>
@@ -747,7 +747,7 @@
         <v/>
       </c>
       <c r="Q6" s="12" t="n">
-        <v>28.39</v>
+        <v>28.38</v>
       </c>
     </row>
     <row r="7">
@@ -790,7 +790,7 @@
         <v>0.04559999999999999</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0</v>
       </c>
       <c r="K7" s="9" t="n"/>
       <c r="L7" s="9" t="n"/>
@@ -853,7 +853,7 @@
         <v>0.0455</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>-0.0004</v>
+        <v>0</v>
       </c>
       <c r="K8" s="9" t="n"/>
       <c r="L8" s="9" t="n"/>
@@ -873,7 +873,7 @@
         <v/>
       </c>
       <c r="Q8" s="12" t="n">
-        <v>4.82</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="9">
@@ -916,7 +916,7 @@
         <v>0.0454</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0</v>
       </c>
       <c r="K9" s="9" t="n"/>
       <c r="L9" s="9" t="n"/>
@@ -936,7 +936,7 @@
         <v/>
       </c>
       <c r="Q9" s="12" t="n">
-        <v>4.82</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="10">
@@ -979,7 +979,7 @@
         <v>0.0452</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0</v>
       </c>
       <c r="K10" s="9" t="n"/>
       <c r="L10" s="9" t="n"/>
@@ -999,7 +999,7 @@
         <v/>
       </c>
       <c r="Q10" s="12" t="n">
-        <v>4.73</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="11">
@@ -1042,7 +1042,7 @@
         <v>0.0449</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0</v>
       </c>
       <c r="K11" s="9" t="n"/>
       <c r="L11" s="9" t="n"/>
@@ -1062,7 +1062,7 @@
         <v/>
       </c>
       <c r="Q11" s="12" t="n">
-        <v>33.58</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="12">
@@ -1102,10 +1102,10 @@
         <v>0.0346</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>0.0445</v>
+        <v>0.0444</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>-0.0002</v>
+        <v>-0.0001</v>
       </c>
       <c r="K12" s="9" t="n"/>
       <c r="L12" s="9" t="n"/>
@@ -1125,7 +1125,7 @@
         <v/>
       </c>
       <c r="Q12" s="12" t="n">
-        <v>4.76</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="13">
@@ -1165,7 +1165,7 @@
         <v>0.0338</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0.0443</v>
+        <v>0.0442</v>
       </c>
       <c r="J13" s="9" t="n">
         <v>-0.0001</v>
@@ -1228,7 +1228,7 @@
         <v>0.0338</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>0.0443</v>
+        <v>0.0442</v>
       </c>
       <c r="J14" s="9" t="n">
         <v>-0.0001</v>
@@ -1251,7 +1251,7 @@
         <v/>
       </c>
       <c r="Q14" s="12" t="n">
-        <v>27.92</v>
+        <v>27.93</v>
       </c>
     </row>
     <row r="15">
@@ -1294,7 +1294,7 @@
         <v>0.0438</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0</v>
       </c>
       <c r="K15" s="9" t="n"/>
       <c r="L15" s="9" t="n"/>
@@ -1314,23 +1314,23 @@
         <v/>
       </c>
       <c r="Q15" s="12" t="n">
-        <v>4.78</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2032 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>iShares iBonds Dec 2028 Term € Corp Crossover UCITS ETF</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LU2809864452</t>
+          <t>IE0003HV7CS6</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -1340,29 +1340,29 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>48487</v>
+        <v>47118</v>
       </c>
       <c r="G16" s="7">
         <f>IF(F16="","",MAX(0,YEARFRAC(TODAY(),F16)))</f>
         <v/>
       </c>
       <c r="H16" s="8" t="n">
-        <v>0.0282</v>
+        <v>0.033</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>0.0434</v>
+        <v>0.0441</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0</v>
       </c>
       <c r="K16" s="9" t="n"/>
       <c r="L16" s="9" t="n"/>
       <c r="M16" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.002</v>
       </c>
       <c r="N16" s="10">
         <f>IF(D16="Govt",$B$1,$B$2)</f>
@@ -1377,23 +1377,23 @@
         <v/>
       </c>
       <c r="Q16" s="12" t="n">
-        <v>34.3</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2028 Term € Corp Crossover UCITS ETF</t>
+          <t>Xtrackers II Target Maturity Sept 2032 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>IE0003HV7CS6</t>
+          <t>LU2809864452</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -1403,29 +1403,29 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
-        <v>47118</v>
+        <v>48487</v>
       </c>
       <c r="G17" s="7">
         <f>IF(F17="","",MAX(0,YEARFRAC(TODAY(),F17)))</f>
         <v/>
       </c>
       <c r="H17" s="8" t="n">
-        <v>0.033</v>
+        <v>0.0282</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>0.0441</v>
+        <v>0.0433</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>-0.0003</v>
+        <v>-0.0001</v>
       </c>
       <c r="K17" s="9" t="n"/>
       <c r="L17" s="9" t="n"/>
       <c r="M17" s="8" t="n">
-        <v>0.002</v>
+        <v>0.0012</v>
       </c>
       <c r="N17" s="10">
         <f>IF(D17="Govt",$B$1,$B$2)</f>
@@ -1440,55 +1440,55 @@
         <v/>
       </c>
       <c r="Q17" s="12" t="n">
-        <v>5.1</v>
+        <v>34.32</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2032 Term € Corp UCITS ETF</t>
+          <t>Amundi Fixed Maturity 2030 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>IE0000MR4GH9</t>
+          <t>LU3120976132</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>48579</v>
+        <v>47848</v>
       </c>
       <c r="G18" s="7">
         <f>IF(F18="","",MAX(0,YEARFRAC(TODAY(),F18)))</f>
         <v/>
       </c>
       <c r="H18" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0169</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>0.0428</v>
+        <v>0.0362</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="K18" s="9" t="n"/>
       <c r="L18" s="9" t="n"/>
       <c r="M18" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N18" s="10">
         <f>IF(D18="Govt",$B$1,$B$2)</f>
@@ -1503,47 +1503,47 @@
         <v/>
       </c>
       <c r="Q18" s="12" t="n">
-        <v>4.83</v>
+        <v>9.8558</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2030 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>iShares iBonds Dec 2032 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LU3120976132</t>
+          <t>IE0000MR4GH9</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>47848</v>
+        <v>48579</v>
       </c>
       <c r="G19" s="7">
         <f>IF(F19="","",MAX(0,YEARFRAC(TODAY(),F19)))</f>
         <v/>
       </c>
       <c r="H19" s="8" t="n">
-        <v>0.0169</v>
+        <v>0.03</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>0.036</v>
+        <v>0.04269999999999999</v>
       </c>
       <c r="J19" s="9" t="n">
         <v>-0.0001</v>
@@ -1551,7 +1551,7 @@
       <c r="K19" s="9" t="n"/>
       <c r="L19" s="9" t="n"/>
       <c r="M19" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N19" s="10">
         <f>IF(D19="Govt",$B$1,$B$2)</f>
@@ -1566,7 +1566,7 @@
         <v/>
       </c>
       <c r="Q19" s="12" t="n">
-        <v>9.8316</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="20">
@@ -1603,13 +1603,13 @@
         <v/>
       </c>
       <c r="H20" s="8" t="n">
-        <v>0.0285</v>
+        <v>0.0286</v>
       </c>
       <c r="I20" s="8" t="n">
         <v>0.0421</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0</v>
       </c>
       <c r="K20" s="9" t="n"/>
       <c r="L20" s="9" t="n"/>
@@ -1629,28 +1629,28 @@
         <v/>
       </c>
       <c r="Q20" s="12" t="n">
-        <v>4.88</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BNP Paribas</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2032 UCITS ETF C</t>
+          <t>Amundi Fixed Maturity 2029 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>LU2823895847</t>
+          <t>LU2872291781</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -1659,25 +1659,25 @@
         </is>
       </c>
       <c r="F21" s="6" t="n">
-        <v>48579</v>
+        <v>47483</v>
       </c>
       <c r="G21" s="7">
         <f>IF(F21="","",MAX(0,YEARFRAC(TODAY(),F21)))</f>
         <v/>
       </c>
       <c r="H21" s="8" t="n">
-        <v>0.0269</v>
+        <v>0.0208</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>0.0421</v>
+        <v>0.0353</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="K21" s="9" t="n"/>
       <c r="L21" s="9" t="n"/>
       <c r="M21" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N21" s="10">
         <f>IF(D21="Govt",$B$1,$B$2)</f>
@@ -1692,23 +1692,23 @@
         <v/>
       </c>
       <c r="Q21" s="12" t="n">
-        <v>10.4344</v>
+        <v>10.0057</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BNP Paribas</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2032 UCITS ETF D</t>
+          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>LU2823895763</t>
+          <t>LU2673523135</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1718,24 +1718,24 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>48579</v>
+        <v>48121</v>
       </c>
       <c r="G22" s="7">
         <f>IF(F22="","",MAX(0,YEARFRAC(TODAY(),F22)))</f>
         <v/>
       </c>
       <c r="H22" s="8" t="n">
-        <v>0.0269</v>
+        <v>0.0287</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>0.0421</v>
+        <v>0.0417</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0</v>
+        <v>-0.0002</v>
       </c>
       <c r="K22" s="9" t="n"/>
       <c r="L22" s="9" t="n"/>
@@ -1755,7 +1755,7 @@
         <v/>
       </c>
       <c r="Q22" s="12" t="n">
-        <v>10.0484</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1C</t>
+          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>LU2673523135</t>
+          <t>LU2673523481</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F23" s="6" t="n">
@@ -1795,10 +1795,10 @@
         <v>0.0287</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>0.04190000000000001</v>
+        <v>0.0417</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>-0.0001</v>
+        <v>-0.0002</v>
       </c>
       <c r="K23" s="9" t="n"/>
       <c r="L23" s="9" t="n"/>
@@ -1818,23 +1818,23 @@
         <v/>
       </c>
       <c r="Q23" s="12" t="n">
-        <v>9.789999999999999</v>
+        <v>29.32</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>BNP Paribas</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2032 UCITS ETF C</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>LU2673523481</t>
+          <t>LU2823895847</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -1844,24 +1844,24 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>48121</v>
+        <v>48579</v>
       </c>
       <c r="G24" s="7">
         <f>IF(F24="","",MAX(0,YEARFRAC(TODAY(),F24)))</f>
         <v/>
       </c>
       <c r="H24" s="8" t="n">
-        <v>0.0287</v>
+        <v>0.0269</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>0.04190000000000001</v>
+        <v>0.0417</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>-0.0001</v>
+        <v>-0.0004</v>
       </c>
       <c r="K24" s="9" t="n"/>
       <c r="L24" s="9" t="n"/>
@@ -1881,55 +1881,55 @@
         <v/>
       </c>
       <c r="Q24" s="12" t="n">
-        <v>29.3</v>
+        <v>10.4426</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>BNP Paribas</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2029 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2032 UCITS ETF D</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>LU2872291781</t>
+          <t>LU2823895763</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F25" s="6" t="n">
-        <v>47483</v>
+        <v>48579</v>
       </c>
       <c r="G25" s="7">
         <f>IF(F25="","",MAX(0,YEARFRAC(TODAY(),F25)))</f>
         <v/>
       </c>
       <c r="H25" s="8" t="n">
-        <v>0.0208</v>
+        <v>0.0269</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>0.0351</v>
+        <v>0.0417</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>-0.0001</v>
+        <v>-0.0004</v>
       </c>
       <c r="K25" s="9" t="n"/>
       <c r="L25" s="9" t="n"/>
       <c r="M25" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N25" s="10">
         <f>IF(D25="Govt",$B$1,$B$2)</f>
@@ -1944,7 +1944,7 @@
         <v/>
       </c>
       <c r="Q25" s="12" t="n">
-        <v>9.9885</v>
+        <v>10.0562</v>
       </c>
     </row>
     <row r="26">
@@ -1984,10 +1984,10 @@
         <v>0.0297</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>0.0349</v>
+        <v>0.0351</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0002</v>
       </c>
       <c r="K26" s="9" t="n"/>
       <c r="L26" s="9" t="n"/>
@@ -2007,7 +2007,7 @@
         <v/>
       </c>
       <c r="Q26" s="12" t="n">
-        <v>204.56</v>
+        <v>204.55</v>
       </c>
     </row>
     <row r="27">
@@ -2070,7 +2070,7 @@
         <v/>
       </c>
       <c r="Q27" s="12" t="n">
-        <v>5.3558</v>
+        <v>5.3639</v>
       </c>
     </row>
     <row r="28">
@@ -2133,7 +2133,7 @@
         <v/>
       </c>
       <c r="Q28" s="12" t="n">
-        <v>4.9888</v>
+        <v>4.9964</v>
       </c>
     </row>
     <row r="29">
@@ -2170,13 +2170,13 @@
         <v/>
       </c>
       <c r="H29" s="8" t="n">
-        <v>0.0282</v>
+        <v>0.028</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>0.0406</v>
+        <v>0.0404</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0</v>
+        <v>-0.0002</v>
       </c>
       <c r="K29" s="9" t="n"/>
       <c r="L29" s="9" t="n"/>
@@ -2196,7 +2196,7 @@
         <v/>
       </c>
       <c r="Q29" s="12" t="n">
-        <v>4.99</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -2236,10 +2236,10 @@
         <v>0.027</v>
       </c>
       <c r="I30" s="8" t="n">
-        <v>0.0405</v>
+        <v>0.0403</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>-0.0001</v>
+        <v>-0.0002</v>
       </c>
       <c r="K30" s="9" t="n"/>
       <c r="L30" s="9" t="n"/>
@@ -2259,7 +2259,7 @@
         <v/>
       </c>
       <c r="Q30" s="12" t="n">
-        <v>35.25</v>
+        <v>35.27</v>
       </c>
     </row>
     <row r="31">
@@ -2299,7 +2299,7 @@
         <v>0.026</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>0.0341</v>
+        <v>0.0342</v>
       </c>
       <c r="J31" s="9" t="n">
         <v>0.0001</v>
@@ -2322,7 +2322,7 @@
         <v/>
       </c>
       <c r="Q31" s="12" t="n">
-        <v>5.06</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="32">
@@ -2362,10 +2362,10 @@
         <v>0.0229</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>0.0332</v>
+        <v>0.0335</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0</v>
+        <v>0.0003</v>
       </c>
       <c r="K32" s="9" t="n"/>
       <c r="L32" s="9" t="n"/>
@@ -2385,7 +2385,7 @@
         <v/>
       </c>
       <c r="Q32" s="12" t="n">
-        <v>10.2862</v>
+        <v>10.2973</v>
       </c>
     </row>
     <row r="33">
@@ -2425,10 +2425,10 @@
         <v>0.0184</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>0.0329</v>
+        <v>0.0331</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="K33" s="9" t="n"/>
       <c r="L33" s="9" t="n"/>
@@ -2448,7 +2448,7 @@
         <v/>
       </c>
       <c r="Q33" s="12" t="n">
-        <v>10.2781</v>
+        <v>10.287</v>
       </c>
     </row>
     <row r="34">
@@ -2488,10 +2488,10 @@
         <v>0.0184</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>0.0329</v>
+        <v>0.0331</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="K34" s="9" t="n"/>
       <c r="L34" s="9" t="n"/>
@@ -2511,7 +2511,7 @@
         <v/>
       </c>
       <c r="Q34" s="12" t="n">
-        <v>10.0774</v>
+        <v>10.0862</v>
       </c>
     </row>
     <row r="35">
@@ -2551,10 +2551,10 @@
         <v>0.0252</v>
       </c>
       <c r="I35" s="8" t="n">
-        <v>0.039</v>
+        <v>0.0388</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.0001</v>
+        <v>-0.0002</v>
       </c>
       <c r="K35" s="9" t="n"/>
       <c r="L35" s="9" t="n"/>
@@ -2637,7 +2637,7 @@
         <v/>
       </c>
       <c r="Q36" s="12" t="n">
-        <v>5.4295</v>
+        <v>5.4347</v>
       </c>
     </row>
     <row r="37">
@@ -2700,7 +2700,7 @@
         <v/>
       </c>
       <c r="Q37" s="12" t="n">
-        <v>5.0593</v>
+        <v>5.0641</v>
       </c>
     </row>
     <row r="38">
@@ -2740,10 +2740,10 @@
         <v>0.0245</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>0.0387</v>
+        <v>0.0385</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0</v>
+        <v>-0.0002</v>
       </c>
       <c r="K38" s="9" t="n"/>
       <c r="L38" s="9" t="n"/>
@@ -2763,7 +2763,7 @@
         <v/>
       </c>
       <c r="Q38" s="12" t="n">
-        <v>25.78</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="39">
@@ -2803,10 +2803,10 @@
         <v>0.0245</v>
       </c>
       <c r="I39" s="8" t="n">
-        <v>0.0387</v>
+        <v>0.0385</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0</v>
+        <v>-0.0002</v>
       </c>
       <c r="K39" s="9" t="n"/>
       <c r="L39" s="9" t="n"/>
@@ -2866,10 +2866,10 @@
         <v>0.0235</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>0.0384</v>
+        <v>0.0381</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.0001</v>
+        <v>-0.0003</v>
       </c>
       <c r="K40" s="9" t="n"/>
       <c r="L40" s="9" t="n"/>
@@ -2889,7 +2889,7 @@
         <v/>
       </c>
       <c r="Q40" s="12" t="n">
-        <v>10.6623</v>
+        <v>10.6686</v>
       </c>
     </row>
     <row r="41">
@@ -2929,10 +2929,10 @@
         <v>0.0235</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>0.0384</v>
+        <v>0.0381</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.0001</v>
+        <v>-0.0003</v>
       </c>
       <c r="K41" s="9" t="n"/>
       <c r="L41" s="9" t="n"/>
@@ -2952,7 +2952,7 @@
         <v/>
       </c>
       <c r="Q41" s="12" t="n">
-        <v>10.3009</v>
+        <v>10.307</v>
       </c>
     </row>
     <row r="42">
@@ -3015,7 +3015,7 @@
         <v/>
       </c>
       <c r="Q42" s="12" t="n">
-        <v>5.5712</v>
+        <v>5.5743</v>
       </c>
     </row>
     <row r="43">
@@ -3078,7 +3078,7 @@
         <v/>
       </c>
       <c r="Q43" s="12" t="n">
-        <v>5.2104</v>
+        <v>5.2133</v>
       </c>
     </row>
     <row r="44">
@@ -3118,10 +3118,10 @@
         <v>0.0213</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>0.0375</v>
+        <v>0.0374</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.0002</v>
+        <v>-0.0001</v>
       </c>
       <c r="K44" s="9" t="n"/>
       <c r="L44" s="9" t="n"/>
@@ -3181,10 +3181,10 @@
         <v>0.0207</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>0.0372</v>
+        <v>0.0371</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0</v>
+        <v>-0.0001</v>
       </c>
       <c r="K45" s="9" t="n"/>
       <c r="L45" s="9" t="n"/>
@@ -3204,7 +3204,7 @@
         <v/>
       </c>
       <c r="Q45" s="12" t="n">
-        <v>35.76</v>
+        <v>35.77</v>
       </c>
     </row>
     <row r="46">
@@ -3244,7 +3244,7 @@
         <v>0.0265</v>
       </c>
       <c r="I46" s="8" t="n">
-        <v>0.0308</v>
+        <v>0.031</v>
       </c>
       <c r="J46" s="9" t="n">
         <v>0.0002</v>
@@ -3267,7 +3267,7 @@
         <v/>
       </c>
       <c r="Q46" s="12" t="n">
-        <v>10.3351</v>
+        <v>10.3401</v>
       </c>
     </row>
     <row r="47">
@@ -3307,7 +3307,7 @@
         <v>0.015</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>0.0296</v>
+        <v>0.0297</v>
       </c>
       <c r="J47" s="9" t="n">
         <v>0.0001</v>
@@ -3330,7 +3330,7 @@
         <v/>
       </c>
       <c r="Q47" s="12" t="n">
-        <v>10.1754</v>
+        <v>10.1785</v>
       </c>
     </row>
     <row r="48">
@@ -3370,10 +3370,10 @@
         <v>0.0105</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>0.0284</v>
+        <v>0.0286</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="K48" s="9" t="n"/>
       <c r="L48" s="9" t="n"/>
@@ -3393,7 +3393,7 @@
         <v/>
       </c>
       <c r="Q48" s="12" t="n">
-        <v>10.3481</v>
+        <v>10.3505</v>
       </c>
     </row>
     <row r="49">
@@ -3456,7 +3456,7 @@
         <v/>
       </c>
       <c r="Q49" s="12" t="n">
-        <v>5.7079</v>
+        <v>5.7089</v>
       </c>
     </row>
     <row r="50">
@@ -3519,7 +3519,7 @@
         <v/>
       </c>
       <c r="Q50" s="12" t="n">
-        <v>5.3356</v>
+        <v>5.3365</v>
       </c>
     </row>
     <row r="51">
@@ -3562,7 +3562,7 @@
         <v>0.0335</v>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="K51" s="9" t="n"/>
       <c r="L51" s="9" t="n"/>
@@ -3625,7 +3625,7 @@
         <v>0.032</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0</v>
       </c>
       <c r="K52" s="9" t="n"/>
       <c r="L52" s="9" t="n"/>
@@ -3688,7 +3688,7 @@
         <v>0.032</v>
       </c>
       <c r="J53" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0</v>
       </c>
       <c r="K53" s="9" t="n"/>
       <c r="L53" s="9" t="n"/>
@@ -3748,10 +3748,10 @@
         <v>0.008800000000000001</v>
       </c>
       <c r="I54" s="8" t="n">
-        <v>0.0269</v>
+        <v>0.0268</v>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0</v>
+        <v>-0.0001</v>
       </c>
       <c r="K54" s="9" t="n"/>
       <c r="L54" s="9" t="n"/>
@@ -3811,10 +3811,10 @@
         <v>0.0023</v>
       </c>
       <c r="I55" s="8" t="n">
-        <v>0.0257</v>
+        <v>0.0265</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0</v>
+        <v>0.0008</v>
       </c>
       <c r="K55" s="9" t="n"/>
       <c r="L55" s="9" t="n"/>
@@ -3834,7 +3834,7 @@
         <v/>
       </c>
       <c r="Q55" s="12" t="n">
-        <v>10.2601</v>
+        <v>10.2625</v>
       </c>
     </row>
     <row r="56">
@@ -3897,7 +3897,7 @@
         <v/>
       </c>
       <c r="Q56" s="12" t="n">
-        <v>5.7933</v>
+        <v>5.7943</v>
       </c>
     </row>
     <row r="57">
@@ -3960,7 +3960,7 @@
         <v/>
       </c>
       <c r="Q57" s="12" t="n">
-        <v>5.4169</v>
+        <v>5.4179</v>
       </c>
     </row>
     <row r="58">
@@ -3997,10 +3997,10 @@
         <v/>
       </c>
       <c r="H58" s="8" t="n">
-        <v>0.0059</v>
+        <v>0.005500000000000001</v>
       </c>
       <c r="I58" s="8" t="n">
-        <v>0.0276</v>
+        <v>0.0279</v>
       </c>
       <c r="J58" s="9" t="n">
         <v>0.0003</v>

--- a/data/rendimenti_etf.xlsx
+++ b/data/rendimenti_etf.xlsx
@@ -533,7 +533,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Aggiornato il 16/10/2026 09:02 da yield_etf.csv</t>
+          <t>Aggiornato il 19/10/2026 09:03 da yield_etf.csv</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
         <v>0.0389</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>0.05019999999999999</v>
+        <v>0.0499</v>
       </c>
       <c r="J5" s="9" t="n">
         <v>-0.0003</v>
@@ -684,7 +684,7 @@
         <v/>
       </c>
       <c r="Q5" s="12" t="n">
-        <v>4.88</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="6">
@@ -724,10 +724,10 @@
         <v>0.03759999999999999</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0.0459</v>
+        <v>0.0453</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="K6" s="9" t="n"/>
       <c r="L6" s="9" t="n"/>
@@ -747,7 +747,7 @@
         <v/>
       </c>
       <c r="Q6" s="12" t="n">
-        <v>28.38</v>
+        <v>28.53</v>
       </c>
     </row>
     <row r="7">
@@ -787,10 +787,10 @@
         <v>0.0365</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0.04559999999999999</v>
+        <v>0.045</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="K7" s="9" t="n"/>
       <c r="L7" s="9" t="n"/>
@@ -810,7 +810,7 @@
         <v/>
       </c>
       <c r="Q7" s="12" t="n">
-        <v>29.19</v>
+        <v>29.32</v>
       </c>
     </row>
     <row r="8">
@@ -850,10 +850,10 @@
         <v>0.0355</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>0.0455</v>
+        <v>0.04480000000000001</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0</v>
+        <v>-0.0007</v>
       </c>
       <c r="K8" s="9" t="n"/>
       <c r="L8" s="9" t="n"/>
@@ -913,10 +913,10 @@
         <v>0.0349</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>0.0454</v>
+        <v>0.04480000000000001</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="K9" s="9" t="n"/>
       <c r="L9" s="9" t="n"/>
@@ -976,10 +976,10 @@
         <v>0.0363</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>0.0452</v>
+        <v>0.0445</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0</v>
+        <v>-0.0007</v>
       </c>
       <c r="K10" s="9" t="n"/>
       <c r="L10" s="9" t="n"/>
@@ -1039,10 +1039,10 @@
         <v>0.0347</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>0.0449</v>
+        <v>0.0443</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="K11" s="9" t="n"/>
       <c r="L11" s="9" t="n"/>
@@ -1062,7 +1062,7 @@
         <v/>
       </c>
       <c r="Q11" s="12" t="n">
-        <v>33.59</v>
+        <v>33.72</v>
       </c>
     </row>
     <row r="12">
@@ -1099,13 +1099,13 @@
         <v/>
       </c>
       <c r="H12" s="8" t="n">
-        <v>0.0346</v>
+        <v>0.0348</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>0.0444</v>
+        <v>0.0438</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>-0.0001</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="K12" s="9" t="n"/>
       <c r="L12" s="9" t="n"/>
@@ -1165,10 +1165,10 @@
         <v>0.0338</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0.0442</v>
+        <v>0.0437</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>-0.0001</v>
+        <v>-0.0005</v>
       </c>
       <c r="K13" s="9" t="n"/>
       <c r="L13" s="9" t="n"/>
@@ -1188,7 +1188,7 @@
         <v/>
       </c>
       <c r="Q13" s="12" t="n">
-        <v>9.32</v>
+        <v>9.35</v>
       </c>
     </row>
     <row r="14">
@@ -1228,10 +1228,10 @@
         <v>0.0338</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>0.0442</v>
+        <v>0.0437</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>-0.0001</v>
+        <v>-0.0005</v>
       </c>
       <c r="K14" s="9" t="n"/>
       <c r="L14" s="9" t="n"/>
@@ -1251,7 +1251,7 @@
         <v/>
       </c>
       <c r="Q14" s="12" t="n">
-        <v>27.93</v>
+        <v>28.02</v>
       </c>
     </row>
     <row r="15">
@@ -1291,10 +1291,10 @@
         <v>0.0331</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>0.0438</v>
+        <v>0.0431</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0</v>
+        <v>-0.0007</v>
       </c>
       <c r="K15" s="9" t="n"/>
       <c r="L15" s="9" t="n"/>
@@ -1351,13 +1351,13 @@
         <v/>
       </c>
       <c r="H16" s="8" t="n">
-        <v>0.033</v>
+        <v>0.0329</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>0.0441</v>
+        <v>0.0438</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0</v>
+        <v>-0.0003</v>
       </c>
       <c r="K16" s="9" t="n"/>
       <c r="L16" s="9" t="n"/>
@@ -1417,10 +1417,10 @@
         <v>0.0282</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>0.0433</v>
+        <v>0.0428</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>-0.0001</v>
+        <v>-0.0005</v>
       </c>
       <c r="K17" s="9" t="n"/>
       <c r="L17" s="9" t="n"/>
@@ -1440,7 +1440,7 @@
         <v/>
       </c>
       <c r="Q17" s="12" t="n">
-        <v>34.32</v>
+        <v>34.41</v>
       </c>
     </row>
     <row r="18">
@@ -1480,10 +1480,10 @@
         <v>0.0169</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>0.0362</v>
+        <v>0.036</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.0002</v>
+        <v>-0.0002</v>
       </c>
       <c r="K18" s="9" t="n"/>
       <c r="L18" s="9" t="n"/>
@@ -1503,7 +1503,7 @@
         <v/>
       </c>
       <c r="Q18" s="12" t="n">
-        <v>9.8558</v>
+        <v>9.861800000000001</v>
       </c>
     </row>
     <row r="19">
@@ -1543,10 +1543,10 @@
         <v>0.03</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>0.04269999999999999</v>
+        <v>0.042</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>-0.0001</v>
+        <v>-0.0007</v>
       </c>
       <c r="K19" s="9" t="n"/>
       <c r="L19" s="9" t="n"/>
@@ -1566,55 +1566,55 @@
         <v/>
       </c>
       <c r="Q19" s="12" t="n">
-        <v>4.84</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2031 Term € Corp UCITS ETF</t>
+          <t>Amundi Fixed Maturity 2029 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>IE000I2WYEU9</t>
+          <t>LU2872291781</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>48213</v>
+        <v>47483</v>
       </c>
       <c r="G20" s="7">
         <f>IF(F20="","",MAX(0,YEARFRAC(TODAY(),F20)))</f>
         <v/>
       </c>
       <c r="H20" s="8" t="n">
-        <v>0.0286</v>
+        <v>0.0208</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>0.0421</v>
+        <v>0.0351</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0</v>
+        <v>-0.0002</v>
       </c>
       <c r="K20" s="9" t="n"/>
       <c r="L20" s="9" t="n"/>
       <c r="M20" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N20" s="10">
         <f>IF(D20="Govt",$B$1,$B$2)</f>
@@ -1629,55 +1629,55 @@
         <v/>
       </c>
       <c r="Q20" s="12" t="n">
-        <v>4.89</v>
+        <v>10.0107</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2029 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>iShares iBonds Dec 2031 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>LU2872291781</t>
+          <t>IE000I2WYEU9</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F21" s="6" t="n">
-        <v>47483</v>
+        <v>48213</v>
       </c>
       <c r="G21" s="7">
         <f>IF(F21="","",MAX(0,YEARFRAC(TODAY(),F21)))</f>
         <v/>
       </c>
       <c r="H21" s="8" t="n">
-        <v>0.0208</v>
+        <v>0.0286</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>0.0353</v>
+        <v>0.0414</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.0002</v>
+        <v>-0.0007</v>
       </c>
       <c r="K21" s="9" t="n"/>
       <c r="L21" s="9" t="n"/>
       <c r="M21" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N21" s="10">
         <f>IF(D21="Govt",$B$1,$B$2)</f>
@@ -1692,23 +1692,23 @@
         <v/>
       </c>
       <c r="Q21" s="12" t="n">
-        <v>10.0057</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>BNP Paribas</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1C</t>
+          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2032 UCITS ETF C</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>LU2673523135</t>
+          <t>LU2823895847</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1722,20 +1722,20 @@
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>48121</v>
+        <v>48579</v>
       </c>
       <c r="G22" s="7">
         <f>IF(F22="","",MAX(0,YEARFRAC(TODAY(),F22)))</f>
         <v/>
       </c>
       <c r="H22" s="8" t="n">
-        <v>0.0287</v>
+        <v>0.0269</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>0.0417</v>
+        <v>0.0414</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>-0.0002</v>
+        <v>-0.0003</v>
       </c>
       <c r="K22" s="9" t="n"/>
       <c r="L22" s="9" t="n"/>
@@ -1755,23 +1755,23 @@
         <v/>
       </c>
       <c r="Q22" s="12" t="n">
-        <v>9.800000000000001</v>
+        <v>10.4731</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>BNP Paribas</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2032 UCITS ETF D</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>LU2673523481</t>
+          <t>LU2823895763</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -1785,20 +1785,20 @@
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>48121</v>
+        <v>48579</v>
       </c>
       <c r="G23" s="7">
         <f>IF(F23="","",MAX(0,YEARFRAC(TODAY(),F23)))</f>
         <v/>
       </c>
       <c r="H23" s="8" t="n">
-        <v>0.0287</v>
+        <v>0.0269</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>0.0417</v>
+        <v>0.0414</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>-0.0002</v>
+        <v>-0.0003</v>
       </c>
       <c r="K23" s="9" t="n"/>
       <c r="L23" s="9" t="n"/>
@@ -1818,23 +1818,23 @@
         <v/>
       </c>
       <c r="Q23" s="12" t="n">
-        <v>29.32</v>
+        <v>10.0856</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BNP Paribas</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2032 UCITS ETF C</t>
+          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>LU2823895847</t>
+          <t>LU2673523135</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -1848,20 +1848,20 @@
         </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>48579</v>
+        <v>48121</v>
       </c>
       <c r="G24" s="7">
         <f>IF(F24="","",MAX(0,YEARFRAC(TODAY(),F24)))</f>
         <v/>
       </c>
       <c r="H24" s="8" t="n">
-        <v>0.0269</v>
+        <v>0.0288</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>0.0417</v>
+        <v>0.0412</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>-0.0004</v>
+        <v>-0.0005</v>
       </c>
       <c r="K24" s="9" t="n"/>
       <c r="L24" s="9" t="n"/>
@@ -1881,23 +1881,23 @@
         <v/>
       </c>
       <c r="Q24" s="12" t="n">
-        <v>10.4426</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BNP Paribas</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2032 UCITS ETF D</t>
+          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>LU2823895763</t>
+          <t>LU2673523481</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -1911,20 +1911,20 @@
         </is>
       </c>
       <c r="F25" s="6" t="n">
-        <v>48579</v>
+        <v>48121</v>
       </c>
       <c r="G25" s="7">
         <f>IF(F25="","",MAX(0,YEARFRAC(TODAY(),F25)))</f>
         <v/>
       </c>
       <c r="H25" s="8" t="n">
-        <v>0.0269</v>
+        <v>0.0288</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>0.0417</v>
+        <v>0.0412</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>-0.0004</v>
+        <v>-0.0005</v>
       </c>
       <c r="K25" s="9" t="n"/>
       <c r="L25" s="9" t="n"/>
@@ -1944,28 +1944,28 @@
         <v/>
       </c>
       <c r="Q25" s="12" t="n">
-        <v>10.0562</v>
+        <v>29.38</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2029 Italy and Spain Government Bond UCITS ETF 1C</t>
+          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>LU0484969463</t>
+          <t>IE000I25S1V5</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -1974,25 +1974,25 @@
         </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>47391</v>
+        <v>47848</v>
       </c>
       <c r="G26" s="7">
         <f>IF(F26="","",MAX(0,YEARFRAC(TODAY(),F26)))</f>
         <v/>
       </c>
       <c r="H26" s="8" t="n">
-        <v>0.0297</v>
+        <v>0.0286</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>0.0351</v>
+        <v>0.0406</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="K26" s="9" t="n"/>
       <c r="L26" s="9" t="n"/>
       <c r="M26" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="N26" s="10">
         <f>IF(D26="Govt",$B$1,$B$2)</f>
@@ -2007,7 +2007,7 @@
         <v/>
       </c>
       <c r="Q26" s="12" t="n">
-        <v>204.55</v>
+        <v>5.3678</v>
       </c>
     </row>
     <row r="27">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>IE000I25S1V5</t>
+          <t>IE000W6YTDH7</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F27" s="6" t="n">
@@ -2070,55 +2070,55 @@
         <v/>
       </c>
       <c r="Q27" s="12" t="n">
-        <v>5.3639</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>Xtrackers II Target Maturity Sept 2029 Italy and Spain Government Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>IE000W6YTDH7</t>
+          <t>LU0484969463</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F28" s="6" t="n">
-        <v>47848</v>
+        <v>47391</v>
       </c>
       <c r="G28" s="7">
         <f>IF(F28="","",MAX(0,YEARFRAC(TODAY(),F28)))</f>
         <v/>
       </c>
       <c r="H28" s="8" t="n">
-        <v>0.0286</v>
+        <v>0.0297</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>0.0406</v>
+        <v>0.0344</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0</v>
+        <v>-0.0007</v>
       </c>
       <c r="K28" s="9" t="n"/>
       <c r="L28" s="9" t="n"/>
       <c r="M28" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N28" s="10">
         <f>IF(D28="Govt",$B$1,$B$2)</f>
@@ -2133,23 +2133,23 @@
         <v/>
       </c>
       <c r="Q28" s="12" t="n">
-        <v>4.9964</v>
+        <v>204.91</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2030 Term € Corp UCITS ETF</t>
+          <t>Xtrackers II Target Maturity Sept 2030 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>IE000LX17BP9</t>
+          <t>LU2809864296</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -2163,20 +2163,20 @@
         </is>
       </c>
       <c r="F29" s="6" t="n">
-        <v>47848</v>
+        <v>47756</v>
       </c>
       <c r="G29" s="7">
         <f>IF(F29="","",MAX(0,YEARFRAC(TODAY(),F29)))</f>
         <v/>
       </c>
       <c r="H29" s="8" t="n">
-        <v>0.028</v>
+        <v>0.027</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>0.0404</v>
+        <v>0.0399</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>-0.0002</v>
+        <v>-0.0004</v>
       </c>
       <c r="K29" s="9" t="n"/>
       <c r="L29" s="9" t="n"/>
@@ -2196,23 +2196,23 @@
         <v/>
       </c>
       <c r="Q29" s="12" t="n">
-        <v>5</v>
+        <v>35.32</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2030 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>iShares iBonds Dec 2030 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>LU2809864296</t>
+          <t>IE000LX17BP9</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -2226,20 +2226,20 @@
         </is>
       </c>
       <c r="F30" s="6" t="n">
-        <v>47756</v>
+        <v>47848</v>
       </c>
       <c r="G30" s="7">
         <f>IF(F30="","",MAX(0,YEARFRAC(TODAY(),F30)))</f>
         <v/>
       </c>
       <c r="H30" s="8" t="n">
-        <v>0.027</v>
+        <v>0.028</v>
       </c>
       <c r="I30" s="8" t="n">
-        <v>0.0403</v>
+        <v>0.0398</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>-0.0002</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="K30" s="9" t="n"/>
       <c r="L30" s="9" t="n"/>
@@ -2259,23 +2259,23 @@
         <v/>
       </c>
       <c r="Q30" s="12" t="n">
-        <v>35.27</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2028 Term € Italy Govt Bond UCITS ETF</t>
+          <t>Amundi Fixed Maturity 2028 Euro Government Bond Yield + UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>IE000Q2EQ5K8</t>
+          <t>LU2780871666</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -2296,18 +2296,18 @@
         <v/>
       </c>
       <c r="H31" s="8" t="n">
-        <v>0.026</v>
+        <v>0.023</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>0.0342</v>
+        <v>0.0333</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.0001</v>
+        <v>-0.0002</v>
       </c>
       <c r="K31" s="9" t="n"/>
       <c r="L31" s="9" t="n"/>
       <c r="M31" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N31" s="10">
         <f>IF(D31="Govt",$B$1,$B$2)</f>
@@ -2322,23 +2322,23 @@
         <v/>
       </c>
       <c r="Q31" s="12" t="n">
-        <v>5.07</v>
+        <v>10.3014</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2028 Euro Government Bond Yield + UCITS ETF Dist</t>
+          <t>iShares iBonds Dec 2028 Term € Italy Govt Bond UCITS ETF</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>LU2780871666</t>
+          <t>IE000Q2EQ5K8</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -2359,18 +2359,18 @@
         <v/>
       </c>
       <c r="H32" s="8" t="n">
-        <v>0.0229</v>
+        <v>0.0261</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>0.0335</v>
+        <v>0.0334</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.0003</v>
+        <v>-0.0008</v>
       </c>
       <c r="K32" s="9" t="n"/>
       <c r="L32" s="9" t="n"/>
       <c r="M32" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N32" s="10">
         <f>IF(D32="Govt",$B$1,$B$2)</f>
@@ -2385,7 +2385,7 @@
         <v/>
       </c>
       <c r="Q32" s="12" t="n">
-        <v>10.2973</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="33">
@@ -2425,10 +2425,10 @@
         <v>0.0184</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>0.0331</v>
+        <v>0.033</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.0002</v>
+        <v>-0.0001</v>
       </c>
       <c r="K33" s="9" t="n"/>
       <c r="L33" s="9" t="n"/>
@@ -2448,7 +2448,7 @@
         <v/>
       </c>
       <c r="Q33" s="12" t="n">
-        <v>10.287</v>
+        <v>10.2902</v>
       </c>
     </row>
     <row r="34">
@@ -2488,10 +2488,10 @@
         <v>0.0184</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>0.0331</v>
+        <v>0.033</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.0002</v>
+        <v>-0.0001</v>
       </c>
       <c r="K34" s="9" t="n"/>
       <c r="L34" s="9" t="n"/>
@@ -2511,23 +2511,23 @@
         <v/>
       </c>
       <c r="Q34" s="12" t="n">
-        <v>10.0862</v>
+        <v>10.0893</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2029 Term € Corp UCITS ETF</t>
+          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>IE000IHURBR0</t>
+          <t>IE000P5IB8I8</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F35" s="6" t="n">
@@ -2548,18 +2548,18 @@
         <v/>
       </c>
       <c r="H35" s="8" t="n">
-        <v>0.0252</v>
+        <v>0.0242</v>
       </c>
       <c r="I35" s="8" t="n">
-        <v>0.0388</v>
+        <v>0.0386</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0</v>
       </c>
       <c r="K35" s="9" t="n"/>
       <c r="L35" s="9" t="n"/>
       <c r="M35" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="N35" s="10">
         <f>IF(D35="Govt",$B$1,$B$2)</f>
@@ -2574,7 +2574,7 @@
         <v/>
       </c>
       <c r="Q35" s="12" t="n">
-        <v>5.04</v>
+        <v>5.4384</v>
       </c>
     </row>
     <row r="36">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>IE000P5IB8I8</t>
+          <t>IE000ZC4C5Q1</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F36" s="6" t="n">
@@ -2637,23 +2637,23 @@
         <v/>
       </c>
       <c r="Q36" s="12" t="n">
-        <v>5.4347</v>
+        <v>5.0675</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>iShares iBonds Dec 2029 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>IE000ZC4C5Q1</t>
+          <t>IE000IHURBR0</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -2674,18 +2674,18 @@
         <v/>
       </c>
       <c r="H37" s="8" t="n">
-        <v>0.0242</v>
+        <v>0.0252</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>0.0386</v>
+        <v>0.0382</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="K37" s="9" t="n"/>
       <c r="L37" s="9" t="n"/>
       <c r="M37" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N37" s="10">
         <f>IF(D37="Govt",$B$1,$B$2)</f>
@@ -2700,7 +2700,7 @@
         <v/>
       </c>
       <c r="Q37" s="12" t="n">
-        <v>5.0641</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="38">
@@ -2740,10 +2740,10 @@
         <v>0.0245</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>0.0385</v>
+        <v>0.0382</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>-0.0002</v>
+        <v>-0.0003</v>
       </c>
       <c r="K38" s="9" t="n"/>
       <c r="L38" s="9" t="n"/>
@@ -2763,7 +2763,7 @@
         <v/>
       </c>
       <c r="Q38" s="12" t="n">
-        <v>25.8</v>
+        <v>25.82</v>
       </c>
     </row>
     <row r="39">
@@ -2803,10 +2803,10 @@
         <v>0.0245</v>
       </c>
       <c r="I39" s="8" t="n">
-        <v>0.0385</v>
+        <v>0.0382</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>-0.0002</v>
+        <v>-0.0003</v>
       </c>
       <c r="K39" s="9" t="n"/>
       <c r="L39" s="9" t="n"/>
@@ -2826,7 +2826,7 @@
         <v/>
       </c>
       <c r="Q39" s="12" t="n">
-        <v>9.17</v>
+        <v>9.18</v>
       </c>
     </row>
     <row r="40">
@@ -2866,10 +2866,10 @@
         <v>0.0235</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>0.0381</v>
+        <v>0.0379</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>-0.0003</v>
+        <v>-0.0002</v>
       </c>
       <c r="K40" s="9" t="n"/>
       <c r="L40" s="9" t="n"/>
@@ -2889,7 +2889,7 @@
         <v/>
       </c>
       <c r="Q40" s="12" t="n">
-        <v>10.6686</v>
+        <v>10.6791</v>
       </c>
     </row>
     <row r="41">
@@ -2929,10 +2929,10 @@
         <v>0.0235</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>0.0381</v>
+        <v>0.0379</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>-0.0003</v>
+        <v>-0.0002</v>
       </c>
       <c r="K41" s="9" t="n"/>
       <c r="L41" s="9" t="n"/>
@@ -2952,7 +2952,7 @@
         <v/>
       </c>
       <c r="Q41" s="12" t="n">
-        <v>10.307</v>
+        <v>10.3172</v>
       </c>
     </row>
     <row r="42">
@@ -3015,7 +3015,7 @@
         <v/>
       </c>
       <c r="Q42" s="12" t="n">
-        <v>5.5743</v>
+        <v>5.5771</v>
       </c>
     </row>
     <row r="43">
@@ -3078,7 +3078,7 @@
         <v/>
       </c>
       <c r="Q43" s="12" t="n">
-        <v>5.2133</v>
+        <v>5.2159</v>
       </c>
     </row>
     <row r="44">
@@ -3118,10 +3118,10 @@
         <v>0.0213</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>0.0374</v>
+        <v>0.0369</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>-0.0001</v>
+        <v>-0.0005</v>
       </c>
       <c r="K44" s="9" t="n"/>
       <c r="L44" s="9" t="n"/>
@@ -3141,7 +3141,7 @@
         <v/>
       </c>
       <c r="Q44" s="12" t="n">
-        <v>5.1</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="45">
@@ -3181,10 +3181,10 @@
         <v>0.0207</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>0.0371</v>
+        <v>0.0368</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>-0.0001</v>
+        <v>-0.0003</v>
       </c>
       <c r="K45" s="9" t="n"/>
       <c r="L45" s="9" t="n"/>
@@ -3204,7 +3204,7 @@
         <v/>
       </c>
       <c r="Q45" s="12" t="n">
-        <v>35.77</v>
+        <v>35.78</v>
       </c>
     </row>
     <row r="46">
@@ -3244,10 +3244,10 @@
         <v>0.0265</v>
       </c>
       <c r="I46" s="8" t="n">
-        <v>0.031</v>
+        <v>0.0309</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.0002</v>
+        <v>-0.0001</v>
       </c>
       <c r="K46" s="9" t="n"/>
       <c r="L46" s="9" t="n"/>
@@ -3267,7 +3267,7 @@
         <v/>
       </c>
       <c r="Q46" s="12" t="n">
-        <v>10.3401</v>
+        <v>10.3407</v>
       </c>
     </row>
     <row r="47">
@@ -3307,7 +3307,7 @@
         <v>0.015</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>0.0297</v>
+        <v>0.0298</v>
       </c>
       <c r="J47" s="9" t="n">
         <v>0.0001</v>
@@ -3330,7 +3330,7 @@
         <v/>
       </c>
       <c r="Q47" s="12" t="n">
-        <v>10.1785</v>
+        <v>10.1793</v>
       </c>
     </row>
     <row r="48">
@@ -3370,10 +3370,10 @@
         <v>0.0105</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>0.0286</v>
+        <v>0.0287</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="K48" s="9" t="n"/>
       <c r="L48" s="9" t="n"/>
@@ -3393,7 +3393,7 @@
         <v/>
       </c>
       <c r="Q48" s="12" t="n">
-        <v>10.3505</v>
+        <v>10.3526</v>
       </c>
     </row>
     <row r="49">
@@ -3456,7 +3456,7 @@
         <v/>
       </c>
       <c r="Q49" s="12" t="n">
-        <v>5.7089</v>
+        <v>5.7102</v>
       </c>
     </row>
     <row r="50">
@@ -3519,7 +3519,7 @@
         <v/>
       </c>
       <c r="Q50" s="12" t="n">
-        <v>5.3365</v>
+        <v>5.3377</v>
       </c>
     </row>
     <row r="51">
@@ -3559,10 +3559,10 @@
         <v>0.0195</v>
       </c>
       <c r="I51" s="8" t="n">
-        <v>0.0335</v>
+        <v>0.0331</v>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0</v>
+        <v>-0.0004</v>
       </c>
       <c r="K51" s="9" t="n"/>
       <c r="L51" s="9" t="n"/>
@@ -3622,10 +3622,10 @@
         <v>0.0186</v>
       </c>
       <c r="I52" s="8" t="n">
-        <v>0.032</v>
+        <v>0.0318</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0</v>
+        <v>-0.0002</v>
       </c>
       <c r="K52" s="9" t="n"/>
       <c r="L52" s="9" t="n"/>
@@ -3645,7 +3645,7 @@
         <v/>
       </c>
       <c r="Q52" s="12" t="n">
-        <v>25.96</v>
+        <v>25.97</v>
       </c>
     </row>
     <row r="53">
@@ -3685,10 +3685,10 @@
         <v>0.0186</v>
       </c>
       <c r="I53" s="8" t="n">
-        <v>0.032</v>
+        <v>0.0318</v>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0</v>
+        <v>-0.0002</v>
       </c>
       <c r="K53" s="9" t="n"/>
       <c r="L53" s="9" t="n"/>
@@ -3714,17 +3714,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2026 Term € Italy Govt Bond UCITS ETF</t>
+          <t>Amundi Fixed Maturity 2026 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>IE000LZ7BZW8</t>
+          <t>LU2872291278</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F54" s="6" t="n">
@@ -3745,10 +3745,10 @@
         <v/>
       </c>
       <c r="H54" s="8" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0023</v>
       </c>
       <c r="I54" s="8" t="n">
-        <v>0.0268</v>
+        <v>0.0264</v>
       </c>
       <c r="J54" s="9" t="n">
         <v>-0.0001</v>
@@ -3756,7 +3756,7 @@
       <c r="K54" s="9" t="n"/>
       <c r="L54" s="9" t="n"/>
       <c r="M54" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N54" s="10">
         <f>IF(D54="Govt",$B$1,$B$2)</f>
@@ -3771,23 +3771,23 @@
         <v/>
       </c>
       <c r="Q54" s="12" t="n">
-        <v>5.06</v>
+        <v>10.2634</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2026 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>iShares iBonds Dec 2026 Term € Italy Govt Bond UCITS ETF</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>LU2872291278</t>
+          <t>IE000LZ7BZW8</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F55" s="6" t="n">
@@ -3808,18 +3808,18 @@
         <v/>
       </c>
       <c r="H55" s="8" t="n">
-        <v>0.0023</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="I55" s="8" t="n">
         <v>0.0265</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.0008</v>
+        <v>-0.0003</v>
       </c>
       <c r="K55" s="9" t="n"/>
       <c r="L55" s="9" t="n"/>
       <c r="M55" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N55" s="10">
         <f>IF(D55="Govt",$B$1,$B$2)</f>
@@ -3834,7 +3834,7 @@
         <v/>
       </c>
       <c r="Q55" s="12" t="n">
-        <v>10.2625</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="56">
@@ -3897,7 +3897,7 @@
         <v/>
       </c>
       <c r="Q56" s="12" t="n">
-        <v>5.7943</v>
+        <v>5.7948</v>
       </c>
     </row>
     <row r="57">
@@ -3960,7 +3960,7 @@
         <v/>
       </c>
       <c r="Q57" s="12" t="n">
-        <v>5.4179</v>
+        <v>5.4184</v>
       </c>
     </row>
     <row r="58">
@@ -3997,13 +3997,13 @@
         <v/>
       </c>
       <c r="H58" s="8" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.0054</v>
       </c>
       <c r="I58" s="8" t="n">
-        <v>0.0279</v>
+        <v>0.0273</v>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.0003</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="K58" s="9" t="n"/>
       <c r="L58" s="9" t="n"/>

--- a/data/rendimenti_etf.xlsx
+++ b/data/rendimenti_etf.xlsx
@@ -533,7 +533,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Aggiornato il 19/10/2026 09:03 da yield_etf.csv</t>
+          <t>Aggiornato il 20/10/2026 09:03 da yield_etf.csv</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
         <v>0.0499</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0</v>
       </c>
       <c r="K5" s="9" t="n"/>
       <c r="L5" s="9" t="n"/>
@@ -684,7 +684,7 @@
         <v/>
       </c>
       <c r="Q5" s="12" t="n">
-        <v>4.89</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="6">
@@ -727,7 +727,7 @@
         <v>0.0453</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0</v>
       </c>
       <c r="K6" s="9" t="n"/>
       <c r="L6" s="9" t="n"/>
@@ -787,10 +787,10 @@
         <v>0.0365</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0.045</v>
+        <v>0.0449</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0001</v>
       </c>
       <c r="K7" s="9" t="n"/>
       <c r="L7" s="9" t="n"/>
@@ -810,7 +810,7 @@
         <v/>
       </c>
       <c r="Q7" s="12" t="n">
-        <v>29.32</v>
+        <v>29.33</v>
       </c>
     </row>
     <row r="8">
@@ -853,7 +853,7 @@
         <v>0.04480000000000001</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>-0.0007</v>
+        <v>0</v>
       </c>
       <c r="K8" s="9" t="n"/>
       <c r="L8" s="9" t="n"/>
@@ -873,7 +873,7 @@
         <v/>
       </c>
       <c r="Q8" s="12" t="n">
-        <v>4.85</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="9">
@@ -916,7 +916,7 @@
         <v>0.04480000000000001</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0</v>
       </c>
       <c r="K9" s="9" t="n"/>
       <c r="L9" s="9" t="n"/>
@@ -936,7 +936,7 @@
         <v/>
       </c>
       <c r="Q9" s="12" t="n">
-        <v>4.85</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="10">
@@ -979,7 +979,7 @@
         <v>0.0445</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>-0.0007</v>
+        <v>0</v>
       </c>
       <c r="K10" s="9" t="n"/>
       <c r="L10" s="9" t="n"/>
@@ -999,7 +999,7 @@
         <v/>
       </c>
       <c r="Q10" s="12" t="n">
-        <v>4.76</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="11">
@@ -1042,7 +1042,7 @@
         <v>0.0443</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0</v>
       </c>
       <c r="K11" s="9" t="n"/>
       <c r="L11" s="9" t="n"/>
@@ -1062,7 +1062,7 @@
         <v/>
       </c>
       <c r="Q11" s="12" t="n">
-        <v>33.72</v>
+        <v>33.74</v>
       </c>
     </row>
     <row r="12">
@@ -1105,7 +1105,7 @@
         <v>0.0438</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0</v>
       </c>
       <c r="K12" s="9" t="n"/>
       <c r="L12" s="9" t="n"/>
@@ -1125,7 +1125,7 @@
         <v/>
       </c>
       <c r="Q12" s="12" t="n">
-        <v>4.78</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="13">
@@ -1165,10 +1165,10 @@
         <v>0.0338</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0.0437</v>
+        <v>0.0436</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>-0.0005</v>
+        <v>-0.0001</v>
       </c>
       <c r="K13" s="9" t="n"/>
       <c r="L13" s="9" t="n"/>
@@ -1188,7 +1188,7 @@
         <v/>
       </c>
       <c r="Q13" s="12" t="n">
-        <v>9.35</v>
+        <v>9.359999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1228,10 +1228,10 @@
         <v>0.0338</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>0.0437</v>
+        <v>0.0436</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>-0.0005</v>
+        <v>-0.0001</v>
       </c>
       <c r="K14" s="9" t="n"/>
       <c r="L14" s="9" t="n"/>
@@ -1251,7 +1251,7 @@
         <v/>
       </c>
       <c r="Q14" s="12" t="n">
-        <v>28.02</v>
+        <v>28.04</v>
       </c>
     </row>
     <row r="15">
@@ -1294,7 +1294,7 @@
         <v>0.0431</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>-0.0007</v>
+        <v>0</v>
       </c>
       <c r="K15" s="9" t="n"/>
       <c r="L15" s="9" t="n"/>
@@ -1314,7 +1314,7 @@
         <v/>
       </c>
       <c r="Q15" s="12" t="n">
-        <v>4.8</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="16">
@@ -1357,7 +1357,7 @@
         <v>0.0438</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0</v>
       </c>
       <c r="K16" s="9" t="n"/>
       <c r="L16" s="9" t="n"/>
@@ -1383,49 +1383,49 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2032 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>Amundi Fixed Maturity 2030 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LU2809864452</t>
+          <t>LU3120976132</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
-        <v>48487</v>
+        <v>47848</v>
       </c>
       <c r="G17" s="7">
         <f>IF(F17="","",MAX(0,YEARFRAC(TODAY(),F17)))</f>
         <v/>
       </c>
       <c r="H17" s="8" t="n">
-        <v>0.0282</v>
+        <v>0.0169</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>0.0428</v>
+        <v>0.0361</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>-0.0005</v>
+        <v>0.0001</v>
       </c>
       <c r="K17" s="9" t="n"/>
       <c r="L17" s="9" t="n"/>
       <c r="M17" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N17" s="10">
         <f>IF(D17="Govt",$B$1,$B$2)</f>
@@ -1440,55 +1440,55 @@
         <v/>
       </c>
       <c r="Q17" s="12" t="n">
-        <v>34.41</v>
+        <v>9.835100000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2030 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>Xtrackers II Target Maturity Sept 2032 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LU3120976132</t>
+          <t>LU2809864452</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>47848</v>
+        <v>48487</v>
       </c>
       <c r="G18" s="7">
         <f>IF(F18="","",MAX(0,YEARFRAC(TODAY(),F18)))</f>
         <v/>
       </c>
       <c r="H18" s="8" t="n">
-        <v>0.0169</v>
+        <v>0.0282</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>0.036</v>
+        <v>0.04269999999999999</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>-0.0002</v>
+        <v>-0.0001</v>
       </c>
       <c r="K18" s="9" t="n"/>
       <c r="L18" s="9" t="n"/>
       <c r="M18" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N18" s="10">
         <f>IF(D18="Govt",$B$1,$B$2)</f>
@@ -1503,7 +1503,7 @@
         <v/>
       </c>
       <c r="Q18" s="12" t="n">
-        <v>9.861800000000001</v>
+        <v>34.44</v>
       </c>
     </row>
     <row r="19">
@@ -1546,7 +1546,7 @@
         <v>0.042</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>-0.0007</v>
+        <v>0</v>
       </c>
       <c r="K19" s="9" t="n"/>
       <c r="L19" s="9" t="n"/>
@@ -1566,7 +1566,7 @@
         <v/>
       </c>
       <c r="Q19" s="12" t="n">
-        <v>4.85</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="20">
@@ -1606,10 +1606,10 @@
         <v>0.0208</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>0.0351</v>
+        <v>0.0352</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="K20" s="9" t="n"/>
       <c r="L20" s="9" t="n"/>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="Q20" s="12" t="n">
-        <v>10.0107</v>
+        <v>9.9909</v>
       </c>
     </row>
     <row r="21">
@@ -1672,7 +1672,7 @@
         <v>0.0414</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>-0.0007</v>
+        <v>0</v>
       </c>
       <c r="K21" s="9" t="n"/>
       <c r="L21" s="9" t="n"/>
@@ -1692,7 +1692,7 @@
         <v/>
       </c>
       <c r="Q21" s="12" t="n">
-        <v>4.89</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="22">
@@ -1735,7 +1735,7 @@
         <v>0.0414</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0</v>
       </c>
       <c r="K22" s="9" t="n"/>
       <c r="L22" s="9" t="n"/>
@@ -1755,7 +1755,7 @@
         <v/>
       </c>
       <c r="Q22" s="12" t="n">
-        <v>10.4731</v>
+        <v>10.4811</v>
       </c>
     </row>
     <row r="23">
@@ -1798,7 +1798,7 @@
         <v>0.0414</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0</v>
       </c>
       <c r="K23" s="9" t="n"/>
       <c r="L23" s="9" t="n"/>
@@ -1818,7 +1818,7 @@
         <v/>
       </c>
       <c r="Q23" s="12" t="n">
-        <v>10.0856</v>
+        <v>10.0933</v>
       </c>
     </row>
     <row r="24">
@@ -1858,10 +1858,10 @@
         <v>0.0288</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>0.0412</v>
+        <v>0.0408</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>-0.0005</v>
+        <v>-0.0004</v>
       </c>
       <c r="K24" s="9" t="n"/>
       <c r="L24" s="9" t="n"/>
@@ -1881,7 +1881,7 @@
         <v/>
       </c>
       <c r="Q24" s="12" t="n">
-        <v>9.82</v>
+        <v>9.83</v>
       </c>
     </row>
     <row r="25">
@@ -1921,10 +1921,10 @@
         <v>0.0288</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>0.0412</v>
+        <v>0.0408</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>-0.0005</v>
+        <v>-0.0004</v>
       </c>
       <c r="K25" s="9" t="n"/>
       <c r="L25" s="9" t="n"/>
@@ -1944,7 +1944,7 @@
         <v/>
       </c>
       <c r="Q25" s="12" t="n">
-        <v>29.38</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="26">
@@ -2007,7 +2007,7 @@
         <v/>
       </c>
       <c r="Q26" s="12" t="n">
-        <v>5.3678</v>
+        <v>5.3596</v>
       </c>
     </row>
     <row r="27">
@@ -2070,7 +2070,7 @@
         <v/>
       </c>
       <c r="Q27" s="12" t="n">
-        <v>5</v>
+        <v>4.9924</v>
       </c>
     </row>
     <row r="28">
@@ -2110,10 +2110,10 @@
         <v>0.0297</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>0.0344</v>
+        <v>0.0342</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>-0.0007</v>
+        <v>-0.0002</v>
       </c>
       <c r="K28" s="9" t="n"/>
       <c r="L28" s="9" t="n"/>
@@ -2133,23 +2133,23 @@
         <v/>
       </c>
       <c r="Q28" s="12" t="n">
-        <v>204.91</v>
+        <v>204.99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2030 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>iShares iBonds Dec 2030 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>LU2809864296</t>
+          <t>IE000LX17BP9</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -2163,20 +2163,20 @@
         </is>
       </c>
       <c r="F29" s="6" t="n">
-        <v>47756</v>
+        <v>47848</v>
       </c>
       <c r="G29" s="7">
         <f>IF(F29="","",MAX(0,YEARFRAC(TODAY(),F29)))</f>
         <v/>
       </c>
       <c r="H29" s="8" t="n">
-        <v>0.027</v>
+        <v>0.028</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>0.0399</v>
+        <v>0.0398</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>-0.0004</v>
+        <v>0</v>
       </c>
       <c r="K29" s="9" t="n"/>
       <c r="L29" s="9" t="n"/>
@@ -2196,23 +2196,23 @@
         <v/>
       </c>
       <c r="Q29" s="12" t="n">
-        <v>35.32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2030 Term € Corp UCITS ETF</t>
+          <t>Xtrackers II Target Maturity Sept 2030 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>IE000LX17BP9</t>
+          <t>LU2809864296</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -2226,20 +2226,20 @@
         </is>
       </c>
       <c r="F30" s="6" t="n">
-        <v>47848</v>
+        <v>47756</v>
       </c>
       <c r="G30" s="7">
         <f>IF(F30="","",MAX(0,YEARFRAC(TODAY(),F30)))</f>
         <v/>
       </c>
       <c r="H30" s="8" t="n">
-        <v>0.028</v>
+        <v>0.027</v>
       </c>
       <c r="I30" s="8" t="n">
-        <v>0.0398</v>
+        <v>0.0397</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0002</v>
       </c>
       <c r="K30" s="9" t="n"/>
       <c r="L30" s="9" t="n"/>
@@ -2259,7 +2259,7 @@
         <v/>
       </c>
       <c r="Q30" s="12" t="n">
-        <v>5.01</v>
+        <v>35.35</v>
       </c>
     </row>
     <row r="31">
@@ -2296,13 +2296,13 @@
         <v/>
       </c>
       <c r="H31" s="8" t="n">
-        <v>0.023</v>
+        <v>0.0229</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>0.0333</v>
+        <v>0.0334</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="K31" s="9" t="n"/>
       <c r="L31" s="9" t="n"/>
@@ -2322,7 +2322,7 @@
         <v/>
       </c>
       <c r="Q31" s="12" t="n">
-        <v>10.3014</v>
+        <v>10.2894</v>
       </c>
     </row>
     <row r="32">
@@ -2365,7 +2365,7 @@
         <v>0.0334</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>-0.0008</v>
+        <v>0</v>
       </c>
       <c r="K32" s="9" t="n"/>
       <c r="L32" s="9" t="n"/>
@@ -2385,7 +2385,7 @@
         <v/>
       </c>
       <c r="Q32" s="12" t="n">
-        <v>5.07</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="33">
@@ -2428,7 +2428,7 @@
         <v>0.033</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0</v>
       </c>
       <c r="K33" s="9" t="n"/>
       <c r="L33" s="9" t="n"/>
@@ -2448,7 +2448,7 @@
         <v/>
       </c>
       <c r="Q33" s="12" t="n">
-        <v>10.2902</v>
+        <v>10.2802</v>
       </c>
     </row>
     <row r="34">
@@ -2491,7 +2491,7 @@
         <v>0.033</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0</v>
       </c>
       <c r="K34" s="9" t="n"/>
       <c r="L34" s="9" t="n"/>
@@ -2511,7 +2511,7 @@
         <v/>
       </c>
       <c r="Q34" s="12" t="n">
-        <v>10.0893</v>
+        <v>10.0795</v>
       </c>
     </row>
     <row r="35">
@@ -2574,7 +2574,7 @@
         <v/>
       </c>
       <c r="Q35" s="12" t="n">
-        <v>5.4384</v>
+        <v>5.4328</v>
       </c>
     </row>
     <row r="36">
@@ -2637,7 +2637,7 @@
         <v/>
       </c>
       <c r="Q36" s="12" t="n">
-        <v>5.0675</v>
+        <v>5.0623</v>
       </c>
     </row>
     <row r="37">
@@ -2680,7 +2680,7 @@
         <v>0.0382</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0</v>
       </c>
       <c r="K37" s="9" t="n"/>
       <c r="L37" s="9" t="n"/>
@@ -2700,7 +2700,7 @@
         <v/>
       </c>
       <c r="Q37" s="12" t="n">
-        <v>5.05</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="38">
@@ -2740,10 +2740,10 @@
         <v>0.0245</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>0.0382</v>
+        <v>0.038</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>-0.0003</v>
+        <v>-0.0002</v>
       </c>
       <c r="K38" s="9" t="n"/>
       <c r="L38" s="9" t="n"/>
@@ -2763,7 +2763,7 @@
         <v/>
       </c>
       <c r="Q38" s="12" t="n">
-        <v>25.82</v>
+        <v>25.84</v>
       </c>
     </row>
     <row r="39">
@@ -2803,10 +2803,10 @@
         <v>0.0245</v>
       </c>
       <c r="I39" s="8" t="n">
-        <v>0.0382</v>
+        <v>0.038</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>-0.0003</v>
+        <v>-0.0002</v>
       </c>
       <c r="K39" s="9" t="n"/>
       <c r="L39" s="9" t="n"/>
@@ -2826,7 +2826,7 @@
         <v/>
       </c>
       <c r="Q39" s="12" t="n">
-        <v>9.18</v>
+        <v>9.19</v>
       </c>
     </row>
     <row r="40">
@@ -2866,10 +2866,10 @@
         <v>0.0235</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>0.0379</v>
+        <v>0.0378</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>-0.0002</v>
+        <v>-0.0001</v>
       </c>
       <c r="K40" s="9" t="n"/>
       <c r="L40" s="9" t="n"/>
@@ -2889,7 +2889,7 @@
         <v/>
       </c>
       <c r="Q40" s="12" t="n">
-        <v>10.6791</v>
+        <v>10.6864</v>
       </c>
     </row>
     <row r="41">
@@ -2929,10 +2929,10 @@
         <v>0.0235</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>0.0379</v>
+        <v>0.0378</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>-0.0002</v>
+        <v>-0.0001</v>
       </c>
       <c r="K41" s="9" t="n"/>
       <c r="L41" s="9" t="n"/>
@@ -2952,7 +2952,7 @@
         <v/>
       </c>
       <c r="Q41" s="12" t="n">
-        <v>10.3172</v>
+        <v>10.3242</v>
       </c>
     </row>
     <row r="42">
@@ -3015,7 +3015,7 @@
         <v/>
       </c>
       <c r="Q42" s="12" t="n">
-        <v>5.5771</v>
+        <v>5.5745</v>
       </c>
     </row>
     <row r="43">
@@ -3078,7 +3078,7 @@
         <v/>
       </c>
       <c r="Q43" s="12" t="n">
-        <v>5.2159</v>
+        <v>5.2135</v>
       </c>
     </row>
     <row r="44">
@@ -3121,7 +3121,7 @@
         <v>0.0369</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>-0.0005</v>
+        <v>0</v>
       </c>
       <c r="K44" s="9" t="n"/>
       <c r="L44" s="9" t="n"/>
@@ -3141,28 +3141,28 @@
         <v/>
       </c>
       <c r="Q44" s="12" t="n">
-        <v>5.11</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2028 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>Amundi Fixed Maturity 2027 Italy BTP Government Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>LU2810185665</t>
+          <t>LU2780872128</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -3171,25 +3171,25 @@
         </is>
       </c>
       <c r="F45" s="6" t="n">
-        <v>47026</v>
+        <v>46752</v>
       </c>
       <c r="G45" s="7">
         <f>IF(F45="","",MAX(0,YEARFRAC(TODAY(),F45)))</f>
         <v/>
       </c>
       <c r="H45" s="8" t="n">
-        <v>0.0207</v>
+        <v>0.0265</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>0.0368</v>
+        <v>0.031</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0.0001</v>
       </c>
       <c r="K45" s="9" t="n"/>
       <c r="L45" s="9" t="n"/>
       <c r="M45" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N45" s="10">
         <f>IF(D45="Govt",$B$1,$B$2)</f>
@@ -3204,28 +3204,28 @@
         <v/>
       </c>
       <c r="Q45" s="12" t="n">
-        <v>35.78</v>
+        <v>10.3372</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2027 Italy BTP Government Bond UCITS ETF Dist</t>
+          <t>Xtrackers II Target Maturity Sept 2028 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>LU2780872128</t>
+          <t>LU2810185665</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -3234,25 +3234,25 @@
         </is>
       </c>
       <c r="F46" s="6" t="n">
-        <v>46752</v>
+        <v>47026</v>
       </c>
       <c r="G46" s="7">
         <f>IF(F46="","",MAX(0,YEARFRAC(TODAY(),F46)))</f>
         <v/>
       </c>
       <c r="H46" s="8" t="n">
-        <v>0.0265</v>
+        <v>0.0207</v>
       </c>
       <c r="I46" s="8" t="n">
-        <v>0.0309</v>
+        <v>0.0365</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>-0.0001</v>
+        <v>-0.0003</v>
       </c>
       <c r="K46" s="9" t="n"/>
       <c r="L46" s="9" t="n"/>
       <c r="M46" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N46" s="10">
         <f>IF(D46="Govt",$B$1,$B$2)</f>
@@ -3267,7 +3267,7 @@
         <v/>
       </c>
       <c r="Q46" s="12" t="n">
-        <v>10.3407</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="47">
@@ -3307,7 +3307,7 @@
         <v>0.015</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>0.0298</v>
+        <v>0.0299</v>
       </c>
       <c r="J47" s="9" t="n">
         <v>0.0001</v>
@@ -3330,7 +3330,7 @@
         <v/>
       </c>
       <c r="Q47" s="12" t="n">
-        <v>10.1793</v>
+        <v>10.1779</v>
       </c>
     </row>
     <row r="48">
@@ -3370,7 +3370,7 @@
         <v>0.0105</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>0.0287</v>
+        <v>0.0288</v>
       </c>
       <c r="J48" s="9" t="n">
         <v>0.0001</v>
@@ -3393,28 +3393,28 @@
         <v/>
       </c>
       <c r="Q48" s="12" t="n">
-        <v>10.3526</v>
+        <v>10.3511</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2027 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>Amundi Fixed Maturity 2026 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>IE000LGHLQ71</t>
+          <t>LU2872291278</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -3423,25 +3423,25 @@
         </is>
       </c>
       <c r="F49" s="6" t="n">
-        <v>46752</v>
+        <v>46387</v>
       </c>
       <c r="G49" s="7">
         <f>IF(F49="","",MAX(0,YEARFRAC(TODAY(),F49)))</f>
         <v/>
       </c>
       <c r="H49" s="8" t="n">
-        <v>0.0197</v>
+        <v>0.0023</v>
       </c>
       <c r="I49" s="8" t="n">
-        <v>0.0335</v>
+        <v>0.0285</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0</v>
+        <v>0.0021</v>
       </c>
       <c r="K49" s="9" t="n"/>
       <c r="L49" s="9" t="n"/>
       <c r="M49" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0009</v>
       </c>
       <c r="N49" s="10">
         <f>IF(D49="Govt",$B$1,$B$2)</f>
@@ -3456,7 +3456,7 @@
         <v/>
       </c>
       <c r="Q49" s="12" t="n">
-        <v>5.7102</v>
+        <v>10.2638</v>
       </c>
     </row>
     <row r="50">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2027 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>Invesco BulletShares 2027 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>IE000XOS4OJ6</t>
+          <t>IE000LGHLQ71</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
@@ -3519,23 +3519,23 @@
         <v/>
       </c>
       <c r="Q50" s="12" t="n">
-        <v>5.3377</v>
+        <v>5.7106</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2027 Term € Corp UCITS ETF</t>
+          <t>Invesco BulletShares 2027 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>IE000ZOI8OK5</t>
+          <t>IE000XOS4OJ6</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F51" s="6" t="n">
@@ -3556,18 +3556,18 @@
         <v/>
       </c>
       <c r="H51" s="8" t="n">
-        <v>0.0195</v>
+        <v>0.0197</v>
       </c>
       <c r="I51" s="8" t="n">
-        <v>0.0331</v>
+        <v>0.0335</v>
       </c>
       <c r="J51" s="9" t="n">
-        <v>-0.0004</v>
+        <v>0</v>
       </c>
       <c r="K51" s="9" t="n"/>
       <c r="L51" s="9" t="n"/>
       <c r="M51" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="N51" s="10">
         <f>IF(D51="Govt",$B$1,$B$2)</f>
@@ -3582,23 +3582,23 @@
         <v/>
       </c>
       <c r="Q51" s="12" t="n">
-        <v>5.65</v>
+        <v>5.3381</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>iShares iBonds Dec 2027 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>LU2673523218</t>
+          <t>IE000ZOI8OK5</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -3608,24 +3608,24 @@
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F52" s="6" t="n">
-        <v>46660</v>
+        <v>46752</v>
       </c>
       <c r="G52" s="7">
         <f>IF(F52="","",MAX(0,YEARFRAC(TODAY(),F52)))</f>
         <v/>
       </c>
       <c r="H52" s="8" t="n">
-        <v>0.0186</v>
+        <v>0.0195</v>
       </c>
       <c r="I52" s="8" t="n">
-        <v>0.0318</v>
+        <v>0.0331</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0</v>
       </c>
       <c r="K52" s="9" t="n"/>
       <c r="L52" s="9" t="n"/>
@@ -3645,7 +3645,7 @@
         <v/>
       </c>
       <c r="Q52" s="12" t="n">
-        <v>25.97</v>
+        <v>5.65</v>
       </c>
     </row>
     <row r="53">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1C</t>
+          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LU2673522830</t>
+          <t>LU2673523218</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F53" s="6" t="n">
@@ -3685,7 +3685,7 @@
         <v>0.0186</v>
       </c>
       <c r="I53" s="8" t="n">
-        <v>0.0318</v>
+        <v>0.0316</v>
       </c>
       <c r="J53" s="9" t="n">
         <v>-0.0002</v>
@@ -3708,28 +3708,28 @@
         <v/>
       </c>
       <c r="Q53" s="12" t="n">
-        <v>9.31</v>
+        <v>25.97</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2026 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>LU2872291278</t>
+          <t>LU2673522830</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -3738,25 +3738,25 @@
         </is>
       </c>
       <c r="F54" s="6" t="n">
-        <v>46387</v>
+        <v>46660</v>
       </c>
       <c r="G54" s="7">
         <f>IF(F54="","",MAX(0,YEARFRAC(TODAY(),F54)))</f>
         <v/>
       </c>
       <c r="H54" s="8" t="n">
-        <v>0.0023</v>
+        <v>0.0186</v>
       </c>
       <c r="I54" s="8" t="n">
-        <v>0.0264</v>
+        <v>0.0316</v>
       </c>
       <c r="J54" s="9" t="n">
-        <v>-0.0001</v>
+        <v>-0.0002</v>
       </c>
       <c r="K54" s="9" t="n"/>
       <c r="L54" s="9" t="n"/>
       <c r="M54" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N54" s="10">
         <f>IF(D54="Govt",$B$1,$B$2)</f>
@@ -3771,7 +3771,7 @@
         <v/>
       </c>
       <c r="Q54" s="12" t="n">
-        <v>10.2634</v>
+        <v>9.31</v>
       </c>
     </row>
     <row r="55">
@@ -3814,7 +3814,7 @@
         <v>0.0265</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0</v>
       </c>
       <c r="K55" s="9" t="n"/>
       <c r="L55" s="9" t="n"/>
@@ -3897,7 +3897,7 @@
         <v/>
       </c>
       <c r="Q56" s="12" t="n">
-        <v>5.7948</v>
+        <v>5.7955</v>
       </c>
     </row>
     <row r="57">
@@ -3960,7 +3960,7 @@
         <v/>
       </c>
       <c r="Q57" s="12" t="n">
-        <v>5.4184</v>
+        <v>5.419</v>
       </c>
     </row>
     <row r="58">
@@ -4003,7 +4003,7 @@
         <v>0.0273</v>
       </c>
       <c r="J58" s="9" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0</v>
       </c>
       <c r="K58" s="9" t="n"/>
       <c r="L58" s="9" t="n"/>

--- a/data/rendimenti_etf.xlsx
+++ b/data/rendimenti_etf.xlsx
@@ -533,7 +533,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Aggiornato il 20/10/2026 09:03 da yield_etf.csv</t>
+          <t>Aggiornato il 21/10/2026 09:03 da yield_etf.csv</t>
         </is>
       </c>
     </row>
@@ -658,13 +658,13 @@
         <v/>
       </c>
       <c r="H5" s="8" t="n">
-        <v>0.0389</v>
+        <v>0.0388</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>0.0499</v>
+        <v>0.0503</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="K5" s="9" t="n"/>
       <c r="L5" s="9" t="n"/>
@@ -721,13 +721,13 @@
         <v/>
       </c>
       <c r="H6" s="8" t="n">
-        <v>0.03759999999999999</v>
+        <v>0.0375</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0.0453</v>
+        <v>0.046</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0</v>
+        <v>0.0007</v>
       </c>
       <c r="K6" s="9" t="n"/>
       <c r="L6" s="9" t="n"/>
@@ -747,7 +747,7 @@
         <v/>
       </c>
       <c r="Q6" s="12" t="n">
-        <v>28.53</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="7">
@@ -787,10 +787,10 @@
         <v>0.0365</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0.0449</v>
+        <v>0.04559999999999999</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0.0007</v>
       </c>
       <c r="K7" s="9" t="n"/>
       <c r="L7" s="9" t="n"/>
@@ -810,7 +810,7 @@
         <v/>
       </c>
       <c r="Q7" s="12" t="n">
-        <v>29.33</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="8">
@@ -850,10 +850,10 @@
         <v>0.0355</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>0.04480000000000001</v>
+        <v>0.0455</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0</v>
+        <v>0.0007</v>
       </c>
       <c r="K8" s="9" t="n"/>
       <c r="L8" s="9" t="n"/>
@@ -873,7 +873,7 @@
         <v/>
       </c>
       <c r="Q8" s="12" t="n">
-        <v>4.83</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="9">
@@ -913,10 +913,10 @@
         <v>0.0349</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>0.04480000000000001</v>
+        <v>0.0453</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="K9" s="9" t="n"/>
       <c r="L9" s="9" t="n"/>
@@ -936,7 +936,7 @@
         <v/>
       </c>
       <c r="Q9" s="12" t="n">
-        <v>4.82</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="10">
@@ -976,10 +976,10 @@
         <v>0.0363</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>0.0445</v>
+        <v>0.0451</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="K10" s="9" t="n"/>
       <c r="L10" s="9" t="n"/>
@@ -999,7 +999,7 @@
         <v/>
       </c>
       <c r="Q10" s="12" t="n">
-        <v>4.74</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="11">
@@ -1039,10 +1039,10 @@
         <v>0.0347</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>0.0443</v>
+        <v>0.0449</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="K11" s="9" t="n"/>
       <c r="L11" s="9" t="n"/>
@@ -1062,7 +1062,7 @@
         <v/>
       </c>
       <c r="Q11" s="12" t="n">
-        <v>33.74</v>
+        <v>33.61</v>
       </c>
     </row>
     <row r="12">
@@ -1102,10 +1102,10 @@
         <v>0.0348</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>0.0438</v>
+        <v>0.0444</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="K12" s="9" t="n"/>
       <c r="L12" s="9" t="n"/>
@@ -1125,7 +1125,7 @@
         <v/>
       </c>
       <c r="Q12" s="12" t="n">
-        <v>4.76</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="13">
@@ -1165,10 +1165,10 @@
         <v>0.0338</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0.0436</v>
+        <v>0.0442</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="K13" s="9" t="n"/>
       <c r="L13" s="9" t="n"/>
@@ -1188,7 +1188,7 @@
         <v/>
       </c>
       <c r="Q13" s="12" t="n">
-        <v>9.359999999999999</v>
+        <v>9.33</v>
       </c>
     </row>
     <row r="14">
@@ -1228,10 +1228,10 @@
         <v>0.0338</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>0.0436</v>
+        <v>0.0442</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="K14" s="9" t="n"/>
       <c r="L14" s="9" t="n"/>
@@ -1251,7 +1251,7 @@
         <v/>
       </c>
       <c r="Q14" s="12" t="n">
-        <v>28.04</v>
+        <v>27.95</v>
       </c>
     </row>
     <row r="15">
@@ -1291,10 +1291,10 @@
         <v>0.0331</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>0.0431</v>
+        <v>0.0437</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="K15" s="9" t="n"/>
       <c r="L15" s="9" t="n"/>
@@ -1314,7 +1314,7 @@
         <v/>
       </c>
       <c r="Q15" s="12" t="n">
-        <v>4.78</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="16">
@@ -1354,10 +1354,10 @@
         <v>0.0329</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>0.0438</v>
+        <v>0.0443</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="K16" s="9" t="n"/>
       <c r="L16" s="9" t="n"/>
@@ -1383,49 +1383,49 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2030 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>Xtrackers II Target Maturity Sept 2032 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LU3120976132</t>
+          <t>LU2809864452</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
-        <v>47848</v>
+        <v>48487</v>
       </c>
       <c r="G17" s="7">
         <f>IF(F17="","",MAX(0,YEARFRAC(TODAY(),F17)))</f>
         <v/>
       </c>
       <c r="H17" s="8" t="n">
-        <v>0.0169</v>
+        <v>0.0282</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>0.0361</v>
+        <v>0.0433</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.0001</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="K17" s="9" t="n"/>
       <c r="L17" s="9" t="n"/>
       <c r="M17" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N17" s="10">
         <f>IF(D17="Govt",$B$1,$B$2)</f>
@@ -1440,23 +1440,23 @@
         <v/>
       </c>
       <c r="Q17" s="12" t="n">
-        <v>9.835100000000001</v>
+        <v>34.35</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2032 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>iShares iBonds Dec 2032 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LU2809864452</t>
+          <t>IE0000MR4GH9</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -1470,20 +1470,20 @@
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>48487</v>
+        <v>48579</v>
       </c>
       <c r="G18" s="7">
         <f>IF(F18="","",MAX(0,YEARFRAC(TODAY(),F18)))</f>
         <v/>
       </c>
       <c r="H18" s="8" t="n">
-        <v>0.0282</v>
+        <v>0.03</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>0.04269999999999999</v>
+        <v>0.0426</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="K18" s="9" t="n"/>
       <c r="L18" s="9" t="n"/>
@@ -1503,7 +1503,7 @@
         <v/>
       </c>
       <c r="Q18" s="12" t="n">
-        <v>34.44</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="19">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2032 Term € Corp UCITS ETF</t>
+          <t>iShares iBonds Dec 2031 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>IE0000MR4GH9</t>
+          <t>IE000I2WYEU9</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -1533,20 +1533,20 @@
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>48579</v>
+        <v>48213</v>
       </c>
       <c r="G19" s="7">
         <f>IF(F19="","",MAX(0,YEARFRAC(TODAY(),F19)))</f>
         <v/>
       </c>
       <c r="H19" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0286</v>
       </c>
       <c r="I19" s="8" t="n">
         <v>0.042</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="K19" s="9" t="n"/>
       <c r="L19" s="9" t="n"/>
@@ -1566,7 +1566,7 @@
         <v/>
       </c>
       <c r="Q19" s="12" t="n">
-        <v>4.83</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="20">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2029 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>Amundi Fixed Maturity 2030 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LU2872291781</t>
+          <t>LU3120976132</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -1596,20 +1596,20 @@
         </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>47483</v>
+        <v>47848</v>
       </c>
       <c r="G20" s="7">
         <f>IF(F20="","",MAX(0,YEARFRAC(TODAY(),F20)))</f>
         <v/>
       </c>
       <c r="H20" s="8" t="n">
-        <v>0.0208</v>
+        <v>0.0169</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>0.0352</v>
+        <v>0.0354</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.0001</v>
+        <v>-0.0007</v>
       </c>
       <c r="K20" s="9" t="n"/>
       <c r="L20" s="9" t="n"/>
@@ -1629,23 +1629,23 @@
         <v/>
       </c>
       <c r="Q20" s="12" t="n">
-        <v>9.9909</v>
+        <v>9.844799999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>BNP Paribas</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2031 Term € Corp UCITS ETF</t>
+          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2032 UCITS ETF C</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>IE000I2WYEU9</t>
+          <t>LU2823895847</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -1655,24 +1655,24 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F21" s="6" t="n">
-        <v>48213</v>
+        <v>48579</v>
       </c>
       <c r="G21" s="7">
         <f>IF(F21="","",MAX(0,YEARFRAC(TODAY(),F21)))</f>
         <v/>
       </c>
       <c r="H21" s="8" t="n">
-        <v>0.0286</v>
+        <v>0.0269</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>0.0414</v>
+        <v>0.04190000000000001</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="K21" s="9" t="n"/>
       <c r="L21" s="9" t="n"/>
@@ -1692,7 +1692,7 @@
         <v/>
       </c>
       <c r="Q21" s="12" t="n">
-        <v>4.88</v>
+        <v>10.453</v>
       </c>
     </row>
     <row r="22">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2032 UCITS ETF C</t>
+          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2032 UCITS ETF D</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>LU2823895847</t>
+          <t>LU2823895763</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
@@ -1732,10 +1732,10 @@
         <v>0.0269</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>0.0414</v>
+        <v>0.04190000000000001</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="K22" s="9" t="n"/>
       <c r="L22" s="9" t="n"/>
@@ -1755,23 +1755,23 @@
         <v/>
       </c>
       <c r="Q22" s="12" t="n">
-        <v>10.4811</v>
+        <v>10.0663</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BNP Paribas</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2032 UCITS ETF D</t>
+          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>LU2823895763</t>
+          <t>LU2673523135</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -1781,24 +1781,24 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>48579</v>
+        <v>48121</v>
       </c>
       <c r="G23" s="7">
         <f>IF(F23="","",MAX(0,YEARFRAC(TODAY(),F23)))</f>
         <v/>
       </c>
       <c r="H23" s="8" t="n">
-        <v>0.0269</v>
+        <v>0.0288</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>0.0414</v>
+        <v>0.0416</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0</v>
+        <v>0.0008</v>
       </c>
       <c r="K23" s="9" t="n"/>
       <c r="L23" s="9" t="n"/>
@@ -1818,7 +1818,7 @@
         <v/>
       </c>
       <c r="Q23" s="12" t="n">
-        <v>10.0933</v>
+        <v>9.81</v>
       </c>
     </row>
     <row r="24">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1C</t>
+          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>LU2673523135</t>
+          <t>LU2673523481</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
@@ -1858,10 +1858,10 @@
         <v>0.0288</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>0.0408</v>
+        <v>0.0416</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>-0.0004</v>
+        <v>0.0008</v>
       </c>
       <c r="K24" s="9" t="n"/>
       <c r="L24" s="9" t="n"/>
@@ -1881,7 +1881,7 @@
         <v/>
       </c>
       <c r="Q24" s="12" t="n">
-        <v>9.83</v>
+        <v>29.34</v>
       </c>
     </row>
     <row r="25">
@@ -1892,39 +1892,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>Xtrackers II Target Maturity Sept 2029 Italy and Spain Government Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>LU2673523481</t>
+          <t>LU0484969463</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F25" s="6" t="n">
-        <v>48121</v>
+        <v>47391</v>
       </c>
       <c r="G25" s="7">
         <f>IF(F25="","",MAX(0,YEARFRAC(TODAY(),F25)))</f>
         <v/>
       </c>
       <c r="H25" s="8" t="n">
-        <v>0.0288</v>
+        <v>0.0297</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>0.0408</v>
+        <v>0.035</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>-0.0004</v>
+        <v>0.0008</v>
       </c>
       <c r="K25" s="9" t="n"/>
       <c r="L25" s="9" t="n"/>
@@ -1944,28 +1944,28 @@
         <v/>
       </c>
       <c r="Q25" s="12" t="n">
-        <v>29.4</v>
+        <v>204.68</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>Amundi Fixed Maturity 2029 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>IE000I25S1V5</t>
+          <t>LU2872291781</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -1974,25 +1974,25 @@
         </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>47848</v>
+        <v>47483</v>
       </c>
       <c r="G26" s="7">
         <f>IF(F26="","",MAX(0,YEARFRAC(TODAY(),F26)))</f>
         <v/>
       </c>
       <c r="H26" s="8" t="n">
-        <v>0.0286</v>
+        <v>0.0208</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>0.0406</v>
+        <v>0.0346</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="K26" s="9" t="n"/>
       <c r="L26" s="9" t="n"/>
       <c r="M26" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0009</v>
       </c>
       <c r="N26" s="10">
         <f>IF(D26="Govt",$B$1,$B$2)</f>
@@ -2007,7 +2007,7 @@
         <v/>
       </c>
       <c r="Q26" s="12" t="n">
-        <v>5.3596</v>
+        <v>9.9977</v>
       </c>
     </row>
     <row r="27">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>IE000W6YTDH7</t>
+          <t>IE000I25S1V5</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F27" s="6" t="n">
@@ -2070,55 +2070,55 @@
         <v/>
       </c>
       <c r="Q27" s="12" t="n">
-        <v>4.9924</v>
+        <v>5.3645</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2029 Italy and Spain Government Bond UCITS ETF 1C</t>
+          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>LU0484969463</t>
+          <t>IE000W6YTDH7</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F28" s="6" t="n">
-        <v>47391</v>
+        <v>47848</v>
       </c>
       <c r="G28" s="7">
         <f>IF(F28="","",MAX(0,YEARFRAC(TODAY(),F28)))</f>
         <v/>
       </c>
       <c r="H28" s="8" t="n">
-        <v>0.0297</v>
+        <v>0.0286</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>0.0342</v>
+        <v>0.0406</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0</v>
       </c>
       <c r="K28" s="9" t="n"/>
       <c r="L28" s="9" t="n"/>
       <c r="M28" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="N28" s="10">
         <f>IF(D28="Govt",$B$1,$B$2)</f>
@@ -2133,7 +2133,7 @@
         <v/>
       </c>
       <c r="Q28" s="12" t="n">
-        <v>204.99</v>
+        <v>4.997</v>
       </c>
     </row>
     <row r="29">
@@ -2144,17 +2144,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2030 Term € Corp UCITS ETF</t>
+          <t>iShares iBonds Dec 2028 Term € Italy Govt Bond UCITS ETF</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>IE000LX17BP9</t>
+          <t>IE000Q2EQ5K8</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -2163,20 +2163,20 @@
         </is>
       </c>
       <c r="F29" s="6" t="n">
-        <v>47848</v>
+        <v>47118</v>
       </c>
       <c r="G29" s="7">
         <f>IF(F29="","",MAX(0,YEARFRAC(TODAY(),F29)))</f>
         <v/>
       </c>
       <c r="H29" s="8" t="n">
-        <v>0.028</v>
+        <v>0.0261</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>0.0398</v>
+        <v>0.0344</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="K29" s="9" t="n"/>
       <c r="L29" s="9" t="n"/>
@@ -2196,23 +2196,23 @@
         <v/>
       </c>
       <c r="Q29" s="12" t="n">
-        <v>5</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2030 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>iShares iBonds Dec 2030 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>LU2809864296</t>
+          <t>IE000LX17BP9</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -2226,20 +2226,20 @@
         </is>
       </c>
       <c r="F30" s="6" t="n">
-        <v>47756</v>
+        <v>47848</v>
       </c>
       <c r="G30" s="7">
         <f>IF(F30="","",MAX(0,YEARFRAC(TODAY(),F30)))</f>
         <v/>
       </c>
       <c r="H30" s="8" t="n">
-        <v>0.027</v>
+        <v>0.028</v>
       </c>
       <c r="I30" s="8" t="n">
-        <v>0.0397</v>
+        <v>0.0403</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0005</v>
       </c>
       <c r="K30" s="9" t="n"/>
       <c r="L30" s="9" t="n"/>
@@ -2259,28 +2259,28 @@
         <v/>
       </c>
       <c r="Q30" s="12" t="n">
-        <v>35.35</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2028 Euro Government Bond Yield + UCITS ETF Dist</t>
+          <t>Xtrackers II Target Maturity Sept 2030 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>LU2780871666</t>
+          <t>LU2809864296</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -2289,25 +2289,25 @@
         </is>
       </c>
       <c r="F31" s="6" t="n">
-        <v>47118</v>
+        <v>47756</v>
       </c>
       <c r="G31" s="7">
         <f>IF(F31="","",MAX(0,YEARFRAC(TODAY(),F31)))</f>
         <v/>
       </c>
       <c r="H31" s="8" t="n">
-        <v>0.0229</v>
+        <v>0.027</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>0.0334</v>
+        <v>0.04019999999999999</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.0001</v>
+        <v>0.0005</v>
       </c>
       <c r="K31" s="9" t="n"/>
       <c r="L31" s="9" t="n"/>
       <c r="M31" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N31" s="10">
         <f>IF(D31="Govt",$B$1,$B$2)</f>
@@ -2322,23 +2322,23 @@
         <v/>
       </c>
       <c r="Q31" s="12" t="n">
-        <v>10.2894</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2028 Term € Italy Govt Bond UCITS ETF</t>
+          <t>Amundi Fixed Maturity 2028 Euro Government Bond Yield + UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>IE000Q2EQ5K8</t>
+          <t>LU2780871666</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -2359,18 +2359,18 @@
         <v/>
       </c>
       <c r="H32" s="8" t="n">
-        <v>0.0261</v>
+        <v>0.0229</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>0.0334</v>
+        <v>0.0328</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="K32" s="9" t="n"/>
       <c r="L32" s="9" t="n"/>
       <c r="M32" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N32" s="10">
         <f>IF(D32="Govt",$B$1,$B$2)</f>
@@ -2385,47 +2385,47 @@
         <v/>
       </c>
       <c r="Q32" s="12" t="n">
-        <v>5.06</v>
+        <v>10.2969</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Dist</t>
+          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>LU2780871401</t>
+          <t>IE000P5IB8I8</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F33" s="6" t="n">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="G33" s="7">
         <f>IF(F33="","",MAX(0,YEARFRAC(TODAY(),F33)))</f>
         <v/>
       </c>
       <c r="H33" s="8" t="n">
-        <v>0.0184</v>
+        <v>0.0242</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>0.033</v>
+        <v>0.0386</v>
       </c>
       <c r="J33" s="9" t="n">
         <v>0</v>
@@ -2433,7 +2433,7 @@
       <c r="K33" s="9" t="n"/>
       <c r="L33" s="9" t="n"/>
       <c r="M33" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="N33" s="10">
         <f>IF(D33="Govt",$B$1,$B$2)</f>
@@ -2448,47 +2448,47 @@
         <v/>
       </c>
       <c r="Q33" s="12" t="n">
-        <v>10.2802</v>
+        <v>5.4362</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>LU2780871310</t>
+          <t>IE000ZC4C5Q1</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F34" s="6" t="n">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="G34" s="7">
         <f>IF(F34="","",MAX(0,YEARFRAC(TODAY(),F34)))</f>
         <v/>
       </c>
       <c r="H34" s="8" t="n">
-        <v>0.0184</v>
+        <v>0.0242</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>0.033</v>
+        <v>0.0386</v>
       </c>
       <c r="J34" s="9" t="n">
         <v>0</v>
@@ -2496,7 +2496,7 @@
       <c r="K34" s="9" t="n"/>
       <c r="L34" s="9" t="n"/>
       <c r="M34" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="N34" s="10">
         <f>IF(D34="Govt",$B$1,$B$2)</f>
@@ -2511,23 +2511,23 @@
         <v/>
       </c>
       <c r="Q34" s="12" t="n">
-        <v>10.0795</v>
+        <v>5.0655</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>iShares iBonds Dec 2029 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>IE000P5IB8I8</t>
+          <t>IE000IHURBR0</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F35" s="6" t="n">
@@ -2548,18 +2548,18 @@
         <v/>
       </c>
       <c r="H35" s="8" t="n">
-        <v>0.0242</v>
+        <v>0.0252</v>
       </c>
       <c r="I35" s="8" t="n">
-        <v>0.0386</v>
+        <v>0.0387</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="K35" s="9" t="n"/>
       <c r="L35" s="9" t="n"/>
       <c r="M35" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N35" s="10">
         <f>IF(D35="Govt",$B$1,$B$2)</f>
@@ -2574,28 +2574,28 @@
         <v/>
       </c>
       <c r="Q35" s="12" t="n">
-        <v>5.4328</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>IE000ZC4C5Q1</t>
+          <t>LU2780871401</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -2604,25 +2604,25 @@
         </is>
       </c>
       <c r="F36" s="6" t="n">
-        <v>47483</v>
+        <v>47118</v>
       </c>
       <c r="G36" s="7">
         <f>IF(F36="","",MAX(0,YEARFRAC(TODAY(),F36)))</f>
         <v/>
       </c>
       <c r="H36" s="8" t="n">
-        <v>0.0242</v>
+        <v>0.0184</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>0.0386</v>
+        <v>0.0325</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0</v>
+        <v>-0.0005</v>
       </c>
       <c r="K36" s="9" t="n"/>
       <c r="L36" s="9" t="n"/>
       <c r="M36" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0009</v>
       </c>
       <c r="N36" s="10">
         <f>IF(D36="Govt",$B$1,$B$2)</f>
@@ -2637,55 +2637,55 @@
         <v/>
       </c>
       <c r="Q36" s="12" t="n">
-        <v>5.0623</v>
+        <v>10.2864</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2029 Term € Corp UCITS ETF</t>
+          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>IE000IHURBR0</t>
+          <t>LU2780871310</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F37" s="6" t="n">
-        <v>47483</v>
+        <v>47118</v>
       </c>
       <c r="G37" s="7">
         <f>IF(F37="","",MAX(0,YEARFRAC(TODAY(),F37)))</f>
         <v/>
       </c>
       <c r="H37" s="8" t="n">
-        <v>0.0252</v>
+        <v>0.0184</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>0.0382</v>
+        <v>0.0325</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0</v>
+        <v>-0.0005</v>
       </c>
       <c r="K37" s="9" t="n"/>
       <c r="L37" s="9" t="n"/>
       <c r="M37" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N37" s="10">
         <f>IF(D37="Govt",$B$1,$B$2)</f>
@@ -2700,7 +2700,7 @@
         <v/>
       </c>
       <c r="Q37" s="12" t="n">
-        <v>5.04</v>
+        <v>10.0856</v>
       </c>
     </row>
     <row r="38">
@@ -2740,10 +2740,10 @@
         <v>0.0245</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>0.038</v>
+        <v>0.0385</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0005</v>
       </c>
       <c r="K38" s="9" t="n"/>
       <c r="L38" s="9" t="n"/>
@@ -2763,7 +2763,7 @@
         <v/>
       </c>
       <c r="Q38" s="12" t="n">
-        <v>25.84</v>
+        <v>25.81</v>
       </c>
     </row>
     <row r="39">
@@ -2803,10 +2803,10 @@
         <v>0.0245</v>
       </c>
       <c r="I39" s="8" t="n">
-        <v>0.038</v>
+        <v>0.0385</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0005</v>
       </c>
       <c r="K39" s="9" t="n"/>
       <c r="L39" s="9" t="n"/>
@@ -2826,7 +2826,7 @@
         <v/>
       </c>
       <c r="Q39" s="12" t="n">
-        <v>9.19</v>
+        <v>9.18</v>
       </c>
     </row>
     <row r="40">
@@ -2866,10 +2866,10 @@
         <v>0.0235</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>0.0378</v>
+        <v>0.0382</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0.0004</v>
       </c>
       <c r="K40" s="9" t="n"/>
       <c r="L40" s="9" t="n"/>
@@ -2889,7 +2889,7 @@
         <v/>
       </c>
       <c r="Q40" s="12" t="n">
-        <v>10.6864</v>
+        <v>10.675</v>
       </c>
     </row>
     <row r="41">
@@ -2929,10 +2929,10 @@
         <v>0.0235</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>0.0378</v>
+        <v>0.0382</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0.0004</v>
       </c>
       <c r="K41" s="9" t="n"/>
       <c r="L41" s="9" t="n"/>
@@ -2952,7 +2952,7 @@
         <v/>
       </c>
       <c r="Q41" s="12" t="n">
-        <v>10.3242</v>
+        <v>10.3132</v>
       </c>
     </row>
     <row r="42">
@@ -3015,7 +3015,7 @@
         <v/>
       </c>
       <c r="Q42" s="12" t="n">
-        <v>5.5745</v>
+        <v>5.5769</v>
       </c>
     </row>
     <row r="43">
@@ -3078,7 +3078,7 @@
         <v/>
       </c>
       <c r="Q43" s="12" t="n">
-        <v>5.2135</v>
+        <v>5.2157</v>
       </c>
     </row>
     <row r="44">
@@ -3115,13 +3115,13 @@
         <v/>
       </c>
       <c r="H44" s="8" t="n">
-        <v>0.0213</v>
+        <v>0.0214</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>0.0369</v>
+        <v>0.0373</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="K44" s="9" t="n"/>
       <c r="L44" s="9" t="n"/>
@@ -3147,22 +3147,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2027 Italy BTP Government Bond UCITS ETF Dist</t>
+          <t>Xtrackers II Target Maturity Sept 2028 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>LU2780872128</t>
+          <t>LU2810185665</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -3171,25 +3171,25 @@
         </is>
       </c>
       <c r="F45" s="6" t="n">
-        <v>46752</v>
+        <v>47026</v>
       </c>
       <c r="G45" s="7">
         <f>IF(F45="","",MAX(0,YEARFRAC(TODAY(),F45)))</f>
         <v/>
       </c>
       <c r="H45" s="8" t="n">
-        <v>0.0265</v>
+        <v>0.0207</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>0.031</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.0001</v>
+        <v>0.0005</v>
       </c>
       <c r="K45" s="9" t="n"/>
       <c r="L45" s="9" t="n"/>
       <c r="M45" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N45" s="10">
         <f>IF(D45="Govt",$B$1,$B$2)</f>
@@ -3204,28 +3204,28 @@
         <v/>
       </c>
       <c r="Q45" s="12" t="n">
-        <v>10.3372</v>
+        <v>35.79</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2028 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>Amundi Fixed Maturity 2027 Italy BTP Government Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>LU2810185665</t>
+          <t>LU2780872128</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -3234,25 +3234,25 @@
         </is>
       </c>
       <c r="F46" s="6" t="n">
-        <v>47026</v>
+        <v>46752</v>
       </c>
       <c r="G46" s="7">
         <f>IF(F46="","",MAX(0,YEARFRAC(TODAY(),F46)))</f>
         <v/>
       </c>
       <c r="H46" s="8" t="n">
-        <v>0.0207</v>
+        <v>0.0265</v>
       </c>
       <c r="I46" s="8" t="n">
-        <v>0.0365</v>
+        <v>0.0306</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>-0.0003</v>
+        <v>-0.0004</v>
       </c>
       <c r="K46" s="9" t="n"/>
       <c r="L46" s="9" t="n"/>
       <c r="M46" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N46" s="10">
         <f>IF(D46="Govt",$B$1,$B$2)</f>
@@ -3267,7 +3267,7 @@
         <v/>
       </c>
       <c r="Q46" s="12" t="n">
-        <v>35.8</v>
+        <v>10.3408</v>
       </c>
     </row>
     <row r="47">
@@ -3307,10 +3307,10 @@
         <v>0.015</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>0.0299</v>
+        <v>0.0297</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.0001</v>
+        <v>-0.0002</v>
       </c>
       <c r="K47" s="9" t="n"/>
       <c r="L47" s="9" t="n"/>
@@ -3330,7 +3330,7 @@
         <v/>
       </c>
       <c r="Q47" s="12" t="n">
-        <v>10.1779</v>
+        <v>10.1801</v>
       </c>
     </row>
     <row r="48">
@@ -3370,10 +3370,10 @@
         <v>0.0105</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>0.0288</v>
+        <v>0.0285</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.0001</v>
+        <v>-0.0003</v>
       </c>
       <c r="K48" s="9" t="n"/>
       <c r="L48" s="9" t="n"/>
@@ -3393,28 +3393,28 @@
         <v/>
       </c>
       <c r="Q48" s="12" t="n">
-        <v>10.3511</v>
+        <v>10.3546</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2026 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>Invesco BulletShares 2027 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>LU2872291278</t>
+          <t>IE000LGHLQ71</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -3423,25 +3423,25 @@
         </is>
       </c>
       <c r="F49" s="6" t="n">
-        <v>46387</v>
+        <v>46752</v>
       </c>
       <c r="G49" s="7">
         <f>IF(F49="","",MAX(0,YEARFRAC(TODAY(),F49)))</f>
         <v/>
       </c>
       <c r="H49" s="8" t="n">
-        <v>0.0023</v>
+        <v>0.0197</v>
       </c>
       <c r="I49" s="8" t="n">
-        <v>0.0285</v>
+        <v>0.0335</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.0021</v>
+        <v>0</v>
       </c>
       <c r="K49" s="9" t="n"/>
       <c r="L49" s="9" t="n"/>
       <c r="M49" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="N49" s="10">
         <f>IF(D49="Govt",$B$1,$B$2)</f>
@@ -3456,7 +3456,7 @@
         <v/>
       </c>
       <c r="Q49" s="12" t="n">
-        <v>10.2638</v>
+        <v>5.7114</v>
       </c>
     </row>
     <row r="50">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2027 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>Invesco BulletShares 2027 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>IE000LGHLQ71</t>
+          <t>IE000XOS4OJ6</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
@@ -3519,23 +3519,23 @@
         <v/>
       </c>
       <c r="Q50" s="12" t="n">
-        <v>5.7106</v>
+        <v>5.3388</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2027 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>iShares iBonds Dec 2027 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>IE000XOS4OJ6</t>
+          <t>IE000ZOI8OK5</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F51" s="6" t="n">
@@ -3556,18 +3556,18 @@
         <v/>
       </c>
       <c r="H51" s="8" t="n">
-        <v>0.0197</v>
+        <v>0.0195</v>
       </c>
       <c r="I51" s="8" t="n">
-        <v>0.0335</v>
+        <v>0.0334</v>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0</v>
+        <v>0.0003</v>
       </c>
       <c r="K51" s="9" t="n"/>
       <c r="L51" s="9" t="n"/>
       <c r="M51" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N51" s="10">
         <f>IF(D51="Govt",$B$1,$B$2)</f>
@@ -3582,23 +3582,23 @@
         <v/>
       </c>
       <c r="Q51" s="12" t="n">
-        <v>5.3381</v>
+        <v>5.65</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2027 Term € Corp UCITS ETF</t>
+          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>IE000ZOI8OK5</t>
+          <t>LU2673523218</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -3608,24 +3608,24 @@
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F52" s="6" t="n">
-        <v>46752</v>
+        <v>46660</v>
       </c>
       <c r="G52" s="7">
         <f>IF(F52="","",MAX(0,YEARFRAC(TODAY(),F52)))</f>
         <v/>
       </c>
       <c r="H52" s="8" t="n">
-        <v>0.0195</v>
+        <v>0.0186</v>
       </c>
       <c r="I52" s="8" t="n">
-        <v>0.0331</v>
+        <v>0.0321</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="K52" s="9" t="n"/>
       <c r="L52" s="9" t="n"/>
@@ -3645,7 +3645,7 @@
         <v/>
       </c>
       <c r="Q52" s="12" t="n">
-        <v>5.65</v>
+        <v>25.98</v>
       </c>
     </row>
     <row r="53">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LU2673523218</t>
+          <t>LU2673522830</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F53" s="6" t="n">
@@ -3685,10 +3685,10 @@
         <v>0.0186</v>
       </c>
       <c r="I53" s="8" t="n">
-        <v>0.0316</v>
+        <v>0.0321</v>
       </c>
       <c r="J53" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0005</v>
       </c>
       <c r="K53" s="9" t="n"/>
       <c r="L53" s="9" t="n"/>
@@ -3708,28 +3708,28 @@
         <v/>
       </c>
       <c r="Q53" s="12" t="n">
-        <v>25.97</v>
+        <v>9.31</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1C</t>
+          <t>Amundi Fixed Maturity 2026 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>LU2673522830</t>
+          <t>LU2872291278</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -3738,25 +3738,25 @@
         </is>
       </c>
       <c r="F54" s="6" t="n">
-        <v>46660</v>
+        <v>46387</v>
       </c>
       <c r="G54" s="7">
         <f>IF(F54="","",MAX(0,YEARFRAC(TODAY(),F54)))</f>
         <v/>
       </c>
       <c r="H54" s="8" t="n">
-        <v>0.0186</v>
+        <v>0.0023</v>
       </c>
       <c r="I54" s="8" t="n">
-        <v>0.0316</v>
+        <v>0.0266</v>
       </c>
       <c r="J54" s="9" t="n">
-        <v>-0.0002</v>
+        <v>-0.0019</v>
       </c>
       <c r="K54" s="9" t="n"/>
       <c r="L54" s="9" t="n"/>
       <c r="M54" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N54" s="10">
         <f>IF(D54="Govt",$B$1,$B$2)</f>
@@ -3771,7 +3771,7 @@
         <v/>
       </c>
       <c r="Q54" s="12" t="n">
-        <v>9.31</v>
+        <v>10.2644</v>
       </c>
     </row>
     <row r="55">
@@ -3811,10 +3811,10 @@
         <v>0.008800000000000001</v>
       </c>
       <c r="I55" s="8" t="n">
-        <v>0.0265</v>
+        <v>0.0268</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0</v>
+        <v>0.0003</v>
       </c>
       <c r="K55" s="9" t="n"/>
       <c r="L55" s="9" t="n"/>
@@ -3897,7 +3897,7 @@
         <v/>
       </c>
       <c r="Q56" s="12" t="n">
-        <v>5.7955</v>
+        <v>5.7961</v>
       </c>
     </row>
     <row r="57">
@@ -3960,7 +3960,7 @@
         <v/>
       </c>
       <c r="Q57" s="12" t="n">
-        <v>5.419</v>
+        <v>5.4196</v>
       </c>
     </row>
     <row r="58">
@@ -4000,10 +4000,10 @@
         <v>0.0054</v>
       </c>
       <c r="I58" s="8" t="n">
-        <v>0.0273</v>
+        <v>0.0279</v>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="K58" s="9" t="n"/>
       <c r="L58" s="9" t="n"/>

--- a/data/rendimenti_etf.xlsx
+++ b/data/rendimenti_etf.xlsx
@@ -533,7 +533,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Aggiornato il 21/10/2026 09:03 da yield_etf.csv</t>
+          <t>Aggiornato il 22/10/2026 09:03 da yield_etf.csv</t>
         </is>
       </c>
     </row>
@@ -658,13 +658,13 @@
         <v/>
       </c>
       <c r="H5" s="8" t="n">
-        <v>0.0388</v>
+        <v>0.039</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>0.0503</v>
+        <v>0.0505</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.0004</v>
+        <v>0.0002</v>
       </c>
       <c r="K5" s="9" t="n"/>
       <c r="L5" s="9" t="n"/>
@@ -721,13 +721,13 @@
         <v/>
       </c>
       <c r="H6" s="8" t="n">
-        <v>0.0375</v>
+        <v>0.0377</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0.046</v>
+        <v>0.0457</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.0007</v>
+        <v>-0.0003</v>
       </c>
       <c r="K6" s="9" t="n"/>
       <c r="L6" s="9" t="n"/>
@@ -747,7 +747,7 @@
         <v/>
       </c>
       <c r="Q6" s="12" t="n">
-        <v>28.39</v>
+        <v>28.46</v>
       </c>
     </row>
     <row r="7">
@@ -784,13 +784,13 @@
         <v/>
       </c>
       <c r="H7" s="8" t="n">
-        <v>0.0365</v>
+        <v>0.0367</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0.04559999999999999</v>
+        <v>0.0454</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.0007</v>
+        <v>-0.0002</v>
       </c>
       <c r="K7" s="9" t="n"/>
       <c r="L7" s="9" t="n"/>
@@ -810,7 +810,7 @@
         <v/>
       </c>
       <c r="Q7" s="12" t="n">
-        <v>29.2</v>
+        <v>29.26</v>
       </c>
     </row>
     <row r="8">
@@ -847,13 +847,13 @@
         <v/>
       </c>
       <c r="H8" s="8" t="n">
-        <v>0.0355</v>
+        <v>0.0356</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>0.0455</v>
+        <v>0.0451</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.0007</v>
+        <v>-0.0004</v>
       </c>
       <c r="K8" s="9" t="n"/>
       <c r="L8" s="9" t="n"/>
@@ -873,7 +873,7 @@
         <v/>
       </c>
       <c r="Q8" s="12" t="n">
-        <v>4.84</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="9">
@@ -913,10 +913,10 @@
         <v>0.0349</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>0.0453</v>
+        <v>0.0449</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.0005</v>
+        <v>-0.0004</v>
       </c>
       <c r="K9" s="9" t="n"/>
       <c r="L9" s="9" t="n"/>
@@ -936,7 +936,7 @@
         <v/>
       </c>
       <c r="Q9" s="12" t="n">
-        <v>4.84</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="10">
@@ -976,10 +976,10 @@
         <v>0.0363</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>0.0451</v>
+        <v>0.0447</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.0004</v>
       </c>
       <c r="K10" s="9" t="n"/>
       <c r="L10" s="9" t="n"/>
@@ -999,7 +999,7 @@
         <v/>
       </c>
       <c r="Q10" s="12" t="n">
-        <v>4.75</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="11">
@@ -1036,13 +1036,13 @@
         <v/>
       </c>
       <c r="H11" s="8" t="n">
-        <v>0.0347</v>
+        <v>0.0351</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>0.0449</v>
+        <v>0.0445</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.0004</v>
       </c>
       <c r="K11" s="9" t="n"/>
       <c r="L11" s="9" t="n"/>
@@ -1062,7 +1062,7 @@
         <v/>
       </c>
       <c r="Q11" s="12" t="n">
-        <v>33.61</v>
+        <v>33.67</v>
       </c>
     </row>
     <row r="12">
@@ -1102,10 +1102,10 @@
         <v>0.0348</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>0.0444</v>
+        <v>0.044</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.0004</v>
       </c>
       <c r="K12" s="9" t="n"/>
       <c r="L12" s="9" t="n"/>
@@ -1125,7 +1125,7 @@
         <v/>
       </c>
       <c r="Q12" s="12" t="n">
-        <v>4.77</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="13">
@@ -1165,10 +1165,10 @@
         <v>0.0338</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0.0442</v>
+        <v>0.044</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.0002</v>
       </c>
       <c r="K13" s="9" t="n"/>
       <c r="L13" s="9" t="n"/>
@@ -1188,7 +1188,7 @@
         <v/>
       </c>
       <c r="Q13" s="12" t="n">
-        <v>9.33</v>
+        <v>9.34</v>
       </c>
     </row>
     <row r="14">
@@ -1228,10 +1228,10 @@
         <v>0.0338</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>0.0442</v>
+        <v>0.044</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.0002</v>
       </c>
       <c r="K14" s="9" t="n"/>
       <c r="L14" s="9" t="n"/>
@@ -1251,7 +1251,7 @@
         <v/>
       </c>
       <c r="Q14" s="12" t="n">
-        <v>27.95</v>
+        <v>27.98</v>
       </c>
     </row>
     <row r="15">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2033 Term € Corp UCITS ETF</t>
+          <t>iShares iBonds Dec 2028 Term € Corp Crossover UCITS ETF</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>IE000E0NL9T3</t>
+          <t>IE0003HV7CS6</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -1277,29 +1277,29 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
-        <v>48944</v>
+        <v>47118</v>
       </c>
       <c r="G15" s="7">
         <f>IF(F15="","",MAX(0,YEARFRAC(TODAY(),F15)))</f>
         <v/>
       </c>
       <c r="H15" s="8" t="n">
-        <v>0.0331</v>
+        <v>0.0329</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>0.0437</v>
+        <v>0.0444</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0001</v>
       </c>
       <c r="K15" s="9" t="n"/>
       <c r="L15" s="9" t="n"/>
       <c r="M15" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.002</v>
       </c>
       <c r="N15" s="10">
         <f>IF(D15="Govt",$B$1,$B$2)</f>
@@ -1314,7 +1314,7 @@
         <v/>
       </c>
       <c r="Q15" s="12" t="n">
-        <v>4.79</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="16">
@@ -1325,12 +1325,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2028 Term € Corp Crossover UCITS ETF</t>
+          <t>iShares iBonds Dec 2033 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>IE0003HV7CS6</t>
+          <t>IE000E0NL9T3</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -1340,29 +1340,29 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>47118</v>
+        <v>48944</v>
       </c>
       <c r="G16" s="7">
         <f>IF(F16="","",MAX(0,YEARFRAC(TODAY(),F16)))</f>
         <v/>
       </c>
       <c r="H16" s="8" t="n">
-        <v>0.0329</v>
+        <v>0.0331</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>0.0443</v>
+        <v>0.0434</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.0005</v>
+        <v>-0.0003</v>
       </c>
       <c r="K16" s="9" t="n"/>
       <c r="L16" s="9" t="n"/>
       <c r="M16" s="8" t="n">
-        <v>0.002</v>
+        <v>0.0012</v>
       </c>
       <c r="N16" s="10">
         <f>IF(D16="Govt",$B$1,$B$2)</f>
@@ -1377,7 +1377,7 @@
         <v/>
       </c>
       <c r="Q16" s="12" t="n">
-        <v>5.1</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="17">
@@ -1417,10 +1417,10 @@
         <v>0.0282</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>0.0433</v>
+        <v>0.0431</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.0002</v>
       </c>
       <c r="K17" s="9" t="n"/>
       <c r="L17" s="9" t="n"/>
@@ -1440,7 +1440,7 @@
         <v/>
       </c>
       <c r="Q17" s="12" t="n">
-        <v>34.35</v>
+        <v>34.38</v>
       </c>
     </row>
     <row r="18">
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="H18" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0305</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>0.0426</v>
+        <v>0.0424</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.0002</v>
       </c>
       <c r="K18" s="9" t="n"/>
       <c r="L18" s="9" t="n"/>
@@ -1503,55 +1503,55 @@
         <v/>
       </c>
       <c r="Q18" s="12" t="n">
-        <v>4.84</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2031 Term € Corp UCITS ETF</t>
+          <t>Amundi Fixed Maturity 2030 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>IE000I2WYEU9</t>
+          <t>LU3120976132</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>48213</v>
+        <v>47848</v>
       </c>
       <c r="G19" s="7">
         <f>IF(F19="","",MAX(0,YEARFRAC(TODAY(),F19)))</f>
         <v/>
       </c>
       <c r="H19" s="8" t="n">
-        <v>0.0286</v>
+        <v>0.0169</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>0.042</v>
+        <v>0.0353</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.0001</v>
       </c>
       <c r="K19" s="9" t="n"/>
       <c r="L19" s="9" t="n"/>
       <c r="M19" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N19" s="10">
         <f>IF(D19="Govt",$B$1,$B$2)</f>
@@ -1566,55 +1566,55 @@
         <v/>
       </c>
       <c r="Q19" s="12" t="n">
-        <v>4.89</v>
+        <v>9.826599999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2030 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>iShares iBonds Dec 2031 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LU3120976132</t>
+          <t>IE000I2WYEU9</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>47848</v>
+        <v>48213</v>
       </c>
       <c r="G20" s="7">
         <f>IF(F20="","",MAX(0,YEARFRAC(TODAY(),F20)))</f>
         <v/>
       </c>
       <c r="H20" s="8" t="n">
-        <v>0.0169</v>
+        <v>0.0286</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>0.0354</v>
+        <v>0.0417</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>-0.0007</v>
+        <v>-0.0003</v>
       </c>
       <c r="K20" s="9" t="n"/>
       <c r="L20" s="9" t="n"/>
       <c r="M20" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N20" s="10">
         <f>IF(D20="Govt",$B$1,$B$2)</f>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="Q20" s="12" t="n">
-        <v>9.844799999999999</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="21">
@@ -1669,10 +1669,10 @@
         <v>0.0269</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>0.04190000000000001</v>
+        <v>0.0416</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.0005</v>
+        <v>-0.0003</v>
       </c>
       <c r="K21" s="9" t="n"/>
       <c r="L21" s="9" t="n"/>
@@ -1692,7 +1692,7 @@
         <v/>
       </c>
       <c r="Q21" s="12" t="n">
-        <v>10.453</v>
+        <v>10.4692</v>
       </c>
     </row>
     <row r="22">
@@ -1732,10 +1732,10 @@
         <v>0.0269</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>0.04190000000000001</v>
+        <v>0.0416</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.0005</v>
+        <v>-0.0003</v>
       </c>
       <c r="K22" s="9" t="n"/>
       <c r="L22" s="9" t="n"/>
@@ -1755,7 +1755,7 @@
         <v/>
       </c>
       <c r="Q22" s="12" t="n">
-        <v>10.0663</v>
+        <v>10.0818</v>
       </c>
     </row>
     <row r="23">
@@ -1792,13 +1792,13 @@
         <v/>
       </c>
       <c r="H23" s="8" t="n">
-        <v>0.0288</v>
+        <v>0.0287</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>0.0416</v>
+        <v>0.0414</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.0008</v>
+        <v>-0.0002</v>
       </c>
       <c r="K23" s="9" t="n"/>
       <c r="L23" s="9" t="n"/>
@@ -1818,7 +1818,7 @@
         <v/>
       </c>
       <c r="Q23" s="12" t="n">
-        <v>9.81</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="24">
@@ -1855,13 +1855,13 @@
         <v/>
       </c>
       <c r="H24" s="8" t="n">
-        <v>0.0288</v>
+        <v>0.0287</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>0.0416</v>
+        <v>0.0414</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.0008</v>
+        <v>-0.0002</v>
       </c>
       <c r="K24" s="9" t="n"/>
       <c r="L24" s="9" t="n"/>
@@ -1881,23 +1881,23 @@
         <v/>
       </c>
       <c r="Q24" s="12" t="n">
-        <v>29.34</v>
+        <v>29.38</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2029 Italy and Spain Government Bond UCITS ETF 1C</t>
+          <t>Amundi Fixed Maturity 2029 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>LU0484969463</t>
+          <t>LU2872291781</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -1911,25 +1911,25 @@
         </is>
       </c>
       <c r="F25" s="6" t="n">
-        <v>47391</v>
+        <v>47483</v>
       </c>
       <c r="G25" s="7">
         <f>IF(F25="","",MAX(0,YEARFRAC(TODAY(),F25)))</f>
         <v/>
       </c>
       <c r="H25" s="8" t="n">
-        <v>0.0297</v>
+        <v>0.0208</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>0.035</v>
+        <v>0.0344</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.0008</v>
+        <v>-0.0002</v>
       </c>
       <c r="K25" s="9" t="n"/>
       <c r="L25" s="9" t="n"/>
       <c r="M25" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N25" s="10">
         <f>IF(D25="Govt",$B$1,$B$2)</f>
@@ -1944,28 +1944,28 @@
         <v/>
       </c>
       <c r="Q25" s="12" t="n">
-        <v>204.68</v>
+        <v>9.9834</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2029 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>LU2872291781</t>
+          <t>IE000I25S1V5</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -1974,25 +1974,25 @@
         </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>47483</v>
+        <v>47848</v>
       </c>
       <c r="G26" s="7">
         <f>IF(F26="","",MAX(0,YEARFRAC(TODAY(),F26)))</f>
         <v/>
       </c>
       <c r="H26" s="8" t="n">
-        <v>0.0208</v>
+        <v>0.0286</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>0.0346</v>
+        <v>0.0406</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0</v>
       </c>
       <c r="K26" s="9" t="n"/>
       <c r="L26" s="9" t="n"/>
       <c r="M26" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="N26" s="10">
         <f>IF(D26="Govt",$B$1,$B$2)</f>
@@ -2007,7 +2007,7 @@
         <v/>
       </c>
       <c r="Q26" s="12" t="n">
-        <v>9.9977</v>
+        <v>5.357</v>
       </c>
     </row>
     <row r="27">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>IE000I25S1V5</t>
+          <t>IE000W6YTDH7</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F27" s="6" t="n">
@@ -2070,55 +2070,55 @@
         <v/>
       </c>
       <c r="Q27" s="12" t="n">
-        <v>5.3645</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>Xtrackers II Target Maturity Sept 2029 Italy and Spain Government Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>IE000W6YTDH7</t>
+          <t>LU0484969463</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F28" s="6" t="n">
-        <v>47848</v>
+        <v>47391</v>
       </c>
       <c r="G28" s="7">
         <f>IF(F28="","",MAX(0,YEARFRAC(TODAY(),F28)))</f>
         <v/>
       </c>
       <c r="H28" s="8" t="n">
-        <v>0.0286</v>
+        <v>0.0297</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>0.0406</v>
+        <v>0.0346</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0</v>
+        <v>-0.0004</v>
       </c>
       <c r="K28" s="9" t="n"/>
       <c r="L28" s="9" t="n"/>
       <c r="M28" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N28" s="10">
         <f>IF(D28="Govt",$B$1,$B$2)</f>
@@ -2133,7 +2133,7 @@
         <v/>
       </c>
       <c r="Q28" s="12" t="n">
-        <v>4.997</v>
+        <v>204.93</v>
       </c>
     </row>
     <row r="29">
@@ -2173,10 +2173,10 @@
         <v>0.0261</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>0.0344</v>
+        <v>0.0341</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.001</v>
+        <v>-0.0003</v>
       </c>
       <c r="K29" s="9" t="n"/>
       <c r="L29" s="9" t="n"/>
@@ -2236,10 +2236,10 @@
         <v>0.028</v>
       </c>
       <c r="I30" s="8" t="n">
-        <v>0.0403</v>
+        <v>0.0401</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.0005</v>
+        <v>-0.0002</v>
       </c>
       <c r="K30" s="9" t="n"/>
       <c r="L30" s="9" t="n"/>
@@ -2259,7 +2259,7 @@
         <v/>
       </c>
       <c r="Q30" s="12" t="n">
-        <v>5</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="31">
@@ -2299,10 +2299,10 @@
         <v>0.027</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>0.04019999999999999</v>
+        <v>0.04</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.0005</v>
+        <v>-0.0002</v>
       </c>
       <c r="K31" s="9" t="n"/>
       <c r="L31" s="9" t="n"/>
@@ -2322,55 +2322,55 @@
         <v/>
       </c>
       <c r="Q31" s="12" t="n">
-        <v>35.3</v>
+        <v>35.33</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2028 Euro Government Bond Yield + UCITS ETF Dist</t>
+          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>LU2780871666</t>
+          <t>IE000P5IB8I8</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F32" s="6" t="n">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="G32" s="7">
         <f>IF(F32="","",MAX(0,YEARFRAC(TODAY(),F32)))</f>
         <v/>
       </c>
       <c r="H32" s="8" t="n">
-        <v>0.0229</v>
+        <v>0.0242</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>0.0328</v>
+        <v>0.0386</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0</v>
       </c>
       <c r="K32" s="9" t="n"/>
       <c r="L32" s="9" t="n"/>
       <c r="M32" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="N32" s="10">
         <f>IF(D32="Govt",$B$1,$B$2)</f>
@@ -2385,7 +2385,7 @@
         <v/>
       </c>
       <c r="Q32" s="12" t="n">
-        <v>10.2969</v>
+        <v>5.4314</v>
       </c>
     </row>
     <row r="33">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>IE000P5IB8I8</t>
+          <t>IE000ZC4C5Q1</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F33" s="6" t="n">
@@ -2448,28 +2448,28 @@
         <v/>
       </c>
       <c r="Q33" s="12" t="n">
-        <v>5.4362</v>
+        <v>5.061</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>Amundi Fixed Maturity 2028 Euro Government Bond Yield + UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>IE000ZC4C5Q1</t>
+          <t>LU2780871666</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -2478,25 +2478,25 @@
         </is>
       </c>
       <c r="F34" s="6" t="n">
-        <v>47483</v>
+        <v>47118</v>
       </c>
       <c r="G34" s="7">
         <f>IF(F34="","",MAX(0,YEARFRAC(TODAY(),F34)))</f>
         <v/>
       </c>
       <c r="H34" s="8" t="n">
-        <v>0.0242</v>
+        <v>0.0229</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>0.0386</v>
+        <v>0.0326</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0</v>
+        <v>-0.0002</v>
       </c>
       <c r="K34" s="9" t="n"/>
       <c r="L34" s="9" t="n"/>
       <c r="M34" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0009</v>
       </c>
       <c r="N34" s="10">
         <f>IF(D34="Govt",$B$1,$B$2)</f>
@@ -2511,7 +2511,7 @@
         <v/>
       </c>
       <c r="Q34" s="12" t="n">
-        <v>5.0655</v>
+        <v>10.2883</v>
       </c>
     </row>
     <row r="35">
@@ -2551,10 +2551,10 @@
         <v>0.0252</v>
       </c>
       <c r="I35" s="8" t="n">
-        <v>0.0387</v>
+        <v>0.0385</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.0005</v>
+        <v>-0.0002</v>
       </c>
       <c r="K35" s="9" t="n"/>
       <c r="L35" s="9" t="n"/>
@@ -2574,7 +2574,7 @@
         <v/>
       </c>
       <c r="Q35" s="12" t="n">
-        <v>5.05</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="36">
@@ -2614,10 +2614,10 @@
         <v>0.0184</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>0.0325</v>
+        <v>0.0323</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>-0.0005</v>
+        <v>-0.0002</v>
       </c>
       <c r="K36" s="9" t="n"/>
       <c r="L36" s="9" t="n"/>
@@ -2637,7 +2637,7 @@
         <v/>
       </c>
       <c r="Q36" s="12" t="n">
-        <v>10.2864</v>
+        <v>10.2787</v>
       </c>
     </row>
     <row r="37">
@@ -2677,10 +2677,10 @@
         <v>0.0184</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>0.0325</v>
+        <v>0.0323</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>-0.0005</v>
+        <v>-0.0002</v>
       </c>
       <c r="K37" s="9" t="n"/>
       <c r="L37" s="9" t="n"/>
@@ -2700,7 +2700,7 @@
         <v/>
       </c>
       <c r="Q37" s="12" t="n">
-        <v>10.0856</v>
+        <v>10.078</v>
       </c>
     </row>
     <row r="38">
@@ -2740,10 +2740,10 @@
         <v>0.0245</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>0.0385</v>
+        <v>0.0383</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.0005</v>
+        <v>-0.0002</v>
       </c>
       <c r="K38" s="9" t="n"/>
       <c r="L38" s="9" t="n"/>
@@ -2763,7 +2763,7 @@
         <v/>
       </c>
       <c r="Q38" s="12" t="n">
-        <v>25.81</v>
+        <v>25.83</v>
       </c>
     </row>
     <row r="39">
@@ -2803,10 +2803,10 @@
         <v>0.0245</v>
       </c>
       <c r="I39" s="8" t="n">
-        <v>0.0385</v>
+        <v>0.0383</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.0005</v>
+        <v>-0.0002</v>
       </c>
       <c r="K39" s="9" t="n"/>
       <c r="L39" s="9" t="n"/>
@@ -2866,10 +2866,10 @@
         <v>0.0235</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>0.0382</v>
+        <v>0.038</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.0004</v>
+        <v>-0.0002</v>
       </c>
       <c r="K40" s="9" t="n"/>
       <c r="L40" s="9" t="n"/>
@@ -2889,7 +2889,7 @@
         <v/>
       </c>
       <c r="Q40" s="12" t="n">
-        <v>10.675</v>
+        <v>10.6825</v>
       </c>
     </row>
     <row r="41">
@@ -2929,10 +2929,10 @@
         <v>0.0235</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>0.0382</v>
+        <v>0.038</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.0004</v>
+        <v>-0.0002</v>
       </c>
       <c r="K41" s="9" t="n"/>
       <c r="L41" s="9" t="n"/>
@@ -2952,7 +2952,7 @@
         <v/>
       </c>
       <c r="Q41" s="12" t="n">
-        <v>10.3132</v>
+        <v>10.3204</v>
       </c>
     </row>
     <row r="42">
@@ -3015,7 +3015,7 @@
         <v/>
       </c>
       <c r="Q42" s="12" t="n">
-        <v>5.5769</v>
+        <v>5.5747</v>
       </c>
     </row>
     <row r="43">
@@ -3078,7 +3078,7 @@
         <v/>
       </c>
       <c r="Q43" s="12" t="n">
-        <v>5.2157</v>
+        <v>5.2137</v>
       </c>
     </row>
     <row r="44">
@@ -3118,10 +3118,10 @@
         <v>0.0214</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>0.0373</v>
+        <v>0.0371</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.0004</v>
+        <v>-0.0002</v>
       </c>
       <c r="K44" s="9" t="n"/>
       <c r="L44" s="9" t="n"/>
@@ -3181,10 +3181,10 @@
         <v>0.0207</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.0368</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.0005</v>
+        <v>-0.0002</v>
       </c>
       <c r="K45" s="9" t="n"/>
       <c r="L45" s="9" t="n"/>
@@ -3204,7 +3204,7 @@
         <v/>
       </c>
       <c r="Q45" s="12" t="n">
-        <v>35.79</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="46">
@@ -3244,10 +3244,10 @@
         <v>0.0265</v>
       </c>
       <c r="I46" s="8" t="n">
-        <v>0.0306</v>
+        <v>0.0305</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>-0.0004</v>
+        <v>-0.0001</v>
       </c>
       <c r="K46" s="9" t="n"/>
       <c r="L46" s="9" t="n"/>
@@ -3267,7 +3267,7 @@
         <v/>
       </c>
       <c r="Q46" s="12" t="n">
-        <v>10.3408</v>
+        <v>10.3405</v>
       </c>
     </row>
     <row r="47">
@@ -3307,7 +3307,7 @@
         <v>0.015</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>0.0297</v>
+        <v>0.0295</v>
       </c>
       <c r="J47" s="9" t="n">
         <v>-0.0002</v>
@@ -3336,27 +3336,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2027 German Bund Government Bond UCITS ETF Dist</t>
+          <t>Invesco BulletShares 2027 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>LU2780871823</t>
+          <t>IE000LGHLQ71</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
@@ -3367,18 +3367,18 @@
         <v/>
       </c>
       <c r="H48" s="8" t="n">
-        <v>0.0105</v>
+        <v>0.0197</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>0.0285</v>
+        <v>0.0335</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0</v>
       </c>
       <c r="K48" s="9" t="n"/>
       <c r="L48" s="9" t="n"/>
       <c r="M48" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="N48" s="10">
         <f>IF(D48="Govt",$B$1,$B$2)</f>
@@ -3393,7 +3393,7 @@
         <v/>
       </c>
       <c r="Q48" s="12" t="n">
-        <v>10.3546</v>
+        <v>5.7117</v>
       </c>
     </row>
     <row r="49">
@@ -3404,12 +3404,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2027 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>Invesco BulletShares 2027 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>IE000LGHLQ71</t>
+          <t>IE000XOS4OJ6</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F49" s="6" t="n">
@@ -3456,28 +3456,28 @@
         <v/>
       </c>
       <c r="Q49" s="12" t="n">
-        <v>5.7114</v>
+        <v>5.3391</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2027 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>Amundi Fixed Maturity 2027 German Bund Government Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>IE000XOS4OJ6</t>
+          <t>LU2780871823</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -3493,18 +3493,18 @@
         <v/>
       </c>
       <c r="H50" s="8" t="n">
-        <v>0.0197</v>
+        <v>0.0105</v>
       </c>
       <c r="I50" s="8" t="n">
-        <v>0.0335</v>
+        <v>0.0283</v>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0</v>
+        <v>-0.0002</v>
       </c>
       <c r="K50" s="9" t="n"/>
       <c r="L50" s="9" t="n"/>
       <c r="M50" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0009</v>
       </c>
       <c r="N50" s="10">
         <f>IF(D50="Govt",$B$1,$B$2)</f>
@@ -3519,7 +3519,7 @@
         <v/>
       </c>
       <c r="Q50" s="12" t="n">
-        <v>5.3388</v>
+        <v>10.3551</v>
       </c>
     </row>
     <row r="51">
@@ -3562,7 +3562,7 @@
         <v>0.0334</v>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.0003</v>
+        <v>0</v>
       </c>
       <c r="K51" s="9" t="n"/>
       <c r="L51" s="9" t="n"/>
@@ -3619,13 +3619,13 @@
         <v/>
       </c>
       <c r="H52" s="8" t="n">
-        <v>0.0186</v>
+        <v>0.0187</v>
       </c>
       <c r="I52" s="8" t="n">
-        <v>0.0321</v>
+        <v>0.0319</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.0005</v>
+        <v>-0.0002</v>
       </c>
       <c r="K52" s="9" t="n"/>
       <c r="L52" s="9" t="n"/>
@@ -3682,13 +3682,13 @@
         <v/>
       </c>
       <c r="H53" s="8" t="n">
-        <v>0.0186</v>
+        <v>0.0187</v>
       </c>
       <c r="I53" s="8" t="n">
-        <v>0.0321</v>
+        <v>0.0319</v>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.0005</v>
+        <v>-0.0002</v>
       </c>
       <c r="K53" s="9" t="n"/>
       <c r="L53" s="9" t="n"/>
@@ -3714,17 +3714,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2026 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>iShares iBonds Dec 2026 Term € Italy Govt Bond UCITS ETF</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>LU2872291278</t>
+          <t>IE000LZ7BZW8</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F54" s="6" t="n">
@@ -3745,18 +3745,18 @@
         <v/>
       </c>
       <c r="H54" s="8" t="n">
-        <v>0.0023</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="I54" s="8" t="n">
-        <v>0.0266</v>
+        <v>0.0269</v>
       </c>
       <c r="J54" s="9" t="n">
-        <v>-0.0019</v>
+        <v>0.0001</v>
       </c>
       <c r="K54" s="9" t="n"/>
       <c r="L54" s="9" t="n"/>
       <c r="M54" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N54" s="10">
         <f>IF(D54="Govt",$B$1,$B$2)</f>
@@ -3771,23 +3771,23 @@
         <v/>
       </c>
       <c r="Q54" s="12" t="n">
-        <v>10.2644</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2026 Term € Italy Govt Bond UCITS ETF</t>
+          <t>Amundi Fixed Maturity 2026 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>IE000LZ7BZW8</t>
+          <t>LU2872291278</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F55" s="6" t="n">
@@ -3808,18 +3808,18 @@
         <v/>
       </c>
       <c r="H55" s="8" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0023</v>
       </c>
       <c r="I55" s="8" t="n">
-        <v>0.0268</v>
+        <v>0.0264</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.0003</v>
+        <v>-0.0002</v>
       </c>
       <c r="K55" s="9" t="n"/>
       <c r="L55" s="9" t="n"/>
       <c r="M55" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N55" s="10">
         <f>IF(D55="Govt",$B$1,$B$2)</f>
@@ -3834,7 +3834,7 @@
         <v/>
       </c>
       <c r="Q55" s="12" t="n">
-        <v>5.06</v>
+        <v>10.2651</v>
       </c>
     </row>
     <row r="56">
@@ -3897,7 +3897,7 @@
         <v/>
       </c>
       <c r="Q56" s="12" t="n">
-        <v>5.7961</v>
+        <v>5.7965</v>
       </c>
     </row>
     <row r="57">
@@ -3960,7 +3960,7 @@
         <v/>
       </c>
       <c r="Q57" s="12" t="n">
-        <v>5.4196</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="58">
@@ -3997,13 +3997,13 @@
         <v/>
       </c>
       <c r="H58" s="8" t="n">
-        <v>0.0054</v>
+        <v>0.005500000000000001</v>
       </c>
       <c r="I58" s="8" t="n">
-        <v>0.0279</v>
+        <v>0.0275</v>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.0004</v>
       </c>
       <c r="K58" s="9" t="n"/>
       <c r="L58" s="9" t="n"/>

--- a/data/rendimenti_etf.xlsx
+++ b/data/rendimenti_etf.xlsx
@@ -533,7 +533,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Aggiornato il 22/10/2026 09:03 da yield_etf.csv</t>
+          <t>Aggiornato il 23/10/2026 09:02 da yield_etf.csv</t>
         </is>
       </c>
     </row>
@@ -658,13 +658,13 @@
         <v/>
       </c>
       <c r="H5" s="8" t="n">
-        <v>0.039</v>
+        <v>0.0388</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>0.0505</v>
+        <v>0.0508</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.0002</v>
+        <v>0.0003</v>
       </c>
       <c r="K5" s="9" t="n"/>
       <c r="L5" s="9" t="n"/>
@@ -684,7 +684,7 @@
         <v/>
       </c>
       <c r="Q5" s="12" t="n">
-        <v>4.88</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="6">
@@ -724,10 +724,10 @@
         <v>0.0377</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0.0457</v>
+        <v>0.0459</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0.0002</v>
       </c>
       <c r="K6" s="9" t="n"/>
       <c r="L6" s="9" t="n"/>
@@ -747,7 +747,7 @@
         <v/>
       </c>
       <c r="Q6" s="12" t="n">
-        <v>28.46</v>
+        <v>28.38</v>
       </c>
     </row>
     <row r="7">
@@ -787,10 +787,10 @@
         <v>0.0367</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0.0454</v>
+        <v>0.0458</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0004</v>
       </c>
       <c r="K7" s="9" t="n"/>
       <c r="L7" s="9" t="n"/>
@@ -810,7 +810,7 @@
         <v/>
       </c>
       <c r="Q7" s="12" t="n">
-        <v>29.26</v>
+        <v>29.18</v>
       </c>
     </row>
     <row r="8">
@@ -850,10 +850,10 @@
         <v>0.0356</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>0.0451</v>
+        <v>0.0455</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>-0.0004</v>
+        <v>0.0004</v>
       </c>
       <c r="K8" s="9" t="n"/>
       <c r="L8" s="9" t="n"/>
@@ -873,7 +873,7 @@
         <v/>
       </c>
       <c r="Q8" s="12" t="n">
-        <v>4.83</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="9">
@@ -913,10 +913,10 @@
         <v>0.0349</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>0.0449</v>
+        <v>0.0452</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>-0.0004</v>
+        <v>0.0003</v>
       </c>
       <c r="K9" s="9" t="n"/>
       <c r="L9" s="9" t="n"/>
@@ -936,7 +936,7 @@
         <v/>
       </c>
       <c r="Q9" s="12" t="n">
-        <v>4.83</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="10">
@@ -976,10 +976,10 @@
         <v>0.0363</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>0.0447</v>
+        <v>0.0451</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>-0.0004</v>
+        <v>0.0004</v>
       </c>
       <c r="K10" s="9" t="n"/>
       <c r="L10" s="9" t="n"/>
@@ -1039,10 +1039,10 @@
         <v>0.0351</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>0.0445</v>
+        <v>0.045</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>-0.0004</v>
+        <v>0.0005</v>
       </c>
       <c r="K11" s="9" t="n"/>
       <c r="L11" s="9" t="n"/>
@@ -1062,7 +1062,7 @@
         <v/>
       </c>
       <c r="Q11" s="12" t="n">
-        <v>33.67</v>
+        <v>33.58</v>
       </c>
     </row>
     <row r="12">
@@ -1102,10 +1102,10 @@
         <v>0.0348</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>0.044</v>
+        <v>0.0445</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>-0.0004</v>
+        <v>0.0005</v>
       </c>
       <c r="K12" s="9" t="n"/>
       <c r="L12" s="9" t="n"/>
@@ -1125,7 +1125,7 @@
         <v/>
       </c>
       <c r="Q12" s="12" t="n">
-        <v>4.76</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="13">
@@ -1165,10 +1165,10 @@
         <v>0.0338</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0.044</v>
+        <v>0.0445</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0005</v>
       </c>
       <c r="K13" s="9" t="n"/>
       <c r="L13" s="9" t="n"/>
@@ -1188,7 +1188,7 @@
         <v/>
       </c>
       <c r="Q13" s="12" t="n">
-        <v>9.34</v>
+        <v>9.32</v>
       </c>
     </row>
     <row r="14">
@@ -1228,10 +1228,10 @@
         <v>0.0338</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>0.044</v>
+        <v>0.0445</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0005</v>
       </c>
       <c r="K14" s="9" t="n"/>
       <c r="L14" s="9" t="n"/>
@@ -1251,7 +1251,7 @@
         <v/>
       </c>
       <c r="Q14" s="12" t="n">
-        <v>27.98</v>
+        <v>27.92</v>
       </c>
     </row>
     <row r="15">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2028 Term € Corp Crossover UCITS ETF</t>
+          <t>iShares iBonds Dec 2033 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>IE0003HV7CS6</t>
+          <t>IE000E0NL9T3</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -1277,29 +1277,29 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
-        <v>47118</v>
+        <v>48944</v>
       </c>
       <c r="G15" s="7">
         <f>IF(F15="","",MAX(0,YEARFRAC(TODAY(),F15)))</f>
         <v/>
       </c>
       <c r="H15" s="8" t="n">
-        <v>0.0329</v>
+        <v>0.0331</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>0.0444</v>
+        <v>0.04389999999999999</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.0001</v>
+        <v>0.0005</v>
       </c>
       <c r="K15" s="9" t="n"/>
       <c r="L15" s="9" t="n"/>
       <c r="M15" s="8" t="n">
-        <v>0.002</v>
+        <v>0.0012</v>
       </c>
       <c r="N15" s="10">
         <f>IF(D15="Govt",$B$1,$B$2)</f>
@@ -1314,7 +1314,7 @@
         <v/>
       </c>
       <c r="Q15" s="12" t="n">
-        <v>5.1</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="16">
@@ -1325,12 +1325,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2033 Term € Corp UCITS ETF</t>
+          <t>iShares iBonds Dec 2028 Term € Corp Crossover UCITS ETF</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>IE000E0NL9T3</t>
+          <t>IE0003HV7CS6</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -1340,29 +1340,29 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>48944</v>
+        <v>47118</v>
       </c>
       <c r="G16" s="7">
         <f>IF(F16="","",MAX(0,YEARFRAC(TODAY(),F16)))</f>
         <v/>
       </c>
       <c r="H16" s="8" t="n">
-        <v>0.0331</v>
+        <v>0.0329</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>0.0434</v>
+        <v>0.0446</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0.0002</v>
       </c>
       <c r="K16" s="9" t="n"/>
       <c r="L16" s="9" t="n"/>
       <c r="M16" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.002</v>
       </c>
       <c r="N16" s="10">
         <f>IF(D16="Govt",$B$1,$B$2)</f>
@@ -1377,7 +1377,7 @@
         <v/>
       </c>
       <c r="Q16" s="12" t="n">
-        <v>4.78</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="17">
@@ -1417,10 +1417,10 @@
         <v>0.0282</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>0.0431</v>
+        <v>0.0436</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0005</v>
       </c>
       <c r="K17" s="9" t="n"/>
       <c r="L17" s="9" t="n"/>
@@ -1440,55 +1440,55 @@
         <v/>
       </c>
       <c r="Q17" s="12" t="n">
-        <v>34.38</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2032 Term € Corp UCITS ETF</t>
+          <t>Amundi Fixed Maturity 2030 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>IE0000MR4GH9</t>
+          <t>LU3120976132</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>48579</v>
+        <v>47848</v>
       </c>
       <c r="G18" s="7">
         <f>IF(F18="","",MAX(0,YEARFRAC(TODAY(),F18)))</f>
         <v/>
       </c>
       <c r="H18" s="8" t="n">
-        <v>0.0305</v>
+        <v>0.0169</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>0.0424</v>
+        <v>0.0361</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0008</v>
       </c>
       <c r="K18" s="9" t="n"/>
       <c r="L18" s="9" t="n"/>
       <c r="M18" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N18" s="10">
         <f>IF(D18="Govt",$B$1,$B$2)</f>
@@ -1503,55 +1503,55 @@
         <v/>
       </c>
       <c r="Q18" s="12" t="n">
-        <v>4.83</v>
+        <v>9.827500000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2030 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>iShares iBonds Dec 2032 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LU3120976132</t>
+          <t>IE0000MR4GH9</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>47848</v>
+        <v>48579</v>
       </c>
       <c r="G19" s="7">
         <f>IF(F19="","",MAX(0,YEARFRAC(TODAY(),F19)))</f>
         <v/>
       </c>
       <c r="H19" s="8" t="n">
-        <v>0.0169</v>
+        <v>0.0301</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>0.0353</v>
+        <v>0.0428</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0.0004</v>
       </c>
       <c r="K19" s="9" t="n"/>
       <c r="L19" s="9" t="n"/>
       <c r="M19" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N19" s="10">
         <f>IF(D19="Govt",$B$1,$B$2)</f>
@@ -1566,7 +1566,7 @@
         <v/>
       </c>
       <c r="Q19" s="12" t="n">
-        <v>9.826599999999999</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="20">
@@ -1606,10 +1606,10 @@
         <v>0.0286</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>0.0417</v>
+        <v>0.04219999999999999</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0.0005</v>
       </c>
       <c r="K20" s="9" t="n"/>
       <c r="L20" s="9" t="n"/>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="Q20" s="12" t="n">
-        <v>4.88</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="21">
@@ -1669,10 +1669,10 @@
         <v>0.0269</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>0.0416</v>
+        <v>0.04190000000000001</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0.0003</v>
       </c>
       <c r="K21" s="9" t="n"/>
       <c r="L21" s="9" t="n"/>
@@ -1692,7 +1692,7 @@
         <v/>
       </c>
       <c r="Q21" s="12" t="n">
-        <v>10.4692</v>
+        <v>10.4459</v>
       </c>
     </row>
     <row r="22">
@@ -1732,10 +1732,10 @@
         <v>0.0269</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>0.0416</v>
+        <v>0.04190000000000001</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0.0003</v>
       </c>
       <c r="K22" s="9" t="n"/>
       <c r="L22" s="9" t="n"/>
@@ -1755,7 +1755,7 @@
         <v/>
       </c>
       <c r="Q22" s="12" t="n">
-        <v>10.0818</v>
+        <v>10.0594</v>
       </c>
     </row>
     <row r="23">
@@ -1795,10 +1795,10 @@
         <v>0.0287</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>0.0414</v>
+        <v>0.0418</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0004</v>
       </c>
       <c r="K23" s="9" t="n"/>
       <c r="L23" s="9" t="n"/>
@@ -1818,7 +1818,7 @@
         <v/>
       </c>
       <c r="Q23" s="12" t="n">
-        <v>9.82</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1858,10 +1858,10 @@
         <v>0.0287</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>0.0414</v>
+        <v>0.0418</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0004</v>
       </c>
       <c r="K24" s="9" t="n"/>
       <c r="L24" s="9" t="n"/>
@@ -1881,7 +1881,7 @@
         <v/>
       </c>
       <c r="Q24" s="12" t="n">
-        <v>29.38</v>
+        <v>29.33</v>
       </c>
     </row>
     <row r="25">
@@ -1921,10 +1921,10 @@
         <v>0.0208</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>0.0344</v>
+        <v>0.0352</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0008</v>
       </c>
       <c r="K25" s="9" t="n"/>
       <c r="L25" s="9" t="n"/>
@@ -1944,28 +1944,28 @@
         <v/>
       </c>
       <c r="Q25" s="12" t="n">
-        <v>9.9834</v>
+        <v>9.9846</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>Xtrackers II Target Maturity Sept 2029 Italy and Spain Government Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>IE000I25S1V5</t>
+          <t>LU0484969463</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -1974,25 +1974,25 @@
         </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>47848</v>
+        <v>47391</v>
       </c>
       <c r="G26" s="7">
         <f>IF(F26="","",MAX(0,YEARFRAC(TODAY(),F26)))</f>
         <v/>
       </c>
       <c r="H26" s="8" t="n">
-        <v>0.0286</v>
+        <v>0.0297</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>0.0406</v>
+        <v>0.0353</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0</v>
+        <v>0.0007</v>
       </c>
       <c r="K26" s="9" t="n"/>
       <c r="L26" s="9" t="n"/>
       <c r="M26" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N26" s="10">
         <f>IF(D26="Govt",$B$1,$B$2)</f>
@@ -2007,28 +2007,28 @@
         <v/>
       </c>
       <c r="Q26" s="12" t="n">
-        <v>5.357</v>
+        <v>204.62</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>iShares iBonds Dec 2028 Term € Italy Govt Bond UCITS ETF</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>IE000W6YTDH7</t>
+          <t>IE000Q2EQ5K8</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -2037,25 +2037,25 @@
         </is>
       </c>
       <c r="F27" s="6" t="n">
-        <v>47848</v>
+        <v>47118</v>
       </c>
       <c r="G27" s="7">
         <f>IF(F27="","",MAX(0,YEARFRAC(TODAY(),F27)))</f>
         <v/>
       </c>
       <c r="H27" s="8" t="n">
-        <v>0.0286</v>
+        <v>0.0261</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>0.0406</v>
+        <v>0.0348</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0</v>
+        <v>0.0007</v>
       </c>
       <c r="K27" s="9" t="n"/>
       <c r="L27" s="9" t="n"/>
       <c r="M27" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N27" s="10">
         <f>IF(D27="Govt",$B$1,$B$2)</f>
@@ -2070,28 +2070,28 @@
         <v/>
       </c>
       <c r="Q27" s="12" t="n">
-        <v>4.99</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2029 Italy and Spain Government Bond UCITS ETF 1C</t>
+          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>LU0484969463</t>
+          <t>IE000I25S1V5</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -2100,25 +2100,25 @@
         </is>
       </c>
       <c r="F28" s="6" t="n">
-        <v>47391</v>
+        <v>47848</v>
       </c>
       <c r="G28" s="7">
         <f>IF(F28="","",MAX(0,YEARFRAC(TODAY(),F28)))</f>
         <v/>
       </c>
       <c r="H28" s="8" t="n">
-        <v>0.0297</v>
+        <v>0.0286</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>0.0346</v>
+        <v>0.0406</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>-0.0004</v>
+        <v>0</v>
       </c>
       <c r="K28" s="9" t="n"/>
       <c r="L28" s="9" t="n"/>
       <c r="M28" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="N28" s="10">
         <f>IF(D28="Govt",$B$1,$B$2)</f>
@@ -2133,28 +2133,28 @@
         <v/>
       </c>
       <c r="Q28" s="12" t="n">
-        <v>204.93</v>
+        <v>5.3624</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2028 Term € Italy Govt Bond UCITS ETF</t>
+          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>IE000Q2EQ5K8</t>
+          <t>IE000W6YTDH7</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -2163,25 +2163,25 @@
         </is>
       </c>
       <c r="F29" s="6" t="n">
-        <v>47118</v>
+        <v>47848</v>
       </c>
       <c r="G29" s="7">
         <f>IF(F29="","",MAX(0,YEARFRAC(TODAY(),F29)))</f>
         <v/>
       </c>
       <c r="H29" s="8" t="n">
-        <v>0.0261</v>
+        <v>0.0286</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>0.0341</v>
+        <v>0.0406</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0</v>
       </c>
       <c r="K29" s="9" t="n"/>
       <c r="L29" s="9" t="n"/>
       <c r="M29" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="N29" s="10">
         <f>IF(D29="Govt",$B$1,$B$2)</f>
@@ -2196,7 +2196,7 @@
         <v/>
       </c>
       <c r="Q29" s="12" t="n">
-        <v>5.06</v>
+        <v>4.9949</v>
       </c>
     </row>
     <row r="30">
@@ -2236,10 +2236,10 @@
         <v>0.028</v>
       </c>
       <c r="I30" s="8" t="n">
-        <v>0.0401</v>
+        <v>0.0405</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0004</v>
       </c>
       <c r="K30" s="9" t="n"/>
       <c r="L30" s="9" t="n"/>
@@ -2259,7 +2259,7 @@
         <v/>
       </c>
       <c r="Q30" s="12" t="n">
-        <v>4.99</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -2299,10 +2299,10 @@
         <v>0.027</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>0.04</v>
+        <v>0.0405</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0005</v>
       </c>
       <c r="K31" s="9" t="n"/>
       <c r="L31" s="9" t="n"/>
@@ -2322,55 +2322,55 @@
         <v/>
       </c>
       <c r="Q31" s="12" t="n">
-        <v>35.33</v>
+        <v>35.28</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>Amundi Fixed Maturity 2028 Euro Government Bond Yield + UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>IE000P5IB8I8</t>
+          <t>LU2780871666</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F32" s="6" t="n">
-        <v>47483</v>
+        <v>47118</v>
       </c>
       <c r="G32" s="7">
         <f>IF(F32="","",MAX(0,YEARFRAC(TODAY(),F32)))</f>
         <v/>
       </c>
       <c r="H32" s="8" t="n">
-        <v>0.0242</v>
+        <v>0.023</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>0.0386</v>
+        <v>0.0334</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0</v>
+        <v>0.0008</v>
       </c>
       <c r="K32" s="9" t="n"/>
       <c r="L32" s="9" t="n"/>
       <c r="M32" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0009</v>
       </c>
       <c r="N32" s="10">
         <f>IF(D32="Govt",$B$1,$B$2)</f>
@@ -2385,28 +2385,28 @@
         <v/>
       </c>
       <c r="Q32" s="12" t="n">
-        <v>5.4314</v>
+        <v>10.2934</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>IE000ZC4C5Q1</t>
+          <t>LU2780871401</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -2415,25 +2415,25 @@
         </is>
       </c>
       <c r="F33" s="6" t="n">
-        <v>47483</v>
+        <v>47118</v>
       </c>
       <c r="G33" s="7">
         <f>IF(F33="","",MAX(0,YEARFRAC(TODAY(),F33)))</f>
         <v/>
       </c>
       <c r="H33" s="8" t="n">
-        <v>0.0242</v>
+        <v>0.0184</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>0.0386</v>
+        <v>0.033</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0</v>
+        <v>0.0007</v>
       </c>
       <c r="K33" s="9" t="n"/>
       <c r="L33" s="9" t="n"/>
       <c r="M33" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0009</v>
       </c>
       <c r="N33" s="10">
         <f>IF(D33="Govt",$B$1,$B$2)</f>
@@ -2448,7 +2448,7 @@
         <v/>
       </c>
       <c r="Q33" s="12" t="n">
-        <v>5.061</v>
+        <v>10.2834</v>
       </c>
     </row>
     <row r="34">
@@ -2459,12 +2459,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2028 Euro Government Bond Yield + UCITS ETF Dist</t>
+          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>LU2780871666</t>
+          <t>LU2780871310</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F34" s="6" t="n">
@@ -2485,13 +2485,13 @@
         <v/>
       </c>
       <c r="H34" s="8" t="n">
-        <v>0.0229</v>
+        <v>0.0184</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>0.0326</v>
+        <v>0.033</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0007</v>
       </c>
       <c r="K34" s="9" t="n"/>
       <c r="L34" s="9" t="n"/>
@@ -2511,7 +2511,7 @@
         <v/>
       </c>
       <c r="Q34" s="12" t="n">
-        <v>10.2883</v>
+        <v>10.0826</v>
       </c>
     </row>
     <row r="35">
@@ -2551,10 +2551,10 @@
         <v>0.0252</v>
       </c>
       <c r="I35" s="8" t="n">
-        <v>0.0385</v>
+        <v>0.0389</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0004</v>
       </c>
       <c r="K35" s="9" t="n"/>
       <c r="L35" s="9" t="n"/>
@@ -2580,49 +2580,49 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Dist</t>
+          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>LU2780871401</t>
+          <t>IE000P5IB8I8</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F36" s="6" t="n">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="G36" s="7">
         <f>IF(F36="","",MAX(0,YEARFRAC(TODAY(),F36)))</f>
         <v/>
       </c>
       <c r="H36" s="8" t="n">
-        <v>0.0184</v>
+        <v>0.0242</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>0.0323</v>
+        <v>0.0386</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0</v>
       </c>
       <c r="K36" s="9" t="n"/>
       <c r="L36" s="9" t="n"/>
       <c r="M36" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="N36" s="10">
         <f>IF(D36="Govt",$B$1,$B$2)</f>
@@ -2637,55 +2637,55 @@
         <v/>
       </c>
       <c r="Q36" s="12" t="n">
-        <v>10.2787</v>
+        <v>5.4353</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>LU2780871310</t>
+          <t>IE000ZC4C5Q1</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F37" s="6" t="n">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="G37" s="7">
         <f>IF(F37="","",MAX(0,YEARFRAC(TODAY(),F37)))</f>
         <v/>
       </c>
       <c r="H37" s="8" t="n">
-        <v>0.0184</v>
+        <v>0.0242</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>0.0323</v>
+        <v>0.0386</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0</v>
       </c>
       <c r="K37" s="9" t="n"/>
       <c r="L37" s="9" t="n"/>
       <c r="M37" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="N37" s="10">
         <f>IF(D37="Govt",$B$1,$B$2)</f>
@@ -2700,7 +2700,7 @@
         <v/>
       </c>
       <c r="Q37" s="12" t="n">
-        <v>10.078</v>
+        <v>5.0647</v>
       </c>
     </row>
     <row r="38">
@@ -2740,10 +2740,10 @@
         <v>0.0245</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>0.0383</v>
+        <v>0.0387</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0004</v>
       </c>
       <c r="K38" s="9" t="n"/>
       <c r="L38" s="9" t="n"/>
@@ -2763,7 +2763,7 @@
         <v/>
       </c>
       <c r="Q38" s="12" t="n">
-        <v>25.83</v>
+        <v>25.81</v>
       </c>
     </row>
     <row r="39">
@@ -2803,10 +2803,10 @@
         <v>0.0245</v>
       </c>
       <c r="I39" s="8" t="n">
-        <v>0.0383</v>
+        <v>0.0387</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0004</v>
       </c>
       <c r="K39" s="9" t="n"/>
       <c r="L39" s="9" t="n"/>
@@ -2866,10 +2866,10 @@
         <v>0.0235</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>0.038</v>
+        <v>0.0383</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0003</v>
       </c>
       <c r="K40" s="9" t="n"/>
       <c r="L40" s="9" t="n"/>
@@ -2889,7 +2889,7 @@
         <v/>
       </c>
       <c r="Q40" s="12" t="n">
-        <v>10.6825</v>
+        <v>10.6722</v>
       </c>
     </row>
     <row r="41">
@@ -2929,10 +2929,10 @@
         <v>0.0235</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>0.038</v>
+        <v>0.0383</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0003</v>
       </c>
       <c r="K41" s="9" t="n"/>
       <c r="L41" s="9" t="n"/>
@@ -2952,7 +2952,7 @@
         <v/>
       </c>
       <c r="Q41" s="12" t="n">
-        <v>10.3204</v>
+        <v>10.3105</v>
       </c>
     </row>
     <row r="42">
@@ -3015,7 +3015,7 @@
         <v/>
       </c>
       <c r="Q42" s="12" t="n">
-        <v>5.5747</v>
+        <v>5.5774</v>
       </c>
     </row>
     <row r="43">
@@ -3078,7 +3078,7 @@
         <v/>
       </c>
       <c r="Q43" s="12" t="n">
-        <v>5.2137</v>
+        <v>5.2162</v>
       </c>
     </row>
     <row r="44">
@@ -3118,10 +3118,10 @@
         <v>0.0214</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>0.0371</v>
+        <v>0.0375</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0004</v>
       </c>
       <c r="K44" s="9" t="n"/>
       <c r="L44" s="9" t="n"/>
@@ -3141,7 +3141,7 @@
         <v/>
       </c>
       <c r="Q44" s="12" t="n">
-        <v>5.1</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="45">
@@ -3181,10 +3181,10 @@
         <v>0.0207</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>0.0368</v>
+        <v>0.0371</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0003</v>
       </c>
       <c r="K45" s="9" t="n"/>
       <c r="L45" s="9" t="n"/>
@@ -3204,7 +3204,7 @@
         <v/>
       </c>
       <c r="Q45" s="12" t="n">
-        <v>35.8</v>
+        <v>35.79</v>
       </c>
     </row>
     <row r="46">
@@ -3244,10 +3244,10 @@
         <v>0.0265</v>
       </c>
       <c r="I46" s="8" t="n">
-        <v>0.0305</v>
+        <v>0.0311</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="K46" s="9" t="n"/>
       <c r="L46" s="9" t="n"/>
@@ -3267,7 +3267,7 @@
         <v/>
       </c>
       <c r="Q46" s="12" t="n">
-        <v>10.3405</v>
+        <v>10.3442</v>
       </c>
     </row>
     <row r="47">
@@ -3307,10 +3307,10 @@
         <v>0.015</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>0.0295</v>
+        <v>0.0299</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0004</v>
       </c>
       <c r="K47" s="9" t="n"/>
       <c r="L47" s="9" t="n"/>
@@ -3330,33 +3330,33 @@
         <v/>
       </c>
       <c r="Q47" s="12" t="n">
-        <v>10.1801</v>
+        <v>10.1839</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2027 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>Amundi Fixed Maturity 2027 German Bund Government Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>IE000LGHLQ71</t>
+          <t>LU2780871823</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
@@ -3367,18 +3367,18 @@
         <v/>
       </c>
       <c r="H48" s="8" t="n">
-        <v>0.0197</v>
+        <v>0.0105</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>0.0335</v>
+        <v>0.0286</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0</v>
+        <v>0.0003</v>
       </c>
       <c r="K48" s="9" t="n"/>
       <c r="L48" s="9" t="n"/>
       <c r="M48" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0009</v>
       </c>
       <c r="N48" s="10">
         <f>IF(D48="Govt",$B$1,$B$2)</f>
@@ -3393,7 +3393,7 @@
         <v/>
       </c>
       <c r="Q48" s="12" t="n">
-        <v>5.7117</v>
+        <v>10.3597</v>
       </c>
     </row>
     <row r="49">
@@ -3404,12 +3404,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2027 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>Invesco BulletShares 2027 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>IE000XOS4OJ6</t>
+          <t>IE000LGHLQ71</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F49" s="6" t="n">
@@ -3456,28 +3456,28 @@
         <v/>
       </c>
       <c r="Q49" s="12" t="n">
-        <v>5.3391</v>
+        <v>5.7123</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2027 German Bund Government Bond UCITS ETF Dist</t>
+          <t>Invesco BulletShares 2027 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>LU2780871823</t>
+          <t>IE000XOS4OJ6</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -3493,18 +3493,18 @@
         <v/>
       </c>
       <c r="H50" s="8" t="n">
-        <v>0.0105</v>
+        <v>0.0197</v>
       </c>
       <c r="I50" s="8" t="n">
-        <v>0.0283</v>
+        <v>0.0335</v>
       </c>
       <c r="J50" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0</v>
       </c>
       <c r="K50" s="9" t="n"/>
       <c r="L50" s="9" t="n"/>
       <c r="M50" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="N50" s="10">
         <f>IF(D50="Govt",$B$1,$B$2)</f>
@@ -3519,7 +3519,7 @@
         <v/>
       </c>
       <c r="Q50" s="12" t="n">
-        <v>10.3551</v>
+        <v>5.3397</v>
       </c>
     </row>
     <row r="51">
@@ -3559,10 +3559,10 @@
         <v>0.0195</v>
       </c>
       <c r="I51" s="8" t="n">
-        <v>0.0334</v>
+        <v>0.0335</v>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="K51" s="9" t="n"/>
       <c r="L51" s="9" t="n"/>
@@ -3625,7 +3625,7 @@
         <v>0.0319</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0</v>
       </c>
       <c r="K52" s="9" t="n"/>
       <c r="L52" s="9" t="n"/>
@@ -3688,7 +3688,7 @@
         <v>0.0319</v>
       </c>
       <c r="J53" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0</v>
       </c>
       <c r="K53" s="9" t="n"/>
       <c r="L53" s="9" t="n"/>
@@ -3748,7 +3748,7 @@
         <v>0.008800000000000001</v>
       </c>
       <c r="I54" s="8" t="n">
-        <v>0.0269</v>
+        <v>0.027</v>
       </c>
       <c r="J54" s="9" t="n">
         <v>0.0001</v>
@@ -3811,10 +3811,10 @@
         <v>0.0023</v>
       </c>
       <c r="I55" s="8" t="n">
-        <v>0.0264</v>
+        <v>0.026</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>-0.0002</v>
+        <v>-0.0004</v>
       </c>
       <c r="K55" s="9" t="n"/>
       <c r="L55" s="9" t="n"/>
@@ -3834,7 +3834,7 @@
         <v/>
       </c>
       <c r="Q55" s="12" t="n">
-        <v>10.2651</v>
+        <v>10.2674</v>
       </c>
     </row>
     <row r="56">
@@ -3897,7 +3897,7 @@
         <v/>
       </c>
       <c r="Q56" s="12" t="n">
-        <v>5.7965</v>
+        <v>5.7972</v>
       </c>
     </row>
     <row r="57">
@@ -3960,7 +3960,7 @@
         <v/>
       </c>
       <c r="Q57" s="12" t="n">
-        <v>5.42</v>
+        <v>5.4206</v>
       </c>
     </row>
     <row r="58">
@@ -4000,10 +4000,10 @@
         <v>0.005500000000000001</v>
       </c>
       <c r="I58" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0274</v>
       </c>
       <c r="J58" s="9" t="n">
-        <v>-0.0004</v>
+        <v>-0.0001</v>
       </c>
       <c r="K58" s="9" t="n"/>
       <c r="L58" s="9" t="n"/>

--- a/data/rendimenti_etf.xlsx
+++ b/data/rendimenti_etf.xlsx
@@ -533,7 +533,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Aggiornato il 23/10/2026 09:02 da yield_etf.csv</t>
+          <t>Aggiornato il 26/10/2026 09:03 da yield_etf.csv</t>
         </is>
       </c>
     </row>
@@ -661,12 +661,14 @@
         <v>0.0388</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>0.0508</v>
+        <v>0.0528</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.0003</v>
-      </c>
-      <c r="K5" s="9" t="n"/>
+        <v>0.002</v>
+      </c>
+      <c r="K5" s="9" t="n">
+        <v>0.0044</v>
+      </c>
       <c r="L5" s="9" t="n"/>
       <c r="M5" s="8" t="n">
         <v>0.002</v>
@@ -684,7 +686,7 @@
         <v/>
       </c>
       <c r="Q5" s="12" t="n">
-        <v>4.87</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="6">
@@ -724,12 +726,14 @@
         <v>0.0377</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0.0459</v>
+        <v>0.046</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="K6" s="9" t="n"/>
+        <v>0.0001</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="L6" s="9" t="n"/>
       <c r="M6" s="8" t="n">
         <v>0.0012</v>
@@ -747,23 +751,23 @@
         <v/>
       </c>
       <c r="Q6" s="12" t="n">
-        <v>28.38</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2035 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>iShares iBonds Dec 2036 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LU3152892546</t>
+          <t>IE000RQJBQI6</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -777,22 +781,24 @@
         </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>49582</v>
+        <v>50040</v>
       </c>
       <c r="G7" s="7">
         <f>IF(F7="","",MAX(0,YEARFRAC(TODAY(),F7)))</f>
         <v/>
       </c>
       <c r="H7" s="8" t="n">
-        <v>0.0367</v>
+        <v>0.0356</v>
       </c>
       <c r="I7" s="8" t="n">
         <v>0.0458</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.0004</v>
-      </c>
-      <c r="K7" s="9" t="n"/>
+        <v>0.0003</v>
+      </c>
+      <c r="K7" s="9" t="n">
+        <v>0.0003</v>
+      </c>
       <c r="L7" s="9" t="n"/>
       <c r="M7" s="8" t="n">
         <v>0.0012</v>
@@ -810,23 +816,23 @@
         <v/>
       </c>
       <c r="Q7" s="12" t="n">
-        <v>29.18</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2036 Term € Corp UCITS ETF</t>
+          <t>Xtrackers II Target Maturity Sept 2035 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>IE000RQJBQI6</t>
+          <t>LU3152892546</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -840,22 +846,24 @@
         </is>
       </c>
       <c r="F8" s="6" t="n">
-        <v>50040</v>
+        <v>49582</v>
       </c>
       <c r="G8" s="7">
         <f>IF(F8="","",MAX(0,YEARFRAC(TODAY(),F8)))</f>
         <v/>
       </c>
       <c r="H8" s="8" t="n">
-        <v>0.0356</v>
+        <v>0.0367</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>0.0455</v>
+        <v>0.0457</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.0004</v>
-      </c>
-      <c r="K8" s="9" t="n"/>
+        <v>-0.0001</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>0.0001</v>
+      </c>
       <c r="L8" s="9" t="n"/>
       <c r="M8" s="8" t="n">
         <v>0.0012</v>
@@ -873,7 +881,7 @@
         <v/>
       </c>
       <c r="Q8" s="12" t="n">
-        <v>4.84</v>
+        <v>29.21</v>
       </c>
     </row>
     <row r="9">
@@ -884,12 +892,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2037 Term € Corp UCITS ETF</t>
+          <t>iShares iBonds Dec 2035 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>IE000PWSK6H1</t>
+          <t>IE000WLR06P0</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -903,22 +911,24 @@
         </is>
       </c>
       <c r="F9" s="6" t="n">
-        <v>50405</v>
+        <v>49674</v>
       </c>
       <c r="G9" s="7">
         <f>IF(F9="","",MAX(0,YEARFRAC(TODAY(),F9)))</f>
         <v/>
       </c>
       <c r="H9" s="8" t="n">
-        <v>0.0349</v>
+        <v>0.0364</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>0.0452</v>
+        <v>0.0455</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.0003</v>
-      </c>
-      <c r="K9" s="9" t="n"/>
+        <v>0.0004</v>
+      </c>
+      <c r="K9" s="9" t="n">
+        <v>0.0002</v>
+      </c>
       <c r="L9" s="9" t="n"/>
       <c r="M9" s="8" t="n">
         <v>0.0012</v>
@@ -936,7 +946,7 @@
         <v/>
       </c>
       <c r="Q9" s="12" t="n">
-        <v>4.85</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="10">
@@ -947,12 +957,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2035 Term € Corp UCITS ETF</t>
+          <t>iShares iBonds Dec 2037 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IE000WLR06P0</t>
+          <t>IE000PWSK6H1</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -966,22 +976,24 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>49674</v>
+        <v>50405</v>
       </c>
       <c r="G10" s="7">
         <f>IF(F10="","",MAX(0,YEARFRAC(TODAY(),F10)))</f>
         <v/>
       </c>
       <c r="H10" s="8" t="n">
-        <v>0.0363</v>
+        <v>0.0349</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>0.0451</v>
+        <v>0.0453</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.0004</v>
-      </c>
-      <c r="K10" s="9" t="n"/>
+        <v>0.0001</v>
+      </c>
+      <c r="K10" s="9" t="n">
+        <v>-0.0001</v>
+      </c>
       <c r="L10" s="9" t="n"/>
       <c r="M10" s="8" t="n">
         <v>0.0012</v>
@@ -999,23 +1011,23 @@
         <v/>
       </c>
       <c r="Q10" s="12" t="n">
-        <v>4.74</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2034 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>iShares iBonds Dec 2028 Term € Corp Crossover UCITS ETF</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LU2809864619</t>
+          <t>IE0003HV7CS6</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -1025,29 +1037,31 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F11" s="6" t="n">
-        <v>49217</v>
+        <v>47118</v>
       </c>
       <c r="G11" s="7">
         <f>IF(F11="","",MAX(0,YEARFRAC(TODAY(),F11)))</f>
         <v/>
       </c>
       <c r="H11" s="8" t="n">
-        <v>0.0351</v>
+        <v>0.0329</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>0.045</v>
+        <v>0.0459</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="K11" s="9" t="n"/>
+        <v>0.0013</v>
+      </c>
+      <c r="K11" s="9" t="n">
+        <v>0.0041</v>
+      </c>
       <c r="L11" s="9" t="n"/>
       <c r="M11" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.002</v>
       </c>
       <c r="N11" s="10">
         <f>IF(D11="Govt",$B$1,$B$2)</f>
@@ -1062,23 +1076,23 @@
         <v/>
       </c>
       <c r="Q11" s="12" t="n">
-        <v>33.58</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2034 Term € Corp UCITS ETF</t>
+          <t>Xtrackers II Target Maturity Sept 2034 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>IE000SBJO6L2</t>
+          <t>LU2809864619</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -1092,22 +1106,24 @@
         </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>49309</v>
+        <v>49217</v>
       </c>
       <c r="G12" s="7">
         <f>IF(F12="","",MAX(0,YEARFRAC(TODAY(),F12)))</f>
         <v/>
       </c>
       <c r="H12" s="8" t="n">
-        <v>0.0348</v>
+        <v>0.0351</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>0.0445</v>
+        <v>0.04480000000000001</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="K12" s="9" t="n"/>
+        <v>-0.0002</v>
+      </c>
+      <c r="K12" s="9" t="n">
+        <v>-0.0003</v>
+      </c>
       <c r="L12" s="9" t="n"/>
       <c r="M12" s="8" t="n">
         <v>0.0012</v>
@@ -1125,23 +1141,23 @@
         <v/>
       </c>
       <c r="Q12" s="12" t="n">
-        <v>4.77</v>
+        <v>33.62</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2033 EUR Corporate Bond UCITS ETF 1C</t>
+          <t>iShares iBonds Dec 2034 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LU2673523051</t>
+          <t>IE000SBJO6L2</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -1151,26 +1167,28 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>48852</v>
+        <v>49309</v>
       </c>
       <c r="G13" s="7">
         <f>IF(F13="","",MAX(0,YEARFRAC(TODAY(),F13)))</f>
         <v/>
       </c>
       <c r="H13" s="8" t="n">
-        <v>0.0338</v>
+        <v>0.0348</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0.0445</v>
+        <v>0.0447</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="K13" s="9" t="n"/>
+        <v>0.0002</v>
+      </c>
+      <c r="K13" s="9" t="n">
+        <v>-0.0001</v>
+      </c>
       <c r="L13" s="9" t="n"/>
       <c r="M13" s="8" t="n">
         <v>0.0012</v>
@@ -1188,7 +1206,7 @@
         <v/>
       </c>
       <c r="Q13" s="12" t="n">
-        <v>9.32</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="14">
@@ -1199,12 +1217,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2033 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>Xtrackers II Target Maturity Sept 2033 EUR Corporate Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LU2673523564</t>
+          <t>LU2673523051</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -1214,7 +1232,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F14" s="6" t="n">
@@ -1228,12 +1246,14 @@
         <v>0.0338</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>0.0445</v>
+        <v>0.0443</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="K14" s="9" t="n"/>
+        <v>-0.0002</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>-0.0003</v>
+      </c>
       <c r="L14" s="9" t="n"/>
       <c r="M14" s="8" t="n">
         <v>0.0012</v>
@@ -1251,23 +1271,23 @@
         <v/>
       </c>
       <c r="Q14" s="12" t="n">
-        <v>27.92</v>
+        <v>9.33</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2033 Term € Corp UCITS ETF</t>
+          <t>Xtrackers II Target Maturity Sept 2033 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>IE000E0NL9T3</t>
+          <t>LU2673523564</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -1281,22 +1301,24 @@
         </is>
       </c>
       <c r="F15" s="6" t="n">
-        <v>48944</v>
+        <v>48852</v>
       </c>
       <c r="G15" s="7">
         <f>IF(F15="","",MAX(0,YEARFRAC(TODAY(),F15)))</f>
         <v/>
       </c>
       <c r="H15" s="8" t="n">
-        <v>0.0331</v>
+        <v>0.0338</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>0.04389999999999999</v>
+        <v>0.0443</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="K15" s="9" t="n"/>
+        <v>-0.0002</v>
+      </c>
+      <c r="K15" s="9" t="n">
+        <v>-0.0003</v>
+      </c>
       <c r="L15" s="9" t="n"/>
       <c r="M15" s="8" t="n">
         <v>0.0012</v>
@@ -1314,7 +1336,7 @@
         <v/>
       </c>
       <c r="Q15" s="12" t="n">
-        <v>4.79</v>
+        <v>27.94</v>
       </c>
     </row>
     <row r="16">
@@ -1325,12 +1347,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2028 Term € Corp Crossover UCITS ETF</t>
+          <t>iShares iBonds Dec 2033 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>IE0003HV7CS6</t>
+          <t>IE000E0NL9T3</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -1340,29 +1362,31 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>47118</v>
+        <v>48944</v>
       </c>
       <c r="G16" s="7">
         <f>IF(F16="","",MAX(0,YEARFRAC(TODAY(),F16)))</f>
         <v/>
       </c>
       <c r="H16" s="8" t="n">
-        <v>0.0329</v>
+        <v>0.0331</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>0.0446</v>
+        <v>0.0441</v>
       </c>
       <c r="J16" s="9" t="n">
         <v>0.0002</v>
       </c>
-      <c r="K16" s="9" t="n"/>
+      <c r="K16" s="9" t="n">
+        <v>-0.0003</v>
+      </c>
       <c r="L16" s="9" t="n"/>
       <c r="M16" s="8" t="n">
-        <v>0.002</v>
+        <v>0.0012</v>
       </c>
       <c r="N16" s="10">
         <f>IF(D16="Govt",$B$1,$B$2)</f>
@@ -1377,7 +1401,7 @@
         <v/>
       </c>
       <c r="Q16" s="12" t="n">
-        <v>5.1</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="17">
@@ -1417,12 +1441,14 @@
         <v>0.0282</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>0.0436</v>
+        <v>0.0435</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="K17" s="9" t="n"/>
+        <v>-0.0001</v>
+      </c>
+      <c r="K17" s="9" t="n">
+        <v>-0.0002</v>
+      </c>
       <c r="L17" s="9" t="n"/>
       <c r="M17" s="8" t="n">
         <v>0.0012</v>
@@ -1440,55 +1466,57 @@
         <v/>
       </c>
       <c r="Q17" s="12" t="n">
-        <v>34.3</v>
+        <v>34.32</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2030 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>iShares iBonds Dec 2032 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LU3120976132</t>
+          <t>IE0000MR4GH9</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>47848</v>
+        <v>48579</v>
       </c>
       <c r="G18" s="7">
         <f>IF(F18="","",MAX(0,YEARFRAC(TODAY(),F18)))</f>
         <v/>
       </c>
       <c r="H18" s="8" t="n">
-        <v>0.0169</v>
+        <v>0.0301</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>0.0361</v>
+        <v>0.043</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.0008</v>
-      </c>
-      <c r="K18" s="9" t="n"/>
+        <v>0.0002</v>
+      </c>
+      <c r="K18" s="9" t="n">
+        <v>-0.0003</v>
+      </c>
       <c r="L18" s="9" t="n"/>
       <c r="M18" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N18" s="10">
         <f>IF(D18="Govt",$B$1,$B$2)</f>
@@ -1503,55 +1531,57 @@
         <v/>
       </c>
       <c r="Q18" s="12" t="n">
-        <v>9.827500000000001</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2032 Term € Corp UCITS ETF</t>
+          <t>Amundi Fixed Maturity 2030 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>IE0000MR4GH9</t>
+          <t>LU3120976132</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>48579</v>
+        <v>47848</v>
       </c>
       <c r="G19" s="7">
         <f>IF(F19="","",MAX(0,YEARFRAC(TODAY(),F19)))</f>
         <v/>
       </c>
       <c r="H19" s="8" t="n">
-        <v>0.0301</v>
+        <v>0.0169</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>0.0428</v>
+        <v>0.0358</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.0004</v>
-      </c>
-      <c r="K19" s="9" t="n"/>
+        <v>-0.0003</v>
+      </c>
+      <c r="K19" s="9" t="n">
+        <v>0.001</v>
+      </c>
       <c r="L19" s="9" t="n"/>
       <c r="M19" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N19" s="10">
         <f>IF(D19="Govt",$B$1,$B$2)</f>
@@ -1566,7 +1596,7 @@
         <v/>
       </c>
       <c r="Q19" s="12" t="n">
-        <v>4.84</v>
+        <v>9.8352</v>
       </c>
     </row>
     <row r="20">
@@ -1603,15 +1633,17 @@
         <v/>
       </c>
       <c r="H20" s="8" t="n">
-        <v>0.0286</v>
+        <v>0.0285</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>0.04219999999999999</v>
+        <v>0.0424</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="K20" s="9" t="n"/>
+        <v>0.0002</v>
+      </c>
+      <c r="K20" s="9" t="n">
+        <v>-0.0003</v>
+      </c>
       <c r="L20" s="9" t="n"/>
       <c r="M20" s="8" t="n">
         <v>0.0012</v>
@@ -1629,7 +1661,7 @@
         <v/>
       </c>
       <c r="Q20" s="12" t="n">
-        <v>4.89</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="21">
@@ -1669,12 +1701,14 @@
         <v>0.0269</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>0.04190000000000001</v>
+        <v>0.0417</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.0003</v>
-      </c>
-      <c r="K21" s="9" t="n"/>
+        <v>-0.0002</v>
+      </c>
+      <c r="K21" s="9" t="n">
+        <v>-0.0014</v>
+      </c>
       <c r="L21" s="9" t="n"/>
       <c r="M21" s="8" t="n">
         <v>0.0012</v>
@@ -1692,7 +1726,7 @@
         <v/>
       </c>
       <c r="Q21" s="12" t="n">
-        <v>10.4459</v>
+        <v>10.4595</v>
       </c>
     </row>
     <row r="22">
@@ -1732,12 +1766,14 @@
         <v>0.0269</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>0.04190000000000001</v>
+        <v>0.0417</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.0003</v>
-      </c>
-      <c r="K22" s="9" t="n"/>
+        <v>-0.0002</v>
+      </c>
+      <c r="K22" s="9" t="n">
+        <v>-0.0014</v>
+      </c>
       <c r="L22" s="9" t="n"/>
       <c r="M22" s="8" t="n">
         <v>0.0012</v>
@@ -1755,7 +1791,7 @@
         <v/>
       </c>
       <c r="Q22" s="12" t="n">
-        <v>10.0594</v>
+        <v>10.0725</v>
       </c>
     </row>
     <row r="23">
@@ -1795,12 +1831,14 @@
         <v>0.0287</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>0.0418</v>
+        <v>0.0416</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.0004</v>
-      </c>
-      <c r="K23" s="9" t="n"/>
+        <v>-0.0002</v>
+      </c>
+      <c r="K23" s="9" t="n">
+        <v>-0.0008</v>
+      </c>
       <c r="L23" s="9" t="n"/>
       <c r="M23" s="8" t="n">
         <v>0.0012</v>
@@ -1818,7 +1856,7 @@
         <v/>
       </c>
       <c r="Q23" s="12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.81</v>
       </c>
     </row>
     <row r="24">
@@ -1858,12 +1896,14 @@
         <v>0.0287</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>0.0418</v>
+        <v>0.0416</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.0004</v>
-      </c>
-      <c r="K24" s="9" t="n"/>
+        <v>-0.0002</v>
+      </c>
+      <c r="K24" s="9" t="n">
+        <v>-0.0008</v>
+      </c>
       <c r="L24" s="9" t="n"/>
       <c r="M24" s="8" t="n">
         <v>0.0012</v>
@@ -1881,7 +1921,7 @@
         <v/>
       </c>
       <c r="Q24" s="12" t="n">
-        <v>29.33</v>
+        <v>29.36</v>
       </c>
     </row>
     <row r="25">
@@ -1921,12 +1961,14 @@
         <v>0.0208</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>0.0352</v>
+        <v>0.0349</v>
       </c>
       <c r="J25" s="9" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="K25" s="9" t="n">
         <v>0.0008</v>
       </c>
-      <c r="K25" s="9" t="n"/>
       <c r="L25" s="9" t="n"/>
       <c r="M25" s="8" t="n">
         <v>0.0009</v>
@@ -1944,7 +1986,7 @@
         <v/>
       </c>
       <c r="Q25" s="12" t="n">
-        <v>9.9846</v>
+        <v>9.991199999999999</v>
       </c>
     </row>
     <row r="26">
@@ -1984,12 +2026,14 @@
         <v>0.0297</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>0.0353</v>
+        <v>0.0352</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.0007</v>
-      </c>
-      <c r="K26" s="9" t="n"/>
+        <v>-0.0001</v>
+      </c>
+      <c r="K26" s="9" t="n">
+        <v>-0.0004</v>
+      </c>
       <c r="L26" s="9" t="n"/>
       <c r="M26" s="8" t="n">
         <v>0.0012</v>
@@ -2007,55 +2051,57 @@
         <v/>
       </c>
       <c r="Q26" s="12" t="n">
-        <v>204.62</v>
+        <v>204.63</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2028 Term € Italy Govt Bond UCITS ETF</t>
+          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>IE000Q2EQ5K8</t>
+          <t>IE000I25S1V5</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F27" s="6" t="n">
-        <v>47118</v>
+        <v>47848</v>
       </c>
       <c r="G27" s="7">
         <f>IF(F27="","",MAX(0,YEARFRAC(TODAY(),F27)))</f>
         <v/>
       </c>
       <c r="H27" s="8" t="n">
-        <v>0.0261</v>
+        <v>0.0286</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>0.0348</v>
+        <v>0.0406</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.0007</v>
-      </c>
-      <c r="K27" s="9" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="9" t="n">
+        <v>0.0002</v>
+      </c>
       <c r="L27" s="9" t="n"/>
       <c r="M27" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="N27" s="10">
         <f>IF(D27="Govt",$B$1,$B$2)</f>
@@ -2070,7 +2116,7 @@
         <v/>
       </c>
       <c r="Q27" s="12" t="n">
-        <v>5.06</v>
+        <v>5.3551</v>
       </c>
     </row>
     <row r="28">
@@ -2081,12 +2127,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>IE000I25S1V5</t>
+          <t>IE000W6YTDH7</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -2096,7 +2142,7 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F28" s="6" t="n">
@@ -2115,7 +2161,9 @@
       <c r="J28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="K28" s="9" t="n"/>
+      <c r="K28" s="9" t="n">
+        <v>0.0002</v>
+      </c>
       <c r="L28" s="9" t="n"/>
       <c r="M28" s="8" t="n">
         <v>0.001</v>
@@ -2133,23 +2181,23 @@
         <v/>
       </c>
       <c r="Q28" s="12" t="n">
-        <v>5.3624</v>
+        <v>4.9882</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>iShares iBonds Dec 2030 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>IE000W6YTDH7</t>
+          <t>IE000LX17BP9</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -2170,18 +2218,20 @@
         <v/>
       </c>
       <c r="H29" s="8" t="n">
-        <v>0.0286</v>
+        <v>0.028</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>0.0406</v>
+        <v>0.0407</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="9" t="n"/>
+        <v>0.0002</v>
+      </c>
+      <c r="K29" s="9" t="n">
+        <v>-0.0004</v>
+      </c>
       <c r="L29" s="9" t="n"/>
       <c r="M29" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N29" s="10">
         <f>IF(D29="Govt",$B$1,$B$2)</f>
@@ -2196,7 +2246,7 @@
         <v/>
       </c>
       <c r="Q29" s="12" t="n">
-        <v>4.9949</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="30">
@@ -2207,17 +2257,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2030 Term € Corp UCITS ETF</t>
+          <t>iShares iBonds Dec 2028 Term € Italy Govt Bond UCITS ETF</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>IE000LX17BP9</t>
+          <t>IE000Q2EQ5K8</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -2226,22 +2276,24 @@
         </is>
       </c>
       <c r="F30" s="6" t="n">
-        <v>47848</v>
+        <v>47118</v>
       </c>
       <c r="G30" s="7">
         <f>IF(F30="","",MAX(0,YEARFRAC(TODAY(),F30)))</f>
         <v/>
       </c>
       <c r="H30" s="8" t="n">
-        <v>0.028</v>
+        <v>0.0261</v>
       </c>
       <c r="I30" s="8" t="n">
-        <v>0.0405</v>
+        <v>0.0343</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.0004</v>
-      </c>
-      <c r="K30" s="9" t="n"/>
+        <v>-0.0005</v>
+      </c>
+      <c r="K30" s="9" t="n">
+        <v>-0.0009</v>
+      </c>
       <c r="L30" s="9" t="n"/>
       <c r="M30" s="8" t="n">
         <v>0.0012</v>
@@ -2259,7 +2311,7 @@
         <v/>
       </c>
       <c r="Q30" s="12" t="n">
-        <v>5</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="31">
@@ -2299,12 +2351,14 @@
         <v>0.027</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>0.0405</v>
+        <v>0.04019999999999999</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="K31" s="9" t="n"/>
+        <v>-0.0003</v>
+      </c>
+      <c r="K31" s="9" t="n">
+        <v>-0.0009</v>
+      </c>
       <c r="L31" s="9" t="n"/>
       <c r="M31" s="8" t="n">
         <v>0.0012</v>
@@ -2322,7 +2376,7 @@
         <v/>
       </c>
       <c r="Q31" s="12" t="n">
-        <v>35.28</v>
+        <v>35.31</v>
       </c>
     </row>
     <row r="32">
@@ -2362,12 +2416,14 @@
         <v>0.023</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>0.0334</v>
+        <v>0.033</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.0008</v>
-      </c>
-      <c r="K32" s="9" t="n"/>
+        <v>-0.0004</v>
+      </c>
+      <c r="K32" s="9" t="n">
+        <v>-0.0001</v>
+      </c>
       <c r="L32" s="9" t="n"/>
       <c r="M32" s="8" t="n">
         <v>0.0009</v>
@@ -2385,28 +2441,28 @@
         <v/>
       </c>
       <c r="Q32" s="12" t="n">
-        <v>10.2934</v>
+        <v>10.2995</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Dist</t>
+          <t>iShares iBonds Dec 2029 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>LU2780871401</t>
+          <t>IE000IHURBR0</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -2415,25 +2471,27 @@
         </is>
       </c>
       <c r="F33" s="6" t="n">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="G33" s="7">
         <f>IF(F33="","",MAX(0,YEARFRAC(TODAY(),F33)))</f>
         <v/>
       </c>
       <c r="H33" s="8" t="n">
-        <v>0.0184</v>
+        <v>0.0253</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>0.033</v>
+        <v>0.0391</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.0007</v>
-      </c>
-      <c r="K33" s="9" t="n"/>
+        <v>0.0002</v>
+      </c>
+      <c r="K33" s="9" t="n">
+        <v>-0.0004</v>
+      </c>
       <c r="L33" s="9" t="n"/>
       <c r="M33" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N33" s="10">
         <f>IF(D33="Govt",$B$1,$B$2)</f>
@@ -2448,7 +2506,7 @@
         <v/>
       </c>
       <c r="Q33" s="12" t="n">
-        <v>10.2834</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="34">
@@ -2459,12 +2517,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>LU2780871310</t>
+          <t>LU2780871401</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -2474,7 +2532,7 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F34" s="6" t="n">
@@ -2488,12 +2546,14 @@
         <v>0.0184</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>0.033</v>
+        <v>0.0327</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.0007</v>
-      </c>
-      <c r="K34" s="9" t="n"/>
+        <v>-0.0003</v>
+      </c>
+      <c r="K34" s="9" t="n">
+        <v>-0.0001</v>
+      </c>
       <c r="L34" s="9" t="n"/>
       <c r="M34" s="8" t="n">
         <v>0.0009</v>
@@ -2511,55 +2571,57 @@
         <v/>
       </c>
       <c r="Q34" s="12" t="n">
-        <v>10.0826</v>
+        <v>10.2872</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2029 Term € Corp UCITS ETF</t>
+          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>IE000IHURBR0</t>
+          <t>LU2780871310</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F35" s="6" t="n">
-        <v>47483</v>
+        <v>47118</v>
       </c>
       <c r="G35" s="7">
         <f>IF(F35="","",MAX(0,YEARFRAC(TODAY(),F35)))</f>
         <v/>
       </c>
       <c r="H35" s="8" t="n">
-        <v>0.0252</v>
+        <v>0.0184</v>
       </c>
       <c r="I35" s="8" t="n">
-        <v>0.0389</v>
+        <v>0.0327</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.0004</v>
-      </c>
-      <c r="K35" s="9" t="n"/>
+        <v>-0.0003</v>
+      </c>
+      <c r="K35" s="9" t="n">
+        <v>-0.0001</v>
+      </c>
       <c r="L35" s="9" t="n"/>
       <c r="M35" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N35" s="10">
         <f>IF(D35="Govt",$B$1,$B$2)</f>
@@ -2574,7 +2636,7 @@
         <v/>
       </c>
       <c r="Q35" s="12" t="n">
-        <v>5.04</v>
+        <v>10.0864</v>
       </c>
     </row>
     <row r="36">
@@ -2619,7 +2681,9 @@
       <c r="J36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="K36" s="9" t="n"/>
+      <c r="K36" s="9" t="n">
+        <v>0.0002</v>
+      </c>
       <c r="L36" s="9" t="n"/>
       <c r="M36" s="8" t="n">
         <v>0.001</v>
@@ -2637,7 +2701,7 @@
         <v/>
       </c>
       <c r="Q36" s="12" t="n">
-        <v>5.4353</v>
+        <v>5.4297</v>
       </c>
     </row>
     <row r="37">
@@ -2682,7 +2746,9 @@
       <c r="J37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="K37" s="9" t="n"/>
+      <c r="K37" s="9" t="n">
+        <v>0.0002</v>
+      </c>
       <c r="L37" s="9" t="n"/>
       <c r="M37" s="8" t="n">
         <v>0.001</v>
@@ -2700,7 +2766,7 @@
         <v/>
       </c>
       <c r="Q37" s="12" t="n">
-        <v>5.0647</v>
+        <v>5.0595</v>
       </c>
     </row>
     <row r="38">
@@ -2740,12 +2806,14 @@
         <v>0.0245</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>0.0387</v>
+        <v>0.0384</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.0004</v>
-      </c>
-      <c r="K38" s="9" t="n"/>
+        <v>-0.0003</v>
+      </c>
+      <c r="K38" s="9" t="n">
+        <v>-0.0007</v>
+      </c>
       <c r="L38" s="9" t="n"/>
       <c r="M38" s="8" t="n">
         <v>0.0012</v>
@@ -2763,7 +2831,7 @@
         <v/>
       </c>
       <c r="Q38" s="12" t="n">
-        <v>25.81</v>
+        <v>25.82</v>
       </c>
     </row>
     <row r="39">
@@ -2803,12 +2871,14 @@
         <v>0.0245</v>
       </c>
       <c r="I39" s="8" t="n">
-        <v>0.0387</v>
+        <v>0.0384</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.0004</v>
-      </c>
-      <c r="K39" s="9" t="n"/>
+        <v>-0.0003</v>
+      </c>
+      <c r="K39" s="9" t="n">
+        <v>-0.0007</v>
+      </c>
       <c r="L39" s="9" t="n"/>
       <c r="M39" s="8" t="n">
         <v>0.0012</v>
@@ -2866,12 +2936,14 @@
         <v>0.0235</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>0.0383</v>
+        <v>0.038</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.0003</v>
-      </c>
-      <c r="K40" s="9" t="n"/>
+        <v>-0.0003</v>
+      </c>
+      <c r="K40" s="9" t="n">
+        <v>-0.0013</v>
+      </c>
       <c r="L40" s="9" t="n"/>
       <c r="M40" s="8" t="n">
         <v>0.0012</v>
@@ -2889,7 +2961,7 @@
         <v/>
       </c>
       <c r="Q40" s="12" t="n">
-        <v>10.6722</v>
+        <v>10.6798</v>
       </c>
     </row>
     <row r="41">
@@ -2929,12 +3001,14 @@
         <v>0.0235</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>0.0383</v>
+        <v>0.038</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.0003</v>
-      </c>
-      <c r="K41" s="9" t="n"/>
+        <v>-0.0003</v>
+      </c>
+      <c r="K41" s="9" t="n">
+        <v>-0.0013</v>
+      </c>
       <c r="L41" s="9" t="n"/>
       <c r="M41" s="8" t="n">
         <v>0.0012</v>
@@ -2952,7 +3026,7 @@
         <v/>
       </c>
       <c r="Q41" s="12" t="n">
-        <v>10.3105</v>
+        <v>10.3178</v>
       </c>
     </row>
     <row r="42">
@@ -2997,7 +3071,9 @@
       <c r="J42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="K42" s="9" t="n"/>
+      <c r="K42" s="9" t="n">
+        <v>0.0008</v>
+      </c>
       <c r="L42" s="9" t="n"/>
       <c r="M42" s="8" t="n">
         <v>0.001</v>
@@ -3015,7 +3091,7 @@
         <v/>
       </c>
       <c r="Q42" s="12" t="n">
-        <v>5.5774</v>
+        <v>5.5751</v>
       </c>
     </row>
     <row r="43">
@@ -3060,7 +3136,9 @@
       <c r="J43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="K43" s="9" t="n"/>
+      <c r="K43" s="9" t="n">
+        <v>0.0008</v>
+      </c>
       <c r="L43" s="9" t="n"/>
       <c r="M43" s="8" t="n">
         <v>0.001</v>
@@ -3078,7 +3156,7 @@
         <v/>
       </c>
       <c r="Q43" s="12" t="n">
-        <v>5.2162</v>
+        <v>5.214</v>
       </c>
     </row>
     <row r="44">
@@ -3121,9 +3199,11 @@
         <v>0.0375</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.0004</v>
-      </c>
-      <c r="K44" s="9" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="K44" s="9" t="n">
+        <v>0.0001</v>
+      </c>
       <c r="L44" s="9" t="n"/>
       <c r="M44" s="8" t="n">
         <v>0.0012</v>
@@ -3141,7 +3221,7 @@
         <v/>
       </c>
       <c r="Q44" s="12" t="n">
-        <v>5.11</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="45">
@@ -3181,12 +3261,14 @@
         <v>0.0207</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>0.0371</v>
+        <v>0.0369</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.0003</v>
-      </c>
-      <c r="K45" s="9" t="n"/>
+        <v>-0.0002</v>
+      </c>
+      <c r="K45" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="L45" s="9" t="n"/>
       <c r="M45" s="8" t="n">
         <v>0.0012</v>
@@ -3204,7 +3286,7 @@
         <v/>
       </c>
       <c r="Q45" s="12" t="n">
-        <v>35.79</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="46">
@@ -3244,12 +3326,14 @@
         <v>0.0265</v>
       </c>
       <c r="I46" s="8" t="n">
-        <v>0.0311</v>
+        <v>0.0308</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.0005999999999999999</v>
-      </c>
-      <c r="K46" s="9" t="n"/>
+        <v>-0.0003</v>
+      </c>
+      <c r="K46" s="9" t="n">
+        <v>0.0003</v>
+      </c>
       <c r="L46" s="9" t="n"/>
       <c r="M46" s="8" t="n">
         <v>0.0009</v>
@@ -3267,7 +3351,7 @@
         <v/>
       </c>
       <c r="Q46" s="12" t="n">
-        <v>10.3442</v>
+        <v>10.3463</v>
       </c>
     </row>
     <row r="47">
@@ -3307,12 +3391,14 @@
         <v>0.015</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>0.0299</v>
+        <v>0.0297</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.0004</v>
-      </c>
-      <c r="K47" s="9" t="n"/>
+        <v>-0.0002</v>
+      </c>
+      <c r="K47" s="9" t="n">
+        <v>-0.0001</v>
+      </c>
       <c r="L47" s="9" t="n"/>
       <c r="M47" s="8" t="n">
         <v>0.0009</v>
@@ -3330,7 +3416,7 @@
         <v/>
       </c>
       <c r="Q47" s="12" t="n">
-        <v>10.1839</v>
+        <v>10.1847</v>
       </c>
     </row>
     <row r="48">
@@ -3370,12 +3456,14 @@
         <v>0.0105</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>0.0286</v>
+        <v>0.0284</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.0003</v>
-      </c>
-      <c r="K48" s="9" t="n"/>
+        <v>-0.0002</v>
+      </c>
+      <c r="K48" s="9" t="n">
+        <v>-0.0009</v>
+      </c>
       <c r="L48" s="9" t="n"/>
       <c r="M48" s="8" t="n">
         <v>0.0009</v>
@@ -3393,7 +3481,7 @@
         <v/>
       </c>
       <c r="Q48" s="12" t="n">
-        <v>10.3597</v>
+        <v>10.361</v>
       </c>
     </row>
     <row r="49">
@@ -3438,7 +3526,9 @@
       <c r="J49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="K49" s="9" t="n"/>
+      <c r="K49" s="9" t="n">
+        <v>0.0009</v>
+      </c>
       <c r="L49" s="9" t="n"/>
       <c r="M49" s="8" t="n">
         <v>0.001</v>
@@ -3456,7 +3546,7 @@
         <v/>
       </c>
       <c r="Q49" s="12" t="n">
-        <v>5.7123</v>
+        <v>5.7121</v>
       </c>
     </row>
     <row r="50">
@@ -3501,7 +3591,9 @@
       <c r="J50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="K50" s="9" t="n"/>
+      <c r="K50" s="9" t="n">
+        <v>0.0009</v>
+      </c>
       <c r="L50" s="9" t="n"/>
       <c r="M50" s="8" t="n">
         <v>0.001</v>
@@ -3519,7 +3611,7 @@
         <v/>
       </c>
       <c r="Q50" s="12" t="n">
-        <v>5.3397</v>
+        <v>5.3395</v>
       </c>
     </row>
     <row r="51">
@@ -3559,12 +3651,14 @@
         <v>0.0195</v>
       </c>
       <c r="I51" s="8" t="n">
-        <v>0.0335</v>
+        <v>0.0336</v>
       </c>
       <c r="J51" s="9" t="n">
         <v>0.0001</v>
       </c>
-      <c r="K51" s="9" t="n"/>
+      <c r="K51" s="9" t="n">
+        <v>0.0008</v>
+      </c>
       <c r="L51" s="9" t="n"/>
       <c r="M51" s="8" t="n">
         <v>0.0012</v>
@@ -3622,12 +3716,14 @@
         <v>0.0187</v>
       </c>
       <c r="I52" s="8" t="n">
-        <v>0.0319</v>
+        <v>0.0316</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" s="9" t="n"/>
+        <v>-0.0003</v>
+      </c>
+      <c r="K52" s="9" t="n">
+        <v>0.0001</v>
+      </c>
       <c r="L52" s="9" t="n"/>
       <c r="M52" s="8" t="n">
         <v>0.0012</v>
@@ -3685,12 +3781,14 @@
         <v>0.0187</v>
       </c>
       <c r="I53" s="8" t="n">
-        <v>0.0319</v>
+        <v>0.0316</v>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" s="9" t="n"/>
+        <v>-0.0003</v>
+      </c>
+      <c r="K53" s="9" t="n">
+        <v>0.0001</v>
+      </c>
       <c r="L53" s="9" t="n"/>
       <c r="M53" s="8" t="n">
         <v>0.0012</v>
@@ -3708,7 +3806,7 @@
         <v/>
       </c>
       <c r="Q53" s="12" t="n">
-        <v>9.31</v>
+        <v>9.32</v>
       </c>
     </row>
     <row r="54">
@@ -3748,12 +3846,14 @@
         <v>0.008800000000000001</v>
       </c>
       <c r="I54" s="8" t="n">
-        <v>0.027</v>
+        <v>0.0269</v>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="K54" s="9" t="n"/>
+        <v>-0.0001</v>
+      </c>
+      <c r="K54" s="9" t="n">
+        <v>0.0002</v>
+      </c>
       <c r="L54" s="9" t="n"/>
       <c r="M54" s="8" t="n">
         <v>0.0012</v>
@@ -3811,12 +3911,14 @@
         <v>0.0023</v>
       </c>
       <c r="I55" s="8" t="n">
-        <v>0.026</v>
+        <v>0.0258</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>-0.0004</v>
-      </c>
-      <c r="K55" s="9" t="n"/>
+        <v>-0.0002</v>
+      </c>
+      <c r="K55" s="9" t="n">
+        <v>-0.0001</v>
+      </c>
       <c r="L55" s="9" t="n"/>
       <c r="M55" s="8" t="n">
         <v>0.0009</v>
@@ -3834,7 +3936,7 @@
         <v/>
       </c>
       <c r="Q55" s="12" t="n">
-        <v>10.2674</v>
+        <v>10.268</v>
       </c>
     </row>
     <row r="56">
@@ -3879,7 +3981,9 @@
       <c r="J56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="K56" s="9" t="n"/>
+      <c r="K56" s="9" t="n">
+        <v>0.0005</v>
+      </c>
       <c r="L56" s="9" t="n"/>
       <c r="M56" s="8" t="n">
         <v>0.001</v>
@@ -3897,7 +4001,7 @@
         <v/>
       </c>
       <c r="Q56" s="12" t="n">
-        <v>5.7972</v>
+        <v>5.7977</v>
       </c>
     </row>
     <row r="57">
@@ -3942,7 +4046,9 @@
       <c r="J57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="K57" s="9" t="n"/>
+      <c r="K57" s="9" t="n">
+        <v>0.0005</v>
+      </c>
       <c r="L57" s="9" t="n"/>
       <c r="M57" s="8" t="n">
         <v>0.001</v>
@@ -3960,7 +4066,7 @@
         <v/>
       </c>
       <c r="Q57" s="12" t="n">
-        <v>5.4206</v>
+        <v>5.4211</v>
       </c>
     </row>
     <row r="58">
@@ -3997,15 +4103,17 @@
         <v/>
       </c>
       <c r="H58" s="8" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.0044</v>
       </c>
       <c r="I58" s="8" t="n">
-        <v>0.0274</v>
+        <v>0.0269</v>
       </c>
       <c r="J58" s="9" t="n">
-        <v>-0.0001</v>
-      </c>
-      <c r="K58" s="9" t="n"/>
+        <v>-0.0005</v>
+      </c>
+      <c r="K58" s="9" t="n">
+        <v>-0.0008</v>
+      </c>
       <c r="L58" s="9" t="n"/>
       <c r="M58" s="8" t="n">
         <v>0.0012</v>

--- a/data/rendimenti_etf.xlsx
+++ b/data/rendimenti_etf.xlsx
@@ -533,7 +533,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Aggiornato il 26/10/2026 09:03 da yield_etf.csv</t>
+          <t>Aggiornato il 27/10/2026 09:03 da yield_etf.csv</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
         <v>0.0528</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>0.0044</v>
@@ -686,7 +686,7 @@
         <v/>
       </c>
       <c r="Q5" s="12" t="n">
-        <v>4.86</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="6">
@@ -726,13 +726,13 @@
         <v>0.0377</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0.046</v>
+        <v>0.04650000000000001</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.0001</v>
+        <v>0.0005</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="L6" s="9" t="n"/>
       <c r="M6" s="8" t="n">
@@ -751,23 +751,23 @@
         <v/>
       </c>
       <c r="Q6" s="12" t="n">
-        <v>28.4</v>
+        <v>28.28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2036 Term € Corp UCITS ETF</t>
+          <t>Xtrackers II Target Maturity Sept 2035 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>IE000RQJBQI6</t>
+          <t>LU3152892546</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -781,23 +781,23 @@
         </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>50040</v>
+        <v>49582</v>
       </c>
       <c r="G7" s="7">
         <f>IF(F7="","",MAX(0,YEARFRAC(TODAY(),F7)))</f>
         <v/>
       </c>
       <c r="H7" s="8" t="n">
-        <v>0.0356</v>
+        <v>0.0368</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0.0458</v>
+        <v>0.0461</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.0003</v>
+        <v>0.0004</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.0003</v>
+        <v>0.0005</v>
       </c>
       <c r="L7" s="9" t="n"/>
       <c r="M7" s="8" t="n">
@@ -816,23 +816,23 @@
         <v/>
       </c>
       <c r="Q7" s="12" t="n">
-        <v>4.82</v>
+        <v>29.11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2035 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>iShares iBonds Dec 2036 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LU3152892546</t>
+          <t>IE000RQJBQI6</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -846,23 +846,23 @@
         </is>
       </c>
       <c r="F8" s="6" t="n">
-        <v>49582</v>
+        <v>50040</v>
       </c>
       <c r="G8" s="7">
         <f>IF(F8="","",MAX(0,YEARFRAC(TODAY(),F8)))</f>
         <v/>
       </c>
       <c r="H8" s="8" t="n">
-        <v>0.0367</v>
+        <v>0.0356</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>0.0457</v>
+        <v>0.0458</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.0001</v>
+        <v>0.0003</v>
       </c>
       <c r="L8" s="9" t="n"/>
       <c r="M8" s="8" t="n">
@@ -881,7 +881,7 @@
         <v/>
       </c>
       <c r="Q8" s="12" t="n">
-        <v>29.21</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="9">
@@ -924,7 +924,7 @@
         <v>0.0455</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.0004</v>
+        <v>0</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>0.0002</v>
@@ -946,7 +946,7 @@
         <v/>
       </c>
       <c r="Q9" s="12" t="n">
-        <v>4.73</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="10">
@@ -989,7 +989,7 @@
         <v>0.0453</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>-0.0001</v>
@@ -1011,23 +1011,23 @@
         <v/>
       </c>
       <c r="Q10" s="12" t="n">
-        <v>4.83</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2028 Term € Corp Crossover UCITS ETF</t>
+          <t>Xtrackers II Target Maturity Sept 2034 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>IE0003HV7CS6</t>
+          <t>LU2809864619</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -1037,31 +1037,31 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F11" s="6" t="n">
-        <v>47118</v>
+        <v>49217</v>
       </c>
       <c r="G11" s="7">
         <f>IF(F11="","",MAX(0,YEARFRAC(TODAY(),F11)))</f>
         <v/>
       </c>
       <c r="H11" s="8" t="n">
-        <v>0.0329</v>
+        <v>0.0351</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>0.0459</v>
+        <v>0.0453</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.0013</v>
+        <v>0.0005</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.0041</v>
+        <v>0.0002</v>
       </c>
       <c r="L11" s="9" t="n"/>
       <c r="M11" s="8" t="n">
-        <v>0.002</v>
+        <v>0.0012</v>
       </c>
       <c r="N11" s="10">
         <f>IF(D11="Govt",$B$1,$B$2)</f>
@@ -1076,23 +1076,23 @@
         <v/>
       </c>
       <c r="Q11" s="12" t="n">
-        <v>5.09</v>
+        <v>33.52</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2034 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>iShares iBonds Dec 2028 Term € Corp Crossover UCITS ETF</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LU2809864619</t>
+          <t>IE0003HV7CS6</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -1102,31 +1102,31 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>49217</v>
+        <v>47118</v>
       </c>
       <c r="G12" s="7">
         <f>IF(F12="","",MAX(0,YEARFRAC(TODAY(),F12)))</f>
         <v/>
       </c>
       <c r="H12" s="8" t="n">
-        <v>0.0351</v>
+        <v>0.0329</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>0.04480000000000001</v>
+        <v>0.0459</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0.0041</v>
       </c>
       <c r="L12" s="9" t="n"/>
       <c r="M12" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.002</v>
       </c>
       <c r="N12" s="10">
         <f>IF(D12="Govt",$B$1,$B$2)</f>
@@ -1141,23 +1141,23 @@
         <v/>
       </c>
       <c r="Q12" s="12" t="n">
-        <v>33.62</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2034 Term € Corp UCITS ETF</t>
+          <t>Xtrackers II Target Maturity Sept 2033 EUR Corporate Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>IE000SBJO6L2</t>
+          <t>LU2673523051</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -1167,27 +1167,27 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>49309</v>
+        <v>48852</v>
       </c>
       <c r="G13" s="7">
         <f>IF(F13="","",MAX(0,YEARFRAC(TODAY(),F13)))</f>
         <v/>
       </c>
       <c r="H13" s="8" t="n">
-        <v>0.0348</v>
+        <v>0.0338</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0.0447</v>
+        <v>0.04480000000000001</v>
       </c>
       <c r="J13" s="9" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K13" s="9" t="n">
         <v>0.0002</v>
-      </c>
-      <c r="K13" s="9" t="n">
-        <v>-0.0001</v>
       </c>
       <c r="L13" s="9" t="n"/>
       <c r="M13" s="8" t="n">
@@ -1206,7 +1206,7 @@
         <v/>
       </c>
       <c r="Q13" s="12" t="n">
-        <v>4.75</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2033 EUR Corporate Bond UCITS ETF 1C</t>
+          <t>Xtrackers II Target Maturity Sept 2033 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LU2673523051</t>
+          <t>LU2673523564</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F14" s="6" t="n">
@@ -1246,13 +1246,13 @@
         <v>0.0338</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>0.0443</v>
+        <v>0.04480000000000001</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0005</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0.0002</v>
       </c>
       <c r="L14" s="9" t="n"/>
       <c r="M14" s="8" t="n">
@@ -1271,23 +1271,23 @@
         <v/>
       </c>
       <c r="Q14" s="12" t="n">
-        <v>9.33</v>
+        <v>27.86</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2033 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>iShares iBonds Dec 2034 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>LU2673523564</t>
+          <t>IE000SBJO6L2</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -1301,23 +1301,23 @@
         </is>
       </c>
       <c r="F15" s="6" t="n">
-        <v>48852</v>
+        <v>49309</v>
       </c>
       <c r="G15" s="7">
         <f>IF(F15="","",MAX(0,YEARFRAC(TODAY(),F15)))</f>
         <v/>
       </c>
       <c r="H15" s="8" t="n">
-        <v>0.0338</v>
+        <v>0.0348</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>0.0443</v>
+        <v>0.0447</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>-0.0003</v>
+        <v>-0.0001</v>
       </c>
       <c r="L15" s="9" t="n"/>
       <c r="M15" s="8" t="n">
@@ -1336,7 +1336,7 @@
         <v/>
       </c>
       <c r="Q15" s="12" t="n">
-        <v>27.94</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="16">
@@ -1379,7 +1379,7 @@
         <v>0.0441</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>-0.0003</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="Q16" s="12" t="n">
-        <v>4.78</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="17">
@@ -1441,13 +1441,13 @@
         <v>0.0282</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>0.0435</v>
+        <v>0.044</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0.0005</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0003</v>
       </c>
       <c r="L17" s="9" t="n"/>
       <c r="M17" s="8" t="n">
@@ -1466,57 +1466,57 @@
         <v/>
       </c>
       <c r="Q17" s="12" t="n">
-        <v>34.32</v>
+        <v>34.24</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2032 Term € Corp UCITS ETF</t>
+          <t>Amundi Fixed Maturity 2030 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>IE0000MR4GH9</t>
+          <t>LU3120976132</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>48579</v>
+        <v>47848</v>
       </c>
       <c r="G18" s="7">
         <f>IF(F18="","",MAX(0,YEARFRAC(TODAY(),F18)))</f>
         <v/>
       </c>
       <c r="H18" s="8" t="n">
-        <v>0.0301</v>
+        <v>0.0169</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>0.043</v>
+        <v>0.0365</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.0002</v>
+        <v>0.0007</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0.0017</v>
       </c>
       <c r="L18" s="9" t="n"/>
       <c r="M18" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N18" s="10">
         <f>IF(D18="Govt",$B$1,$B$2)</f>
@@ -1531,57 +1531,57 @@
         <v/>
       </c>
       <c r="Q18" s="12" t="n">
-        <v>4.83</v>
+        <v>9.840299999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2030 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>iShares iBonds Dec 2032 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LU3120976132</t>
+          <t>IE0000MR4GH9</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>47848</v>
+        <v>48579</v>
       </c>
       <c r="G19" s="7">
         <f>IF(F19="","",MAX(0,YEARFRAC(TODAY(),F19)))</f>
         <v/>
       </c>
       <c r="H19" s="8" t="n">
-        <v>0.0169</v>
+        <v>0.0301</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>0.0358</v>
+        <v>0.043</v>
       </c>
       <c r="J19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="9" t="n">
         <v>-0.0003</v>
-      </c>
-      <c r="K19" s="9" t="n">
-        <v>0.001</v>
       </c>
       <c r="L19" s="9" t="n"/>
       <c r="M19" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N19" s="10">
         <f>IF(D19="Govt",$B$1,$B$2)</f>
@@ -1596,7 +1596,7 @@
         <v/>
       </c>
       <c r="Q19" s="12" t="n">
-        <v>9.8352</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="20">
@@ -1639,7 +1639,7 @@
         <v>0.0424</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>-0.0003</v>
@@ -1661,7 +1661,7 @@
         <v/>
       </c>
       <c r="Q20" s="12" t="n">
-        <v>4.88</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="21">
@@ -1701,13 +1701,13 @@
         <v>0.0269</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>0.0417</v>
+        <v>0.0423</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>-0.0014</v>
+        <v>-0.0008</v>
       </c>
       <c r="L21" s="9" t="n"/>
       <c r="M21" s="8" t="n">
@@ -1726,7 +1726,7 @@
         <v/>
       </c>
       <c r="Q21" s="12" t="n">
-        <v>10.4595</v>
+        <v>10.4377</v>
       </c>
     </row>
     <row r="22">
@@ -1766,13 +1766,13 @@
         <v>0.0269</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>0.0417</v>
+        <v>0.0423</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>-0.0014</v>
+        <v>-0.0008</v>
       </c>
       <c r="L22" s="9" t="n"/>
       <c r="M22" s="8" t="n">
@@ -1791,28 +1791,28 @@
         <v/>
       </c>
       <c r="Q22" s="12" t="n">
-        <v>10.0725</v>
+        <v>10.0515</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1C</t>
+          <t>Amundi Fixed Maturity 2029 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>LU2673523135</t>
+          <t>LU2872291781</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -1821,27 +1821,27 @@
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>48121</v>
+        <v>47483</v>
       </c>
       <c r="G23" s="7">
         <f>IF(F23="","",MAX(0,YEARFRAC(TODAY(),F23)))</f>
         <v/>
       </c>
       <c r="H23" s="8" t="n">
-        <v>0.0287</v>
+        <v>0.0208</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>0.0416</v>
+        <v>0.0356</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0007</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>-0.0008</v>
+        <v>0.0015</v>
       </c>
       <c r="L23" s="9" t="n"/>
       <c r="M23" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N23" s="10">
         <f>IF(D23="Govt",$B$1,$B$2)</f>
@@ -1856,7 +1856,7 @@
         <v/>
       </c>
       <c r="Q23" s="12" t="n">
-        <v>9.81</v>
+        <v>9.994199999999999</v>
       </c>
     </row>
     <row r="24">
@@ -1867,12 +1867,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>LU2673523481</t>
+          <t>LU2673523135</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
@@ -1896,13 +1896,13 @@
         <v>0.0287</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>0.0416</v>
+        <v>0.042</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0004</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>-0.0008</v>
+        <v>-0.0004</v>
       </c>
       <c r="L24" s="9" t="n"/>
       <c r="M24" s="8" t="n">
@@ -1921,57 +1921,57 @@
         <v/>
       </c>
       <c r="Q24" s="12" t="n">
-        <v>29.36</v>
+        <v>9.789999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2029 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>LU2872291781</t>
+          <t>LU2673523481</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F25" s="6" t="n">
-        <v>47483</v>
+        <v>48121</v>
       </c>
       <c r="G25" s="7">
         <f>IF(F25="","",MAX(0,YEARFRAC(TODAY(),F25)))</f>
         <v/>
       </c>
       <c r="H25" s="8" t="n">
-        <v>0.0208</v>
+        <v>0.0287</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>0.0349</v>
+        <v>0.042</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0.0004</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.0008</v>
+        <v>-0.0004</v>
       </c>
       <c r="L25" s="9" t="n"/>
       <c r="M25" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N25" s="10">
         <f>IF(D25="Govt",$B$1,$B$2)</f>
@@ -1986,28 +1986,28 @@
         <v/>
       </c>
       <c r="Q25" s="12" t="n">
-        <v>9.991199999999999</v>
+        <v>29.31</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2029 Italy and Spain Government Bond UCITS ETF 1C</t>
+          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>LU0484969463</t>
+          <t>IE000I25S1V5</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -2016,27 +2016,27 @@
         </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>47391</v>
+        <v>47848</v>
       </c>
       <c r="G26" s="7">
         <f>IF(F26="","",MAX(0,YEARFRAC(TODAY(),F26)))</f>
         <v/>
       </c>
       <c r="H26" s="8" t="n">
-        <v>0.0297</v>
+        <v>0.0286</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>0.0352</v>
+        <v>0.0411</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0.0005</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>-0.0004</v>
+        <v>0.0007</v>
       </c>
       <c r="L26" s="9" t="n"/>
       <c r="M26" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="N26" s="10">
         <f>IF(D26="Govt",$B$1,$B$2)</f>
@@ -2051,7 +2051,7 @@
         <v/>
       </c>
       <c r="Q26" s="12" t="n">
-        <v>204.63</v>
+        <v>5.3455</v>
       </c>
     </row>
     <row r="27">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>IE000I25S1V5</t>
+          <t>IE000W6YTDH7</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F27" s="6" t="n">
@@ -2091,13 +2091,13 @@
         <v>0.0286</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>0.0406</v>
+        <v>0.0411</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.0002</v>
+        <v>0.0007</v>
       </c>
       <c r="L27" s="9" t="n"/>
       <c r="M27" s="8" t="n">
@@ -2116,57 +2116,57 @@
         <v/>
       </c>
       <c r="Q27" s="12" t="n">
-        <v>5.3551</v>
+        <v>4.9792</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>Xtrackers II Target Maturity Sept 2029 Italy and Spain Government Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>IE000W6YTDH7</t>
+          <t>LU0484969463</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F28" s="6" t="n">
-        <v>47848</v>
+        <v>47391</v>
       </c>
       <c r="G28" s="7">
         <f>IF(F28="","",MAX(0,YEARFRAC(TODAY(),F28)))</f>
         <v/>
       </c>
       <c r="H28" s="8" t="n">
-        <v>0.0286</v>
+        <v>0.0297</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>0.0406</v>
+        <v>0.0348</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0</v>
+        <v>-0.0004</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.0002</v>
+        <v>-0.0008</v>
       </c>
       <c r="L28" s="9" t="n"/>
       <c r="M28" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N28" s="10">
         <f>IF(D28="Govt",$B$1,$B$2)</f>
@@ -2181,7 +2181,7 @@
         <v/>
       </c>
       <c r="Q28" s="12" t="n">
-        <v>4.9882</v>
+        <v>204.82</v>
       </c>
     </row>
     <row r="29">
@@ -2224,7 +2224,7 @@
         <v>0.0407</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>-0.0004</v>
@@ -2246,28 +2246,28 @@
         <v/>
       </c>
       <c r="Q29" s="12" t="n">
-        <v>4.99</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2028 Term € Italy Govt Bond UCITS ETF</t>
+          <t>Xtrackers II Target Maturity Sept 2030 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>IE000Q2EQ5K8</t>
+          <t>LU2809864296</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -2276,23 +2276,23 @@
         </is>
       </c>
       <c r="F30" s="6" t="n">
-        <v>47118</v>
+        <v>47756</v>
       </c>
       <c r="G30" s="7">
         <f>IF(F30="","",MAX(0,YEARFRAC(TODAY(),F30)))</f>
         <v/>
       </c>
       <c r="H30" s="8" t="n">
-        <v>0.0261</v>
+        <v>0.027</v>
       </c>
       <c r="I30" s="8" t="n">
-        <v>0.0343</v>
+        <v>0.0406</v>
       </c>
       <c r="J30" s="9" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="K30" s="9" t="n">
         <v>-0.0005</v>
-      </c>
-      <c r="K30" s="9" t="n">
-        <v>-0.0009</v>
       </c>
       <c r="L30" s="9" t="n"/>
       <c r="M30" s="8" t="n">
@@ -2311,28 +2311,28 @@
         <v/>
       </c>
       <c r="Q30" s="12" t="n">
-        <v>5.06</v>
+        <v>35.27</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2030 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>iShares iBonds Dec 2028 Term € Italy Govt Bond UCITS ETF</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>LU2809864296</t>
+          <t>IE000Q2EQ5K8</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -2341,20 +2341,20 @@
         </is>
       </c>
       <c r="F31" s="6" t="n">
-        <v>47756</v>
+        <v>47118</v>
       </c>
       <c r="G31" s="7">
         <f>IF(F31="","",MAX(0,YEARFRAC(TODAY(),F31)))</f>
         <v/>
       </c>
       <c r="H31" s="8" t="n">
-        <v>0.027</v>
+        <v>0.0261</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>0.04019999999999999</v>
+        <v>0.0343</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>-0.0009</v>
@@ -2376,7 +2376,7 @@
         <v/>
       </c>
       <c r="Q31" s="12" t="n">
-        <v>35.31</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="32">
@@ -2413,16 +2413,16 @@
         <v/>
       </c>
       <c r="H32" s="8" t="n">
-        <v>0.023</v>
+        <v>0.0229</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>0.033</v>
+        <v>0.0336</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>-0.0004</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0.0005</v>
       </c>
       <c r="L32" s="9" t="n"/>
       <c r="M32" s="8" t="n">
@@ -2441,28 +2441,28 @@
         <v/>
       </c>
       <c r="Q32" s="12" t="n">
-        <v>10.2995</v>
+        <v>10.2983</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2029 Term € Corp UCITS ETF</t>
+          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>IE000IHURBR0</t>
+          <t>LU2780871401</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -2471,27 +2471,27 @@
         </is>
       </c>
       <c r="F33" s="6" t="n">
-        <v>47483</v>
+        <v>47118</v>
       </c>
       <c r="G33" s="7">
         <f>IF(F33="","",MAX(0,YEARFRAC(TODAY(),F33)))</f>
         <v/>
       </c>
       <c r="H33" s="8" t="n">
-        <v>0.0253</v>
+        <v>0.0184</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>0.0391</v>
+        <v>0.0333</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.0002</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>-0.0004</v>
+        <v>0.0005</v>
       </c>
       <c r="L33" s="9" t="n"/>
       <c r="M33" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N33" s="10">
         <f>IF(D33="Govt",$B$1,$B$2)</f>
@@ -2506,7 +2506,7 @@
         <v/>
       </c>
       <c r="Q33" s="12" t="n">
-        <v>5.04</v>
+        <v>10.2851</v>
       </c>
     </row>
     <row r="34">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Dist</t>
+          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>LU2780871401</t>
+          <t>LU2780871310</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F34" s="6" t="n">
@@ -2546,13 +2546,13 @@
         <v>0.0184</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>0.0327</v>
+        <v>0.0333</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0.0005</v>
       </c>
       <c r="L34" s="9" t="n"/>
       <c r="M34" s="8" t="n">
@@ -2571,28 +2571,28 @@
         <v/>
       </c>
       <c r="Q34" s="12" t="n">
-        <v>10.2872</v>
+        <v>10.0843</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>LU2780871310</t>
+          <t>IE000P5IB8I8</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -2601,27 +2601,27 @@
         </is>
       </c>
       <c r="F35" s="6" t="n">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="G35" s="7">
         <f>IF(F35="","",MAX(0,YEARFRAC(TODAY(),F35)))</f>
         <v/>
       </c>
       <c r="H35" s="8" t="n">
-        <v>0.0184</v>
+        <v>0.0242</v>
       </c>
       <c r="I35" s="8" t="n">
-        <v>0.0327</v>
+        <v>0.0392</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0.0008</v>
       </c>
       <c r="L35" s="9" t="n"/>
       <c r="M35" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="N35" s="10">
         <f>IF(D35="Govt",$B$1,$B$2)</f>
@@ -2636,7 +2636,7 @@
         <v/>
       </c>
       <c r="Q35" s="12" t="n">
-        <v>10.0864</v>
+        <v>5.4224</v>
       </c>
     </row>
     <row r="36">
@@ -2647,12 +2647,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>IE000P5IB8I8</t>
+          <t>IE000ZC4C5Q1</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F36" s="6" t="n">
@@ -2676,13 +2676,13 @@
         <v>0.0242</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>0.0386</v>
+        <v>0.0392</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.0002</v>
+        <v>0.0008</v>
       </c>
       <c r="L36" s="9" t="n"/>
       <c r="M36" s="8" t="n">
@@ -2701,23 +2701,23 @@
         <v/>
       </c>
       <c r="Q36" s="12" t="n">
-        <v>5.4297</v>
+        <v>5.0527</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>iShares iBonds Dec 2029 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>IE000ZC4C5Q1</t>
+          <t>IE000IHURBR0</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -2738,20 +2738,20 @@
         <v/>
       </c>
       <c r="H37" s="8" t="n">
-        <v>0.0242</v>
+        <v>0.0253</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>0.0386</v>
+        <v>0.0391</v>
       </c>
       <c r="J37" s="9" t="n">
         <v>0</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.0002</v>
+        <v>-0.0004</v>
       </c>
       <c r="L37" s="9" t="n"/>
       <c r="M37" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N37" s="10">
         <f>IF(D37="Govt",$B$1,$B$2)</f>
@@ -2766,7 +2766,7 @@
         <v/>
       </c>
       <c r="Q37" s="12" t="n">
-        <v>5.0595</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="38">
@@ -2806,13 +2806,13 @@
         <v>0.0245</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>0.0384</v>
+        <v>0.0388</v>
       </c>
       <c r="J38" s="9" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="K38" s="9" t="n">
         <v>-0.0003</v>
-      </c>
-      <c r="K38" s="9" t="n">
-        <v>-0.0007</v>
       </c>
       <c r="L38" s="9" t="n"/>
       <c r="M38" s="8" t="n">
@@ -2831,7 +2831,7 @@
         <v/>
       </c>
       <c r="Q38" s="12" t="n">
-        <v>25.82</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="39">
@@ -2871,13 +2871,13 @@
         <v>0.0245</v>
       </c>
       <c r="I39" s="8" t="n">
-        <v>0.0384</v>
+        <v>0.0388</v>
       </c>
       <c r="J39" s="9" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="K39" s="9" t="n">
         <v>-0.0003</v>
-      </c>
-      <c r="K39" s="9" t="n">
-        <v>-0.0007</v>
       </c>
       <c r="L39" s="9" t="n"/>
       <c r="M39" s="8" t="n">
@@ -2896,7 +2896,7 @@
         <v/>
       </c>
       <c r="Q39" s="12" t="n">
-        <v>9.18</v>
+        <v>9.17</v>
       </c>
     </row>
     <row r="40">
@@ -2936,13 +2936,13 @@
         <v>0.0235</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>0.038</v>
+        <v>0.0386</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>-0.0013</v>
+        <v>-0.0007</v>
       </c>
       <c r="L40" s="9" t="n"/>
       <c r="M40" s="8" t="n">
@@ -2961,7 +2961,7 @@
         <v/>
       </c>
       <c r="Q40" s="12" t="n">
-        <v>10.6798</v>
+        <v>10.6691</v>
       </c>
     </row>
     <row r="41">
@@ -3001,13 +3001,13 @@
         <v>0.0235</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>0.038</v>
+        <v>0.0386</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>-0.0013</v>
+        <v>-0.0007</v>
       </c>
       <c r="L41" s="9" t="n"/>
       <c r="M41" s="8" t="n">
@@ -3026,7 +3026,7 @@
         <v/>
       </c>
       <c r="Q41" s="12" t="n">
-        <v>10.3178</v>
+        <v>10.3075</v>
       </c>
     </row>
     <row r="42">
@@ -3066,13 +3066,13 @@
         <v>0.0242</v>
       </c>
       <c r="I42" s="8" t="n">
-        <v>0.0375</v>
+        <v>0.0381</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.0008</v>
+        <v>0.0014</v>
       </c>
       <c r="L42" s="9" t="n"/>
       <c r="M42" s="8" t="n">
@@ -3091,7 +3091,7 @@
         <v/>
       </c>
       <c r="Q42" s="12" t="n">
-        <v>5.5751</v>
+        <v>5.5709</v>
       </c>
     </row>
     <row r="43">
@@ -3131,13 +3131,13 @@
         <v>0.0242</v>
       </c>
       <c r="I43" s="8" t="n">
-        <v>0.0375</v>
+        <v>0.0381</v>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.0008</v>
+        <v>0.0014</v>
       </c>
       <c r="L43" s="9" t="n"/>
       <c r="M43" s="8" t="n">
@@ -3156,7 +3156,7 @@
         <v/>
       </c>
       <c r="Q43" s="12" t="n">
-        <v>5.214</v>
+        <v>5.2102</v>
       </c>
     </row>
     <row r="44">
@@ -3261,13 +3261,13 @@
         <v>0.0207</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>0.0369</v>
+        <v>0.0372</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0003</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0</v>
+        <v>0.0003</v>
       </c>
       <c r="L45" s="9" t="n"/>
       <c r="M45" s="8" t="n">
@@ -3286,7 +3286,7 @@
         <v/>
       </c>
       <c r="Q45" s="12" t="n">
-        <v>35.8</v>
+        <v>35.79</v>
       </c>
     </row>
     <row r="46">
@@ -3326,13 +3326,13 @@
         <v>0.0265</v>
       </c>
       <c r="I46" s="8" t="n">
-        <v>0.0308</v>
+        <v>0.0311</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0.0003</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.0003</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="L46" s="9" t="n"/>
       <c r="M46" s="8" t="n">
@@ -3351,7 +3351,7 @@
         <v/>
       </c>
       <c r="Q46" s="12" t="n">
-        <v>10.3463</v>
+        <v>10.3459</v>
       </c>
     </row>
     <row r="47">
@@ -3391,13 +3391,13 @@
         <v>0.015</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>0.0297</v>
+        <v>0.03</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0003</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="L47" s="9" t="n"/>
       <c r="M47" s="8" t="n">
@@ -3416,33 +3416,33 @@
         <v/>
       </c>
       <c r="Q47" s="12" t="n">
-        <v>10.1847</v>
+        <v>10.1835</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2027 German Bund Government Bond UCITS ETF Dist</t>
+          <t>Invesco BulletShares 2027 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>LU2780871823</t>
+          <t>IE000LGHLQ71</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
@@ -3453,20 +3453,20 @@
         <v/>
       </c>
       <c r="H48" s="8" t="n">
-        <v>0.0105</v>
+        <v>0.0197</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>0.0284</v>
+        <v>0.0348</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0013</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>-0.0009</v>
+        <v>0.0022</v>
       </c>
       <c r="L48" s="9" t="n"/>
       <c r="M48" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="N48" s="10">
         <f>IF(D48="Govt",$B$1,$B$2)</f>
@@ -3481,7 +3481,7 @@
         <v/>
       </c>
       <c r="Q48" s="12" t="n">
-        <v>10.361</v>
+        <v>5.7122</v>
       </c>
     </row>
     <row r="49">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2027 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>Invesco BulletShares 2027 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>IE000LGHLQ71</t>
+          <t>IE000XOS4OJ6</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F49" s="6" t="n">
@@ -3521,13 +3521,13 @@
         <v>0.0197</v>
       </c>
       <c r="I49" s="8" t="n">
-        <v>0.0335</v>
+        <v>0.0348</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0</v>
+        <v>0.0013</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.0009</v>
+        <v>0.0022</v>
       </c>
       <c r="L49" s="9" t="n"/>
       <c r="M49" s="8" t="n">
@@ -3546,28 +3546,28 @@
         <v/>
       </c>
       <c r="Q49" s="12" t="n">
-        <v>5.7121</v>
+        <v>5.3396</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2027 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>Amundi Fixed Maturity 2027 German Bund Government Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>IE000XOS4OJ6</t>
+          <t>LU2780871823</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -3583,20 +3583,20 @@
         <v/>
       </c>
       <c r="H50" s="8" t="n">
-        <v>0.0197</v>
+        <v>0.0105</v>
       </c>
       <c r="I50" s="8" t="n">
-        <v>0.0335</v>
+        <v>0.0286</v>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.0009</v>
+        <v>-0.0007</v>
       </c>
       <c r="L50" s="9" t="n"/>
       <c r="M50" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0009</v>
       </c>
       <c r="N50" s="10">
         <f>IF(D50="Govt",$B$1,$B$2)</f>
@@ -3611,7 +3611,7 @@
         <v/>
       </c>
       <c r="Q50" s="12" t="n">
-        <v>5.3395</v>
+        <v>10.358</v>
       </c>
     </row>
     <row r="51">
@@ -3654,7 +3654,7 @@
         <v>0.0336</v>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="K51" s="9" t="n">
         <v>0.0008</v>
@@ -3682,51 +3682,51 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>Amundi Fixed Maturity 2026 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>LU2673523218</t>
+          <t>LU2872291278</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F52" s="6" t="n">
-        <v>46660</v>
+        <v>46387</v>
       </c>
       <c r="G52" s="7">
         <f>IF(F52="","",MAX(0,YEARFRAC(TODAY(),F52)))</f>
         <v/>
       </c>
       <c r="H52" s="8" t="n">
-        <v>0.0187</v>
+        <v>0.0021</v>
       </c>
       <c r="I52" s="8" t="n">
-        <v>0.0316</v>
+        <v>0.0275</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0.0017</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.0001</v>
+        <v>0.0016</v>
       </c>
       <c r="L52" s="9" t="n"/>
       <c r="M52" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N52" s="10">
         <f>IF(D52="Govt",$B$1,$B$2)</f>
@@ -3741,7 +3741,7 @@
         <v/>
       </c>
       <c r="Q52" s="12" t="n">
-        <v>25.98</v>
+        <v>10.2687</v>
       </c>
     </row>
     <row r="53">
@@ -3752,12 +3752,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1C</t>
+          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LU2673522830</t>
+          <t>LU2673523218</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F53" s="6" t="n">
@@ -3781,13 +3781,13 @@
         <v>0.0187</v>
       </c>
       <c r="I53" s="8" t="n">
-        <v>0.0316</v>
+        <v>0.032</v>
       </c>
       <c r="J53" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0.0004</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.0001</v>
+        <v>0.0005</v>
       </c>
       <c r="L53" s="9" t="n"/>
       <c r="M53" s="8" t="n">
@@ -3806,53 +3806,53 @@
         <v/>
       </c>
       <c r="Q53" s="12" t="n">
-        <v>9.32</v>
+        <v>25.98</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2026 Term € Italy Govt Bond UCITS ETF</t>
+          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>IE000LZ7BZW8</t>
+          <t>LU2673522830</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F54" s="6" t="n">
-        <v>46387</v>
+        <v>46660</v>
       </c>
       <c r="G54" s="7">
         <f>IF(F54="","",MAX(0,YEARFRAC(TODAY(),F54)))</f>
         <v/>
       </c>
       <c r="H54" s="8" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0187</v>
       </c>
       <c r="I54" s="8" t="n">
-        <v>0.0269</v>
+        <v>0.032</v>
       </c>
       <c r="J54" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0.0004</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.0002</v>
+        <v>0.0005</v>
       </c>
       <c r="L54" s="9" t="n"/>
       <c r="M54" s="8" t="n">
@@ -3871,23 +3871,23 @@
         <v/>
       </c>
       <c r="Q54" s="12" t="n">
-        <v>5.06</v>
+        <v>9.32</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2026 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>iShares iBonds Dec 2026 Term € Italy Govt Bond UCITS ETF</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>LU2872291278</t>
+          <t>IE000LZ7BZW8</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -3897,7 +3897,7 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F55" s="6" t="n">
@@ -3908,20 +3908,20 @@
         <v/>
       </c>
       <c r="H55" s="8" t="n">
-        <v>0.0023</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="I55" s="8" t="n">
-        <v>0.0258</v>
+        <v>0.0269</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="L55" s="9" t="n"/>
       <c r="M55" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N55" s="10">
         <f>IF(D55="Govt",$B$1,$B$2)</f>
@@ -3936,7 +3936,7 @@
         <v/>
       </c>
       <c r="Q55" s="12" t="n">
-        <v>10.268</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="56">
@@ -3973,16 +3973,16 @@
         <v/>
       </c>
       <c r="H56" s="8" t="n">
-        <v>0.0119</v>
+        <v>0.0109</v>
       </c>
       <c r="I56" s="8" t="n">
-        <v>0.0298</v>
+        <v>0.0274</v>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0</v>
+        <v>-0.0024</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.0005</v>
+        <v>-0.0019</v>
       </c>
       <c r="L56" s="9" t="n"/>
       <c r="M56" s="8" t="n">
@@ -4001,7 +4001,7 @@
         <v/>
       </c>
       <c r="Q56" s="12" t="n">
-        <v>5.7977</v>
+        <v>5.7986</v>
       </c>
     </row>
     <row r="57">
@@ -4038,16 +4038,16 @@
         <v/>
       </c>
       <c r="H57" s="8" t="n">
-        <v>0.0119</v>
+        <v>0.0109</v>
       </c>
       <c r="I57" s="8" t="n">
-        <v>0.0298</v>
+        <v>0.0274</v>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0</v>
+        <v>-0.0024</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.0005</v>
+        <v>-0.0019</v>
       </c>
       <c r="L57" s="9" t="n"/>
       <c r="M57" s="8" t="n">
@@ -4066,7 +4066,7 @@
         <v/>
       </c>
       <c r="Q57" s="12" t="n">
-        <v>5.4211</v>
+        <v>5.4219</v>
       </c>
     </row>
     <row r="58">
@@ -4109,7 +4109,7 @@
         <v>0.0269</v>
       </c>
       <c r="J58" s="9" t="n">
-        <v>-0.0005</v>
+        <v>0</v>
       </c>
       <c r="K58" s="9" t="n">
         <v>-0.0008</v>

--- a/data/rendimenti_etf.xlsx
+++ b/data/rendimenti_etf.xlsx
@@ -533,7 +533,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Aggiornato il 27/10/2026 09:03 da yield_etf.csv</t>
+          <t>Aggiornato il 28/10/2026 09:03 da yield_etf.csv</t>
         </is>
       </c>
     </row>
@@ -658,16 +658,16 @@
         <v/>
       </c>
       <c r="H5" s="8" t="n">
-        <v>0.0388</v>
+        <v>0.0389</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>0.0528</v>
+        <v>0.0533</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.0044</v>
+        <v>0.0038</v>
       </c>
       <c r="L5" s="9" t="n"/>
       <c r="M5" s="8" t="n">
@@ -686,7 +686,7 @@
         <v/>
       </c>
       <c r="Q5" s="12" t="n">
-        <v>4.85</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="6">
@@ -726,13 +726,13 @@
         <v>0.0377</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0.04650000000000001</v>
+        <v>0.04679999999999999</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.0005</v>
+        <v>0.0003</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.0005</v>
+        <v>-0.0002</v>
       </c>
       <c r="L6" s="9" t="n"/>
       <c r="M6" s="8" t="n">
@@ -751,7 +751,7 @@
         <v/>
       </c>
       <c r="Q6" s="12" t="n">
-        <v>28.28</v>
+        <v>28.24</v>
       </c>
     </row>
     <row r="7">
@@ -791,13 +791,13 @@
         <v>0.0368</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0.0461</v>
+        <v>0.0464</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.0004</v>
+        <v>0.0003</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.0005</v>
+        <v>-0.0002</v>
       </c>
       <c r="L7" s="9" t="n"/>
       <c r="M7" s="8" t="n">
@@ -816,7 +816,7 @@
         <v/>
       </c>
       <c r="Q7" s="12" t="n">
-        <v>29.11</v>
+        <v>29.06</v>
       </c>
     </row>
     <row r="8">
@@ -856,13 +856,13 @@
         <v>0.0356</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>0.0458</v>
+        <v>0.0461</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0</v>
+        <v>0.0003</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.0003</v>
+        <v>-0.0005</v>
       </c>
       <c r="L8" s="9" t="n"/>
       <c r="M8" s="8" t="n">
@@ -918,16 +918,16 @@
         <v/>
       </c>
       <c r="H9" s="8" t="n">
-        <v>0.0364</v>
+        <v>0.0365</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>0.0455</v>
+        <v>0.0459</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.0002</v>
+        <v>-0.0005</v>
       </c>
       <c r="L9" s="9" t="n"/>
       <c r="M9" s="8" t="n">
@@ -986,13 +986,13 @@
         <v>0.0349</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>0.0453</v>
+        <v>0.0457</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>-0.0001</v>
+        <v>-0.0007</v>
       </c>
       <c r="L10" s="9" t="n"/>
       <c r="M10" s="8" t="n">
@@ -1011,7 +1011,7 @@
         <v/>
       </c>
       <c r="Q10" s="12" t="n">
-        <v>4.81</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="11">
@@ -1051,13 +1051,13 @@
         <v>0.0351</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>0.0453</v>
+        <v>0.0457</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.0005</v>
+        <v>0.0004</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.0002</v>
+        <v>-0.0002</v>
       </c>
       <c r="L11" s="9" t="n"/>
       <c r="M11" s="8" t="n">
@@ -1076,7 +1076,7 @@
         <v/>
       </c>
       <c r="Q11" s="12" t="n">
-        <v>33.52</v>
+        <v>33.45</v>
       </c>
     </row>
     <row r="12">
@@ -1116,13 +1116,13 @@
         <v>0.0329</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>0.0459</v>
+        <v>0.0463</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.0041</v>
+        <v>0.0031</v>
       </c>
       <c r="L12" s="9" t="n"/>
       <c r="M12" s="8" t="n">
@@ -1181,13 +1181,13 @@
         <v>0.0338</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0.04480000000000001</v>
+        <v>0.0452</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.0005</v>
+        <v>0.0004</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.0002</v>
+        <v>-0.0002</v>
       </c>
       <c r="L13" s="9" t="n"/>
       <c r="M13" s="8" t="n">
@@ -1206,7 +1206,7 @@
         <v/>
       </c>
       <c r="Q13" s="12" t="n">
-        <v>9.300000000000001</v>
+        <v>9.279999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1246,13 +1246,13 @@
         <v>0.0338</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>0.04480000000000001</v>
+        <v>0.0452</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.0005</v>
+        <v>0.0004</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.0002</v>
+        <v>-0.0002</v>
       </c>
       <c r="L14" s="9" t="n"/>
       <c r="M14" s="8" t="n">
@@ -1271,7 +1271,7 @@
         <v/>
       </c>
       <c r="Q14" s="12" t="n">
-        <v>27.86</v>
+        <v>27.81</v>
       </c>
     </row>
     <row r="15">
@@ -1311,13 +1311,13 @@
         <v>0.0348</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>0.0447</v>
+        <v>0.0451</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>-0.0001</v>
+        <v>-0.0005</v>
       </c>
       <c r="L15" s="9" t="n"/>
       <c r="M15" s="8" t="n">
@@ -1336,7 +1336,7 @@
         <v/>
       </c>
       <c r="Q15" s="12" t="n">
-        <v>4.74</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="16">
@@ -1376,13 +1376,13 @@
         <v>0.0331</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>0.0441</v>
+        <v>0.0446</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>-0.0003</v>
+        <v>-0.0005</v>
       </c>
       <c r="L16" s="9" t="n"/>
       <c r="M16" s="8" t="n">
@@ -1441,13 +1441,13 @@
         <v>0.0282</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>0.044</v>
+        <v>0.0445</v>
       </c>
       <c r="J17" s="9" t="n">
         <v>0.0005</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.0003</v>
+        <v>0.0001</v>
       </c>
       <c r="L17" s="9" t="n"/>
       <c r="M17" s="8" t="n">
@@ -1466,57 +1466,57 @@
         <v/>
       </c>
       <c r="Q17" s="12" t="n">
-        <v>34.24</v>
+        <v>34.18</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2030 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>iShares iBonds Dec 2032 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LU3120976132</t>
+          <t>IE0000MR4GH9</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>47848</v>
+        <v>48579</v>
       </c>
       <c r="G18" s="7">
         <f>IF(F18="","",MAX(0,YEARFRAC(TODAY(),F18)))</f>
         <v/>
       </c>
       <c r="H18" s="8" t="n">
-        <v>0.0169</v>
+        <v>0.0301</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>0.0365</v>
+        <v>0.0435</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.0007</v>
+        <v>0.0005</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.0017</v>
+        <v>-0.0004</v>
       </c>
       <c r="L18" s="9" t="n"/>
       <c r="M18" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N18" s="10">
         <f>IF(D18="Govt",$B$1,$B$2)</f>
@@ -1531,57 +1531,57 @@
         <v/>
       </c>
       <c r="Q18" s="12" t="n">
-        <v>9.840299999999999</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2032 Term € Corp UCITS ETF</t>
+          <t>Amundi Fixed Maturity 2030 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>IE0000MR4GH9</t>
+          <t>LU3120976132</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>48579</v>
+        <v>47848</v>
       </c>
       <c r="G19" s="7">
         <f>IF(F19="","",MAX(0,YEARFRAC(TODAY(),F19)))</f>
         <v/>
       </c>
       <c r="H19" s="8" t="n">
-        <v>0.0301</v>
+        <v>0.0169</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>0.043</v>
+        <v>0.0364</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0</v>
+        <v>-0.0001</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0.0015</v>
       </c>
       <c r="L19" s="9" t="n"/>
       <c r="M19" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N19" s="10">
         <f>IF(D19="Govt",$B$1,$B$2)</f>
@@ -1596,7 +1596,7 @@
         <v/>
       </c>
       <c r="Q19" s="12" t="n">
-        <v>4.82</v>
+        <v>9.8497</v>
       </c>
     </row>
     <row r="20">
@@ -1636,13 +1636,13 @@
         <v>0.0285</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>0.0424</v>
+        <v>0.0429</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>-0.0003</v>
+        <v>-0.0004</v>
       </c>
       <c r="L20" s="9" t="n"/>
       <c r="M20" s="8" t="n">
@@ -1701,13 +1701,13 @@
         <v>0.0269</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>0.0423</v>
+        <v>0.04269999999999999</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0004</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>-0.0008</v>
+        <v>-0.0003</v>
       </c>
       <c r="L21" s="9" t="n"/>
       <c r="M21" s="8" t="n">
@@ -1766,13 +1766,13 @@
         <v>0.0269</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>0.0423</v>
+        <v>0.04269999999999999</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0004</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>-0.0008</v>
+        <v>-0.0003</v>
       </c>
       <c r="L22" s="9" t="n"/>
       <c r="M22" s="8" t="n">
@@ -1797,22 +1797,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2029 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>LU2872291781</t>
+          <t>LU2673523135</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -1821,27 +1821,27 @@
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>47483</v>
+        <v>48121</v>
       </c>
       <c r="G23" s="7">
         <f>IF(F23="","",MAX(0,YEARFRAC(TODAY(),F23)))</f>
         <v/>
       </c>
       <c r="H23" s="8" t="n">
-        <v>0.0208</v>
+        <v>0.0287</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>0.0356</v>
+        <v>0.0426</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.0007</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.0015</v>
+        <v>-0.0003</v>
       </c>
       <c r="L23" s="9" t="n"/>
       <c r="M23" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N23" s="10">
         <f>IF(D23="Govt",$B$1,$B$2)</f>
@@ -1856,7 +1856,7 @@
         <v/>
       </c>
       <c r="Q23" s="12" t="n">
-        <v>9.994199999999999</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="24">
@@ -1867,12 +1867,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1C</t>
+          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>LU2673523135</t>
+          <t>LU2673523481</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
@@ -1896,13 +1896,13 @@
         <v>0.0287</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>0.042</v>
+        <v>0.0426</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.0004</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>-0.0004</v>
+        <v>-0.0003</v>
       </c>
       <c r="L24" s="9" t="n"/>
       <c r="M24" s="8" t="n">
@@ -1921,57 +1921,57 @@
         <v/>
       </c>
       <c r="Q24" s="12" t="n">
-        <v>9.789999999999999</v>
+        <v>29.25</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>Amundi Fixed Maturity 2029 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>LU2673523481</t>
+          <t>LU2872291781</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F25" s="6" t="n">
-        <v>48121</v>
+        <v>47483</v>
       </c>
       <c r="G25" s="7">
         <f>IF(F25="","",MAX(0,YEARFRAC(TODAY(),F25)))</f>
         <v/>
       </c>
       <c r="H25" s="8" t="n">
-        <v>0.0287</v>
+        <v>0.0208</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>0.042</v>
+        <v>0.0356</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.0004</v>
+        <v>0</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>-0.0004</v>
+        <v>0.0014</v>
       </c>
       <c r="L25" s="9" t="n"/>
       <c r="M25" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N25" s="10">
         <f>IF(D25="Govt",$B$1,$B$2)</f>
@@ -1986,7 +1986,7 @@
         <v/>
       </c>
       <c r="Q25" s="12" t="n">
-        <v>29.31</v>
+        <v>10.0024</v>
       </c>
     </row>
     <row r="26">
@@ -2026,13 +2026,13 @@
         <v>0.0286</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>0.0411</v>
+        <v>0.0417</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.0005</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.0007</v>
+        <v>0.0013</v>
       </c>
       <c r="L26" s="9" t="n"/>
       <c r="M26" s="8" t="n">
@@ -2051,7 +2051,7 @@
         <v/>
       </c>
       <c r="Q26" s="12" t="n">
-        <v>5.3455</v>
+        <v>5.3515</v>
       </c>
     </row>
     <row r="27">
@@ -2091,13 +2091,13 @@
         <v>0.0286</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>0.0411</v>
+        <v>0.0417</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.0005</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.0007</v>
+        <v>0.0013</v>
       </c>
       <c r="L27" s="9" t="n"/>
       <c r="M27" s="8" t="n">
@@ -2116,53 +2116,53 @@
         <v/>
       </c>
       <c r="Q27" s="12" t="n">
-        <v>4.9792</v>
+        <v>4.9848</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2029 Italy and Spain Government Bond UCITS ETF 1C</t>
+          <t>iShares iBonds Dec 2030 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>LU0484969463</t>
+          <t>IE000LX17BP9</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F28" s="6" t="n">
-        <v>47391</v>
+        <v>47848</v>
       </c>
       <c r="G28" s="7">
         <f>IF(F28="","",MAX(0,YEARFRAC(TODAY(),F28)))</f>
         <v/>
       </c>
       <c r="H28" s="8" t="n">
-        <v>0.0297</v>
+        <v>0.0281</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>0.0348</v>
+        <v>0.0414</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>-0.0004</v>
+        <v>0.0007</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>-0.0008</v>
+        <v>-0.0001</v>
       </c>
       <c r="L28" s="9" t="n"/>
       <c r="M28" s="8" t="n">
@@ -2181,23 +2181,23 @@
         <v/>
       </c>
       <c r="Q28" s="12" t="n">
-        <v>204.82</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2030 Term € Corp UCITS ETF</t>
+          <t>Xtrackers II Target Maturity Sept 2030 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>IE000LX17BP9</t>
+          <t>LU2809864296</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -2211,23 +2211,23 @@
         </is>
       </c>
       <c r="F29" s="6" t="n">
-        <v>47848</v>
+        <v>47756</v>
       </c>
       <c r="G29" s="7">
         <f>IF(F29="","",MAX(0,YEARFRAC(TODAY(),F29)))</f>
         <v/>
       </c>
       <c r="H29" s="8" t="n">
-        <v>0.028</v>
+        <v>0.027</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>0.0407</v>
+        <v>0.0413</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0</v>
+        <v>0.0007</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>-0.0004</v>
+        <v>-0.0001</v>
       </c>
       <c r="L29" s="9" t="n"/>
       <c r="M29" s="8" t="n">
@@ -2246,7 +2246,7 @@
         <v/>
       </c>
       <c r="Q29" s="12" t="n">
-        <v>4.98</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="30">
@@ -2257,42 +2257,42 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2030 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>Xtrackers II Target Maturity Sept 2029 Italy and Spain Government Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>LU2809864296</t>
+          <t>LU0484969463</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F30" s="6" t="n">
-        <v>47756</v>
+        <v>47391</v>
       </c>
       <c r="G30" s="7">
         <f>IF(F30="","",MAX(0,YEARFRAC(TODAY(),F30)))</f>
         <v/>
       </c>
       <c r="H30" s="8" t="n">
-        <v>0.027</v>
+        <v>0.0297</v>
       </c>
       <c r="I30" s="8" t="n">
-        <v>0.0406</v>
+        <v>0.0348</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.0004</v>
+        <v>0</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>-0.0005</v>
+        <v>-0.0008</v>
       </c>
       <c r="L30" s="9" t="n"/>
       <c r="M30" s="8" t="n">
@@ -2311,7 +2311,7 @@
         <v/>
       </c>
       <c r="Q30" s="12" t="n">
-        <v>35.27</v>
+        <v>204.93</v>
       </c>
     </row>
     <row r="31">
@@ -2351,13 +2351,13 @@
         <v>0.0261</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>0.0343</v>
+        <v>0.0342</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0</v>
+        <v>-0.0001</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>-0.0009</v>
+        <v>-0.0008</v>
       </c>
       <c r="L31" s="9" t="n"/>
       <c r="M31" s="8" t="n">
@@ -2382,51 +2382,51 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2028 Euro Government Bond Yield + UCITS ETF Dist</t>
+          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>LU2780871666</t>
+          <t>IE000P5IB8I8</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F32" s="6" t="n">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="G32" s="7">
         <f>IF(F32="","",MAX(0,YEARFRAC(TODAY(),F32)))</f>
         <v/>
       </c>
       <c r="H32" s="8" t="n">
-        <v>0.0229</v>
+        <v>0.0242</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>0.0336</v>
+        <v>0.0399</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0007</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.0005</v>
+        <v>0.0015</v>
       </c>
       <c r="L32" s="9" t="n"/>
       <c r="M32" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="N32" s="10">
         <f>IF(D32="Govt",$B$1,$B$2)</f>
@@ -2441,28 +2441,28 @@
         <v/>
       </c>
       <c r="Q32" s="12" t="n">
-        <v>10.2983</v>
+        <v>5.4272</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Dist</t>
+          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>LU2780871401</t>
+          <t>IE000ZC4C5Q1</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -2471,27 +2471,27 @@
         </is>
       </c>
       <c r="F33" s="6" t="n">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="G33" s="7">
         <f>IF(F33="","",MAX(0,YEARFRAC(TODAY(),F33)))</f>
         <v/>
       </c>
       <c r="H33" s="8" t="n">
-        <v>0.0184</v>
+        <v>0.0242</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>0.0333</v>
+        <v>0.0399</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0007</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.0005</v>
+        <v>0.0015</v>
       </c>
       <c r="L33" s="9" t="n"/>
       <c r="M33" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="N33" s="10">
         <f>IF(D33="Govt",$B$1,$B$2)</f>
@@ -2506,57 +2506,57 @@
         <v/>
       </c>
       <c r="Q33" s="12" t="n">
-        <v>10.2851</v>
+        <v>5.0572</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>iShares iBonds Dec 2029 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>LU2780871310</t>
+          <t>IE000IHURBR0</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F34" s="6" t="n">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="G34" s="7">
         <f>IF(F34="","",MAX(0,YEARFRAC(TODAY(),F34)))</f>
         <v/>
       </c>
       <c r="H34" s="8" t="n">
-        <v>0.0184</v>
+        <v>0.0253</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>0.0333</v>
+        <v>0.0398</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0007</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.0005</v>
+        <v>0</v>
       </c>
       <c r="L34" s="9" t="n"/>
       <c r="M34" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N34" s="10">
         <f>IF(D34="Govt",$B$1,$B$2)</f>
@@ -2571,57 +2571,57 @@
         <v/>
       </c>
       <c r="Q34" s="12" t="n">
-        <v>10.0843</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>Amundi Fixed Maturity 2028 Euro Government Bond Yield + UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>IE000P5IB8I8</t>
+          <t>LU2780871666</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F35" s="6" t="n">
-        <v>47483</v>
+        <v>47118</v>
       </c>
       <c r="G35" s="7">
         <f>IF(F35="","",MAX(0,YEARFRAC(TODAY(),F35)))</f>
         <v/>
       </c>
       <c r="H35" s="8" t="n">
-        <v>0.0242</v>
+        <v>0.0229</v>
       </c>
       <c r="I35" s="8" t="n">
-        <v>0.0392</v>
+        <v>0.0334</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.0002</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.0008</v>
+        <v>0.0002</v>
       </c>
       <c r="L35" s="9" t="n"/>
       <c r="M35" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0009</v>
       </c>
       <c r="N35" s="10">
         <f>IF(D35="Govt",$B$1,$B$2)</f>
@@ -2636,23 +2636,23 @@
         <v/>
       </c>
       <c r="Q35" s="12" t="n">
-        <v>5.4224</v>
+        <v>10.3051</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>Xtrackers II Target Maturity Sept 2029 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>IE000ZC4C5Q1</t>
+          <t>LU2673523309</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -2666,27 +2666,27 @@
         </is>
       </c>
       <c r="F36" s="6" t="n">
-        <v>47483</v>
+        <v>47391</v>
       </c>
       <c r="G36" s="7">
         <f>IF(F36="","",MAX(0,YEARFRAC(TODAY(),F36)))</f>
         <v/>
       </c>
       <c r="H36" s="8" t="n">
-        <v>0.0242</v>
+        <v>0.0245</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>0.0392</v>
+        <v>0.0395</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0007</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.0008</v>
+        <v>0.0002</v>
       </c>
       <c r="L36" s="9" t="n"/>
       <c r="M36" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N36" s="10">
         <f>IF(D36="Govt",$B$1,$B$2)</f>
@@ -2701,23 +2701,23 @@
         <v/>
       </c>
       <c r="Q36" s="12" t="n">
-        <v>5.0527</v>
+        <v>25.77</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2029 Term € Corp UCITS ETF</t>
+          <t>Xtrackers II Target Maturity Sept 2029 EUR Corporate Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>IE000IHURBR0</t>
+          <t>LU2673522913</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -2727,27 +2727,27 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F37" s="6" t="n">
-        <v>47483</v>
+        <v>47391</v>
       </c>
       <c r="G37" s="7">
         <f>IF(F37="","",MAX(0,YEARFRAC(TODAY(),F37)))</f>
         <v/>
       </c>
       <c r="H37" s="8" t="n">
-        <v>0.0253</v>
+        <v>0.0245</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>0.0391</v>
+        <v>0.0395</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0</v>
+        <v>0.0007</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>-0.0004</v>
+        <v>0.0002</v>
       </c>
       <c r="L37" s="9" t="n"/>
       <c r="M37" s="8" t="n">
@@ -2766,28 +2766,28 @@
         <v/>
       </c>
       <c r="Q37" s="12" t="n">
-        <v>5.03</v>
+        <v>9.16</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2029 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LU2673523309</t>
+          <t>LU2780871401</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -2796,27 +2796,27 @@
         </is>
       </c>
       <c r="F38" s="6" t="n">
-        <v>47391</v>
+        <v>47118</v>
       </c>
       <c r="G38" s="7">
         <f>IF(F38="","",MAX(0,YEARFRAC(TODAY(),F38)))</f>
         <v/>
       </c>
       <c r="H38" s="8" t="n">
-        <v>0.0245</v>
+        <v>0.0184</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>0.0388</v>
+        <v>0.0331</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.0004</v>
+        <v>-0.0002</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0.0003</v>
       </c>
       <c r="L38" s="9" t="n"/>
       <c r="M38" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N38" s="10">
         <f>IF(D38="Govt",$B$1,$B$2)</f>
@@ -2831,28 +2831,28 @@
         <v/>
       </c>
       <c r="Q38" s="12" t="n">
-        <v>25.8</v>
+        <v>10.2911</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2029 EUR Corporate Bond UCITS ETF 1C</t>
+          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>LU2673522913</t>
+          <t>LU2780871310</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -2861,27 +2861,27 @@
         </is>
       </c>
       <c r="F39" s="6" t="n">
-        <v>47391</v>
+        <v>47118</v>
       </c>
       <c r="G39" s="7">
         <f>IF(F39="","",MAX(0,YEARFRAC(TODAY(),F39)))</f>
         <v/>
       </c>
       <c r="H39" s="8" t="n">
-        <v>0.0245</v>
+        <v>0.0184</v>
       </c>
       <c r="I39" s="8" t="n">
-        <v>0.0388</v>
+        <v>0.0331</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.0004</v>
+        <v>-0.0002</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0.0003</v>
       </c>
       <c r="L39" s="9" t="n"/>
       <c r="M39" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N39" s="10">
         <f>IF(D39="Govt",$B$1,$B$2)</f>
@@ -2896,7 +2896,7 @@
         <v/>
       </c>
       <c r="Q39" s="12" t="n">
-        <v>9.17</v>
+        <v>10.0902</v>
       </c>
     </row>
     <row r="40">
@@ -2936,13 +2936,13 @@
         <v>0.0235</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>0.0386</v>
+        <v>0.0392</v>
       </c>
       <c r="J40" s="9" t="n">
         <v>0.0005999999999999999</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>-0.0007</v>
+        <v>0.0002</v>
       </c>
       <c r="L40" s="9" t="n"/>
       <c r="M40" s="8" t="n">
@@ -3001,13 +3001,13 @@
         <v>0.0235</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>0.0386</v>
+        <v>0.0392</v>
       </c>
       <c r="J41" s="9" t="n">
         <v>0.0005999999999999999</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>-0.0007</v>
+        <v>0.0002</v>
       </c>
       <c r="L41" s="9" t="n"/>
       <c r="M41" s="8" t="n">
@@ -3026,7 +3026,7 @@
         <v/>
       </c>
       <c r="Q41" s="12" t="n">
-        <v>10.3075</v>
+        <v>10.2931</v>
       </c>
     </row>
     <row r="42">
@@ -3066,13 +3066,13 @@
         <v>0.0242</v>
       </c>
       <c r="I42" s="8" t="n">
-        <v>0.0381</v>
+        <v>0.0387</v>
       </c>
       <c r="J42" s="9" t="n">
         <v>0.0005999999999999999</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.0014</v>
+        <v>0.002</v>
       </c>
       <c r="L42" s="9" t="n"/>
       <c r="M42" s="8" t="n">
@@ -3091,7 +3091,7 @@
         <v/>
       </c>
       <c r="Q42" s="12" t="n">
-        <v>5.5709</v>
+        <v>5.5737</v>
       </c>
     </row>
     <row r="43">
@@ -3131,13 +3131,13 @@
         <v>0.0242</v>
       </c>
       <c r="I43" s="8" t="n">
-        <v>0.0381</v>
+        <v>0.0387</v>
       </c>
       <c r="J43" s="9" t="n">
         <v>0.0005999999999999999</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.0014</v>
+        <v>0.002</v>
       </c>
       <c r="L43" s="9" t="n"/>
       <c r="M43" s="8" t="n">
@@ -3156,7 +3156,7 @@
         <v/>
       </c>
       <c r="Q43" s="12" t="n">
-        <v>5.2102</v>
+        <v>5.2127</v>
       </c>
     </row>
     <row r="44">
@@ -3196,13 +3196,13 @@
         <v>0.0214</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>0.0375</v>
+        <v>0.0382</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0</v>
+        <v>0.0007</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.0001</v>
+        <v>0.0007</v>
       </c>
       <c r="L44" s="9" t="n"/>
       <c r="M44" s="8" t="n">
@@ -3261,13 +3261,13 @@
         <v>0.0207</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>0.0372</v>
+        <v>0.0378</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.0003</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.0003</v>
+        <v>0.0008</v>
       </c>
       <c r="L45" s="9" t="n"/>
       <c r="M45" s="8" t="n">
@@ -3286,7 +3286,7 @@
         <v/>
       </c>
       <c r="Q45" s="12" t="n">
-        <v>35.79</v>
+        <v>35.77</v>
       </c>
     </row>
     <row r="46">
@@ -3326,13 +3326,13 @@
         <v>0.0265</v>
       </c>
       <c r="I46" s="8" t="n">
-        <v>0.0311</v>
+        <v>0.0309</v>
       </c>
       <c r="J46" s="9" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="K46" s="9" t="n">
         <v>0.0003</v>
-      </c>
-      <c r="K46" s="9" t="n">
-        <v>0.0005999999999999999</v>
       </c>
       <c r="L46" s="9" t="n"/>
       <c r="M46" s="8" t="n">
@@ -3351,7 +3351,7 @@
         <v/>
       </c>
       <c r="Q46" s="12" t="n">
-        <v>10.3459</v>
+        <v>10.3491</v>
       </c>
     </row>
     <row r="47">
@@ -3391,13 +3391,13 @@
         <v>0.015</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0297</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.0003</v>
+        <v>-0.0003</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.0002</v>
+        <v>-0.0001</v>
       </c>
       <c r="L47" s="9" t="n"/>
       <c r="M47" s="8" t="n">
@@ -3416,7 +3416,7 @@
         <v/>
       </c>
       <c r="Q47" s="12" t="n">
-        <v>10.1835</v>
+        <v>10.1856</v>
       </c>
     </row>
     <row r="48">
@@ -3456,13 +3456,13 @@
         <v>0.0197</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>0.0348</v>
+        <v>0.0347</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.0013</v>
+        <v>-0.0001</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.0022</v>
+        <v>0.0021</v>
       </c>
       <c r="L48" s="9" t="n"/>
       <c r="M48" s="8" t="n">
@@ -3481,7 +3481,7 @@
         <v/>
       </c>
       <c r="Q48" s="12" t="n">
-        <v>5.7122</v>
+        <v>5.7128</v>
       </c>
     </row>
     <row r="49">
@@ -3521,13 +3521,13 @@
         <v>0.0197</v>
       </c>
       <c r="I49" s="8" t="n">
-        <v>0.0348</v>
+        <v>0.0347</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.0013</v>
+        <v>-0.0001</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.0022</v>
+        <v>0.0021</v>
       </c>
       <c r="L49" s="9" t="n"/>
       <c r="M49" s="8" t="n">
@@ -3546,33 +3546,33 @@
         <v/>
       </c>
       <c r="Q49" s="12" t="n">
-        <v>5.3396</v>
+        <v>5.3402</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2027 German Bund Government Bond UCITS ETF Dist</t>
+          <t>iShares iBonds Dec 2027 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>LU2780871823</t>
+          <t>IE000ZOI8OK5</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
@@ -3583,20 +3583,20 @@
         <v/>
       </c>
       <c r="H50" s="8" t="n">
-        <v>0.0105</v>
+        <v>0.0195</v>
       </c>
       <c r="I50" s="8" t="n">
-        <v>0.0286</v>
+        <v>0.034</v>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.0002</v>
+        <v>0.0004</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>-0.0007</v>
+        <v>0.0012</v>
       </c>
       <c r="L50" s="9" t="n"/>
       <c r="M50" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N50" s="10">
         <f>IF(D50="Govt",$B$1,$B$2)</f>
@@ -3611,33 +3611,33 @@
         <v/>
       </c>
       <c r="Q50" s="12" t="n">
-        <v>10.358</v>
+        <v>5.65</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2027 Term € Corp UCITS ETF</t>
+          <t>Amundi Fixed Maturity 2027 German Bund Government Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>IE000ZOI8OK5</t>
+          <t>LU2780871823</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F51" s="6" t="n">
@@ -3648,20 +3648,20 @@
         <v/>
       </c>
       <c r="H51" s="8" t="n">
-        <v>0.0195</v>
+        <v>0.0105</v>
       </c>
       <c r="I51" s="8" t="n">
-        <v>0.0336</v>
+        <v>0.0281</v>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0</v>
+        <v>-0.0005</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.0008</v>
+        <v>-0.0012</v>
       </c>
       <c r="L51" s="9" t="n"/>
       <c r="M51" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N51" s="10">
         <f>IF(D51="Govt",$B$1,$B$2)</f>
@@ -3676,57 +3676,57 @@
         <v/>
       </c>
       <c r="Q51" s="12" t="n">
-        <v>5.65</v>
+        <v>10.3607</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2026 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>LU2872291278</t>
+          <t>LU2673523218</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F52" s="6" t="n">
-        <v>46387</v>
+        <v>46660</v>
       </c>
       <c r="G52" s="7">
         <f>IF(F52="","",MAX(0,YEARFRAC(TODAY(),F52)))</f>
         <v/>
       </c>
       <c r="H52" s="8" t="n">
-        <v>0.0021</v>
+        <v>0.0188</v>
       </c>
       <c r="I52" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.03240000000000001</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.0017</v>
+        <v>0.0004</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.0016</v>
+        <v>0.0009</v>
       </c>
       <c r="L52" s="9" t="n"/>
       <c r="M52" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N52" s="10">
         <f>IF(D52="Govt",$B$1,$B$2)</f>
@@ -3741,7 +3741,7 @@
         <v/>
       </c>
       <c r="Q52" s="12" t="n">
-        <v>10.2687</v>
+        <v>25.98</v>
       </c>
     </row>
     <row r="53">
@@ -3752,12 +3752,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LU2673523218</t>
+          <t>LU2673522830</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F53" s="6" t="n">
@@ -3778,16 +3778,16 @@
         <v/>
       </c>
       <c r="H53" s="8" t="n">
-        <v>0.0187</v>
+        <v>0.0188</v>
       </c>
       <c r="I53" s="8" t="n">
-        <v>0.032</v>
+        <v>0.03240000000000001</v>
       </c>
       <c r="J53" s="9" t="n">
         <v>0.0004</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.0005</v>
+        <v>0.0009</v>
       </c>
       <c r="L53" s="9" t="n"/>
       <c r="M53" s="8" t="n">
@@ -3806,50 +3806,50 @@
         <v/>
       </c>
       <c r="Q53" s="12" t="n">
-        <v>25.98</v>
+        <v>9.32</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1C</t>
+          <t>iShares iBonds Dec 2026 Term € Italy Govt Bond UCITS ETF</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>LU2673522830</t>
+          <t>IE000LZ7BZW8</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F54" s="6" t="n">
-        <v>46660</v>
+        <v>46387</v>
       </c>
       <c r="G54" s="7">
         <f>IF(F54="","",MAX(0,YEARFRAC(TODAY(),F54)))</f>
         <v/>
       </c>
       <c r="H54" s="8" t="n">
-        <v>0.0187</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="I54" s="8" t="n">
-        <v>0.032</v>
+        <v>0.027</v>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.0004</v>
+        <v>0.0001</v>
       </c>
       <c r="K54" s="9" t="n">
         <v>0.0005</v>
@@ -3871,23 +3871,23 @@
         <v/>
       </c>
       <c r="Q54" s="12" t="n">
-        <v>9.32</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2026 Term € Italy Govt Bond UCITS ETF</t>
+          <t>Amundi Fixed Maturity 2026 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>IE000LZ7BZW8</t>
+          <t>LU2872291278</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -3897,7 +3897,7 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F55" s="6" t="n">
@@ -3908,20 +3908,20 @@
         <v/>
       </c>
       <c r="H55" s="8" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0021</v>
       </c>
       <c r="I55" s="8" t="n">
-        <v>0.0269</v>
+        <v>0.0266</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0</v>
+        <v>-0.0009</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.0002</v>
+        <v>0.0008</v>
       </c>
       <c r="L55" s="9" t="n"/>
       <c r="M55" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N55" s="10">
         <f>IF(D55="Govt",$B$1,$B$2)</f>
@@ -3936,7 +3936,7 @@
         <v/>
       </c>
       <c r="Q55" s="12" t="n">
-        <v>5.06</v>
+        <v>10.2696</v>
       </c>
     </row>
     <row r="56">
@@ -3976,13 +3976,13 @@
         <v>0.0109</v>
       </c>
       <c r="I56" s="8" t="n">
-        <v>0.0274</v>
+        <v>0.028</v>
       </c>
       <c r="J56" s="9" t="n">
-        <v>-0.0024</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>-0.0019</v>
+        <v>-0.0013</v>
       </c>
       <c r="L56" s="9" t="n"/>
       <c r="M56" s="8" t="n">
@@ -4001,7 +4001,7 @@
         <v/>
       </c>
       <c r="Q56" s="12" t="n">
-        <v>5.7986</v>
+        <v>5.7991</v>
       </c>
     </row>
     <row r="57">
@@ -4041,13 +4041,13 @@
         <v>0.0109</v>
       </c>
       <c r="I57" s="8" t="n">
-        <v>0.0274</v>
+        <v>0.028</v>
       </c>
       <c r="J57" s="9" t="n">
-        <v>-0.0024</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>-0.0019</v>
+        <v>-0.0013</v>
       </c>
       <c r="L57" s="9" t="n"/>
       <c r="M57" s="8" t="n">
@@ -4066,7 +4066,7 @@
         <v/>
       </c>
       <c r="Q57" s="12" t="n">
-        <v>5.4219</v>
+        <v>5.4224</v>
       </c>
     </row>
     <row r="58">
@@ -4106,13 +4106,13 @@
         <v>0.0044</v>
       </c>
       <c r="I58" s="8" t="n">
-        <v>0.0269</v>
+        <v>0.0274</v>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>-0.0008</v>
+        <v>-0.0001</v>
       </c>
       <c r="L58" s="9" t="n"/>
       <c r="M58" s="8" t="n">

--- a/data/rendimenti_etf.xlsx
+++ b/data/rendimenti_etf.xlsx
@@ -533,7 +533,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Aggiornato il 28/10/2026 09:03 da yield_etf.csv</t>
+          <t>Aggiornato il 29/10/2026 09:03 da yield_etf.csv</t>
         </is>
       </c>
     </row>
@@ -658,16 +658,16 @@
         <v/>
       </c>
       <c r="H5" s="8" t="n">
-        <v>0.0389</v>
+        <v>0.04</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>0.0533</v>
+        <v>0.0528</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.0005</v>
+        <v>-0.0005</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.0038</v>
+        <v>0.0033</v>
       </c>
       <c r="L5" s="9" t="n"/>
       <c r="M5" s="8" t="n">
@@ -686,7 +686,7 @@
         <v/>
       </c>
       <c r="Q5" s="12" t="n">
-        <v>4.86</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="6">
@@ -726,13 +726,13 @@
         <v>0.0377</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0.04679999999999999</v>
+        <v>0.0466</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.0003</v>
+        <v>-0.0002</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>-0.0002</v>
+        <v>-0.0004</v>
       </c>
       <c r="L6" s="9" t="n"/>
       <c r="M6" s="8" t="n">
@@ -751,7 +751,7 @@
         <v/>
       </c>
       <c r="Q6" s="12" t="n">
-        <v>28.24</v>
+        <v>28.29</v>
       </c>
     </row>
     <row r="7">
@@ -791,13 +791,13 @@
         <v>0.0368</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0.0464</v>
+        <v>0.0462</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.0003</v>
+        <v>-0.0002</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>-0.0002</v>
+        <v>-0.0004</v>
       </c>
       <c r="L7" s="9" t="n"/>
       <c r="M7" s="8" t="n">
@@ -816,7 +816,7 @@
         <v/>
       </c>
       <c r="Q7" s="12" t="n">
-        <v>29.06</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="8">
@@ -856,13 +856,13 @@
         <v>0.0356</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>0.0461</v>
+        <v>0.046</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.0003</v>
+        <v>-0.0001</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>-0.0005</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="L8" s="9" t="n"/>
       <c r="M8" s="8" t="n">
@@ -881,7 +881,7 @@
         <v/>
       </c>
       <c r="Q8" s="12" t="n">
-        <v>4.81</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="9">
@@ -921,13 +921,13 @@
         <v>0.0365</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>0.0459</v>
+        <v>0.0458</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.0004</v>
+        <v>-0.0001</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>-0.0005</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="L9" s="9" t="n"/>
       <c r="M9" s="8" t="n">
@@ -946,7 +946,7 @@
         <v/>
       </c>
       <c r="Q9" s="12" t="n">
-        <v>4.72</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="10">
@@ -986,13 +986,13 @@
         <v>0.0349</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>0.0457</v>
+        <v>0.04559999999999999</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.0004</v>
+        <v>-0.0001</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>-0.0007</v>
+        <v>-0.0008</v>
       </c>
       <c r="L10" s="9" t="n"/>
       <c r="M10" s="8" t="n">
@@ -1051,13 +1051,13 @@
         <v>0.0351</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>0.0457</v>
+        <v>0.0455</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.0004</v>
+        <v>-0.0002</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>-0.0002</v>
+        <v>-0.0004</v>
       </c>
       <c r="L11" s="9" t="n"/>
       <c r="M11" s="8" t="n">
@@ -1076,7 +1076,7 @@
         <v/>
       </c>
       <c r="Q11" s="12" t="n">
-        <v>33.45</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="12">
@@ -1116,13 +1116,13 @@
         <v>0.0329</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>0.0463</v>
+        <v>0.0461</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.0004</v>
+        <v>-0.0002</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.0031</v>
+        <v>0.0029</v>
       </c>
       <c r="L12" s="9" t="n"/>
       <c r="M12" s="8" t="n">
@@ -1147,17 +1147,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2033 EUR Corporate Bond UCITS ETF 1C</t>
+          <t>iShares iBonds Dec 2034 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LU2673523051</t>
+          <t>IE000SBJO6L2</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -1167,27 +1167,27 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>48852</v>
+        <v>49309</v>
       </c>
       <c r="G13" s="7">
         <f>IF(F13="","",MAX(0,YEARFRAC(TODAY(),F13)))</f>
         <v/>
       </c>
       <c r="H13" s="8" t="n">
-        <v>0.0338</v>
+        <v>0.0349</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0.0452</v>
+        <v>0.045</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.0004</v>
+        <v>-0.0001</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>-0.0002</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="L13" s="9" t="n"/>
       <c r="M13" s="8" t="n">
@@ -1206,7 +1206,7 @@
         <v/>
       </c>
       <c r="Q13" s="12" t="n">
-        <v>9.279999999999999</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="14">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2033 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>Xtrackers II Target Maturity Sept 2033 EUR Corporate Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LU2673523564</t>
+          <t>LU2673523051</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F14" s="6" t="n">
@@ -1246,13 +1246,13 @@
         <v>0.0338</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>0.0452</v>
+        <v>0.0449</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.0004</v>
+        <v>-0.0003</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>-0.0002</v>
+        <v>-0.0005</v>
       </c>
       <c r="L14" s="9" t="n"/>
       <c r="M14" s="8" t="n">
@@ -1271,23 +1271,23 @@
         <v/>
       </c>
       <c r="Q14" s="12" t="n">
-        <v>27.81</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2034 Term € Corp UCITS ETF</t>
+          <t>Xtrackers II Target Maturity Sept 2033 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>IE000SBJO6L2</t>
+          <t>LU2673523564</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -1301,20 +1301,20 @@
         </is>
       </c>
       <c r="F15" s="6" t="n">
-        <v>49309</v>
+        <v>48852</v>
       </c>
       <c r="G15" s="7">
         <f>IF(F15="","",MAX(0,YEARFRAC(TODAY(),F15)))</f>
         <v/>
       </c>
       <c r="H15" s="8" t="n">
-        <v>0.0348</v>
+        <v>0.0338</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>0.0451</v>
+        <v>0.0449</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.0004</v>
+        <v>-0.0003</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>-0.0005</v>
@@ -1336,7 +1336,7 @@
         <v/>
       </c>
       <c r="Q15" s="12" t="n">
-        <v>4.75</v>
+        <v>27.86</v>
       </c>
     </row>
     <row r="16">
@@ -1376,13 +1376,13 @@
         <v>0.0331</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>0.0446</v>
+        <v>0.0443</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.0005</v>
+        <v>-0.0003</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>-0.0005</v>
+        <v>-0.0008</v>
       </c>
       <c r="L16" s="9" t="n"/>
       <c r="M16" s="8" t="n">
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="Q16" s="12" t="n">
-        <v>4.76</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="17">
@@ -1441,13 +1441,13 @@
         <v>0.0282</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>0.0445</v>
+        <v>0.0441</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.0005</v>
+        <v>-0.0004</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.0001</v>
+        <v>-0.0003</v>
       </c>
       <c r="L17" s="9" t="n"/>
       <c r="M17" s="8" t="n">
@@ -1466,7 +1466,7 @@
         <v/>
       </c>
       <c r="Q17" s="12" t="n">
-        <v>34.18</v>
+        <v>34.24</v>
       </c>
     </row>
     <row r="18">
@@ -1506,13 +1506,13 @@
         <v>0.0301</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>0.0435</v>
+        <v>0.0432</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.0005</v>
+        <v>-0.0003</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>-0.0004</v>
+        <v>-0.0007</v>
       </c>
       <c r="L18" s="9" t="n"/>
       <c r="M18" s="8" t="n">
@@ -1537,51 +1537,51 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2030 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>iShares iBonds Dec 2031 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LU3120976132</t>
+          <t>IE000I2WYEU9</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>47848</v>
+        <v>48213</v>
       </c>
       <c r="G19" s="7">
         <f>IF(F19="","",MAX(0,YEARFRAC(TODAY(),F19)))</f>
         <v/>
       </c>
       <c r="H19" s="8" t="n">
-        <v>0.0169</v>
+        <v>0.0286</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>0.0364</v>
+        <v>0.04269999999999999</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>-0.0001</v>
+        <v>-0.0002</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.0015</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="L19" s="9" t="n"/>
       <c r="M19" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N19" s="10">
         <f>IF(D19="Govt",$B$1,$B$2)</f>
@@ -1596,23 +1596,23 @@
         <v/>
       </c>
       <c r="Q19" s="12" t="n">
-        <v>9.8497</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>BNP Paribas</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2031 Term € Corp UCITS ETF</t>
+          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2032 UCITS ETF C</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>IE000I2WYEU9</t>
+          <t>LU2823895847</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -1622,24 +1622,24 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>48213</v>
+        <v>48579</v>
       </c>
       <c r="G20" s="7">
         <f>IF(F20="","",MAX(0,YEARFRAC(TODAY(),F20)))</f>
         <v/>
       </c>
       <c r="H20" s="8" t="n">
-        <v>0.0285</v>
+        <v>0.0269</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>0.0429</v>
+        <v>0.0426</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.0005</v>
+        <v>-0.0001</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>-0.0004</v>
@@ -1661,7 +1661,7 @@
         <v/>
       </c>
       <c r="Q20" s="12" t="n">
-        <v>4.87</v>
+        <v>10.4159</v>
       </c>
     </row>
     <row r="21">
@@ -1672,12 +1672,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2032 UCITS ETF C</t>
+          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2032 UCITS ETF D</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>LU2823895847</t>
+          <t>LU2823895763</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F21" s="6" t="n">
@@ -1701,13 +1701,13 @@
         <v>0.0269</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>0.04269999999999999</v>
+        <v>0.0426</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.0004</v>
+        <v>-0.0001</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>-0.0003</v>
+        <v>-0.0004</v>
       </c>
       <c r="L21" s="9" t="n"/>
       <c r="M21" s="8" t="n">
@@ -1726,23 +1726,23 @@
         <v/>
       </c>
       <c r="Q21" s="12" t="n">
-        <v>10.4377</v>
+        <v>10.0305</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BNP Paribas</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2032 UCITS ETF D</t>
+          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>LU2823895763</t>
+          <t>LU2673523135</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1752,27 +1752,27 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>48579</v>
+        <v>48121</v>
       </c>
       <c r="G22" s="7">
         <f>IF(F22="","",MAX(0,YEARFRAC(TODAY(),F22)))</f>
         <v/>
       </c>
       <c r="H22" s="8" t="n">
-        <v>0.0269</v>
+        <v>0.0287</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>0.04269999999999999</v>
+        <v>0.0423</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.0004</v>
+        <v>-0.0003</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>-0.0003</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="L22" s="9" t="n"/>
       <c r="M22" s="8" t="n">
@@ -1791,7 +1791,7 @@
         <v/>
       </c>
       <c r="Q22" s="12" t="n">
-        <v>10.0515</v>
+        <v>9.789999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1C</t>
+          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>LU2673523135</t>
+          <t>LU2673523481</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F23" s="6" t="n">
@@ -1831,13 +1831,13 @@
         <v>0.0287</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>0.0426</v>
+        <v>0.0423</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.0003</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>-0.0003</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="L23" s="9" t="n"/>
       <c r="M23" s="8" t="n">
@@ -1856,23 +1856,23 @@
         <v/>
       </c>
       <c r="Q23" s="12" t="n">
-        <v>9.77</v>
+        <v>29.28</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>LU2673523481</t>
+          <t>IE000I25S1V5</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -1882,31 +1882,31 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>48121</v>
+        <v>47848</v>
       </c>
       <c r="G24" s="7">
         <f>IF(F24="","",MAX(0,YEARFRAC(TODAY(),F24)))</f>
         <v/>
       </c>
       <c r="H24" s="8" t="n">
-        <v>0.0287</v>
+        <v>0.0286</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>0.0426</v>
+        <v>0.0417</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0.0013</v>
       </c>
       <c r="L24" s="9" t="n"/>
       <c r="M24" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="N24" s="10">
         <f>IF(D24="Govt",$B$1,$B$2)</f>
@@ -1921,57 +1921,57 @@
         <v/>
       </c>
       <c r="Q24" s="12" t="n">
-        <v>29.25</v>
+        <v>5.3488</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2029 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>LU2872291781</t>
+          <t>IE000W6YTDH7</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F25" s="6" t="n">
-        <v>47483</v>
+        <v>47848</v>
       </c>
       <c r="G25" s="7">
         <f>IF(F25="","",MAX(0,YEARFRAC(TODAY(),F25)))</f>
         <v/>
       </c>
       <c r="H25" s="8" t="n">
-        <v>0.0208</v>
+        <v>0.0286</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>0.0356</v>
+        <v>0.0417</v>
       </c>
       <c r="J25" s="9" t="n">
         <v>0</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.0014</v>
+        <v>0.0013</v>
       </c>
       <c r="L25" s="9" t="n"/>
       <c r="M25" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="N25" s="10">
         <f>IF(D25="Govt",$B$1,$B$2)</f>
@@ -1986,23 +1986,23 @@
         <v/>
       </c>
       <c r="Q25" s="12" t="n">
-        <v>10.0024</v>
+        <v>4.9823</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>iShares iBonds Dec 2030 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>IE000I25S1V5</t>
+          <t>IE000LX17BP9</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F26" s="6" t="n">
@@ -2023,20 +2023,20 @@
         <v/>
       </c>
       <c r="H26" s="8" t="n">
-        <v>0.0286</v>
+        <v>0.0282</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>0.0417</v>
+        <v>0.0411</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.0003</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.0013</v>
+        <v>-0.0004</v>
       </c>
       <c r="L26" s="9" t="n"/>
       <c r="M26" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N26" s="10">
         <f>IF(D26="Govt",$B$1,$B$2)</f>
@@ -2051,23 +2051,23 @@
         <v/>
       </c>
       <c r="Q26" s="12" t="n">
-        <v>5.3515</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>Xtrackers II Target Maturity Sept 2030 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>IE000W6YTDH7</t>
+          <t>LU2809864296</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -2081,27 +2081,27 @@
         </is>
       </c>
       <c r="F27" s="6" t="n">
-        <v>47848</v>
+        <v>47756</v>
       </c>
       <c r="G27" s="7">
         <f>IF(F27="","",MAX(0,YEARFRAC(TODAY(),F27)))</f>
         <v/>
       </c>
       <c r="H27" s="8" t="n">
-        <v>0.0286</v>
+        <v>0.027</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>0.0417</v>
+        <v>0.04099999999999999</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.0003</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.0013</v>
+        <v>-0.0004</v>
       </c>
       <c r="L27" s="9" t="n"/>
       <c r="M27" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N27" s="10">
         <f>IF(D27="Govt",$B$1,$B$2)</f>
@@ -2116,53 +2116,53 @@
         <v/>
       </c>
       <c r="Q27" s="12" t="n">
-        <v>4.9848</v>
+        <v>35.24</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2030 Term € Corp UCITS ETF</t>
+          <t>Xtrackers II Target Maturity Sept 2029 Italy and Spain Government Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>IE000LX17BP9</t>
+          <t>LU0484969463</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F28" s="6" t="n">
-        <v>47848</v>
+        <v>47391</v>
       </c>
       <c r="G28" s="7">
         <f>IF(F28="","",MAX(0,YEARFRAC(TODAY(),F28)))</f>
         <v/>
       </c>
       <c r="H28" s="8" t="n">
-        <v>0.0281</v>
+        <v>0.0297</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>0.0414</v>
+        <v>0.0344</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.0007</v>
+        <v>-0.0004</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>-0.0001</v>
+        <v>-0.0012</v>
       </c>
       <c r="L28" s="9" t="n"/>
       <c r="M28" s="8" t="n">
@@ -2181,23 +2181,23 @@
         <v/>
       </c>
       <c r="Q28" s="12" t="n">
-        <v>4.98</v>
+        <v>205.05</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2030 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>LU2809864296</t>
+          <t>IE000P5IB8I8</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -2207,31 +2207,31 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F29" s="6" t="n">
-        <v>47756</v>
+        <v>47483</v>
       </c>
       <c r="G29" s="7">
         <f>IF(F29="","",MAX(0,YEARFRAC(TODAY(),F29)))</f>
         <v/>
       </c>
       <c r="H29" s="8" t="n">
-        <v>0.027</v>
+        <v>0.0242</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>0.0413</v>
+        <v>0.0399</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.0007</v>
+        <v>0</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0.0015</v>
       </c>
       <c r="L29" s="9" t="n"/>
       <c r="M29" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="N29" s="10">
         <f>IF(D29="Govt",$B$1,$B$2)</f>
@@ -2246,57 +2246,57 @@
         <v/>
       </c>
       <c r="Q29" s="12" t="n">
-        <v>35.2</v>
+        <v>5.4253</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2029 Italy and Spain Government Bond UCITS ETF 1C</t>
+          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>LU0484969463</t>
+          <t>IE000ZC4C5Q1</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F30" s="6" t="n">
-        <v>47391</v>
+        <v>47483</v>
       </c>
       <c r="G30" s="7">
         <f>IF(F30="","",MAX(0,YEARFRAC(TODAY(),F30)))</f>
         <v/>
       </c>
       <c r="H30" s="8" t="n">
-        <v>0.0297</v>
+        <v>0.0242</v>
       </c>
       <c r="I30" s="8" t="n">
-        <v>0.0348</v>
+        <v>0.0399</v>
       </c>
       <c r="J30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>-0.0008</v>
+        <v>0.0015</v>
       </c>
       <c r="L30" s="9" t="n"/>
       <c r="M30" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="N30" s="10">
         <f>IF(D30="Govt",$B$1,$B$2)</f>
@@ -2311,7 +2311,7 @@
         <v/>
       </c>
       <c r="Q30" s="12" t="n">
-        <v>204.93</v>
+        <v>5.0553</v>
       </c>
     </row>
     <row r="31">
@@ -2351,13 +2351,13 @@
         <v>0.0261</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>0.0342</v>
+        <v>0.034</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>-0.0001</v>
+        <v>-0.0002</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>-0.0008</v>
+        <v>-0.001</v>
       </c>
       <c r="L31" s="9" t="n"/>
       <c r="M31" s="8" t="n">
@@ -2376,23 +2376,23 @@
         <v/>
       </c>
       <c r="Q31" s="12" t="n">
-        <v>5.07</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>iShares iBonds Dec 2029 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>IE000P5IB8I8</t>
+          <t>IE000IHURBR0</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F32" s="6" t="n">
@@ -2413,20 +2413,20 @@
         <v/>
       </c>
       <c r="H32" s="8" t="n">
-        <v>0.0242</v>
+        <v>0.0253</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>0.0399</v>
+        <v>0.0395</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.0007</v>
+        <v>-0.0003</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.0015</v>
+        <v>-0.0003</v>
       </c>
       <c r="L32" s="9" t="n"/>
       <c r="M32" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N32" s="10">
         <f>IF(D32="Govt",$B$1,$B$2)</f>
@@ -2441,23 +2441,23 @@
         <v/>
       </c>
       <c r="Q32" s="12" t="n">
-        <v>5.4272</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>Xtrackers II Target Maturity Sept 2029 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>IE000ZC4C5Q1</t>
+          <t>LU2673523309</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -2471,27 +2471,27 @@
         </is>
       </c>
       <c r="F33" s="6" t="n">
-        <v>47483</v>
+        <v>47391</v>
       </c>
       <c r="G33" s="7">
         <f>IF(F33="","",MAX(0,YEARFRAC(TODAY(),F33)))</f>
         <v/>
       </c>
       <c r="H33" s="8" t="n">
-        <v>0.0242</v>
+        <v>0.0245</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>0.0399</v>
+        <v>0.0392</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.0007</v>
+        <v>-0.0003</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.0015</v>
+        <v>-0.0001</v>
       </c>
       <c r="L33" s="9" t="n"/>
       <c r="M33" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N33" s="10">
         <f>IF(D33="Govt",$B$1,$B$2)</f>
@@ -2506,23 +2506,23 @@
         <v/>
       </c>
       <c r="Q33" s="12" t="n">
-        <v>5.0572</v>
+        <v>25.79</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2029 Term € Corp UCITS ETF</t>
+          <t>Xtrackers II Target Maturity Sept 2029 EUR Corporate Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>IE000IHURBR0</t>
+          <t>LU2673522913</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -2532,27 +2532,27 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F34" s="6" t="n">
-        <v>47483</v>
+        <v>47391</v>
       </c>
       <c r="G34" s="7">
         <f>IF(F34="","",MAX(0,YEARFRAC(TODAY(),F34)))</f>
         <v/>
       </c>
       <c r="H34" s="8" t="n">
-        <v>0.0253</v>
+        <v>0.0245</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>0.0398</v>
+        <v>0.0392</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.0007</v>
+        <v>-0.0003</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0</v>
+        <v>-0.0001</v>
       </c>
       <c r="L34" s="9" t="n"/>
       <c r="M34" s="8" t="n">
@@ -2571,57 +2571,57 @@
         <v/>
       </c>
       <c r="Q34" s="12" t="n">
-        <v>5.03</v>
+        <v>9.17</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>BNP Paribas</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2028 Euro Government Bond Yield + UCITS ETF Dist</t>
+          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2029 UCITS ETF C</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>LU2780871666</t>
+          <t>LU2823896811</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F35" s="6" t="n">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="G35" s="7">
         <f>IF(F35="","",MAX(0,YEARFRAC(TODAY(),F35)))</f>
         <v/>
       </c>
       <c r="H35" s="8" t="n">
-        <v>0.0229</v>
+        <v>0.0235</v>
       </c>
       <c r="I35" s="8" t="n">
-        <v>0.0334</v>
+        <v>0.039</v>
       </c>
       <c r="J35" s="9" t="n">
         <v>-0.0002</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="L35" s="9" t="n"/>
       <c r="M35" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N35" s="10">
         <f>IF(D35="Govt",$B$1,$B$2)</f>
@@ -2636,23 +2636,23 @@
         <v/>
       </c>
       <c r="Q35" s="12" t="n">
-        <v>10.3051</v>
+        <v>10.6542</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>BNP Paribas</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2029 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2029 UCITS ETF D</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>LU2673523309</t>
+          <t>LU2823896738</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -2666,23 +2666,23 @@
         </is>
       </c>
       <c r="F36" s="6" t="n">
-        <v>47391</v>
+        <v>47483</v>
       </c>
       <c r="G36" s="7">
         <f>IF(F36="","",MAX(0,YEARFRAC(TODAY(),F36)))</f>
         <v/>
       </c>
       <c r="H36" s="8" t="n">
-        <v>0.0245</v>
+        <v>0.0235</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>0.0395</v>
+        <v>0.039</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.0007</v>
+        <v>-0.0002</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="L36" s="9" t="n"/>
       <c r="M36" s="8" t="n">
@@ -2701,23 +2701,23 @@
         <v/>
       </c>
       <c r="Q36" s="12" t="n">
-        <v>25.77</v>
+        <v>10.2931</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2029 EUR Corporate Bond UCITS ETF 1C</t>
+          <t>Invesco BulletShares 2028 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>LU2673522913</t>
+          <t>IE00079EUF59</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -2731,27 +2731,27 @@
         </is>
       </c>
       <c r="F37" s="6" t="n">
-        <v>47391</v>
+        <v>47118</v>
       </c>
       <c r="G37" s="7">
         <f>IF(F37="","",MAX(0,YEARFRAC(TODAY(),F37)))</f>
         <v/>
       </c>
       <c r="H37" s="8" t="n">
-        <v>0.0245</v>
+        <v>0.0242</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>0.0395</v>
+        <v>0.0387</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.0007</v>
+        <v>0</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.0002</v>
+        <v>0.002</v>
       </c>
       <c r="L37" s="9" t="n"/>
       <c r="M37" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="N37" s="10">
         <f>IF(D37="Govt",$B$1,$B$2)</f>
@@ -2766,28 +2766,28 @@
         <v/>
       </c>
       <c r="Q37" s="12" t="n">
-        <v>9.16</v>
+        <v>5.5724</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Dist</t>
+          <t>Invesco BulletShares 2028 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LU2780871401</t>
+          <t>IE000LKGEZQ6</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -2803,20 +2803,20 @@
         <v/>
       </c>
       <c r="H38" s="8" t="n">
-        <v>0.0184</v>
+        <v>0.0242</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>0.0331</v>
+        <v>0.0387</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.0003</v>
+        <v>0.002</v>
       </c>
       <c r="L38" s="9" t="n"/>
       <c r="M38" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="N38" s="10">
         <f>IF(D38="Govt",$B$1,$B$2)</f>
@@ -2831,33 +2831,33 @@
         <v/>
       </c>
       <c r="Q38" s="12" t="n">
-        <v>10.2911</v>
+        <v>5.2116</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>iShares iBonds Dec 2028 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>LU2780871310</t>
+          <t>IE000264WWY0</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F39" s="6" t="n">
@@ -2868,20 +2868,20 @@
         <v/>
       </c>
       <c r="H39" s="8" t="n">
-        <v>0.0184</v>
+        <v>0.0214</v>
       </c>
       <c r="I39" s="8" t="n">
-        <v>0.0331</v>
+        <v>0.0379</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>-0.0002</v>
+        <v>-0.0003</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.0003</v>
+        <v>0.0004</v>
       </c>
       <c r="L39" s="9" t="n"/>
       <c r="M39" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N39" s="10">
         <f>IF(D39="Govt",$B$1,$B$2)</f>
@@ -2896,23 +2896,23 @@
         <v/>
       </c>
       <c r="Q39" s="12" t="n">
-        <v>10.0902</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BNP Paribas</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2029 UCITS ETF C</t>
+          <t>Xtrackers II Target Maturity Sept 2028 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>LU2823896811</t>
+          <t>LU2810185665</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -2922,27 +2922,27 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F40" s="6" t="n">
-        <v>47483</v>
+        <v>47026</v>
       </c>
       <c r="G40" s="7">
         <f>IF(F40="","",MAX(0,YEARFRAC(TODAY(),F40)))</f>
         <v/>
       </c>
       <c r="H40" s="8" t="n">
-        <v>0.0235</v>
+        <v>0.0207</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>0.0392</v>
+        <v>0.03759999999999999</v>
       </c>
       <c r="J40" s="9" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="K40" s="9" t="n">
         <v>0.0005999999999999999</v>
-      </c>
-      <c r="K40" s="9" t="n">
-        <v>0.0002</v>
       </c>
       <c r="L40" s="9" t="n"/>
       <c r="M40" s="8" t="n">
@@ -2961,23 +2961,23 @@
         <v/>
       </c>
       <c r="Q40" s="12" t="n">
-        <v>10.6691</v>
+        <v>35.79</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BNP Paribas</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2029 UCITS ETF D</t>
+          <t>Invesco BulletShares 2027 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>LU2823896738</t>
+          <t>IE000LGHLQ71</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -2987,31 +2987,31 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F41" s="6" t="n">
-        <v>47483</v>
+        <v>46752</v>
       </c>
       <c r="G41" s="7">
         <f>IF(F41="","",MAX(0,YEARFRAC(TODAY(),F41)))</f>
         <v/>
       </c>
       <c r="H41" s="8" t="n">
-        <v>0.0235</v>
+        <v>0.0197</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>0.0392</v>
+        <v>0.0347</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.0002</v>
+        <v>0.0021</v>
       </c>
       <c r="L41" s="9" t="n"/>
       <c r="M41" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="N41" s="10">
         <f>IF(D41="Govt",$B$1,$B$2)</f>
@@ -3026,7 +3026,7 @@
         <v/>
       </c>
       <c r="Q41" s="12" t="n">
-        <v>10.2931</v>
+        <v>5.7135</v>
       </c>
     </row>
     <row r="42">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2028 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>Invesco BulletShares 2027 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>IE00079EUF59</t>
+          <t>IE000XOS4OJ6</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -3052,27 +3052,27 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
-        <v>47118</v>
+        <v>46752</v>
       </c>
       <c r="G42" s="7">
         <f>IF(F42="","",MAX(0,YEARFRAC(TODAY(),F42)))</f>
         <v/>
       </c>
       <c r="H42" s="8" t="n">
-        <v>0.0242</v>
+        <v>0.0197</v>
       </c>
       <c r="I42" s="8" t="n">
-        <v>0.0387</v>
+        <v>0.0347</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.002</v>
+        <v>0.0021</v>
       </c>
       <c r="L42" s="9" t="n"/>
       <c r="M42" s="8" t="n">
@@ -3091,23 +3091,23 @@
         <v/>
       </c>
       <c r="Q42" s="12" t="n">
-        <v>5.5737</v>
+        <v>5.3408</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2028 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>iShares iBonds Dec 2027 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>IE000LKGEZQ6</t>
+          <t>IE000ZOI8OK5</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -3117,31 +3117,31 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
-        <v>47118</v>
+        <v>46752</v>
       </c>
       <c r="G43" s="7">
         <f>IF(F43="","",MAX(0,YEARFRAC(TODAY(),F43)))</f>
         <v/>
       </c>
       <c r="H43" s="8" t="n">
-        <v>0.0242</v>
+        <v>0.0195</v>
       </c>
       <c r="I43" s="8" t="n">
-        <v>0.0387</v>
+        <v>0.0339</v>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.0001</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.002</v>
+        <v>0.0011</v>
       </c>
       <c r="L43" s="9" t="n"/>
       <c r="M43" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N43" s="10">
         <f>IF(D43="Govt",$B$1,$B$2)</f>
@@ -3156,23 +3156,23 @@
         <v/>
       </c>
       <c r="Q43" s="12" t="n">
-        <v>5.2127</v>
+        <v>5.65</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2028 Term € Corp UCITS ETF</t>
+          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>IE000264WWY0</t>
+          <t>LU2673523218</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -3186,23 +3186,23 @@
         </is>
       </c>
       <c r="F44" s="6" t="n">
-        <v>47118</v>
+        <v>46660</v>
       </c>
       <c r="G44" s="7">
         <f>IF(F44="","",MAX(0,YEARFRAC(TODAY(),F44)))</f>
         <v/>
       </c>
       <c r="H44" s="8" t="n">
-        <v>0.0214</v>
+        <v>0.019</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>0.0382</v>
+        <v>0.0325</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.0007</v>
+        <v>0.0001</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.0007</v>
+        <v>0.001</v>
       </c>
       <c r="L44" s="9" t="n"/>
       <c r="M44" s="8" t="n">
@@ -3221,7 +3221,7 @@
         <v/>
       </c>
       <c r="Q44" s="12" t="n">
-        <v>5.1</v>
+        <v>25.99</v>
       </c>
     </row>
     <row r="45">
@@ -3232,12 +3232,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2028 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>LU2810185665</t>
+          <t>LU2673522830</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -3247,27 +3247,27 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F45" s="6" t="n">
-        <v>47026</v>
+        <v>46660</v>
       </c>
       <c r="G45" s="7">
         <f>IF(F45="","",MAX(0,YEARFRAC(TODAY(),F45)))</f>
         <v/>
       </c>
       <c r="H45" s="8" t="n">
-        <v>0.0207</v>
+        <v>0.019</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>0.0378</v>
+        <v>0.0325</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0001</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.0008</v>
+        <v>0.001</v>
       </c>
       <c r="L45" s="9" t="n"/>
       <c r="M45" s="8" t="n">
@@ -3286,23 +3286,23 @@
         <v/>
       </c>
       <c r="Q45" s="12" t="n">
-        <v>35.77</v>
+        <v>9.32</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2027 Italy BTP Government Bond UCITS ETF Dist</t>
+          <t>iShares iBonds Dec 2026 Term € Italy Govt Bond UCITS ETF</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>LU2780872128</t>
+          <t>IE000LZ7BZW8</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -3316,27 +3316,27 @@
         </is>
       </c>
       <c r="F46" s="6" t="n">
-        <v>46752</v>
+        <v>46387</v>
       </c>
       <c r="G46" s="7">
         <f>IF(F46="","",MAX(0,YEARFRAC(TODAY(),F46)))</f>
         <v/>
       </c>
       <c r="H46" s="8" t="n">
-        <v>0.0265</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="I46" s="8" t="n">
-        <v>0.0309</v>
+        <v>0.027</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.0003</v>
+        <v>0.0005</v>
       </c>
       <c r="L46" s="9" t="n"/>
       <c r="M46" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N46" s="10">
         <f>IF(D46="Govt",$B$1,$B$2)</f>
@@ -3351,28 +3351,28 @@
         <v/>
       </c>
       <c r="Q46" s="12" t="n">
-        <v>10.3491</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2027 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>Invesco BulletShares 2026 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>LU2872291435</t>
+          <t>IE0004QWOTD5</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -3381,27 +3381,27 @@
         </is>
       </c>
       <c r="F47" s="6" t="n">
-        <v>46752</v>
+        <v>46387</v>
       </c>
       <c r="G47" s="7">
         <f>IF(F47="","",MAX(0,YEARFRAC(TODAY(),F47)))</f>
         <v/>
       </c>
       <c r="H47" s="8" t="n">
-        <v>0.015</v>
+        <v>0.0109</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>0.0297</v>
+        <v>0.028</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>-0.0001</v>
+        <v>-0.0013</v>
       </c>
       <c r="L47" s="9" t="n"/>
       <c r="M47" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="N47" s="10">
         <f>IF(D47="Govt",$B$1,$B$2)</f>
@@ -3416,7 +3416,7 @@
         <v/>
       </c>
       <c r="Q47" s="12" t="n">
-        <v>10.1856</v>
+        <v>5.7996</v>
       </c>
     </row>
     <row r="48">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2027 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>Invesco BulletShares 2026 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>IE000LGHLQ71</t>
+          <t>IE000AYJ75E5</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -3442,27 +3442,27 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
-        <v>46752</v>
+        <v>46387</v>
       </c>
       <c r="G48" s="7">
         <f>IF(F48="","",MAX(0,YEARFRAC(TODAY(),F48)))</f>
         <v/>
       </c>
       <c r="H48" s="8" t="n">
-        <v>0.0197</v>
+        <v>0.0109</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>0.0347</v>
+        <v>0.028</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.0021</v>
+        <v>-0.0013</v>
       </c>
       <c r="L48" s="9" t="n"/>
       <c r="M48" s="8" t="n">
@@ -3481,23 +3481,23 @@
         <v/>
       </c>
       <c r="Q48" s="12" t="n">
-        <v>5.7128</v>
+        <v>5.4229</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2027 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>iShares iBonds Dec 2026 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>IE000XOS4OJ6</t>
+          <t>IE000SIZJ2B2</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -3511,27 +3511,27 @@
         </is>
       </c>
       <c r="F49" s="6" t="n">
-        <v>46752</v>
+        <v>46387</v>
       </c>
       <c r="G49" s="7">
         <f>IF(F49="","",MAX(0,YEARFRAC(TODAY(),F49)))</f>
         <v/>
       </c>
       <c r="H49" s="8" t="n">
-        <v>0.0197</v>
+        <v>0.004699999999999999</v>
       </c>
       <c r="I49" s="8" t="n">
-        <v>0.0347</v>
+        <v>0.0276</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.0021</v>
+        <v>0.0001</v>
       </c>
       <c r="L49" s="9" t="n"/>
       <c r="M49" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N49" s="10">
         <f>IF(D49="Govt",$B$1,$B$2)</f>
@@ -3546,33 +3546,33 @@
         <v/>
       </c>
       <c r="Q49" s="12" t="n">
-        <v>5.3402</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2027 Term € Corp UCITS ETF</t>
+          <t>Amundi Fixed Maturity 2027 Italy BTP Government Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>IE000ZOI8OK5</t>
+          <t>LU2780872128</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
@@ -3583,20 +3583,20 @@
         <v/>
       </c>
       <c r="H50" s="8" t="n">
-        <v>0.0195</v>
+        <v>0.0265</v>
       </c>
       <c r="I50" s="8" t="n">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.0004</v>
+        <v>-0.0309</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.0012</v>
+        <v>-0.0312</v>
       </c>
       <c r="L50" s="9" t="n"/>
       <c r="M50" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N50" s="10">
         <f>IF(D50="Govt",$B$1,$B$2)</f>
@@ -3611,7 +3611,7 @@
         <v/>
       </c>
       <c r="Q50" s="12" t="n">
-        <v>5.65</v>
+        <v>10.3477</v>
       </c>
     </row>
     <row r="51">
@@ -3651,13 +3651,13 @@
         <v>0.0105</v>
       </c>
       <c r="I51" s="8" t="n">
-        <v>0.0281</v>
+        <v>0</v>
       </c>
       <c r="J51" s="9" t="n">
-        <v>-0.0005</v>
+        <v>-0.0281</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>-0.0012</v>
+        <v>-0.0299</v>
       </c>
       <c r="L51" s="9" t="n"/>
       <c r="M51" s="8" t="n">
@@ -3676,57 +3676,57 @@
         <v/>
       </c>
       <c r="Q51" s="12" t="n">
-        <v>10.3607</v>
+        <v>10.3599</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>Amundi Fixed Maturity 2026 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>LU2673523218</t>
+          <t>LU2872291278</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F52" s="6" t="n">
-        <v>46660</v>
+        <v>46387</v>
       </c>
       <c r="G52" s="7">
         <f>IF(F52="","",MAX(0,YEARFRAC(TODAY(),F52)))</f>
         <v/>
       </c>
       <c r="H52" s="8" t="n">
-        <v>0.0188</v>
+        <v>0.0021</v>
       </c>
       <c r="I52" s="8" t="n">
-        <v>0.03240000000000001</v>
+        <v>0</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.0004</v>
+        <v>-0.0266</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.0009</v>
+        <v>-0.0274</v>
       </c>
       <c r="L52" s="9" t="n"/>
       <c r="M52" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N52" s="10">
         <f>IF(D52="Govt",$B$1,$B$2)</f>
@@ -3741,28 +3741,28 @@
         <v/>
       </c>
       <c r="Q52" s="12" t="n">
-        <v>25.98</v>
+        <v>10.2701</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1C</t>
+          <t>Amundi Fixed Maturity 2027 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LU2673522830</t>
+          <t>LU2872291435</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -3771,27 +3771,27 @@
         </is>
       </c>
       <c r="F53" s="6" t="n">
-        <v>46660</v>
+        <v>46752</v>
       </c>
       <c r="G53" s="7">
         <f>IF(F53="","",MAX(0,YEARFRAC(TODAY(),F53)))</f>
         <v/>
       </c>
       <c r="H53" s="8" t="n">
-        <v>0.0188</v>
+        <v>0.015</v>
       </c>
       <c r="I53" s="8" t="n">
-        <v>0.03240000000000001</v>
+        <v>0</v>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.0004</v>
+        <v>-0.0297</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.0009</v>
+        <v>-0.0305</v>
       </c>
       <c r="L53" s="9" t="n"/>
       <c r="M53" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N53" s="10">
         <f>IF(D53="Govt",$B$1,$B$2)</f>
@@ -3806,23 +3806,23 @@
         <v/>
       </c>
       <c r="Q53" s="12" t="n">
-        <v>9.32</v>
+        <v>10.1853</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2026 Term € Italy Govt Bond UCITS ETF</t>
+          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>IE000LZ7BZW8</t>
+          <t>LU2780871401</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -3836,27 +3836,27 @@
         </is>
       </c>
       <c r="F54" s="6" t="n">
-        <v>46387</v>
+        <v>47118</v>
       </c>
       <c r="G54" s="7">
         <f>IF(F54="","",MAX(0,YEARFRAC(TODAY(),F54)))</f>
         <v/>
       </c>
       <c r="H54" s="8" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0184</v>
       </c>
       <c r="I54" s="8" t="n">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.0001</v>
+        <v>-0.0331</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.0005</v>
+        <v>-0.0339</v>
       </c>
       <c r="L54" s="9" t="n"/>
       <c r="M54" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N54" s="10">
         <f>IF(D54="Govt",$B$1,$B$2)</f>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="Q54" s="12" t="n">
-        <v>5.06</v>
+        <v>10.2851</v>
       </c>
     </row>
     <row r="55">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2026 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>LU2872291278</t>
+          <t>LU2780871310</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -3901,23 +3901,23 @@
         </is>
       </c>
       <c r="F55" s="6" t="n">
-        <v>46387</v>
+        <v>47118</v>
       </c>
       <c r="G55" s="7">
         <f>IF(F55="","",MAX(0,YEARFRAC(TODAY(),F55)))</f>
         <v/>
       </c>
       <c r="H55" s="8" t="n">
-        <v>0.0021</v>
+        <v>0.0184</v>
       </c>
       <c r="I55" s="8" t="n">
-        <v>0.0266</v>
+        <v>0</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>-0.0009</v>
+        <v>-0.0331</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.0008</v>
+        <v>-0.0339</v>
       </c>
       <c r="L55" s="9" t="n"/>
       <c r="M55" s="8" t="n">
@@ -3936,28 +3936,28 @@
         <v/>
       </c>
       <c r="Q55" s="12" t="n">
-        <v>10.2696</v>
+        <v>10.0843</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2026 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>Amundi Fixed Maturity 2029 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>IE0004QWOTD5</t>
+          <t>LU2872291781</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -3966,27 +3966,27 @@
         </is>
       </c>
       <c r="F56" s="6" t="n">
-        <v>46387</v>
+        <v>47483</v>
       </c>
       <c r="G56" s="7">
         <f>IF(F56="","",MAX(0,YEARFRAC(TODAY(),F56)))</f>
         <v/>
       </c>
       <c r="H56" s="8" t="n">
-        <v>0.0109</v>
+        <v>0.0208</v>
       </c>
       <c r="I56" s="8" t="n">
-        <v>0.028</v>
+        <v>0</v>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.0356</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>-0.0013</v>
+        <v>-0.0355</v>
       </c>
       <c r="L56" s="9" t="n"/>
       <c r="M56" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0009</v>
       </c>
       <c r="N56" s="10">
         <f>IF(D56="Govt",$B$1,$B$2)</f>
@@ -4001,28 +4001,28 @@
         <v/>
       </c>
       <c r="Q56" s="12" t="n">
-        <v>5.7991</v>
+        <v>9.992699999999999</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2026 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>Amundi Fixed Maturity 2028 Euro Government Bond Yield + UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>IE000AYJ75E5</t>
+          <t>LU2780871666</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -4031,27 +4031,27 @@
         </is>
       </c>
       <c r="F57" s="6" t="n">
-        <v>46387</v>
+        <v>47118</v>
       </c>
       <c r="G57" s="7">
         <f>IF(F57="","",MAX(0,YEARFRAC(TODAY(),F57)))</f>
         <v/>
       </c>
       <c r="H57" s="8" t="n">
-        <v>0.0109</v>
+        <v>0.0229</v>
       </c>
       <c r="I57" s="8" t="n">
-        <v>0.028</v>
+        <v>0</v>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.0334</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>-0.0013</v>
+        <v>-0.0343</v>
       </c>
       <c r="L57" s="9" t="n"/>
       <c r="M57" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0009</v>
       </c>
       <c r="N57" s="10">
         <f>IF(D57="Govt",$B$1,$B$2)</f>
@@ -4066,57 +4066,57 @@
         <v/>
       </c>
       <c r="Q57" s="12" t="n">
-        <v>5.4224</v>
+        <v>10.2975</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2026 Term € Corp UCITS ETF</t>
+          <t>Amundi Fixed Maturity 2030 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>IE000SIZJ2B2</t>
+          <t>LU3120976132</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F58" s="6" t="n">
-        <v>46387</v>
+        <v>47848</v>
       </c>
       <c r="G58" s="7">
         <f>IF(F58="","",MAX(0,YEARFRAC(TODAY(),F58)))</f>
         <v/>
       </c>
       <c r="H58" s="8" t="n">
-        <v>0.0044</v>
+        <v>0.0169</v>
       </c>
       <c r="I58" s="8" t="n">
-        <v>0.0274</v>
+        <v>0</v>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.0005</v>
+        <v>-0.0364</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>-0.0001</v>
+        <v>-0.0362</v>
       </c>
       <c r="L58" s="9" t="n"/>
       <c r="M58" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N58" s="10">
         <f>IF(D58="Govt",$B$1,$B$2)</f>
@@ -4131,7 +4131,7 @@
         <v/>
       </c>
       <c r="Q58" s="12" t="n">
-        <v>5.06</v>
+        <v>9.837899999999999</v>
       </c>
     </row>
   </sheetData>

--- a/data/rendimenti_etf.xlsx
+++ b/data/rendimenti_etf.xlsx
@@ -533,7 +533,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Aggiornato il 29/10/2026 09:03 da yield_etf.csv</t>
+          <t>Aggiornato il 30/10/2026 09:16 da yield_etf.csv</t>
         </is>
       </c>
     </row>
@@ -658,16 +658,16 @@
         <v/>
       </c>
       <c r="H5" s="8" t="n">
-        <v>0.04</v>
+        <v>0.0389</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>0.0528</v>
+        <v>0.0521</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>-0.0005</v>
+        <v>-0.0007</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.0033</v>
+        <v>0.0018</v>
       </c>
       <c r="L5" s="9" t="n"/>
       <c r="M5" s="8" t="n">
@@ -726,13 +726,13 @@
         <v>0.0377</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0.0466</v>
+        <v>0.0464</v>
       </c>
       <c r="J6" s="9" t="n">
         <v>-0.0002</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>-0.0004</v>
+        <v>0.0035</v>
       </c>
       <c r="L6" s="9" t="n"/>
       <c r="M6" s="8" t="n">
@@ -751,7 +751,7 @@
         <v/>
       </c>
       <c r="Q6" s="12" t="n">
-        <v>28.29</v>
+        <v>28.32</v>
       </c>
     </row>
     <row r="7">
@@ -791,13 +791,13 @@
         <v>0.0368</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0.0462</v>
+        <v>0.0461</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>-0.0002</v>
+        <v>-0.0001</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>-0.0004</v>
+        <v>0.0007</v>
       </c>
       <c r="L7" s="9" t="n"/>
       <c r="M7" s="8" t="n">
@@ -816,7 +816,7 @@
         <v/>
       </c>
       <c r="Q7" s="12" t="n">
-        <v>29.1</v>
+        <v>29.12</v>
       </c>
     </row>
     <row r="8">
@@ -856,13 +856,13 @@
         <v>0.0356</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>0.046</v>
+        <v>0.0459</v>
       </c>
       <c r="J8" s="9" t="n">
         <v>-0.0001</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0011</v>
       </c>
       <c r="L8" s="9" t="n"/>
       <c r="M8" s="8" t="n">
@@ -881,7 +881,7 @@
         <v/>
       </c>
       <c r="Q8" s="12" t="n">
-        <v>4.82</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="9">
@@ -921,13 +921,13 @@
         <v>0.0365</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>0.0458</v>
+        <v>0.04559999999999999</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>-0.0001</v>
+        <v>-0.0002</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0012</v>
       </c>
       <c r="L9" s="9" t="n"/>
       <c r="M9" s="8" t="n">
@@ -946,7 +946,7 @@
         <v/>
       </c>
       <c r="Q9" s="12" t="n">
-        <v>4.73</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="10">
@@ -989,10 +989,10 @@
         <v>0.04559999999999999</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>-0.0008</v>
+        <v>-0.0012</v>
       </c>
       <c r="L10" s="9" t="n"/>
       <c r="M10" s="8" t="n">
@@ -1011,7 +1011,7 @@
         <v/>
       </c>
       <c r="Q10" s="12" t="n">
-        <v>4.82</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="11">
@@ -1051,13 +1051,13 @@
         <v>0.0351</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>0.0455</v>
+        <v>0.0454</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>-0.0002</v>
+        <v>-0.0001</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>-0.0004</v>
+        <v>0.0012</v>
       </c>
       <c r="L11" s="9" t="n"/>
       <c r="M11" s="8" t="n">
@@ -1076,7 +1076,7 @@
         <v/>
       </c>
       <c r="Q11" s="12" t="n">
-        <v>33.5</v>
+        <v>33.51</v>
       </c>
     </row>
     <row r="12">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2028 Term € Corp Crossover UCITS ETF</t>
+          <t>iShares iBonds Dec 2034 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>IE0003HV7CS6</t>
+          <t>IE000SBJO6L2</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -1102,31 +1102,31 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>47118</v>
+        <v>49309</v>
       </c>
       <c r="G12" s="7">
         <f>IF(F12="","",MAX(0,YEARFRAC(TODAY(),F12)))</f>
         <v/>
       </c>
       <c r="H12" s="8" t="n">
-        <v>0.0329</v>
+        <v>0.0349</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>0.0461</v>
+        <v>0.0451</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.0029</v>
+        <v>-0.0009</v>
       </c>
       <c r="L12" s="9" t="n"/>
       <c r="M12" s="8" t="n">
-        <v>0.002</v>
+        <v>0.0012</v>
       </c>
       <c r="N12" s="10">
         <f>IF(D12="Govt",$B$1,$B$2)</f>
@@ -1141,7 +1141,7 @@
         <v/>
       </c>
       <c r="Q12" s="12" t="n">
-        <v>5.09</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="13">
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2034 Term € Corp UCITS ETF</t>
+          <t>iShares iBonds Dec 2028 Term € Corp Crossover UCITS ETF</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>IE000SBJO6L2</t>
+          <t>IE0003HV7CS6</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -1167,31 +1167,31 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>49309</v>
+        <v>47118</v>
       </c>
       <c r="G13" s="7">
         <f>IF(F13="","",MAX(0,YEARFRAC(TODAY(),F13)))</f>
         <v/>
       </c>
       <c r="H13" s="8" t="n">
-        <v>0.0349</v>
+        <v>0.0329</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0.045</v>
+        <v>0.0457</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>-0.0001</v>
+        <v>-0.0004</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0015</v>
       </c>
       <c r="L13" s="9" t="n"/>
       <c r="M13" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.002</v>
       </c>
       <c r="N13" s="10">
         <f>IF(D13="Govt",$B$1,$B$2)</f>
@@ -1206,7 +1206,7 @@
         <v/>
       </c>
       <c r="Q13" s="12" t="n">
-        <v>4.75</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="14">
@@ -1249,10 +1249,10 @@
         <v>0.0449</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>-0.0005</v>
+        <v>0.0036</v>
       </c>
       <c r="L14" s="9" t="n"/>
       <c r="M14" s="8" t="n">
@@ -1314,10 +1314,10 @@
         <v>0.0449</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>-0.0005</v>
+        <v>0.0036</v>
       </c>
       <c r="L15" s="9" t="n"/>
       <c r="M15" s="8" t="n">
@@ -1376,13 +1376,13 @@
         <v>0.0331</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>0.0443</v>
+        <v>0.0444</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0.0001</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>-0.0008</v>
+        <v>-0.001</v>
       </c>
       <c r="L16" s="9" t="n"/>
       <c r="M16" s="8" t="n">
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="Q16" s="12" t="n">
-        <v>4.77</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="17">
@@ -1438,16 +1438,16 @@
         <v/>
       </c>
       <c r="H17" s="8" t="n">
-        <v>0.0282</v>
+        <v>0.0287</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>0.0441</v>
+        <v>0.044</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>-0.0004</v>
+        <v>-0.0001</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0.0007</v>
       </c>
       <c r="L17" s="9" t="n"/>
       <c r="M17" s="8" t="n">
@@ -1506,13 +1506,13 @@
         <v>0.0301</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>0.0432</v>
+        <v>0.0433</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0.0001</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>-0.0007</v>
+        <v>-0.001</v>
       </c>
       <c r="L18" s="9" t="n"/>
       <c r="M18" s="8" t="n">
@@ -1531,57 +1531,57 @@
         <v/>
       </c>
       <c r="Q18" s="12" t="n">
-        <v>4.82</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2031 Term € Corp UCITS ETF</t>
+          <t>Amundi Fixed Maturity 2030 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>IE000I2WYEU9</t>
+          <t>LU3120976132</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>48213</v>
+        <v>47848</v>
       </c>
       <c r="G19" s="7">
         <f>IF(F19="","",MAX(0,YEARFRAC(TODAY(),F19)))</f>
         <v/>
       </c>
       <c r="H19" s="8" t="n">
-        <v>0.0286</v>
+        <v>0.0169</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>0.04269999999999999</v>
+        <v>0.0361</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0361</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0005</v>
       </c>
       <c r="L19" s="9" t="n"/>
       <c r="M19" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N19" s="10">
         <f>IF(D19="Govt",$B$1,$B$2)</f>
@@ -1596,23 +1596,23 @@
         <v/>
       </c>
       <c r="Q19" s="12" t="n">
-        <v>4.87</v>
+        <v>9.8635</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BNP Paribas</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2032 UCITS ETF C</t>
+          <t>iShares iBonds Dec 2031 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LU2823895847</t>
+          <t>IE000I2WYEU9</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -1622,27 +1622,27 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>48579</v>
+        <v>48213</v>
       </c>
       <c r="G20" s="7">
         <f>IF(F20="","",MAX(0,YEARFRAC(TODAY(),F20)))</f>
         <v/>
       </c>
       <c r="H20" s="8" t="n">
-        <v>0.0269</v>
+        <v>0.0286</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>0.0426</v>
+        <v>0.0428</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0.0001</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>-0.0004</v>
+        <v>-0.0009</v>
       </c>
       <c r="L20" s="9" t="n"/>
       <c r="M20" s="8" t="n">
@@ -1661,23 +1661,23 @@
         <v/>
       </c>
       <c r="Q20" s="12" t="n">
-        <v>10.4159</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BNP Paribas</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2032 UCITS ETF D</t>
+          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>LU2823895763</t>
+          <t>LU2673523135</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -1687,27 +1687,27 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F21" s="6" t="n">
-        <v>48579</v>
+        <v>48121</v>
       </c>
       <c r="G21" s="7">
         <f>IF(F21="","",MAX(0,YEARFRAC(TODAY(),F21)))</f>
         <v/>
       </c>
       <c r="H21" s="8" t="n">
-        <v>0.0269</v>
+        <v>0.0287</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>0.0426</v>
+        <v>0.0425</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>-0.0004</v>
+        <v>0.0001</v>
       </c>
       <c r="L21" s="9" t="n"/>
       <c r="M21" s="8" t="n">
@@ -1726,7 +1726,7 @@
         <v/>
       </c>
       <c r="Q21" s="12" t="n">
-        <v>10.0305</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -1737,12 +1737,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1C</t>
+          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>LU2673523135</t>
+          <t>LU2673523481</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
@@ -1766,13 +1766,13 @@
         <v>0.0287</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>0.0423</v>
+        <v>0.0425</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0.0002</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0001</v>
       </c>
       <c r="L22" s="9" t="n"/>
       <c r="M22" s="8" t="n">
@@ -1791,23 +1791,23 @@
         <v/>
       </c>
       <c r="Q22" s="12" t="n">
-        <v>9.789999999999999</v>
+        <v>29.27</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>BNP Paribas</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2031 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2032 UCITS ETF C</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>LU2673523481</t>
+          <t>LU2823895847</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -1817,27 +1817,27 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>48121</v>
+        <v>48579</v>
       </c>
       <c r="G23" s="7">
         <f>IF(F23="","",MAX(0,YEARFRAC(TODAY(),F23)))</f>
         <v/>
       </c>
       <c r="H23" s="8" t="n">
-        <v>0.0287</v>
+        <v>0.0269</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>0.0423</v>
+        <v>0.0424</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>-0.0003</v>
+        <v>-0.0002</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0011</v>
       </c>
       <c r="L23" s="9" t="n"/>
       <c r="M23" s="8" t="n">
@@ -1856,23 +1856,23 @@
         <v/>
       </c>
       <c r="Q23" s="12" t="n">
-        <v>29.28</v>
+        <v>10.4247</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>BNP Paribas</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2032 UCITS ETF D</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>IE000I25S1V5</t>
+          <t>LU2823895763</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -1882,31 +1882,31 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>47848</v>
+        <v>48579</v>
       </c>
       <c r="G24" s="7">
         <f>IF(F24="","",MAX(0,YEARFRAC(TODAY(),F24)))</f>
         <v/>
       </c>
       <c r="H24" s="8" t="n">
-        <v>0.0286</v>
+        <v>0.0269</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>0.0417</v>
+        <v>0.0424</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0</v>
+        <v>-0.0002</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.0013</v>
+        <v>-0.0011</v>
       </c>
       <c r="L24" s="9" t="n"/>
       <c r="M24" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N24" s="10">
         <f>IF(D24="Govt",$B$1,$B$2)</f>
@@ -1921,7 +1921,7 @@
         <v/>
       </c>
       <c r="Q24" s="12" t="n">
-        <v>5.3488</v>
+        <v>10.0389</v>
       </c>
     </row>
     <row r="25">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>IE000W6YTDH7</t>
+          <t>IE000I25S1V5</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F25" s="6" t="n">
@@ -1986,23 +1986,23 @@
         <v/>
       </c>
       <c r="Q25" s="12" t="n">
-        <v>4.9823</v>
+        <v>5.3631</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2030 Term € Corp UCITS ETF</t>
+          <t>Invesco BulletShares 2030 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>IE000LX17BP9</t>
+          <t>IE000W6YTDH7</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -2023,20 +2023,20 @@
         <v/>
       </c>
       <c r="H26" s="8" t="n">
-        <v>0.0282</v>
+        <v>0.0286</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>0.0411</v>
+        <v>0.0417</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>-0.0004</v>
+        <v>0.0013</v>
       </c>
       <c r="L26" s="9" t="n"/>
       <c r="M26" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="N26" s="10">
         <f>IF(D26="Govt",$B$1,$B$2)</f>
@@ -2051,57 +2051,57 @@
         <v/>
       </c>
       <c r="Q26" s="12" t="n">
-        <v>4.99</v>
+        <v>4.9956</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2030 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>Amundi Fixed Maturity 2029 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>LU2809864296</t>
+          <t>LU2872291781</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F27" s="6" t="n">
-        <v>47756</v>
+        <v>47483</v>
       </c>
       <c r="G27" s="7">
         <f>IF(F27="","",MAX(0,YEARFRAC(TODAY(),F27)))</f>
         <v/>
       </c>
       <c r="H27" s="8" t="n">
-        <v>0.027</v>
+        <v>0.0208</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>0.04099999999999999</v>
+        <v>0.0353</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0.0353</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>-0.0004</v>
+        <v>-0.0005</v>
       </c>
       <c r="L27" s="9" t="n"/>
       <c r="M27" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N27" s="10">
         <f>IF(D27="Govt",$B$1,$B$2)</f>
@@ -2116,53 +2116,53 @@
         <v/>
       </c>
       <c r="Q27" s="12" t="n">
-        <v>35.24</v>
+        <v>10.0144</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2029 Italy and Spain Government Bond UCITS ETF 1C</t>
+          <t>iShares iBonds Dec 2030 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>LU0484969463</t>
+          <t>IE000LX17BP9</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F28" s="6" t="n">
-        <v>47391</v>
+        <v>47848</v>
       </c>
       <c r="G28" s="7">
         <f>IF(F28="","",MAX(0,YEARFRAC(TODAY(),F28)))</f>
         <v/>
       </c>
       <c r="H28" s="8" t="n">
-        <v>0.0297</v>
+        <v>0.0282</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>0.0344</v>
+        <v>0.0413</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>-0.0004</v>
+        <v>0.0002</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>-0.0012</v>
+        <v>-0.0007</v>
       </c>
       <c r="L28" s="9" t="n"/>
       <c r="M28" s="8" t="n">
@@ -2181,28 +2181,28 @@
         <v/>
       </c>
       <c r="Q28" s="12" t="n">
-        <v>205.05</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>Xtrackers II Target Maturity Sept 2029 Italy and Spain Government Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>IE000P5IB8I8</t>
+          <t>LU0484969463</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -2211,27 +2211,27 @@
         </is>
       </c>
       <c r="F29" s="6" t="n">
-        <v>47483</v>
+        <v>47391</v>
       </c>
       <c r="G29" s="7">
         <f>IF(F29="","",MAX(0,YEARFRAC(TODAY(),F29)))</f>
         <v/>
       </c>
       <c r="H29" s="8" t="n">
-        <v>0.0242</v>
+        <v>0.0297</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>0.0399</v>
+        <v>0.0351</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0</v>
+        <v>0.0007</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.0015</v>
+        <v>-0.0007</v>
       </c>
       <c r="L29" s="9" t="n"/>
       <c r="M29" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N29" s="10">
         <f>IF(D29="Govt",$B$1,$B$2)</f>
@@ -2246,23 +2246,23 @@
         <v/>
       </c>
       <c r="Q29" s="12" t="n">
-        <v>5.4253</v>
+        <v>204.85</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>Xtrackers II Target Maturity Sept 2030 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>IE000ZC4C5Q1</t>
+          <t>LU2809864296</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -2276,27 +2276,27 @@
         </is>
       </c>
       <c r="F30" s="6" t="n">
-        <v>47483</v>
+        <v>47756</v>
       </c>
       <c r="G30" s="7">
         <f>IF(F30="","",MAX(0,YEARFRAC(TODAY(),F30)))</f>
         <v/>
       </c>
       <c r="H30" s="8" t="n">
-        <v>0.0242</v>
+        <v>0.027</v>
       </c>
       <c r="I30" s="8" t="n">
-        <v>0.0399</v>
+        <v>0.0412</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.0015</v>
+        <v>0.001</v>
       </c>
       <c r="L30" s="9" t="n"/>
       <c r="M30" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N30" s="10">
         <f>IF(D30="Govt",$B$1,$B$2)</f>
@@ -2311,7 +2311,7 @@
         <v/>
       </c>
       <c r="Q30" s="12" t="n">
-        <v>5.0553</v>
+        <v>35.22</v>
       </c>
     </row>
     <row r="31">
@@ -2351,13 +2351,13 @@
         <v>0.0261</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>0.034</v>
+        <v>0.0345</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0005</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>-0.001</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="L31" s="9" t="n"/>
       <c r="M31" s="8" t="n">
@@ -2376,23 +2376,23 @@
         <v/>
       </c>
       <c r="Q31" s="12" t="n">
-        <v>5.06</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2029 Term € Corp UCITS ETF</t>
+          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>IE000IHURBR0</t>
+          <t>IE000P5IB8I8</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F32" s="6" t="n">
@@ -2413,20 +2413,20 @@
         <v/>
       </c>
       <c r="H32" s="8" t="n">
-        <v>0.0253</v>
+        <v>0.0242</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>0.0395</v>
+        <v>0.0399</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0.0015</v>
       </c>
       <c r="L32" s="9" t="n"/>
       <c r="M32" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="N32" s="10">
         <f>IF(D32="Govt",$B$1,$B$2)</f>
@@ -2441,23 +2441,23 @@
         <v/>
       </c>
       <c r="Q32" s="12" t="n">
-        <v>5.03</v>
+        <v>5.4364</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2029 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>Invesco BulletShares 2029 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>LU2673523309</t>
+          <t>IE000ZC4C5Q1</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -2471,27 +2471,27 @@
         </is>
       </c>
       <c r="F33" s="6" t="n">
-        <v>47391</v>
+        <v>47483</v>
       </c>
       <c r="G33" s="7">
         <f>IF(F33="","",MAX(0,YEARFRAC(TODAY(),F33)))</f>
         <v/>
       </c>
       <c r="H33" s="8" t="n">
-        <v>0.0245</v>
+        <v>0.0242</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>0.0392</v>
+        <v>0.0399</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0.0015</v>
       </c>
       <c r="L33" s="9" t="n"/>
       <c r="M33" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="N33" s="10">
         <f>IF(D33="Govt",$B$1,$B$2)</f>
@@ -2506,23 +2506,23 @@
         <v/>
       </c>
       <c r="Q33" s="12" t="n">
-        <v>25.79</v>
+        <v>5.0657</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2029 EUR Corporate Bond UCITS ETF 1C</t>
+          <t>iShares iBonds Dec 2029 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>LU2673522913</t>
+          <t>IE000IHURBR0</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -2532,27 +2532,27 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F34" s="6" t="n">
-        <v>47391</v>
+        <v>47483</v>
       </c>
       <c r="G34" s="7">
         <f>IF(F34="","",MAX(0,YEARFRAC(TODAY(),F34)))</f>
         <v/>
       </c>
       <c r="H34" s="8" t="n">
-        <v>0.0245</v>
+        <v>0.0253</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>0.0392</v>
+        <v>0.0397</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0.0002</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>-0.0001</v>
+        <v>-0.0004</v>
       </c>
       <c r="L34" s="9" t="n"/>
       <c r="M34" s="8" t="n">
@@ -2571,23 +2571,23 @@
         <v/>
       </c>
       <c r="Q34" s="12" t="n">
-        <v>9.17</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BNP Paribas</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2029 UCITS ETF C</t>
+          <t>Xtrackers II Target Maturity Sept 2029 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>LU2823896811</t>
+          <t>LU2673523309</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -2597,27 +2597,27 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F35" s="6" t="n">
-        <v>47483</v>
+        <v>47391</v>
       </c>
       <c r="G35" s="7">
         <f>IF(F35="","",MAX(0,YEARFRAC(TODAY(),F35)))</f>
         <v/>
       </c>
       <c r="H35" s="8" t="n">
-        <v>0.0235</v>
+        <v>0.0245</v>
       </c>
       <c r="I35" s="8" t="n">
-        <v>0.039</v>
+        <v>0.0395</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0003</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0</v>
+        <v>0.0019</v>
       </c>
       <c r="L35" s="9" t="n"/>
       <c r="M35" s="8" t="n">
@@ -2636,23 +2636,23 @@
         <v/>
       </c>
       <c r="Q35" s="12" t="n">
-        <v>10.6542</v>
+        <v>25.78</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BNP Paribas</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2029 UCITS ETF D</t>
+          <t>Xtrackers II Target Maturity Sept 2029 EUR Corporate Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>LU2823896738</t>
+          <t>LU2673522913</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -2662,27 +2662,27 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F36" s="6" t="n">
-        <v>47483</v>
+        <v>47391</v>
       </c>
       <c r="G36" s="7">
         <f>IF(F36="","",MAX(0,YEARFRAC(TODAY(),F36)))</f>
         <v/>
       </c>
       <c r="H36" s="8" t="n">
-        <v>0.0235</v>
+        <v>0.0245</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>0.039</v>
+        <v>0.0395</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>-0.0002</v>
+        <v>0.0003</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0</v>
+        <v>0.0019</v>
       </c>
       <c r="L36" s="9" t="n"/>
       <c r="M36" s="8" t="n">
@@ -2701,33 +2701,33 @@
         <v/>
       </c>
       <c r="Q36" s="12" t="n">
-        <v>10.2931</v>
+        <v>9.17</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2028 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>Amundi Fixed Maturity 2028 Euro Government Bond Yield + UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>IE00079EUF59</t>
+          <t>LU2780871666</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F37" s="6" t="n">
@@ -2738,20 +2738,20 @@
         <v/>
       </c>
       <c r="H37" s="8" t="n">
-        <v>0.0242</v>
+        <v>0.023</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>0.0387</v>
+        <v>0.0332</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0</v>
+        <v>0.0332</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.002</v>
+        <v>-0.0014</v>
       </c>
       <c r="L37" s="9" t="n"/>
       <c r="M37" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0009</v>
       </c>
       <c r="N37" s="10">
         <f>IF(D37="Govt",$B$1,$B$2)</f>
@@ -2766,28 +2766,28 @@
         <v/>
       </c>
       <c r="Q37" s="12" t="n">
-        <v>5.5724</v>
+        <v>10.3132</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2028 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>IE000LKGEZQ6</t>
+          <t>LU2780871401</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -2803,20 +2803,20 @@
         <v/>
       </c>
       <c r="H38" s="8" t="n">
-        <v>0.0242</v>
+        <v>0.0184</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>0.0387</v>
+        <v>0.0331</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0</v>
+        <v>0.0331</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="L38" s="9" t="n"/>
       <c r="M38" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0009</v>
       </c>
       <c r="N38" s="10">
         <f>IF(D38="Govt",$B$1,$B$2)</f>
@@ -2831,33 +2831,33 @@
         <v/>
       </c>
       <c r="Q38" s="12" t="n">
-        <v>5.2116</v>
+        <v>10.2991</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2028 Term € Corp UCITS ETF</t>
+          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>IE000264WWY0</t>
+          <t>LU2780871310</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F39" s="6" t="n">
@@ -2868,20 +2868,20 @@
         <v/>
       </c>
       <c r="H39" s="8" t="n">
-        <v>0.0214</v>
+        <v>0.0184</v>
       </c>
       <c r="I39" s="8" t="n">
-        <v>0.0379</v>
+        <v>0.0331</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0.0331</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.0004</v>
+        <v>-0.001</v>
       </c>
       <c r="L39" s="9" t="n"/>
       <c r="M39" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N39" s="10">
         <f>IF(D39="Govt",$B$1,$B$2)</f>
@@ -2896,23 +2896,23 @@
         <v/>
       </c>
       <c r="Q39" s="12" t="n">
-        <v>5.1</v>
+        <v>10.098</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>BNP Paribas</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2028 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2029 UCITS ETF C</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>LU2810185665</t>
+          <t>LU2823896811</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -2922,27 +2922,27 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F40" s="6" t="n">
-        <v>47026</v>
+        <v>47483</v>
       </c>
       <c r="G40" s="7">
         <f>IF(F40="","",MAX(0,YEARFRAC(TODAY(),F40)))</f>
         <v/>
       </c>
       <c r="H40" s="8" t="n">
-        <v>0.0207</v>
+        <v>0.0235</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>0.03759999999999999</v>
+        <v>0.0389</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>-0.0002</v>
+        <v>-0.0001</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="L40" s="9" t="n"/>
       <c r="M40" s="8" t="n">
@@ -2961,23 +2961,23 @@
         <v/>
       </c>
       <c r="Q40" s="12" t="n">
-        <v>35.79</v>
+        <v>10.6596</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>BNP Paribas</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2027 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>BNP PARIBAS EASY ESG ENHANCED EUR CORP BOND DECEMBER 2029 UCITS ETF D</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>IE000LGHLQ71</t>
+          <t>LU2823896738</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -2987,31 +2987,31 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F41" s="6" t="n">
-        <v>46752</v>
+        <v>47483</v>
       </c>
       <c r="G41" s="7">
         <f>IF(F41="","",MAX(0,YEARFRAC(TODAY(),F41)))</f>
         <v/>
       </c>
       <c r="H41" s="8" t="n">
-        <v>0.0197</v>
+        <v>0.0235</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>0.0347</v>
+        <v>0.0389</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0</v>
+        <v>-0.0001</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.0021</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="L41" s="9" t="n"/>
       <c r="M41" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="N41" s="10">
         <f>IF(D41="Govt",$B$1,$B$2)</f>
@@ -3026,7 +3026,7 @@
         <v/>
       </c>
       <c r="Q41" s="12" t="n">
-        <v>5.7135</v>
+        <v>10.2983</v>
       </c>
     </row>
     <row r="42">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2027 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>Invesco BulletShares 2028 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>IE000XOS4OJ6</t>
+          <t>IE00079EUF59</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -3052,27 +3052,27 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
-        <v>46752</v>
+        <v>47118</v>
       </c>
       <c r="G42" s="7">
         <f>IF(F42="","",MAX(0,YEARFRAC(TODAY(),F42)))</f>
         <v/>
       </c>
       <c r="H42" s="8" t="n">
-        <v>0.0197</v>
+        <v>0.0242</v>
       </c>
       <c r="I42" s="8" t="n">
-        <v>0.0347</v>
+        <v>0.0387</v>
       </c>
       <c r="J42" s="9" t="n">
         <v>0</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.0021</v>
+        <v>0.002</v>
       </c>
       <c r="L42" s="9" t="n"/>
       <c r="M42" s="8" t="n">
@@ -3091,23 +3091,23 @@
         <v/>
       </c>
       <c r="Q42" s="12" t="n">
-        <v>5.3408</v>
+        <v>5.5788</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2027 Term € Corp UCITS ETF</t>
+          <t>Invesco BulletShares 2028 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>IE000ZOI8OK5</t>
+          <t>IE000LKGEZQ6</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -3117,31 +3117,31 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
-        <v>46752</v>
+        <v>47118</v>
       </c>
       <c r="G43" s="7">
         <f>IF(F43="","",MAX(0,YEARFRAC(TODAY(),F43)))</f>
         <v/>
       </c>
       <c r="H43" s="8" t="n">
-        <v>0.0195</v>
+        <v>0.0242</v>
       </c>
       <c r="I43" s="8" t="n">
-        <v>0.0339</v>
+        <v>0.0387</v>
       </c>
       <c r="J43" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.0011</v>
+        <v>0.002</v>
       </c>
       <c r="L43" s="9" t="n"/>
       <c r="M43" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="N43" s="10">
         <f>IF(D43="Govt",$B$1,$B$2)</f>
@@ -3156,23 +3156,23 @@
         <v/>
       </c>
       <c r="Q43" s="12" t="n">
-        <v>5.65</v>
+        <v>5.2176</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DWS</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1D</t>
+          <t>iShares iBonds Dec 2028 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>LU2673523218</t>
+          <t>IE000264WWY0</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -3186,23 +3186,23 @@
         </is>
       </c>
       <c r="F44" s="6" t="n">
-        <v>46660</v>
+        <v>47118</v>
       </c>
       <c r="G44" s="7">
         <f>IF(F44="","",MAX(0,YEARFRAC(TODAY(),F44)))</f>
         <v/>
       </c>
       <c r="H44" s="8" t="n">
-        <v>0.019</v>
+        <v>0.0214</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>0.0325</v>
+        <v>0.0381</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.001</v>
+        <v>0.0002</v>
       </c>
       <c r="L44" s="9" t="n"/>
       <c r="M44" s="8" t="n">
@@ -3221,7 +3221,7 @@
         <v/>
       </c>
       <c r="Q44" s="12" t="n">
-        <v>25.99</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="45">
@@ -3232,12 +3232,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1C</t>
+          <t>Xtrackers II Target Maturity Sept 2028 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>LU2673522830</t>
+          <t>LU2810185665</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -3247,27 +3247,27 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F45" s="6" t="n">
-        <v>46660</v>
+        <v>47026</v>
       </c>
       <c r="G45" s="7">
         <f>IF(F45="","",MAX(0,YEARFRAC(TODAY(),F45)))</f>
         <v/>
       </c>
       <c r="H45" s="8" t="n">
-        <v>0.019</v>
+        <v>0.0207</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>0.0325</v>
+        <v>0.0377</v>
       </c>
       <c r="J45" s="9" t="n">
         <v>0.0001</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.001</v>
+        <v>0.0011</v>
       </c>
       <c r="L45" s="9" t="n"/>
       <c r="M45" s="8" t="n">
@@ -3286,23 +3286,23 @@
         <v/>
       </c>
       <c r="Q45" s="12" t="n">
-        <v>9.32</v>
+        <v>35.78</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2026 Term € Italy Govt Bond UCITS ETF</t>
+          <t>Amundi Fixed Maturity 2027 Italy BTP Government Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>IE000LZ7BZW8</t>
+          <t>LU2780872128</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -3316,27 +3316,27 @@
         </is>
       </c>
       <c r="F46" s="6" t="n">
-        <v>46387</v>
+        <v>46752</v>
       </c>
       <c r="G46" s="7">
         <f>IF(F46="","",MAX(0,YEARFRAC(TODAY(),F46)))</f>
         <v/>
       </c>
       <c r="H46" s="8" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0265</v>
       </c>
       <c r="I46" s="8" t="n">
-        <v>0.027</v>
+        <v>0.0307</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0</v>
+        <v>0.0307</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.0005</v>
+        <v>-0.0005</v>
       </c>
       <c r="L46" s="9" t="n"/>
       <c r="M46" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.0009</v>
       </c>
       <c r="N46" s="10">
         <f>IF(D46="Govt",$B$1,$B$2)</f>
@@ -3351,28 +3351,28 @@
         <v/>
       </c>
       <c r="Q46" s="12" t="n">
-        <v>5.06</v>
+        <v>10.3541</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Amundi</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2026 EUR Corporate Bond UCITS ETF Acc</t>
+          <t>Amundi Fixed Maturity 2027 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>IE0004QWOTD5</t>
+          <t>LU2872291435</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Corp</t>
+          <t>Govt</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -3381,27 +3381,27 @@
         </is>
       </c>
       <c r="F47" s="6" t="n">
-        <v>46387</v>
+        <v>46752</v>
       </c>
       <c r="G47" s="7">
         <f>IF(F47="","",MAX(0,YEARFRAC(TODAY(),F47)))</f>
         <v/>
       </c>
       <c r="H47" s="8" t="n">
-        <v>0.0109</v>
+        <v>0.015</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>0.028</v>
+        <v>0.0298</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0</v>
+        <v>0.0298</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>-0.0013</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="L47" s="9" t="n"/>
       <c r="M47" s="8" t="n">
-        <v>0.001</v>
+        <v>0.0009</v>
       </c>
       <c r="N47" s="10">
         <f>IF(D47="Govt",$B$1,$B$2)</f>
@@ -3416,7 +3416,7 @@
         <v/>
       </c>
       <c r="Q47" s="12" t="n">
-        <v>5.7996</v>
+        <v>10.1905</v>
       </c>
     </row>
     <row r="48">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Invesco BulletShares 2026 EUR Corporate Bond UCITS ETF Dist</t>
+          <t>Invesco BulletShares 2027 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>IE000AYJ75E5</t>
+          <t>IE000LGHLQ71</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -3442,27 +3442,27 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
-        <v>46387</v>
+        <v>46752</v>
       </c>
       <c r="G48" s="7">
         <f>IF(F48="","",MAX(0,YEARFRAC(TODAY(),F48)))</f>
         <v/>
       </c>
       <c r="H48" s="8" t="n">
-        <v>0.0109</v>
+        <v>0.0197</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>0.028</v>
+        <v>0.0347</v>
       </c>
       <c r="J48" s="9" t="n">
         <v>0</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>-0.0013</v>
+        <v>0.0021</v>
       </c>
       <c r="L48" s="9" t="n"/>
       <c r="M48" s="8" t="n">
@@ -3481,23 +3481,23 @@
         <v/>
       </c>
       <c r="Q48" s="12" t="n">
-        <v>5.4229</v>
+        <v>5.7152</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>iShares</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>iShares iBonds Dec 2026 Term € Corp UCITS ETF</t>
+          <t>Invesco BulletShares 2027 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>IE000SIZJ2B2</t>
+          <t>IE000XOS4OJ6</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -3511,27 +3511,27 @@
         </is>
       </c>
       <c r="F49" s="6" t="n">
-        <v>46387</v>
+        <v>46752</v>
       </c>
       <c r="G49" s="7">
         <f>IF(F49="","",MAX(0,YEARFRAC(TODAY(),F49)))</f>
         <v/>
       </c>
       <c r="H49" s="8" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.0197</v>
       </c>
       <c r="I49" s="8" t="n">
-        <v>0.0276</v>
+        <v>0.0347</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.0001</v>
+        <v>0.0021</v>
       </c>
       <c r="L49" s="9" t="n"/>
       <c r="M49" s="8" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="N49" s="10">
         <f>IF(D49="Govt",$B$1,$B$2)</f>
@@ -3546,33 +3546,33 @@
         <v/>
       </c>
       <c r="Q49" s="12" t="n">
-        <v>5.06</v>
+        <v>5.3424</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2027 Italy BTP Government Bond UCITS ETF Dist</t>
+          <t>iShares iBonds Dec 2027 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>LU2780872128</t>
+          <t>IE000ZOI8OK5</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>Dist</t>
+          <t>Acc</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
@@ -3583,20 +3583,20 @@
         <v/>
       </c>
       <c r="H50" s="8" t="n">
-        <v>0.0265</v>
+        <v>0.0195</v>
       </c>
       <c r="I50" s="8" t="n">
+        <v>0.0339</v>
+      </c>
+      <c r="J50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="J50" s="9" t="n">
-        <v>-0.0309</v>
-      </c>
       <c r="K50" s="9" t="n">
-        <v>-0.0312</v>
+        <v>0.0008</v>
       </c>
       <c r="L50" s="9" t="n"/>
       <c r="M50" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N50" s="10">
         <f>IF(D50="Govt",$B$1,$B$2)</f>
@@ -3611,7 +3611,7 @@
         <v/>
       </c>
       <c r="Q50" s="12" t="n">
-        <v>10.3477</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="51">
@@ -3651,13 +3651,13 @@
         <v>0.0105</v>
       </c>
       <c r="I51" s="8" t="n">
-        <v>0</v>
+        <v>0.0283</v>
       </c>
       <c r="J51" s="9" t="n">
-        <v>-0.0281</v>
+        <v>0.0283</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>-0.0299</v>
+        <v>-0.0016</v>
       </c>
       <c r="L51" s="9" t="n"/>
       <c r="M51" s="8" t="n">
@@ -3676,57 +3676,57 @@
         <v/>
       </c>
       <c r="Q51" s="12" t="n">
-        <v>10.3599</v>
+        <v>10.3641</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2026 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1D</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>LU2872291278</t>
+          <t>LU2673523218</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F52" s="6" t="n">
-        <v>46387</v>
+        <v>46660</v>
       </c>
       <c r="G52" s="7">
         <f>IF(F52="","",MAX(0,YEARFRAC(TODAY(),F52)))</f>
         <v/>
       </c>
       <c r="H52" s="8" t="n">
-        <v>0.0021</v>
+        <v>0.019</v>
       </c>
       <c r="I52" s="8" t="n">
-        <v>0</v>
+        <v>0.0322</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>-0.0266</v>
+        <v>-0.0003</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>-0.0274</v>
+        <v>0.0013</v>
       </c>
       <c r="L52" s="9" t="n"/>
       <c r="M52" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N52" s="10">
         <f>IF(D52="Govt",$B$1,$B$2)</f>
@@ -3741,28 +3741,28 @@
         <v/>
       </c>
       <c r="Q52" s="12" t="n">
-        <v>10.2701</v>
+        <v>25.99</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>DWS</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2027 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>Xtrackers II Target Maturity Sept 2027 EUR Corporate Bond UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LU2872291435</t>
+          <t>LU2673522830</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -3771,27 +3771,27 @@
         </is>
       </c>
       <c r="F53" s="6" t="n">
-        <v>46752</v>
+        <v>46660</v>
       </c>
       <c r="G53" s="7">
         <f>IF(F53="","",MAX(0,YEARFRAC(TODAY(),F53)))</f>
         <v/>
       </c>
       <c r="H53" s="8" t="n">
-        <v>0.015</v>
+        <v>0.019</v>
       </c>
       <c r="I53" s="8" t="n">
-        <v>0</v>
+        <v>0.0322</v>
       </c>
       <c r="J53" s="9" t="n">
-        <v>-0.0297</v>
+        <v>-0.0003</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>-0.0305</v>
+        <v>0.0013</v>
       </c>
       <c r="L53" s="9" t="n"/>
       <c r="M53" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N53" s="10">
         <f>IF(D53="Govt",$B$1,$B$2)</f>
@@ -3806,23 +3806,23 @@
         <v/>
       </c>
       <c r="Q53" s="12" t="n">
-        <v>10.1853</v>
+        <v>9.32</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Dist</t>
+          <t>iShares iBonds Dec 2026 Term € Italy Govt Bond UCITS ETF</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>LU2780871401</t>
+          <t>IE000LZ7BZW8</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -3836,27 +3836,27 @@
         </is>
       </c>
       <c r="F54" s="6" t="n">
-        <v>47118</v>
+        <v>46387</v>
       </c>
       <c r="G54" s="7">
         <f>IF(F54="","",MAX(0,YEARFRAC(TODAY(),F54)))</f>
         <v/>
       </c>
       <c r="H54" s="8" t="n">
-        <v>0.0184</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="I54" s="8" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="J54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="J54" s="9" t="n">
-        <v>-0.0331</v>
-      </c>
       <c r="K54" s="9" t="n">
-        <v>-0.0339</v>
+        <v>0.0004</v>
       </c>
       <c r="L54" s="9" t="n"/>
       <c r="M54" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N54" s="10">
         <f>IF(D54="Govt",$B$1,$B$2)</f>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="Q54" s="12" t="n">
-        <v>10.2851</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="55">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2028 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>Amundi Fixed Maturity 2026 Euro Government Bond Broad UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>LU2780871310</t>
+          <t>LU2872291278</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -3901,23 +3901,23 @@
         </is>
       </c>
       <c r="F55" s="6" t="n">
-        <v>47118</v>
+        <v>46387</v>
       </c>
       <c r="G55" s="7">
         <f>IF(F55="","",MAX(0,YEARFRAC(TODAY(),F55)))</f>
         <v/>
       </c>
       <c r="H55" s="8" t="n">
-        <v>0.0184</v>
+        <v>0.0021</v>
       </c>
       <c r="I55" s="8" t="n">
-        <v>0</v>
+        <v>0.0265</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>-0.0331</v>
+        <v>0.0265</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>-0.0339</v>
+        <v>0.0016</v>
       </c>
       <c r="L55" s="9" t="n"/>
       <c r="M55" s="8" t="n">
@@ -3936,28 +3936,28 @@
         <v/>
       </c>
       <c r="Q55" s="12" t="n">
-        <v>10.0843</v>
+        <v>10.2723</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2029 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>Invesco BulletShares 2026 EUR Corporate Bond UCITS ETF Acc</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>LU2872291781</t>
+          <t>IE0004QWOTD5</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -3966,27 +3966,27 @@
         </is>
       </c>
       <c r="F56" s="6" t="n">
-        <v>47483</v>
+        <v>46387</v>
       </c>
       <c r="G56" s="7">
         <f>IF(F56="","",MAX(0,YEARFRAC(TODAY(),F56)))</f>
         <v/>
       </c>
       <c r="H56" s="8" t="n">
-        <v>0.0208</v>
+        <v>0.0109</v>
       </c>
       <c r="I56" s="8" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="J56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="J56" s="9" t="n">
-        <v>-0.0356</v>
-      </c>
       <c r="K56" s="9" t="n">
-        <v>-0.0355</v>
+        <v>-0.0013</v>
       </c>
       <c r="L56" s="9" t="n"/>
       <c r="M56" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="N56" s="10">
         <f>IF(D56="Govt",$B$1,$B$2)</f>
@@ -4001,28 +4001,28 @@
         <v/>
       </c>
       <c r="Q56" s="12" t="n">
-        <v>9.992699999999999</v>
+        <v>5.8007</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2028 Euro Government Bond Yield + UCITS ETF Dist</t>
+          <t>Invesco BulletShares 2026 EUR Corporate Bond UCITS ETF Dist</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>LU2780871666</t>
+          <t>IE000AYJ75E5</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -4031,27 +4031,27 @@
         </is>
       </c>
       <c r="F57" s="6" t="n">
-        <v>47118</v>
+        <v>46387</v>
       </c>
       <c r="G57" s="7">
         <f>IF(F57="","",MAX(0,YEARFRAC(TODAY(),F57)))</f>
         <v/>
       </c>
       <c r="H57" s="8" t="n">
-        <v>0.0229</v>
+        <v>0.0109</v>
       </c>
       <c r="I57" s="8" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="J57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="J57" s="9" t="n">
-        <v>-0.0334</v>
-      </c>
       <c r="K57" s="9" t="n">
-        <v>-0.0343</v>
+        <v>-0.0013</v>
       </c>
       <c r="L57" s="9" t="n"/>
       <c r="M57" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="N57" s="10">
         <f>IF(D57="Govt",$B$1,$B$2)</f>
@@ -4066,57 +4066,57 @@
         <v/>
       </c>
       <c r="Q57" s="12" t="n">
-        <v>10.2975</v>
+        <v>5.4239</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Amundi</t>
+          <t>iShares</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Amundi Fixed Maturity 2030 Euro Government Bond Broad UCITS ETF Acc</t>
+          <t>iShares iBonds Dec 2026 Term € Corp UCITS ETF</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>LU3120976132</t>
+          <t>IE000SIZJ2B2</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Govt</t>
+          <t>Corp</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>Acc</t>
+          <t>Dist</t>
         </is>
       </c>
       <c r="F58" s="6" t="n">
-        <v>47848</v>
+        <v>46387</v>
       </c>
       <c r="G58" s="7">
         <f>IF(F58="","",MAX(0,YEARFRAC(TODAY(),F58)))</f>
         <v/>
       </c>
       <c r="H58" s="8" t="n">
-        <v>0.0169</v>
+        <v>0.004500000000000001</v>
       </c>
       <c r="I58" s="8" t="n">
-        <v>0</v>
+        <v>0.0275</v>
       </c>
       <c r="J58" s="9" t="n">
-        <v>-0.0364</v>
+        <v>-0.0001</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>-0.0362</v>
+        <v>-0.0002</v>
       </c>
       <c r="L58" s="9" t="n"/>
       <c r="M58" s="8" t="n">
-        <v>0.0009</v>
+        <v>0.0012</v>
       </c>
       <c r="N58" s="10">
         <f>IF(D58="Govt",$B$1,$B$2)</f>
@@ -4131,7 +4131,7 @@
         <v/>
       </c>
       <c r="Q58" s="12" t="n">
-        <v>9.837899999999999</v>
+        <v>5.06</v>
       </c>
     </row>
   </sheetData>
